--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 17-Apr-2026  16:38:40    |    Closing Price Date: 17-Apr-2026</t>
+          <t>Scan Run: 18-Apr-2026  15:29:25    |    Closing Price Date: 17-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>17-Apr-2026  16:38:40</t>
+          <t>18-Apr-2026  15:29:25</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>1532.01</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1430.54</v>
+        <v>1430.13</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1051.07</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1086.52</v>
+        <v>1086.12</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>32825.75</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>32583.94</v>
+        <v>32576.19</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>470.19</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>474.86</v>
+        <v>474.85</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>419.07</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>406.29</v>
+        <v>406.96</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>1251.73</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1473.87</v>
+        <v>1473.83</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>6132.31</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5674.14</v>
+        <v>5666.65</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>26614.29</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>28436.13</v>
+        <v>28442.35</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>329.33</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>308.67</v>
+        <v>308.43</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>63.52</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>91.69</v>
+        <v>92.08</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1296.97</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1592.63</v>
+        <v>1590.01</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>922.08</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>834.5700000000001</v>
+        <v>833.41</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1484.12</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1697.56</v>
+        <v>1696.08</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>866.0700000000001</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>983.91</v>
+        <v>982.33</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>252.98</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>246.49</v>
+        <v>246.85</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1027.24</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>949.95</v>
+        <v>949.13</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>2054.36</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2233.92</v>
+        <v>2232.3</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>948.5700000000001</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>969.01</v>
+        <v>968.52</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>1444.68</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1416.95</v>
+        <v>1416.09</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>156.61</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>141.02</v>
+        <v>140.96</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>650.98</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>719.24</v>
+        <v>716.64</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>311.32</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>373.88</v>
+        <v>373.36</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>1456.56</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1641.69</v>
+        <v>1640.03</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>3746.44</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3612.98</v>
+        <v>3614.48</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>476.56</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>510.63</v>
+        <v>510.23</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>2850.7</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2733.31</v>
+        <v>2731.99</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>485.61</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>482.16</v>
+        <v>481.85</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>5444.86</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5412.78</v>
+        <v>5408.15</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>1417.64</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1645.76</v>
+        <v>1651.42</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>13.86</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>15.99</v>
+        <v>15.98</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>7005.95</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7086.76</v>
+        <v>7082.99</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>465.69</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>519.62</v>
+        <v>519.0599999999999</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>3193.57</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2874.88</v>
+        <v>2877.25</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>494.43</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>556.4299999999999</v>
+        <v>555.11</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>251.11</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>248.85</v>
+        <v>248.73</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         <v>10516.51</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>9955.68</v>
+        <v>9955.67</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>9051.950000000001</v>
+        <v>9040.299999999999</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>2023.08</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1876.28</v>
+        <v>1876.81</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>729.15</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>832.21</v>
+        <v>831.74</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>7457.55</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>7351.3</v>
+        <v>7349.09</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>444.86</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>468.05</v>
+        <v>467.74</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>232.04</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>272.4</v>
+        <v>272.27</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>790.27</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>896.3099999999999</v>
+        <v>896.08</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>874.03</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>880.71</v>
+        <v>880.65</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>177.87</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>160.5</v>
+        <v>160.33</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>2355.08</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2464.01</v>
+        <v>2464.69</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>646.05</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>615.38</v>
+        <v>615.11</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>1584.68</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1507.08</v>
+        <v>1506.98</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>8441.299999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>8594.73</v>
+        <v>8603.75</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>544.5</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>580.52</v>
+        <v>579.53</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>6331.08</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>6298.17</v>
+        <v>6301.14</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>942.3</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>874.34</v>
+        <v>874.49</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>1274.22</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1200.35</v>
+        <v>1198.9</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>190.8</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>229.77</v>
+        <v>229.65</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>1288.16</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1235.62</v>
+        <v>1235.05</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>9393.49</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9083.559999999999</v>
+        <v>9091.73</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>1841.62</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1938.66</v>
+        <v>1938.37</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>85.63</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>98.68000000000001</v>
+        <v>98.56</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>10155.35</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>11293.28</v>
+        <v>11288.9</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>913.67</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>937.8200000000001</v>
+        <v>937.48</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>2282.09</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2388.66</v>
+        <v>2388.88</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>474.3</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>480.25</v>
+        <v>479.99</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>162.57</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>159.81</v>
+        <v>159.69</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>282.04</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>272.98</v>
+        <v>272.91</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>151.62</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>139.93</v>
+        <v>139.87</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>3541.59</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>4037.12</v>
+        <v>4040.74</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>750.46</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>958.4</v>
+        <v>958.0599999999999</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>4660.44</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>4787.82</v>
+        <v>4792.36</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>1571.29</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1757.87</v>
+        <v>1757.99</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>1305.92</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1409.07</v>
+        <v>1409.99</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>433.01</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>404.3</v>
+        <v>404.27</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>1628.34</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1790.89</v>
+        <v>1792.04</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>451.31</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>496.69</v>
+        <v>496.98</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>1711.35</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1480.18</v>
+        <v>1479.26</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>1887.89</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1925.31</v>
+        <v>1925.65</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>1582.52</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1656.09</v>
+        <v>1655.94</v>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>267.16</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>256.73</v>
+        <v>256.52</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>642.05</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>687.92</v>
+        <v>688.08</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>369.48</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>371.75</v>
+        <v>371.73</v>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>273.49</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>314.46</v>
+        <v>313.82</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>5268.82</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>5670.02</v>
+        <v>5667.21</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>1776.97</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1826.75</v>
+        <v>1822.77</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>34201.32</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>35106.95</v>
+        <v>35099.05</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>320.62</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>325.78</v>
+        <v>325.51</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>722.55</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>859.79</v>
+        <v>858.1900000000001</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>5752.92</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>5745.68</v>
+        <v>5748.51</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>2945.86</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2646.64</v>
+        <v>2643.83</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>378.99</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>399.79</v>
+        <v>399.77</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>244.39</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>260.17</v>
+        <v>259.91</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>690.23</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>735.83</v>
+        <v>735.4400000000001</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>140.69</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>133.02</v>
+        <v>132.96</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>854.22</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>833.91</v>
+        <v>833.39</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>1692.86</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1883.5</v>
+        <v>1878.94</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>826.91</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>882.0700000000001</v>
+        <v>882.87</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>180.22</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>186.36</v>
+        <v>186.25</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>1045.05</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>941.46</v>
+        <v>940.91</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>1284.93</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1418.78</v>
+        <v>1416.7</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>3594.6</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>3597.91</v>
+        <v>3597.7</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>35.76</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>37.64</v>
+        <v>37.6</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>728.85</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>757.39</v>
+        <v>757.6</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>4963.76</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>5510.55</v>
+        <v>5508.54</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>156.92</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>159.6</v>
+        <v>159.42</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>173.51</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>178.24</v>
+        <v>178.15</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>695.8099999999999</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>682.92</v>
+        <v>682.21</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>782.49</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>854.8200000000001</v>
+        <v>853.91</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>444.13</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>474.12</v>
+        <v>473.76</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>950.73</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>844.16</v>
+        <v>844.02</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>1563.16</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1590.71</v>
+        <v>1591.27</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>1579.65</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1727.57</v>
+        <v>1729.2</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>1289.63</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1410.99</v>
+        <v>1410.71</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>747.9</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>942.5</v>
+        <v>943.72</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>437.83</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>403.13</v>
+        <v>402.8</v>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>1439.9</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1573.19</v>
+        <v>1572.42</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>1294.44</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1548.54</v>
+        <v>1546.19</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>2012.24</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>2178.32</v>
+        <v>2182.59</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>477.23</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>512.87</v>
+        <v>512.92</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>1132.36</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1396.26</v>
+        <v>1398.72</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>2098.23</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>2181.58</v>
+        <v>2182.19</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>7289.69</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>6869.61</v>
+        <v>6869.36</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>1229.14</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1250.81</v>
+        <v>1249.53</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>4174.36</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>4583.84</v>
+        <v>4579.73</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>247.13</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>276.19</v>
+        <v>276.22</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>258.82</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>244.96</v>
+        <v>244.97</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>4663.98</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>4179.71</v>
+        <v>4177.36</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>927.72</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1103.44</v>
+        <v>1103.21</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>459.62</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>490.04</v>
+        <v>490.35</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>1950.81</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>2036.73</v>
+        <v>2036.82</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>3123.86</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>2807.31</v>
+        <v>2807.19</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>104.9</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>132.62</v>
+        <v>132.37</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1113.95</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1152.18</v>
+        <v>1152.75</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>1047.45</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1204.73</v>
+        <v>1205.51</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>1490.41</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1683.88</v>
+        <v>1684.83</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>432.62</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>415.85</v>
+        <v>415.92</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>113.86</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>139.38</v>
+        <v>139.21</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>6142.68</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>6227</v>
+        <v>6225.11</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>10814.96</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>13060</v>
+        <v>13057.7</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>584.62</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>671.63</v>
+        <v>670.6900000000001</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>4064.54</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>4030.73</v>
+        <v>4029.46</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>2332.32</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>2449.5</v>
+        <v>2449.74</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>1253.57</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1256.33</v>
+        <v>1256.37</v>
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>1668.66</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1891.84</v>
+        <v>1890.41</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>7170.73</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>6801.94</v>
+        <v>6800.95</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>855.98</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>938.2</v>
+        <v>937.33</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>317.42</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>350.58</v>
+        <v>350.06</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>411.14</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>480.56</v>
+        <v>480.55</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>495.76</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>494.74</v>
+        <v>494.21</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>442.59</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>501.55</v>
+        <v>502.06</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>2411.58</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>2500.43</v>
+        <v>2500.19</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>201.56</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>196.37</v>
+        <v>196.15</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>1378.19</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>1474.32</v>
+        <v>1474.42</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>3237.07</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>3423.66</v>
+        <v>3425.76</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>249.56</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>271.84</v>
+        <v>271.64</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>320.78</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>353.36</v>
+        <v>353.02</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>810.4299999999999</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>851.5</v>
+        <v>851.4299999999999</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>276.52</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>248.78</v>
+        <v>248.69</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>837.48</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>836.72</v>
+        <v>836.28</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>172.89</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>184.39</v>
+        <v>184.09</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>240.55</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>304.95</v>
+        <v>303.81</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>420.45</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>525.09</v>
+        <v>524.92</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>3295.73</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>3464.39</v>
+        <v>3466.35</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>862.17</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>868.8200000000001</v>
+        <v>868.36</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>240.44</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>298.3</v>
+        <v>298.24</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>153.56</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>163.99</v>
+        <v>163.69</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>1348.33</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>1160.09</v>
+        <v>1159.59</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>378.73</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>380.79</v>
+        <v>381.55</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>7951.66</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>8505.299999999999</v>
+        <v>8504.27</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>1729.74</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>1765.1</v>
+        <v>1764.24</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>2430.6</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>2554.21</v>
+        <v>2554.23</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>2117.47</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>1965.01</v>
+        <v>1963.51</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>585.87</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>522.16</v>
+        <v>522.03</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>94.51000000000001</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>93.31999999999999</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>436.94</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>474.31</v>
+        <v>474.84</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>2102.15</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>2440.69</v>
+        <v>2438.57</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>327.55</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>334.18</v>
+        <v>333.89</v>
       </c>
       <c r="G176" s="14" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>586.72</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>631.41</v>
+        <v>631.62</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>1097.16</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1147.66</v>
+        <v>1148.71</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>909.76</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>1016.01</v>
+        <v>1015.39</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>1694.76</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>1933.09</v>
+        <v>1930.13</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>269.77</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>246.26</v>
+        <v>246.06</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>159.75</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>162.53</v>
+        <v>162.41</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>603.9400000000001</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>567.53</v>
+        <v>567.4299999999999</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>2720.86</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>2738.24</v>
+        <v>2737.15</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>1529.38</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>1674.84</v>
+        <v>1675.1</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>2410.37</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>2404.11</v>
+        <v>2403.81</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>267.49</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>294.4</v>
+        <v>294.36</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>362.6</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>404.38</v>
+        <v>404.29</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>3672.68</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>3084.79</v>
+        <v>3084.75</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>4027.61</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>4268.92</v>
+        <v>4268.39</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>391.55</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>475.8</v>
+        <v>475.4</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>1311.34</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>1416.19</v>
+        <v>1415.62</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>720.9400000000001</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>744.99</v>
+        <v>744.67</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>1441.8</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>1527.54</v>
+        <v>1527.65</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>2536.88</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>2557.69</v>
+        <v>2555.31</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>841.04</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>912.49</v>
+        <v>911.92</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>652.3200000000001</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>706.34</v>
+        <v>706.09</v>
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>549.08</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>529.64</v>
+        <v>529.23</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>5369.65</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>5194.7</v>
+        <v>5194.83</v>
       </c>
       <c r="G200" s="14" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>73.98</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>74.77</v>
+        <v>74.67</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>935.13</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>838</v>
+        <v>838.11</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>522.6799999999999</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>425.09</v>
+        <v>424.92</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>384.35</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>411.9</v>
+        <v>411.62</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9703,10 +9703,10 @@
         <v>2147.26</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>2207.13</v>
+        <v>2207.14</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>2329.18</v>
+        <v>2330.64</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>566.71</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>533.1</v>
+        <v>532.85</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>1059.51</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>1128.48</v>
+        <v>1127.89</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>301.97</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>285.81</v>
+        <v>285.85</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>30061.83</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>33634.02</v>
+        <v>33644.68</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>462.03</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>468.13</v>
+        <v>468.42</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>184.5</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>203.31</v>
+        <v>202.85</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>1980.59</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>2128.45</v>
+        <v>2127.35</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>1316.68</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>1352.83</v>
+        <v>1352.77</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>1832.09</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>1882.63</v>
+        <v>1883.88</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>584</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>614.4299999999999</v>
+        <v>614.17</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>85.92</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>92.34999999999999</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>9.74</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>69.42</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>73.18000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>126.25</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>139.47</v>
+        <v>139.44</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>55.77</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>55.31</v>
+        <v>55.24</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>330.54</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>349.4</v>
+        <v>348.64</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>162.42</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>181.76</v>
+        <v>182.01</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>484.03</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>494.56</v>
+        <v>494.33</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>1464.15</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>1567.76</v>
+        <v>1568.08</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>474.64</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>516.33</v>
+        <v>516.26</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>642.12</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>702.24</v>
+        <v>701.72</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>392.46</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>393.11</v>
+        <v>393.09</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>2121.83</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>2249</v>
+        <v>2249.96</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>904.47</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>803.24</v>
+        <v>802.9400000000001</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>4537.43</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>4987.56</v>
+        <v>4987.49</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>851.02</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>852.53</v>
+        <v>852.52</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>433.47</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>408.17</v>
+        <v>408.19</v>
       </c>
       <c r="G232" s="14" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>1351.55</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>1482.92</v>
+        <v>1482.26</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>1223.2</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>1165.29</v>
+        <v>1165.79</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>92.09</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>122.23</v>
+        <v>121.97</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>714.9299999999999</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>868.97</v>
+        <v>868.12</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>34.25</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>37.12</v>
+        <v>37.09</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>151.94</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>150.36</v>
+        <v>150.27</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>1490.14</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>1455.42</v>
+        <v>1454.03</v>
       </c>
       <c r="G239" s="14" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>21.04</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>21.83</v>
+        <v>21.79</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>139.02</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>157.78</v>
+        <v>157.7</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>562.78</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>644.71</v>
+        <v>644.45</v>
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>122.41</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>140.25</v>
+        <v>139.93</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>102.02</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>114.9</v>
+        <v>114.76</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>311.39</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>356.61</v>
+        <v>356.63</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>275.98</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>300.43</v>
+        <v>298.74</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>115.97</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>107.4</v>
+        <v>107.34</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>1994.33</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>1854.08</v>
+        <v>1852.97</v>
       </c>
       <c r="G248" s="14" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>571.77</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>608.9</v>
+        <v>608.4</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>191.33</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>195.02</v>
+        <v>194.6</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>1166.36</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>1075.45</v>
+        <v>1074.98</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>248.35</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>275.17</v>
+        <v>274.76</v>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>5427.71</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>5657.74</v>
+        <v>5657.12</v>
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>447.95</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>433.7</v>
+        <v>433.51</v>
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>128.93</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>138.01</v>
+        <v>138.06</v>
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>15.83</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>16.69</v>
+        <v>16.68</v>
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>754.51</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>744.29</v>
+        <v>743.71</v>
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>495.33</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>502.33</v>
+        <v>501.39</v>
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>15027.77</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>17620.49</v>
+        <v>17589.41</v>
       </c>
       <c r="G259" s="14" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>258.8</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>276.95</v>
+        <v>276.75</v>
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>1187.67</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>1136.65</v>
+        <v>1136.16</v>
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>479.39</v>
       </c>
       <c r="F262" s="11" t="n">
-        <v>561.5</v>
+        <v>561.3</v>
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>614.4299999999999</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>662.8</v>
+        <v>661.4299999999999</v>
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>891.75</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>989.37</v>
+        <v>987.79</v>
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>574.36</v>
       </c>
       <c r="F265" s="11" t="n">
-        <v>713.4400000000001</v>
+        <v>713.12</v>
       </c>
       <c r="G265" s="12" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>276.62</v>
       </c>
       <c r="F266" s="11" t="n">
-        <v>313.25</v>
+        <v>312.71</v>
       </c>
       <c r="G266" s="12" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>232.2</v>
       </c>
       <c r="F267" s="11" t="n">
-        <v>280.7</v>
+        <v>281.03</v>
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>789.61</v>
       </c>
       <c r="F268" s="11" t="n">
-        <v>912.95</v>
+        <v>910.62</v>
       </c>
       <c r="G268" s="14" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>1001.68</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>1033.57</v>
+        <v>1034.49</v>
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>414.93</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>468.84</v>
+        <v>466.95</v>
       </c>
       <c r="G270" s="12" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>193.46</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>220.82</v>
+        <v>220.81</v>
       </c>
       <c r="G271" s="12" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>286.79</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>256.48</v>
+        <v>256.44</v>
       </c>
       <c r="G272" s="14" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>3848.17</v>
       </c>
       <c r="F273" s="11" t="n">
-        <v>4798.51</v>
+        <v>4788.18</v>
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>580.21</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>703.11</v>
+        <v>701.53</v>
       </c>
       <c r="G274" s="12" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>4406.24</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>4198.16</v>
+        <v>4195.5</v>
       </c>
       <c r="G275" s="12" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>950.05</v>
       </c>
       <c r="F276" s="11" t="n">
-        <v>1048.33</v>
+        <v>1048.61</v>
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>659.86</v>
       </c>
       <c r="F277" s="11" t="n">
-        <v>669.14</v>
+        <v>668.83</v>
       </c>
       <c r="G277" s="12" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>1573.73</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>1713.65</v>
+        <v>1709.63</v>
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>1389.67</v>
       </c>
       <c r="F279" s="11" t="n">
-        <v>1162.26</v>
+        <v>1161.22</v>
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>128.08</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>168.1</v>
+        <v>168.05</v>
       </c>
       <c r="G280" s="12" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>388.68</v>
       </c>
       <c r="F281" s="11" t="n">
-        <v>405.63</v>
+        <v>405.81</v>
       </c>
       <c r="G281" s="12" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>1133.02</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>1157.41</v>
+        <v>1157.48</v>
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>787.88</v>
       </c>
       <c r="F283" s="11" t="n">
-        <v>1039.64</v>
+        <v>1039.72</v>
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>876.6900000000001</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>952.29</v>
+        <v>951.41</v>
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>1383.54</v>
       </c>
       <c r="F285" s="11" t="n">
-        <v>1441.84</v>
+        <v>1442.04</v>
       </c>
       <c r="G285" s="12" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>325.95</v>
       </c>
       <c r="F286" s="11" t="n">
-        <v>393.91</v>
+        <v>393.5</v>
       </c>
       <c r="G286" s="12" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>1039.32</v>
       </c>
       <c r="F287" s="11" t="n">
-        <v>943.14</v>
+        <v>943.23</v>
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>116.86</v>
       </c>
       <c r="F288" s="11" t="n">
-        <v>137.3</v>
+        <v>137.12</v>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>517.47</v>
       </c>
       <c r="F289" s="11" t="n">
-        <v>540.62</v>
+        <v>540.22</v>
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>809.61</v>
       </c>
       <c r="F290" s="11" t="n">
-        <v>846.08</v>
+        <v>844.97</v>
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>6857.47</v>
       </c>
       <c r="F291" s="11" t="n">
-        <v>6468.17</v>
+        <v>6465.83</v>
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>1316.44</v>
       </c>
       <c r="F292" s="11" t="n">
-        <v>1300.04</v>
+        <v>1300.4</v>
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>881.0599999999999</v>
       </c>
       <c r="F293" s="11" t="n">
-        <v>1068.37</v>
+        <v>1066.6</v>
       </c>
       <c r="G293" s="12" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>3871.36</v>
       </c>
       <c r="F294" s="11" t="n">
-        <v>3826.73</v>
+        <v>3823.79</v>
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>273.76</v>
       </c>
       <c r="F295" s="11" t="n">
-        <v>257.59</v>
+        <v>257.56</v>
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>394.64</v>
       </c>
       <c r="F296" s="11" t="n">
-        <v>402.96</v>
+        <v>402.66</v>
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
@@ -13741,20 +13741,20 @@
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="C297" s="11" t="n">
-        <v>4730</v>
+        <v>4753.6</v>
       </c>
       <c r="D297" s="11" t="n">
-        <v>4445.71</v>
+        <v>4475.03</v>
       </c>
       <c r="E297" s="11" t="n">
-        <v>4713.26</v>
+        <v>4714.84</v>
       </c>
       <c r="F297" s="11" t="n">
-        <v>5239.87</v>
+        <v>5233.27</v>
       </c>
       <c r="G297" s="12" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>3472.06</v>
       </c>
       <c r="F298" s="11" t="n">
-        <v>3964.11</v>
+        <v>3962.95</v>
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>2272.37</v>
       </c>
       <c r="F299" s="11" t="n">
-        <v>2141.46</v>
+        <v>2141.49</v>
       </c>
       <c r="G299" s="12" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>3260.2</v>
       </c>
       <c r="F300" s="11" t="n">
-        <v>3357.33</v>
+        <v>3359.06</v>
       </c>
       <c r="G300" s="12" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>326.76</v>
       </c>
       <c r="F301" s="11" t="n">
-        <v>320.87</v>
+        <v>320.91</v>
       </c>
       <c r="G301" s="14" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>66.68000000000001</v>
       </c>
       <c r="F302" s="11" t="n">
-        <v>60.49</v>
+        <v>60.45</v>
       </c>
       <c r="G302" s="12" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>573.6900000000001</v>
       </c>
       <c r="F303" s="11" t="n">
-        <v>589.04</v>
+        <v>588.22</v>
       </c>
       <c r="G303" s="12" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>272.63</v>
       </c>
       <c r="F304" s="11" t="n">
-        <v>271.18</v>
+        <v>271.14</v>
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>2099.16</v>
       </c>
       <c r="F305" s="11" t="n">
-        <v>2264.58</v>
+        <v>2262.36</v>
       </c>
       <c r="G305" s="12" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>415.11</v>
       </c>
       <c r="F306" s="11" t="n">
-        <v>584.47</v>
+        <v>583.1</v>
       </c>
       <c r="G306" s="12" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>1043.84</v>
       </c>
       <c r="F307" s="11" t="n">
-        <v>1415.95</v>
+        <v>1415.84</v>
       </c>
       <c r="G307" s="12" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>755.9299999999999</v>
       </c>
       <c r="F308" s="11" t="n">
-        <v>733.42</v>
+        <v>734.63</v>
       </c>
       <c r="G308" s="12" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>13813.29</v>
       </c>
       <c r="F309" s="11" t="n">
-        <v>14361.38</v>
+        <v>14357.9</v>
       </c>
       <c r="G309" s="12" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>1656.59</v>
       </c>
       <c r="F310" s="11" t="n">
-        <v>2027.34</v>
+        <v>2024.94</v>
       </c>
       <c r="G310" s="12" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>1002.53</v>
       </c>
       <c r="F311" s="11" t="n">
-        <v>1078.91</v>
+        <v>1079.14</v>
       </c>
       <c r="G311" s="12" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>2390.08</v>
       </c>
       <c r="F312" s="11" t="n">
-        <v>2532.73</v>
+        <v>2536.04</v>
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>2504.72</v>
       </c>
       <c r="F313" s="11" t="n">
-        <v>2075.43</v>
+        <v>2074.72</v>
       </c>
       <c r="G313" s="12" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>1079.33</v>
       </c>
       <c r="F314" s="11" t="n">
-        <v>1164.88</v>
+        <v>1164.44</v>
       </c>
       <c r="G314" s="12" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>460.75</v>
       </c>
       <c r="F315" s="11" t="n">
-        <v>473.1</v>
+        <v>472.81</v>
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>1655.34</v>
       </c>
       <c r="F316" s="11" t="n">
-        <v>1595.46</v>
+        <v>1595.5</v>
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>1051.95</v>
       </c>
       <c r="F317" s="11" t="n">
-        <v>1155.58</v>
+        <v>1156.34</v>
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>530.78</v>
       </c>
       <c r="F318" s="11" t="n">
-        <v>545.8</v>
+        <v>545.63</v>
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>59.67</v>
       </c>
       <c r="F319" s="11" t="n">
-        <v>62.89</v>
+        <v>62.81</v>
       </c>
       <c r="G319" s="12" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>117.83</v>
       </c>
       <c r="F320" s="11" t="n">
-        <v>111.64</v>
+        <v>111.56</v>
       </c>
       <c r="G320" s="12" t="inlineStr">
         <is>
@@ -14807,10 +14807,10 @@
         <v>735.1900000000001</v>
       </c>
       <c r="E321" s="11" t="n">
-        <v>742.12</v>
+        <v>742.11</v>
       </c>
       <c r="F321" s="11" t="n">
-        <v>813.74</v>
+        <v>812.09</v>
       </c>
       <c r="G321" s="12" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>2351.61</v>
       </c>
       <c r="F322" s="11" t="n">
-        <v>2586.81</v>
+        <v>2584.57</v>
       </c>
       <c r="G322" s="12" t="inlineStr">
         <is>
@@ -14895,10 +14895,10 @@
         <v>134108.87</v>
       </c>
       <c r="E323" s="11" t="n">
-        <v>136957.78</v>
+        <v>136957.77</v>
       </c>
       <c r="F323" s="11" t="n">
-        <v>141341.35</v>
+        <v>141298.41</v>
       </c>
       <c r="G323" s="12" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>179.14</v>
       </c>
       <c r="F324" s="11" t="n">
-        <v>159.61</v>
+        <v>159.51</v>
       </c>
       <c r="G324" s="12" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>3430.68</v>
       </c>
       <c r="F326" s="11" t="n">
-        <v>3238.53</v>
+        <v>3236.66</v>
       </c>
       <c r="G326" s="12" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>888.89</v>
       </c>
       <c r="F327" s="11" t="n">
-        <v>843.24</v>
+        <v>842.23</v>
       </c>
       <c r="G327" s="12" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>982.9400000000001</v>
       </c>
       <c r="F328" s="11" t="n">
-        <v>932</v>
+        <v>930.7</v>
       </c>
       <c r="G328" s="12" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>380.04</v>
       </c>
       <c r="F329" s="11" t="n">
-        <v>297.63</v>
+        <v>297.42</v>
       </c>
       <c r="G329" s="12" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>1060.38</v>
       </c>
       <c r="F330" s="11" t="n">
-        <v>1245.74</v>
+        <v>1243.27</v>
       </c>
       <c r="G330" s="12" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>576.6</v>
       </c>
       <c r="F331" s="11" t="n">
-        <v>565.46</v>
+        <v>565.12</v>
       </c>
       <c r="G331" s="12" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>6157.35</v>
       </c>
       <c r="F332" s="11" t="n">
-        <v>5588.12</v>
+        <v>5602.57</v>
       </c>
       <c r="G332" s="12" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>90.98999999999999</v>
       </c>
       <c r="F333" s="11" t="n">
-        <v>100.31</v>
+        <v>100.23</v>
       </c>
       <c r="G333" s="12" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>148.72</v>
       </c>
       <c r="F334" s="11" t="n">
-        <v>175.56</v>
+        <v>175.27</v>
       </c>
       <c r="G334" s="12" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>1241.82</v>
       </c>
       <c r="F335" s="11" t="n">
-        <v>1226.99</v>
+        <v>1227.76</v>
       </c>
       <c r="G335" s="12" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>3322.51</v>
       </c>
       <c r="F336" s="11" t="n">
-        <v>3058.7</v>
+        <v>3058.37</v>
       </c>
       <c r="G336" s="12" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>34.07</v>
       </c>
       <c r="F337" s="11" t="n">
-        <v>42.89</v>
+        <v>42.81</v>
       </c>
       <c r="G337" s="12" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>13476.35</v>
       </c>
       <c r="F338" s="11" t="n">
-        <v>14046.73</v>
+        <v>14035.96</v>
       </c>
       <c r="G338" s="12" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>508.83</v>
       </c>
       <c r="F339" s="11" t="n">
-        <v>765.4400000000001</v>
+        <v>763.87</v>
       </c>
       <c r="G339" s="12" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>1748.01</v>
       </c>
       <c r="F340" s="11" t="n">
-        <v>1772.51</v>
+        <v>1770.99</v>
       </c>
       <c r="G340" s="12" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>76.81999999999999</v>
       </c>
       <c r="F341" s="11" t="n">
-        <v>78.31999999999999</v>
+        <v>78.28</v>
       </c>
       <c r="G341" s="12" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>143.75</v>
       </c>
       <c r="F342" s="11" t="n">
-        <v>161.04</v>
+        <v>161.09</v>
       </c>
       <c r="G342" s="12" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>74.09</v>
       </c>
       <c r="F343" s="11" t="n">
-        <v>76.88</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="G343" s="12" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>265.15</v>
       </c>
       <c r="F344" s="11" t="n">
-        <v>251.45</v>
+        <v>251.96</v>
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>80.7</v>
       </c>
       <c r="F345" s="11" t="n">
-        <v>75.31</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="G345" s="12" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>39.16</v>
       </c>
       <c r="F346" s="11" t="n">
-        <v>40.44</v>
+        <v>40.42</v>
       </c>
       <c r="G346" s="12" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>371.26</v>
       </c>
       <c r="F347" s="11" t="n">
-        <v>347.16</v>
+        <v>346.95</v>
       </c>
       <c r="G347" s="12" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>95.87</v>
       </c>
       <c r="F348" s="11" t="n">
-        <v>97.95</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="G348" s="12" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>1266</v>
       </c>
       <c r="F349" s="11" t="n">
-        <v>1304.47</v>
+        <v>1304.07</v>
       </c>
       <c r="G349" s="12" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>253.19</v>
       </c>
       <c r="F350" s="11" t="n">
-        <v>241.12</v>
+        <v>241.15</v>
       </c>
       <c r="G350" s="12" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>1554.73</v>
       </c>
       <c r="F351" s="11" t="n">
-        <v>1638.26</v>
+        <v>1636.71</v>
       </c>
       <c r="G351" s="12" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>7106.23</v>
       </c>
       <c r="F352" s="11" t="n">
-        <v>7860.19</v>
+        <v>7849.75</v>
       </c>
       <c r="G352" s="12" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>466.77</v>
       </c>
       <c r="F353" s="11" t="n">
-        <v>439.8</v>
+        <v>438.77</v>
       </c>
       <c r="G353" s="14" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>30.42</v>
       </c>
       <c r="F354" s="11" t="n">
-        <v>39.86</v>
+        <v>39.69</v>
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>1069.41</v>
       </c>
       <c r="F355" s="11" t="n">
-        <v>1200.22</v>
+        <v>1199.56</v>
       </c>
       <c r="G355" s="12" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>271.73</v>
       </c>
       <c r="F356" s="11" t="n">
-        <v>250.42</v>
+        <v>250.09</v>
       </c>
       <c r="G356" s="12" t="inlineStr">
         <is>
@@ -16391,10 +16391,10 @@
         <v>34574.51</v>
       </c>
       <c r="E357" s="11" t="n">
-        <v>33870.57</v>
+        <v>33870.56</v>
       </c>
       <c r="F357" s="11" t="n">
-        <v>37704.12</v>
+        <v>37681.86</v>
       </c>
       <c r="G357" s="12" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>491.81</v>
       </c>
       <c r="F358" s="11" t="n">
-        <v>541.96</v>
+        <v>542</v>
       </c>
       <c r="G358" s="14" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>1104.73</v>
       </c>
       <c r="F359" s="11" t="n">
-        <v>1129.68</v>
+        <v>1129.36</v>
       </c>
       <c r="G359" s="12" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>275.63</v>
       </c>
       <c r="F360" s="11" t="n">
-        <v>320.09</v>
+        <v>319.22</v>
       </c>
       <c r="G360" s="12" t="inlineStr">
         <is>
@@ -16611,10 +16611,10 @@
         <v>5219.01</v>
       </c>
       <c r="E362" s="11" t="n">
-        <v>5273.17</v>
+        <v>5273.16</v>
       </c>
       <c r="F362" s="11" t="n">
-        <v>5590.94</v>
+        <v>5588.76</v>
       </c>
       <c r="G362" s="12" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>275.98</v>
       </c>
       <c r="F363" s="11" t="n">
-        <v>282.33</v>
+        <v>282.16</v>
       </c>
       <c r="G363" s="12" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>407.51</v>
       </c>
       <c r="F364" s="11" t="n">
-        <v>390.2</v>
+        <v>389.67</v>
       </c>
       <c r="G364" s="12" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>4837.4</v>
       </c>
       <c r="F365" s="11" t="n">
-        <v>4939.13</v>
+        <v>4936.95</v>
       </c>
       <c r="G365" s="12" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>535.39</v>
       </c>
       <c r="F366" s="11" t="n">
-        <v>608.8099999999999</v>
+        <v>607.58</v>
       </c>
       <c r="G366" s="12" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>1665.82</v>
       </c>
       <c r="F367" s="11" t="n">
-        <v>1670.2</v>
+        <v>1667.83</v>
       </c>
       <c r="G367" s="12" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>1385.61</v>
       </c>
       <c r="F368" s="11" t="n">
-        <v>1446.13</v>
+        <v>1447.21</v>
       </c>
       <c r="G368" s="12" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>3008.44</v>
       </c>
       <c r="F369" s="11" t="n">
-        <v>3318.11</v>
+        <v>3319.38</v>
       </c>
       <c r="G369" s="12" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>835.58</v>
       </c>
       <c r="F371" s="11" t="n">
-        <v>877.22</v>
+        <v>877.9400000000001</v>
       </c>
       <c r="G371" s="12" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>199.24</v>
       </c>
       <c r="F372" s="11" t="n">
-        <v>243.65</v>
+        <v>243.57</v>
       </c>
       <c r="G372" s="12" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>1521.67</v>
       </c>
       <c r="F373" s="11" t="n">
-        <v>1666.5</v>
+        <v>1662.85</v>
       </c>
       <c r="G373" s="12" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>7528.1</v>
       </c>
       <c r="F374" s="11" t="n">
-        <v>7274.6</v>
+        <v>7267.91</v>
       </c>
       <c r="G374" s="12" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>1402.4</v>
       </c>
       <c r="F375" s="11" t="n">
-        <v>1741.61</v>
+        <v>1738.75</v>
       </c>
       <c r="G375" s="12" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>420.01</v>
       </c>
       <c r="F376" s="11" t="n">
-        <v>432.73</v>
+        <v>432.37</v>
       </c>
       <c r="G376" s="12" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>294.1</v>
       </c>
       <c r="F377" s="11" t="n">
-        <v>282.55</v>
+        <v>282.49</v>
       </c>
       <c r="G377" s="12" t="inlineStr">
         <is>
@@ -17315,10 +17315,10 @@
         <v>26413.64</v>
       </c>
       <c r="E378" s="11" t="n">
-        <v>24480.86</v>
+        <v>24480.85</v>
       </c>
       <c r="F378" s="11" t="n">
-        <v>20673.4</v>
+        <v>20653</v>
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>150.72</v>
       </c>
       <c r="F379" s="11" t="n">
-        <v>176.04</v>
+        <v>175.67</v>
       </c>
       <c r="G379" s="12" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>322.81</v>
       </c>
       <c r="F380" s="11" t="n">
-        <v>372.72</v>
+        <v>371.95</v>
       </c>
       <c r="G380" s="12" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>866.39</v>
       </c>
       <c r="F381" s="11" t="n">
-        <v>916.24</v>
+        <v>914.36</v>
       </c>
       <c r="G381" s="12" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>1346.54</v>
       </c>
       <c r="F382" s="11" t="n">
-        <v>1486.64</v>
+        <v>1484.59</v>
       </c>
       <c r="G382" s="12" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>16755.83</v>
       </c>
       <c r="F383" s="11" t="n">
-        <v>16642.26</v>
+        <v>16652.71</v>
       </c>
       <c r="G383" s="14" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>983.91</v>
       </c>
       <c r="F384" s="11" t="n">
-        <v>1032.98</v>
+        <v>1032.28</v>
       </c>
       <c r="G384" s="14" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>2797.91</v>
       </c>
       <c r="F385" s="11" t="n">
-        <v>2836.03</v>
+        <v>2835.03</v>
       </c>
       <c r="G385" s="12" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>299.65</v>
       </c>
       <c r="F386" s="11" t="n">
-        <v>335.25</v>
+        <v>334.83</v>
       </c>
       <c r="G386" s="12" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>1207.06</v>
       </c>
       <c r="F387" s="11" t="n">
-        <v>1306.9</v>
+        <v>1305.96</v>
       </c>
       <c r="G387" s="12" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>1014.6</v>
       </c>
       <c r="F388" s="11" t="n">
-        <v>1032.56</v>
+        <v>1032.18</v>
       </c>
       <c r="G388" s="12" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>386.81</v>
       </c>
       <c r="F389" s="11" t="n">
-        <v>571.03</v>
+        <v>570.1</v>
       </c>
       <c r="G389" s="12" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>850.9400000000001</v>
       </c>
       <c r="F390" s="11" t="n">
-        <v>1048.47</v>
+        <v>1047.38</v>
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>308.49</v>
       </c>
       <c r="F391" s="11" t="n">
-        <v>285.15</v>
+        <v>285.01</v>
       </c>
       <c r="G391" s="12" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>124.63</v>
       </c>
       <c r="F392" s="11" t="n">
-        <v>136.81</v>
+        <v>136.78</v>
       </c>
       <c r="G392" s="12" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>342.11</v>
       </c>
       <c r="F393" s="11" t="n">
-        <v>359.37</v>
+        <v>358.87</v>
       </c>
       <c r="G393" s="12" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>235.04</v>
       </c>
       <c r="F394" s="11" t="n">
-        <v>253.13</v>
+        <v>253.17</v>
       </c>
       <c r="G394" s="12" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>1389.87</v>
       </c>
       <c r="F395" s="11" t="n">
-        <v>1415.8</v>
+        <v>1415.34</v>
       </c>
       <c r="G395" s="12" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>25.93</v>
       </c>
       <c r="F396" s="11" t="n">
-        <v>27.75</v>
+        <v>27.72</v>
       </c>
       <c r="G396" s="12" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>398.31</v>
       </c>
       <c r="F397" s="11" t="n">
-        <v>438.24</v>
+        <v>438.58</v>
       </c>
       <c r="G397" s="12" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>206.71</v>
       </c>
       <c r="F398" s="11" t="n">
-        <v>228.35</v>
+        <v>228.14</v>
       </c>
       <c r="G398" s="12" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>528.79</v>
       </c>
       <c r="F399" s="11" t="n">
-        <v>568.77</v>
+        <v>568.79</v>
       </c>
       <c r="G399" s="12" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>509.85</v>
       </c>
       <c r="F400" s="11" t="n">
-        <v>691.92</v>
+        <v>691.95</v>
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>25.84</v>
       </c>
       <c r="F401" s="11" t="n">
-        <v>35.2</v>
+        <v>35.11</v>
       </c>
       <c r="G401" s="12" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>1405.84</v>
       </c>
       <c r="F402" s="11" t="n">
-        <v>1368.4</v>
+        <v>1367.8</v>
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>31.55</v>
       </c>
       <c r="F403" s="11" t="n">
-        <v>41.24</v>
+        <v>41.17</v>
       </c>
       <c r="G403" s="12" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>288.23</v>
       </c>
       <c r="F404" s="11" t="n">
-        <v>323.87</v>
+        <v>323.56</v>
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>42.89</v>
       </c>
       <c r="F405" s="11" t="n">
-        <v>45.74</v>
+        <v>45.7</v>
       </c>
       <c r="G405" s="12" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>156.44</v>
       </c>
       <c r="F406" s="11" t="n">
-        <v>141.74</v>
+        <v>141.68</v>
       </c>
       <c r="G406" s="12" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>961.13</v>
       </c>
       <c r="F407" s="11" t="n">
-        <v>889.4400000000001</v>
+        <v>889.4</v>
       </c>
       <c r="G407" s="14" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>147.61</v>
       </c>
       <c r="F408" s="11" t="n">
-        <v>146.03</v>
+        <v>145.89</v>
       </c>
       <c r="G408" s="12" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>183.14</v>
       </c>
       <c r="F409" s="11" t="n">
-        <v>241.09</v>
+        <v>241.27</v>
       </c>
       <c r="G409" s="12" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>530.61</v>
       </c>
       <c r="F410" s="11" t="n">
-        <v>514.09</v>
+        <v>513.8</v>
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>337.54</v>
       </c>
       <c r="F411" s="11" t="n">
-        <v>395.74</v>
+        <v>395.91</v>
       </c>
       <c r="G411" s="12" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>92.17</v>
       </c>
       <c r="F412" s="11" t="n">
-        <v>98.89</v>
+        <v>98.81</v>
       </c>
       <c r="G412" s="12" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>716.97</v>
       </c>
       <c r="F413" s="11" t="n">
-        <v>797.77</v>
+        <v>797.49</v>
       </c>
       <c r="G413" s="12" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>1938.58</v>
       </c>
       <c r="F414" s="11" t="n">
-        <v>1897.22</v>
+        <v>1897.45</v>
       </c>
       <c r="G414" s="12" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>1071.75</v>
       </c>
       <c r="F415" s="11" t="n">
-        <v>976.66</v>
+        <v>976.2</v>
       </c>
       <c r="G415" s="12" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>3933.38</v>
       </c>
       <c r="F416" s="11" t="n">
-        <v>3888.26</v>
+        <v>3884.64</v>
       </c>
       <c r="G416" s="12" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>883.87</v>
       </c>
       <c r="F417" s="11" t="n">
-        <v>809.36</v>
+        <v>808.65</v>
       </c>
       <c r="G417" s="12" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>242.25</v>
       </c>
       <c r="F418" s="11" t="n">
-        <v>225.35</v>
+        <v>225.29</v>
       </c>
       <c r="G418" s="12" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>24871.61</v>
       </c>
       <c r="F419" s="11" t="n">
-        <v>26813.04</v>
+        <v>26810.22</v>
       </c>
       <c r="G419" s="12" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>985.01</v>
       </c>
       <c r="F420" s="11" t="n">
-        <v>858.24</v>
+        <v>857.48</v>
       </c>
       <c r="G420" s="12" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>822.0700000000001</v>
       </c>
       <c r="F421" s="11" t="n">
-        <v>842.62</v>
+        <v>842.6900000000001</v>
       </c>
       <c r="G421" s="12" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>3210.57</v>
       </c>
       <c r="F422" s="11" t="n">
-        <v>3182.98</v>
+        <v>3181.54</v>
       </c>
       <c r="G422" s="12" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>857.48</v>
       </c>
       <c r="F423" s="11" t="n">
-        <v>1014.38</v>
+        <v>1012.02</v>
       </c>
       <c r="G423" s="14" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>71.73999999999999</v>
       </c>
       <c r="F424" s="11" t="n">
-        <v>79.77</v>
+        <v>79.67</v>
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>1663.55</v>
       </c>
       <c r="F425" s="11" t="n">
-        <v>2552.68</v>
+        <v>2553.38</v>
       </c>
       <c r="G425" s="12" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>1338.18</v>
       </c>
       <c r="F426" s="11" t="n">
-        <v>1429.51</v>
+        <v>1427.22</v>
       </c>
       <c r="G426" s="12" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>13642.46</v>
       </c>
       <c r="F427" s="11" t="n">
-        <v>13377.77</v>
+        <v>13378.41</v>
       </c>
       <c r="G427" s="12" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>518.1900000000001</v>
       </c>
       <c r="F428" s="11" t="n">
-        <v>496.29</v>
+        <v>495.97</v>
       </c>
       <c r="G428" s="12" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>263.48</v>
       </c>
       <c r="F429" s="11" t="n">
-        <v>333.4</v>
+        <v>333.22</v>
       </c>
       <c r="G429" s="12" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>2591.02</v>
       </c>
       <c r="F430" s="11" t="n">
-        <v>2783.85</v>
+        <v>2797.76</v>
       </c>
       <c r="G430" s="12" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>464.73</v>
       </c>
       <c r="F431" s="11" t="n">
-        <v>457.98</v>
+        <v>457.96</v>
       </c>
       <c r="G431" s="12" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>407.89</v>
       </c>
       <c r="F432" s="11" t="n">
-        <v>459.84</v>
+        <v>459.31</v>
       </c>
       <c r="G432" s="12" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>4988.59</v>
       </c>
       <c r="F433" s="11" t="n">
-        <v>4910.53</v>
+        <v>4915.03</v>
       </c>
       <c r="G433" s="12" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>838.53</v>
       </c>
       <c r="F434" s="11" t="n">
-        <v>919.8</v>
+        <v>920.79</v>
       </c>
       <c r="G434" s="12" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>1727.68</v>
       </c>
       <c r="F435" s="11" t="n">
-        <v>1711.62</v>
+        <v>1711.14</v>
       </c>
       <c r="G435" s="14" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>3775.3</v>
       </c>
       <c r="F437" s="11" t="n">
-        <v>3843.6</v>
+        <v>3846.33</v>
       </c>
       <c r="G437" s="14" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>44.81</v>
       </c>
       <c r="F438" s="11" t="n">
-        <v>51.14</v>
+        <v>51.05</v>
       </c>
       <c r="G438" s="12" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>297.69</v>
       </c>
       <c r="F440" s="11" t="n">
-        <v>355.17</v>
+        <v>355.9</v>
       </c>
       <c r="G440" s="14" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>183.66</v>
       </c>
       <c r="F441" s="11" t="n">
-        <v>228.42</v>
+        <v>228.03</v>
       </c>
       <c r="G441" s="12" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>440.98</v>
       </c>
       <c r="F442" s="11" t="n">
-        <v>565.05</v>
+        <v>565.3099999999999</v>
       </c>
       <c r="G442" s="12" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>812.45</v>
       </c>
       <c r="F443" s="11" t="n">
-        <v>751.36</v>
+        <v>750.7</v>
       </c>
       <c r="G443" s="12" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>456.3</v>
       </c>
       <c r="F444" s="11" t="n">
-        <v>530.99</v>
+        <v>530.37</v>
       </c>
       <c r="G444" s="12" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>286.48</v>
       </c>
       <c r="F445" s="11" t="n">
-        <v>358.36</v>
+        <v>357.07</v>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>684.76</v>
       </c>
       <c r="F446" s="11" t="n">
-        <v>785.14</v>
+        <v>785.61</v>
       </c>
       <c r="G446" s="12" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>1524.54</v>
       </c>
       <c r="F447" s="11" t="n">
-        <v>1640.01</v>
+        <v>1640.1</v>
       </c>
       <c r="G447" s="12" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>1099.81</v>
       </c>
       <c r="F448" s="11" t="n">
-        <v>1112.69</v>
+        <v>1113.06</v>
       </c>
       <c r="G448" s="12" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>4565.96</v>
       </c>
       <c r="F449" s="11" t="n">
-        <v>5178.53</v>
+        <v>5177.09</v>
       </c>
       <c r="G449" s="12" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>642.3200000000001</v>
       </c>
       <c r="F450" s="11" t="n">
-        <v>679.42</v>
+        <v>679.2</v>
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>389.13</v>
       </c>
       <c r="F452" s="11" t="n">
-        <v>383.76</v>
+        <v>383.46</v>
       </c>
       <c r="G452" s="12" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>197.64</v>
       </c>
       <c r="F453" s="11" t="n">
-        <v>179.46</v>
+        <v>179.35</v>
       </c>
       <c r="G453" s="12" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>576.47</v>
       </c>
       <c r="F454" s="11" t="n">
-        <v>646.41</v>
+        <v>645.9</v>
       </c>
       <c r="G454" s="12" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>1248.59</v>
       </c>
       <c r="F455" s="11" t="n">
-        <v>1415.8</v>
+        <v>1414.43</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>2620.03</v>
       </c>
       <c r="F456" s="11" t="n">
-        <v>2962.37</v>
+        <v>2959.51</v>
       </c>
       <c r="G456" s="12" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>1456.26</v>
       </c>
       <c r="F457" s="11" t="n">
-        <v>1503.48</v>
+        <v>1502.6</v>
       </c>
       <c r="G457" s="12" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>1096.39</v>
       </c>
       <c r="F458" s="11" t="n">
-        <v>1183.46</v>
+        <v>1181.58</v>
       </c>
       <c r="G458" s="12" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>418.18</v>
       </c>
       <c r="F459" s="11" t="n">
-        <v>517.0700000000001</v>
+        <v>515.1900000000001</v>
       </c>
       <c r="G459" s="14" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>3300.67</v>
       </c>
       <c r="F460" s="11" t="n">
-        <v>3229.65</v>
+        <v>3226.08</v>
       </c>
       <c r="G460" s="12" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>2607.85</v>
       </c>
       <c r="F461" s="11" t="n">
-        <v>2758.45</v>
+        <v>2760.45</v>
       </c>
       <c r="G461" s="12" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>3298.7</v>
       </c>
       <c r="F462" s="11" t="n">
-        <v>3124.75</v>
+        <v>3126.33</v>
       </c>
       <c r="G462" s="12" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>700.23</v>
       </c>
       <c r="F463" s="11" t="n">
-        <v>798.77</v>
+        <v>798</v>
       </c>
       <c r="G463" s="12" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>4199.9</v>
       </c>
       <c r="F464" s="11" t="n">
-        <v>3907.42</v>
+        <v>3907.55</v>
       </c>
       <c r="G464" s="12" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>4153.44</v>
       </c>
       <c r="F465" s="11" t="n">
-        <v>3834.53</v>
+        <v>3834.4</v>
       </c>
       <c r="G465" s="12" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>1429.32</v>
       </c>
       <c r="F466" s="11" t="n">
-        <v>1372.33</v>
+        <v>1371.5</v>
       </c>
       <c r="G466" s="12" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>3827.65</v>
       </c>
       <c r="F467" s="11" t="n">
-        <v>4427.7</v>
+        <v>4424.35</v>
       </c>
       <c r="G467" s="12" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>25.06</v>
       </c>
       <c r="F468" s="11" t="n">
-        <v>26.99</v>
+        <v>26.98</v>
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>475.52</v>
       </c>
       <c r="F469" s="11" t="n">
-        <v>520.39</v>
+        <v>519.54</v>
       </c>
       <c r="G469" s="12" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>376.63</v>
       </c>
       <c r="F470" s="11" t="n">
-        <v>371.65</v>
+        <v>371.44</v>
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>40.88</v>
       </c>
       <c r="F471" s="11" t="n">
-        <v>49.91</v>
+        <v>49.86</v>
       </c>
       <c r="G471" s="12" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>3631.9</v>
       </c>
       <c r="F472" s="11" t="n">
-        <v>3419.9</v>
+        <v>3418.38</v>
       </c>
       <c r="G472" s="12" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>1558.1</v>
       </c>
       <c r="F473" s="11" t="n">
-        <v>1697.07</v>
+        <v>1698.04</v>
       </c>
       <c r="G473" s="14" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>26.55</v>
       </c>
       <c r="F474" s="11" t="n">
-        <v>29.59</v>
+        <v>29.54</v>
       </c>
       <c r="G474" s="12" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>11666.98</v>
       </c>
       <c r="F475" s="11" t="n">
-        <v>11882.77</v>
+        <v>11876.59</v>
       </c>
       <c r="G475" s="12" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>179.36</v>
       </c>
       <c r="F476" s="11" t="n">
-        <v>159.07</v>
+        <v>158.94</v>
       </c>
       <c r="G476" s="12" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>1313.78</v>
       </c>
       <c r="F477" s="11" t="n">
-        <v>1368.29</v>
+        <v>1368.23</v>
       </c>
       <c r="G477" s="12" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>1113.68</v>
       </c>
       <c r="F478" s="11" t="n">
-        <v>1155.18</v>
+        <v>1155.05</v>
       </c>
       <c r="G478" s="12" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>655.71</v>
       </c>
       <c r="F479" s="11" t="n">
-        <v>682.1900000000001</v>
+        <v>682.4400000000001</v>
       </c>
       <c r="G479" s="12" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>419.73</v>
       </c>
       <c r="F480" s="11" t="n">
-        <v>409.7</v>
+        <v>409.37</v>
       </c>
       <c r="G480" s="12" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>997.21</v>
       </c>
       <c r="F481" s="11" t="n">
-        <v>1107.95</v>
+        <v>1106.09</v>
       </c>
       <c r="G481" s="12" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>433.53</v>
       </c>
       <c r="F482" s="11" t="n">
-        <v>466.2</v>
+        <v>466.13</v>
       </c>
       <c r="G482" s="12" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>687.63</v>
       </c>
       <c r="F483" s="11" t="n">
-        <v>575.74</v>
+        <v>575.4400000000001</v>
       </c>
       <c r="G483" s="12" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>322.88</v>
       </c>
       <c r="F484" s="11" t="n">
-        <v>342.48</v>
+        <v>342.29</v>
       </c>
       <c r="G484" s="12" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>961.05</v>
       </c>
       <c r="F485" s="11" t="n">
-        <v>999.8</v>
+        <v>1000.33</v>
       </c>
       <c r="G485" s="12" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>115.25</v>
       </c>
       <c r="F486" s="11" t="n">
-        <v>125.15</v>
+        <v>125.13</v>
       </c>
       <c r="G486" s="12" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>1381.53</v>
       </c>
       <c r="F487" s="11" t="n">
-        <v>1400.42</v>
+        <v>1398.84</v>
       </c>
       <c r="G487" s="12" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>522.29</v>
       </c>
       <c r="F488" s="11" t="n">
-        <v>475.11</v>
+        <v>474.62</v>
       </c>
       <c r="G488" s="12" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>3039.75</v>
       </c>
       <c r="F489" s="11" t="n">
-        <v>2990.05</v>
+        <v>2985.84</v>
       </c>
       <c r="G489" s="12" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>861.5</v>
       </c>
       <c r="F490" s="11" t="n">
-        <v>837.16</v>
+        <v>836.49</v>
       </c>
       <c r="G490" s="12" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>122.46</v>
       </c>
       <c r="F491" s="11" t="n">
-        <v>128.12</v>
+        <v>127.93</v>
       </c>
       <c r="G491" s="12" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>476.3</v>
       </c>
       <c r="F492" s="11" t="n">
-        <v>571.36</v>
+        <v>570.58</v>
       </c>
       <c r="G492" s="12" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>858.63</v>
       </c>
       <c r="F493" s="11" t="n">
-        <v>1041.76</v>
+        <v>1041.36</v>
       </c>
       <c r="G493" s="12" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>207.88</v>
       </c>
       <c r="F494" s="11" t="n">
-        <v>231.6</v>
+        <v>231.39</v>
       </c>
       <c r="G494" s="12" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>1311.29</v>
       </c>
       <c r="F495" s="11" t="n">
-        <v>1382.47</v>
+        <v>1381.83</v>
       </c>
       <c r="G495" s="12" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>19.67</v>
       </c>
       <c r="F496" s="11" t="n">
-        <v>20.51</v>
+        <v>20.5</v>
       </c>
       <c r="G496" s="12" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>81.55</v>
       </c>
       <c r="F497" s="11" t="n">
-        <v>96.52</v>
+        <v>96.48</v>
       </c>
       <c r="G497" s="12" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>582.84</v>
       </c>
       <c r="F498" s="11" t="n">
-        <v>680.03</v>
+        <v>679.48</v>
       </c>
       <c r="G498" s="12" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>1410.29</v>
       </c>
       <c r="F499" s="11" t="n">
-        <v>1481.33</v>
+        <v>1484.36</v>
       </c>
       <c r="G499" s="12" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>14252.53</v>
       </c>
       <c r="F500" s="11" t="n">
-        <v>13839.09</v>
+        <v>13838.87</v>
       </c>
       <c r="G500" s="12" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>903.72</v>
       </c>
       <c r="F501" s="11" t="n">
-        <v>926.66</v>
+        <v>927.91</v>
       </c>
       <c r="G501" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 18-Apr-2026  15:29:25    |    Closing Price Date: 17-Apr-2026</t>
+          <t>Scan Run: 19-Apr-2026  15:29:22    |    Closing Price Date: 17-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>79.2</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46.2</v>
+        <v>46.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>500</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>18-Apr-2026  15:29:25</t>
+          <t>19-Apr-2026  15:29:22</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 46.2% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 46.8% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 231 of 500 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 234 of 500 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>1532.01</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1430.13</v>
+        <v>1426.62</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1051.07</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1086.12</v>
+        <v>1084.48</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>32825.75</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>32576.19</v>
+        <v>32537.09</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>470.19</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>474.85</v>
+        <v>474.87</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>419.07</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>406.96</v>
+        <v>407.32</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>1251.73</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1473.83</v>
+        <v>1473.29</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>6132.31</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5666.65</v>
+        <v>5663.75</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
         <v>26099.92</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>26614.29</v>
+        <v>26614.28</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>28442.35</v>
+        <v>28400.05</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>329.33</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>308.43</v>
+        <v>308.18</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>63.52</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>92.08</v>
+        <v>91.98</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1296.97</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1590.01</v>
+        <v>1585.87</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>922.08</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>833.41</v>
+        <v>833.85</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1484.12</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1696.08</v>
+        <v>1694.22</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>866.0700000000001</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>982.33</v>
+        <v>979.87</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>252.98</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>246.85</v>
+        <v>246.53</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1027.24</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>949.13</v>
+        <v>948.15</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>2054.36</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2232.3</v>
+        <v>2227.78</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>948.5700000000001</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>968.52</v>
+        <v>967</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>1444.68</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1416.09</v>
+        <v>1415.21</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>156.61</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>140.96</v>
+        <v>140.82</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>650.98</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>716.64</v>
+        <v>714.11</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>311.32</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>373.36</v>
+        <v>372.62</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>1456.56</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1640.03</v>
+        <v>1638.14</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>3746.44</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3614.48</v>
+        <v>3611.45</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>476.56</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>510.23</v>
+        <v>510.33</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>2850.7</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2731.99</v>
+        <v>2727.58</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>485.61</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>481.85</v>
+        <v>481.89</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>5444.86</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5408.15</v>
+        <v>5404.77</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>1417.64</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1651.42</v>
+        <v>1646.99</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>13.86</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>15.98</v>
+        <v>15.96</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>7005.95</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7082.99</v>
+        <v>7088.55</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>465.69</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>519.0599999999999</v>
+        <v>518.45</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>3193.57</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2877.25</v>
+        <v>2881.87</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>494.43</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>555.11</v>
+        <v>554.24</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>251.11</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>248.73</v>
+        <v>248.39</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         <v>10516.51</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>9955.67</v>
+        <v>9955.68</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>9040.299999999999</v>
+        <v>9043.85</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>2023.08</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1876.81</v>
+        <v>1875.49</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>729.15</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>831.74</v>
+        <v>829.8099999999999</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>7457.55</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>7349.09</v>
+        <v>7346.71</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>444.86</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>467.74</v>
+        <v>467.16</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>232.04</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>272.27</v>
+        <v>272.01</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>790.27</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>896.08</v>
+        <v>895.1</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>874.03</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>880.65</v>
+        <v>879.8099999999999</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>177.87</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>160.33</v>
+        <v>160.24</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>2355.08</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2464.69</v>
+        <v>2463.41</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2766,9 +2766,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -2798,7 +2798,7 @@
         <v>646.05</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>615.11</v>
+        <v>614.65</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>1584.68</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1506.98</v>
+        <v>1507.57</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>8441.299999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>8603.75</v>
+        <v>8595.75</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>544.5</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>579.53</v>
+        <v>579.49</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>6331.08</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>6301.14</v>
+        <v>6295.84</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>942.3</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>874.49</v>
+        <v>874.71</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>1274.22</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1198.9</v>
+        <v>1196.75</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>190.8</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>229.65</v>
+        <v>228.24</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>1288.16</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1235.05</v>
+        <v>1234.13</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>9393.49</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9091.73</v>
+        <v>9088.67</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>1841.62</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1938.37</v>
+        <v>1938.85</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>85.63</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>98.56</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>10155.35</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>11288.9</v>
+        <v>11274.1</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>913.67</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>937.48</v>
+        <v>937.53</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>2282.09</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2388.88</v>
+        <v>2386.87</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>474.3</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>479.99</v>
+        <v>479.74</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>162.57</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>159.69</v>
+        <v>159.48</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>282.04</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>272.91</v>
+        <v>272.67</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>151.62</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>139.87</v>
+        <v>139.68</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>3541.59</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>4040.74</v>
+        <v>4033.51</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>750.46</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>958.0599999999999</v>
+        <v>958.63</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>4660.44</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>4792.36</v>
+        <v>4781.27</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>1571.29</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1757.99</v>
+        <v>1755.08</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>1305.92</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1409.99</v>
+        <v>1409.87</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>433.01</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>404.27</v>
+        <v>403.82</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>1628.34</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1792.04</v>
+        <v>1790.21</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>451.31</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>496.98</v>
+        <v>496.63</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>1711.35</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1479.26</v>
+        <v>1478.49</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>1887.89</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1925.65</v>
+        <v>1926.03</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>1582.52</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1655.94</v>
+        <v>1654.94</v>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>267.16</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>256.52</v>
+        <v>256</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>642.05</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>688.08</v>
+        <v>687.3099999999999</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>369.48</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>371.73</v>
+        <v>371.3</v>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>273.49</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>313.82</v>
+        <v>313.12</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>5268.82</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>5667.21</v>
+        <v>5656.77</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>1776.97</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1822.77</v>
+        <v>1821.22</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4379,10 +4379,10 @@
         <v>34394.88</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>34201.32</v>
+        <v>34201.31</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>35099.05</v>
+        <v>35050.92</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>320.62</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>325.51</v>
+        <v>325.41</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>722.55</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>858.1900000000001</v>
+        <v>856.61</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>5752.92</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>5748.51</v>
+        <v>5749.07</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>2945.86</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2643.83</v>
+        <v>2642.62</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>378.99</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>399.77</v>
+        <v>400.11</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>244.39</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>259.91</v>
+        <v>259.76</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>690.23</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>735.4400000000001</v>
+        <v>734.25</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>140.69</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>132.96</v>
+        <v>132.84</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>854.22</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>833.39</v>
+        <v>832.8</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>1692.86</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1878.94</v>
+        <v>1874.38</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>826.91</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>882.87</v>
+        <v>882.38</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>180.22</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>186.25</v>
+        <v>185.92</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>1045.05</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>940.91</v>
+        <v>940.22</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>1284.93</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1416.7</v>
+        <v>1413.25</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>3594.6</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>3597.7</v>
+        <v>3596.36</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>35.76</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>37.6</v>
+        <v>37.53</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>728.85</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>757.6</v>
+        <v>755.96</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>4963.76</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>5508.54</v>
+        <v>5497.4</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>156.92</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>159.42</v>
+        <v>159.11</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>173.51</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>178.15</v>
+        <v>177.96</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>695.8099999999999</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>682.21</v>
+        <v>680.99</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>782.49</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>853.91</v>
+        <v>852.74</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>444.13</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>473.76</v>
+        <v>473.3</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>950.73</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>844.02</v>
+        <v>843.5599999999999</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>1563.16</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1591.27</v>
+        <v>1589.82</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>1579.65</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1729.2</v>
+        <v>1725.5</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>1289.63</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1410.71</v>
+        <v>1409.87</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>747.9</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>943.72</v>
+        <v>942.24</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>437.83</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>402.8</v>
+        <v>402.66</v>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>1439.9</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1572.42</v>
+        <v>1570.54</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>1294.44</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1546.19</v>
+        <v>1547.23</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>2012.24</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>2182.59</v>
+        <v>2180.03</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>477.23</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>512.92</v>
+        <v>512.65</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>1132.36</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1398.72</v>
+        <v>1395.96</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>2098.23</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>2182.19</v>
+        <v>2180.91</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>7289.69</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>6869.36</v>
+        <v>6869.49</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>1229.14</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1249.53</v>
+        <v>1248.51</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>4174.36</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>4579.73</v>
+        <v>4579.81</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>247.13</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>276.22</v>
+        <v>275.76</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>258.82</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>244.97</v>
+        <v>244.8</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>4663.98</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>4177.36</v>
+        <v>4172.69</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>927.72</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1103.21</v>
+        <v>1100.94</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>459.62</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>490.35</v>
+        <v>490.21</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>1950.81</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>2036.82</v>
+        <v>2033.57</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>3123.86</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>2807.19</v>
+        <v>2803.86</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>104.9</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>132.37</v>
+        <v>132.21</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1113.95</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1152.75</v>
+        <v>1152.61</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>1047.45</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1205.51</v>
+        <v>1204.04</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>1490.41</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1684.83</v>
+        <v>1683.1</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>432.62</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>415.92</v>
+        <v>415.81</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>113.86</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>139.21</v>
+        <v>138.91</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>6142.68</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>6225.11</v>
+        <v>6222.79</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>10814.96</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>13057.7</v>
+        <v>13051.43</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>584.62</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>670.6900000000001</v>
+        <v>669.45</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>4064.54</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>4029.46</v>
+        <v>4023.89</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>2332.32</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>2449.74</v>
+        <v>2444.19</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>1253.57</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1256.37</v>
+        <v>1255.62</v>
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>1668.66</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1890.41</v>
+        <v>1890.42</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>7170.73</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>6800.95</v>
+        <v>6797.43</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>855.98</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>937.33</v>
+        <v>936.14</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>317.42</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>350.06</v>
+        <v>350.16</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>411.14</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>480.55</v>
+        <v>480.09</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>495.76</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>494.21</v>
+        <v>494.25</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>442.59</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>502.06</v>
+        <v>501.79</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>2411.58</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>2500.19</v>
+        <v>2500.31</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>201.56</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>196.15</v>
+        <v>196</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>1378.19</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>1474.42</v>
+        <v>1473.83</v>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>3237.07</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>3425.76</v>
+        <v>3426.46</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>249.56</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>271.64</v>
+        <v>271.53</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>320.78</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>353.02</v>
+        <v>352.65</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>810.4299999999999</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>851.4299999999999</v>
+        <v>850.23</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>276.52</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>248.69</v>
+        <v>248.5</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>837.48</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>836.28</v>
+        <v>834.25</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>172.89</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>184.09</v>
+        <v>183.83</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>240.55</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>303.81</v>
+        <v>303.36</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>420.45</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>524.92</v>
+        <v>523.04</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>3295.73</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>3466.35</v>
+        <v>3459.72</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>862.17</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>868.36</v>
+        <v>867.22</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>240.44</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>298.24</v>
+        <v>297.55</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>153.56</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>163.69</v>
+        <v>163.55</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>1348.33</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>1159.59</v>
+        <v>1158.98</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>378.73</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>381.55</v>
+        <v>380.05</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>7951.66</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>8504.27</v>
+        <v>8501.559999999999</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>1729.74</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>1764.24</v>
+        <v>1762.14</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>2430.6</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>2554.23</v>
+        <v>2553.45</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>2117.47</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>1963.51</v>
+        <v>1961.26</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>585.87</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>522.03</v>
+        <v>521.45</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>94.51000000000001</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>93.29000000000001</v>
+        <v>93.22</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>436.94</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>474.84</v>
+        <v>473.85</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>2102.15</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>2438.57</v>
+        <v>2439.39</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>327.55</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>333.89</v>
+        <v>333.36</v>
       </c>
       <c r="G176" s="14" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>586.72</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>631.62</v>
+        <v>631.65</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>1097.16</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1148.71</v>
+        <v>1148.42</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>909.76</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>1015.39</v>
+        <v>1013.91</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>1694.76</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>1930.13</v>
+        <v>1925.35</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>269.77</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>246.06</v>
+        <v>245.89</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>159.75</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>162.41</v>
+        <v>162.3</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>603.9400000000001</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>567.4299999999999</v>
+        <v>566.88</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>639.13</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>594.58</v>
+        <v>593.65</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>2720.86</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>2737.15</v>
+        <v>2735.13</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>1529.38</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>1675.1</v>
+        <v>1671.88</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>2410.37</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>2403.81</v>
+        <v>2401.07</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>267.49</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>294.36</v>
+        <v>294.15</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>362.6</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>404.29</v>
+        <v>403.74</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>3672.68</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>3084.75</v>
+        <v>3084.5</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>4027.61</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>4268.39</v>
+        <v>4264.24</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>391.55</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>475.4</v>
+        <v>475.34</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>1311.34</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>1415.62</v>
+        <v>1414.32</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>720.9400000000001</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>744.67</v>
+        <v>743.53</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>1441.8</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>1527.65</v>
+        <v>1530.17</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>2536.88</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>2555.31</v>
+        <v>2553.05</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>841.04</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>911.92</v>
+        <v>911.6900000000001</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>652.3200000000001</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>706.09</v>
+        <v>705.9299999999999</v>
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>549.08</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>529.23</v>
+        <v>528.5599999999999</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>5369.65</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>5194.83</v>
+        <v>5194.04</v>
       </c>
       <c r="G200" s="14" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>73.98</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>74.67</v>
+        <v>74.48</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>935.13</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>838.11</v>
+        <v>837.47</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>522.6799999999999</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>424.92</v>
+        <v>424.81</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>384.35</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>411.62</v>
+        <v>411.78</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>2207.14</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>2330.64</v>
+        <v>2330.92</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>566.71</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>532.85</v>
+        <v>532.66</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>1059.51</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>1127.89</v>
+        <v>1127.7</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>301.97</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>285.85</v>
+        <v>285.65</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>30061.83</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>33644.68</v>
+        <v>33608.98</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>462.03</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>468.42</v>
+        <v>468.24</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>184.5</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>202.85</v>
+        <v>202.3</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>1980.59</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>2127.35</v>
+        <v>2127.43</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>1316.68</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>1352.77</v>
+        <v>1352.23</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>1832.09</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>1883.88</v>
+        <v>1883.42</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>584</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>614.17</v>
+        <v>614.0700000000001</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>85.92</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>92.29000000000001</v>
+        <v>92.13</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>69.42</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>73.17</v>
+        <v>73.08</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>126.25</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>139.44</v>
+        <v>139.23</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>55.77</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>55.24</v>
+        <v>55.1</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>330.54</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>348.64</v>
+        <v>347.9</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>162.42</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>182.01</v>
+        <v>181.87</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>484.03</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>494.33</v>
+        <v>493.73</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>1464.15</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>1568.08</v>
+        <v>1566.32</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>474.64</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>516.26</v>
+        <v>515.65</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>642.12</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>701.72</v>
+        <v>700.98</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>2121.83</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>2249.96</v>
+        <v>2250.09</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>904.47</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>802.9400000000001</v>
+        <v>802.6</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>4537.43</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>4987.49</v>
+        <v>4986.1</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>851.02</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>852.52</v>
+        <v>850.63</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>433.47</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>408.19</v>
+        <v>407.74</v>
       </c>
       <c r="G232" s="14" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>1351.55</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>1482.26</v>
+        <v>1484.37</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>1223.2</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>1165.79</v>
+        <v>1165.39</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>92.09</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>121.97</v>
+        <v>121.64</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>714.9299999999999</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>868.12</v>
+        <v>868.27</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>34.25</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>37.09</v>
+        <v>37.01</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>151.94</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>150.27</v>
+        <v>150.19</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>1490.14</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>1454.03</v>
+        <v>1452.73</v>
       </c>
       <c r="G239" s="14" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>21.04</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>21.79</v>
+        <v>21.73</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>139.02</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>157.7</v>
+        <v>157.18</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>562.78</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>644.45</v>
+        <v>645.11</v>
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>122.41</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>139.93</v>
+        <v>139.28</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>102.02</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>114.76</v>
+        <v>114.56</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>311.39</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>356.63</v>
+        <v>356.42</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>275.98</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>298.74</v>
+        <v>298.84</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>115.97</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>107.34</v>
+        <v>107.17</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>1994.33</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>1852.97</v>
+        <v>1850.94</v>
       </c>
       <c r="G248" s="14" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>571.77</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>608.4</v>
+        <v>607.78</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>191.33</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>194.6</v>
+        <v>194.48</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>1166.36</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>1074.98</v>
+        <v>1074.37</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>248.35</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>274.76</v>
+        <v>274.38</v>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>5427.71</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>5657.12</v>
+        <v>5648.61</v>
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>447.95</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>433.51</v>
+        <v>433.16</v>
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>128.93</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>138.06</v>
+        <v>137.85</v>
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>15.83</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>16.68</v>
+        <v>16.65</v>
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>754.51</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>743.71</v>
+        <v>743.4299999999999</v>
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>495.33</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>501.39</v>
+        <v>500.6</v>
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>15027.77</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>17589.41</v>
+        <v>17570</v>
       </c>
       <c r="G259" s="14" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>258.8</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>276.75</v>
+        <v>276.52</v>
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>1187.67</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>1136.16</v>
+        <v>1136.56</v>
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>479.39</v>
       </c>
       <c r="F262" s="11" t="n">
-        <v>561.3</v>
+        <v>560.92</v>
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>614.4299999999999</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>661.4299999999999</v>
+        <v>660.39</v>
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>891.75</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>987.79</v>
+        <v>986.62</v>
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>574.36</v>
       </c>
       <c r="F265" s="11" t="n">
-        <v>713.12</v>
+        <v>711.37</v>
       </c>
       <c r="G265" s="12" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>276.62</v>
       </c>
       <c r="F266" s="11" t="n">
-        <v>312.71</v>
+        <v>311.85</v>
       </c>
       <c r="G266" s="12" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>232.2</v>
       </c>
       <c r="F267" s="11" t="n">
-        <v>281.03</v>
+        <v>280.61</v>
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>789.61</v>
       </c>
       <c r="F268" s="11" t="n">
-        <v>910.62</v>
+        <v>908.27</v>
       </c>
       <c r="G268" s="14" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>1001.68</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>1034.49</v>
+        <v>1034.02</v>
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>414.93</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>466.95</v>
+        <v>465.38</v>
       </c>
       <c r="G270" s="12" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>193.46</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>220.81</v>
+        <v>220.67</v>
       </c>
       <c r="G271" s="12" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>286.79</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>256.44</v>
+        <v>256.38</v>
       </c>
       <c r="G272" s="14" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>3848.17</v>
       </c>
       <c r="F273" s="11" t="n">
-        <v>4788.18</v>
+        <v>4785.57</v>
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>580.21</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>701.53</v>
+        <v>699.95</v>
       </c>
       <c r="G274" s="12" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>4406.24</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>4195.5</v>
+        <v>4194.37</v>
       </c>
       <c r="G275" s="12" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>950.05</v>
       </c>
       <c r="F276" s="11" t="n">
-        <v>1048.61</v>
+        <v>1045.38</v>
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>659.86</v>
       </c>
       <c r="F277" s="11" t="n">
-        <v>668.83</v>
+        <v>668.66</v>
       </c>
       <c r="G277" s="12" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>1573.73</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>1709.63</v>
+        <v>1706.5</v>
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>1389.67</v>
       </c>
       <c r="F279" s="11" t="n">
-        <v>1161.22</v>
+        <v>1160.13</v>
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>128.08</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>168.05</v>
+        <v>167.47</v>
       </c>
       <c r="G280" s="12" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>388.68</v>
       </c>
       <c r="F281" s="11" t="n">
-        <v>405.81</v>
+        <v>405.52</v>
       </c>
       <c r="G281" s="12" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>1133.02</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>1157.48</v>
+        <v>1155.58</v>
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>787.88</v>
       </c>
       <c r="F283" s="11" t="n">
-        <v>1039.72</v>
+        <v>1037.1</v>
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>876.6900000000001</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>951.41</v>
+        <v>951.13</v>
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>1383.54</v>
       </c>
       <c r="F285" s="11" t="n">
-        <v>1442.04</v>
+        <v>1440.4</v>
       </c>
       <c r="G285" s="12" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>325.95</v>
       </c>
       <c r="F286" s="11" t="n">
-        <v>393.5</v>
+        <v>392.84</v>
       </c>
       <c r="G286" s="12" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>1039.32</v>
       </c>
       <c r="F287" s="11" t="n">
-        <v>943.23</v>
+        <v>941.95</v>
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>116.86</v>
       </c>
       <c r="F288" s="11" t="n">
-        <v>137.12</v>
+        <v>136.99</v>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>517.47</v>
       </c>
       <c r="F289" s="11" t="n">
-        <v>540.22</v>
+        <v>539.42</v>
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
@@ -13414,9 +13414,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I289" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I289" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J289" s="13" t="inlineStr">
@@ -13446,7 +13446,7 @@
         <v>809.61</v>
       </c>
       <c r="F290" s="11" t="n">
-        <v>844.97</v>
+        <v>844.8200000000001</v>
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>6857.47</v>
       </c>
       <c r="F291" s="11" t="n">
-        <v>6465.83</v>
+        <v>6464.98</v>
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>1316.44</v>
       </c>
       <c r="F292" s="11" t="n">
-        <v>1300.4</v>
+        <v>1301.01</v>
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>881.0599999999999</v>
       </c>
       <c r="F293" s="11" t="n">
-        <v>1066.6</v>
+        <v>1065.48</v>
       </c>
       <c r="G293" s="12" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>3871.36</v>
       </c>
       <c r="F294" s="11" t="n">
-        <v>3823.79</v>
+        <v>3824.15</v>
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>273.76</v>
       </c>
       <c r="F295" s="11" t="n">
-        <v>257.56</v>
+        <v>257.41</v>
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>394.64</v>
       </c>
       <c r="F296" s="11" t="n">
-        <v>402.66</v>
+        <v>402.36</v>
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>4714.84</v>
       </c>
       <c r="F297" s="11" t="n">
-        <v>5233.27</v>
+        <v>5245.52</v>
       </c>
       <c r="G297" s="12" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>3472.06</v>
       </c>
       <c r="F298" s="11" t="n">
-        <v>3962.95</v>
+        <v>3965.38</v>
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>2272.37</v>
       </c>
       <c r="F299" s="11" t="n">
-        <v>2141.49</v>
+        <v>2138.81</v>
       </c>
       <c r="G299" s="12" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>3260.2</v>
       </c>
       <c r="F300" s="11" t="n">
-        <v>3359.06</v>
+        <v>3357.6</v>
       </c>
       <c r="G300" s="12" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>326.76</v>
       </c>
       <c r="F301" s="11" t="n">
-        <v>320.91</v>
+        <v>320.74</v>
       </c>
       <c r="G301" s="14" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>66.68000000000001</v>
       </c>
       <c r="F302" s="11" t="n">
-        <v>60.45</v>
+        <v>60.43</v>
       </c>
       <c r="G302" s="12" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>573.6900000000001</v>
       </c>
       <c r="F303" s="11" t="n">
-        <v>588.22</v>
+        <v>586.85</v>
       </c>
       <c r="G303" s="12" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>272.63</v>
       </c>
       <c r="F304" s="11" t="n">
-        <v>271.14</v>
+        <v>271.19</v>
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>2099.16</v>
       </c>
       <c r="F305" s="11" t="n">
-        <v>2262.36</v>
+        <v>2258.51</v>
       </c>
       <c r="G305" s="12" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>415.11</v>
       </c>
       <c r="F306" s="11" t="n">
-        <v>583.1</v>
+        <v>582.14</v>
       </c>
       <c r="G306" s="12" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>1043.84</v>
       </c>
       <c r="F307" s="11" t="n">
-        <v>1415.84</v>
+        <v>1415.13</v>
       </c>
       <c r="G307" s="12" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>755.9299999999999</v>
       </c>
       <c r="F308" s="11" t="n">
-        <v>734.63</v>
+        <v>734.9299999999999</v>
       </c>
       <c r="G308" s="12" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>13813.29</v>
       </c>
       <c r="F309" s="11" t="n">
-        <v>14357.9</v>
+        <v>14353.16</v>
       </c>
       <c r="G309" s="12" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>1656.59</v>
       </c>
       <c r="F310" s="11" t="n">
-        <v>2024.94</v>
+        <v>2024.07</v>
       </c>
       <c r="G310" s="12" t="inlineStr">
         <is>
@@ -14367,10 +14367,10 @@
         <v>976.74</v>
       </c>
       <c r="E311" s="11" t="n">
-        <v>1002.53</v>
+        <v>1002.52</v>
       </c>
       <c r="F311" s="11" t="n">
-        <v>1079.14</v>
+        <v>1076.58</v>
       </c>
       <c r="G311" s="12" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>2390.08</v>
       </c>
       <c r="F312" s="11" t="n">
-        <v>2536.04</v>
+        <v>2535.63</v>
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>2504.72</v>
       </c>
       <c r="F313" s="11" t="n">
-        <v>2074.72</v>
+        <v>2072.8</v>
       </c>
       <c r="G313" s="12" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>1079.33</v>
       </c>
       <c r="F314" s="11" t="n">
-        <v>1164.44</v>
+        <v>1164.59</v>
       </c>
       <c r="G314" s="12" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>460.75</v>
       </c>
       <c r="F315" s="11" t="n">
-        <v>472.81</v>
+        <v>472.31</v>
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>1655.34</v>
       </c>
       <c r="F316" s="11" t="n">
-        <v>1595.5</v>
+        <v>1594.97</v>
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>1051.95</v>
       </c>
       <c r="F317" s="11" t="n">
-        <v>1156.34</v>
+        <v>1156.99</v>
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>530.78</v>
       </c>
       <c r="F318" s="11" t="n">
-        <v>545.63</v>
+        <v>545.48</v>
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>59.67</v>
       </c>
       <c r="F319" s="11" t="n">
-        <v>62.81</v>
+        <v>62.63</v>
       </c>
       <c r="G319" s="12" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>117.83</v>
       </c>
       <c r="F320" s="11" t="n">
-        <v>111.56</v>
+        <v>111.45</v>
       </c>
       <c r="G320" s="12" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>742.11</v>
       </c>
       <c r="F321" s="11" t="n">
-        <v>812.09</v>
+        <v>811.09</v>
       </c>
       <c r="G321" s="12" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>2351.61</v>
       </c>
       <c r="F322" s="11" t="n">
-        <v>2584.57</v>
+        <v>2586.41</v>
       </c>
       <c r="G322" s="12" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>136957.77</v>
       </c>
       <c r="F323" s="11" t="n">
-        <v>141298.41</v>
+        <v>141219.89</v>
       </c>
       <c r="G323" s="12" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>179.14</v>
       </c>
       <c r="F324" s="11" t="n">
-        <v>159.51</v>
+        <v>159.28</v>
       </c>
       <c r="G324" s="12" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>40.4</v>
       </c>
       <c r="F325" s="11" t="n">
-        <v>42.33</v>
+        <v>42.3</v>
       </c>
       <c r="G325" s="12" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>3430.68</v>
       </c>
       <c r="F326" s="11" t="n">
-        <v>3236.66</v>
+        <v>3236.72</v>
       </c>
       <c r="G326" s="12" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>888.89</v>
       </c>
       <c r="F327" s="11" t="n">
-        <v>842.23</v>
+        <v>841.8</v>
       </c>
       <c r="G327" s="12" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>982.9400000000001</v>
       </c>
       <c r="F328" s="11" t="n">
-        <v>930.7</v>
+        <v>928.41</v>
       </c>
       <c r="G328" s="12" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>380.04</v>
       </c>
       <c r="F329" s="11" t="n">
-        <v>297.42</v>
+        <v>297.55</v>
       </c>
       <c r="G329" s="12" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>1060.38</v>
       </c>
       <c r="F330" s="11" t="n">
-        <v>1243.27</v>
+        <v>1242.28</v>
       </c>
       <c r="G330" s="12" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>576.6</v>
       </c>
       <c r="F331" s="11" t="n">
-        <v>565.12</v>
+        <v>564.39</v>
       </c>
       <c r="G331" s="12" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>6157.35</v>
       </c>
       <c r="F332" s="11" t="n">
-        <v>5602.57</v>
+        <v>5594.04</v>
       </c>
       <c r="G332" s="12" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>90.98999999999999</v>
       </c>
       <c r="F333" s="11" t="n">
-        <v>100.23</v>
+        <v>100.09</v>
       </c>
       <c r="G333" s="12" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>148.72</v>
       </c>
       <c r="F334" s="11" t="n">
-        <v>175.27</v>
+        <v>174.95</v>
       </c>
       <c r="G334" s="12" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>1241.82</v>
       </c>
       <c r="F335" s="11" t="n">
-        <v>1227.76</v>
+        <v>1227.58</v>
       </c>
       <c r="G335" s="12" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>3322.51</v>
       </c>
       <c r="F336" s="11" t="n">
-        <v>3058.37</v>
+        <v>3051.24</v>
       </c>
       <c r="G336" s="12" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>34.07</v>
       </c>
       <c r="F337" s="11" t="n">
-        <v>42.81</v>
+        <v>42.66</v>
       </c>
       <c r="G337" s="12" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>13476.35</v>
       </c>
       <c r="F338" s="11" t="n">
-        <v>14035.96</v>
+        <v>14010.27</v>
       </c>
       <c r="G338" s="12" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>508.83</v>
       </c>
       <c r="F339" s="11" t="n">
-        <v>763.87</v>
+        <v>764.75</v>
       </c>
       <c r="G339" s="12" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>1748.01</v>
       </c>
       <c r="F340" s="11" t="n">
-        <v>1770.99</v>
+        <v>1770.2</v>
       </c>
       <c r="G340" s="12" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>76.81999999999999</v>
       </c>
       <c r="F341" s="11" t="n">
-        <v>78.28</v>
+        <v>78.22</v>
       </c>
       <c r="G341" s="12" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>143.75</v>
       </c>
       <c r="F342" s="11" t="n">
-        <v>161.09</v>
+        <v>160.79</v>
       </c>
       <c r="G342" s="12" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>74.09</v>
       </c>
       <c r="F343" s="11" t="n">
-        <v>76.81999999999999</v>
+        <v>76.78</v>
       </c>
       <c r="G343" s="12" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>265.15</v>
       </c>
       <c r="F344" s="11" t="n">
-        <v>251.96</v>
+        <v>251.75</v>
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>80.7</v>
       </c>
       <c r="F345" s="11" t="n">
-        <v>75.26000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="G345" s="12" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>39.16</v>
       </c>
       <c r="F346" s="11" t="n">
-        <v>40.42</v>
+        <v>40.37</v>
       </c>
       <c r="G346" s="12" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>371.26</v>
       </c>
       <c r="F347" s="11" t="n">
-        <v>346.95</v>
+        <v>346.44</v>
       </c>
       <c r="G347" s="12" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>95.87</v>
       </c>
       <c r="F348" s="11" t="n">
-        <v>97.76000000000001</v>
+        <v>97.55</v>
       </c>
       <c r="G348" s="12" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>1266</v>
       </c>
       <c r="F349" s="11" t="n">
-        <v>1304.07</v>
+        <v>1304.36</v>
       </c>
       <c r="G349" s="12" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>253.19</v>
       </c>
       <c r="F350" s="11" t="n">
-        <v>241.15</v>
+        <v>241.13</v>
       </c>
       <c r="G350" s="12" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>1554.73</v>
       </c>
       <c r="F351" s="11" t="n">
-        <v>1636.71</v>
+        <v>1631.58</v>
       </c>
       <c r="G351" s="12" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>7106.23</v>
       </c>
       <c r="F352" s="11" t="n">
-        <v>7849.75</v>
+        <v>7838.25</v>
       </c>
       <c r="G352" s="12" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>466.77</v>
       </c>
       <c r="F353" s="11" t="n">
-        <v>438.77</v>
+        <v>438.31</v>
       </c>
       <c r="G353" s="14" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>30.42</v>
       </c>
       <c r="F354" s="11" t="n">
-        <v>39.69</v>
+        <v>39.59</v>
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>1069.41</v>
       </c>
       <c r="F355" s="11" t="n">
-        <v>1199.56</v>
+        <v>1197.16</v>
       </c>
       <c r="G355" s="12" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>271.73</v>
       </c>
       <c r="F356" s="11" t="n">
-        <v>250.09</v>
+        <v>250.08</v>
       </c>
       <c r="G356" s="12" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>33870.56</v>
       </c>
       <c r="F357" s="11" t="n">
-        <v>37681.86</v>
+        <v>37647.2</v>
       </c>
       <c r="G357" s="12" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>491.81</v>
       </c>
       <c r="F358" s="11" t="n">
-        <v>542</v>
+        <v>541.37</v>
       </c>
       <c r="G358" s="14" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>1104.73</v>
       </c>
       <c r="F359" s="11" t="n">
-        <v>1129.36</v>
+        <v>1127.31</v>
       </c>
       <c r="G359" s="12" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>275.63</v>
       </c>
       <c r="F360" s="11" t="n">
-        <v>319.22</v>
+        <v>318.95</v>
       </c>
       <c r="G360" s="12" t="inlineStr">
         <is>
@@ -16611,10 +16611,10 @@
         <v>5219.01</v>
       </c>
       <c r="E362" s="11" t="n">
-        <v>5273.16</v>
+        <v>5273.17</v>
       </c>
       <c r="F362" s="11" t="n">
-        <v>5588.76</v>
+        <v>5594.83</v>
       </c>
       <c r="G362" s="12" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>275.98</v>
       </c>
       <c r="F363" s="11" t="n">
-        <v>282.16</v>
+        <v>281.88</v>
       </c>
       <c r="G363" s="12" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>407.51</v>
       </c>
       <c r="F364" s="11" t="n">
-        <v>389.67</v>
+        <v>388.94</v>
       </c>
       <c r="G364" s="12" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>4837.4</v>
       </c>
       <c r="F365" s="11" t="n">
-        <v>4936.95</v>
+        <v>4933.74</v>
       </c>
       <c r="G365" s="12" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>535.39</v>
       </c>
       <c r="F366" s="11" t="n">
-        <v>607.58</v>
+        <v>605.8200000000001</v>
       </c>
       <c r="G366" s="12" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>1665.82</v>
       </c>
       <c r="F367" s="11" t="n">
-        <v>1667.83</v>
+        <v>1668.81</v>
       </c>
       <c r="G367" s="12" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>1385.61</v>
       </c>
       <c r="F368" s="11" t="n">
-        <v>1447.21</v>
+        <v>1445.97</v>
       </c>
       <c r="G368" s="12" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>3008.44</v>
       </c>
       <c r="F369" s="11" t="n">
-        <v>3319.38</v>
+        <v>3317.41</v>
       </c>
       <c r="G369" s="12" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>115</v>
       </c>
       <c r="F370" s="11" t="n">
-        <v>114.59</v>
+        <v>114.45</v>
       </c>
       <c r="G370" s="12" t="inlineStr">
         <is>
@@ -16978,9 +16978,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I370" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I370" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J370" s="13" t="inlineStr">
@@ -17010,7 +17010,7 @@
         <v>835.58</v>
       </c>
       <c r="F371" s="11" t="n">
-        <v>877.9400000000001</v>
+        <v>876.4</v>
       </c>
       <c r="G371" s="12" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>199.24</v>
       </c>
       <c r="F372" s="11" t="n">
-        <v>243.57</v>
+        <v>243.13</v>
       </c>
       <c r="G372" s="12" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>1521.67</v>
       </c>
       <c r="F373" s="11" t="n">
-        <v>1662.85</v>
+        <v>1660.35</v>
       </c>
       <c r="G373" s="12" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>7528.1</v>
       </c>
       <c r="F374" s="11" t="n">
-        <v>7267.91</v>
+        <v>7258.77</v>
       </c>
       <c r="G374" s="12" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>1402.4</v>
       </c>
       <c r="F375" s="11" t="n">
-        <v>1738.75</v>
+        <v>1738.13</v>
       </c>
       <c r="G375" s="12" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>420.01</v>
       </c>
       <c r="F376" s="11" t="n">
-        <v>432.37</v>
+        <v>432.14</v>
       </c>
       <c r="G376" s="12" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>294.1</v>
       </c>
       <c r="F377" s="11" t="n">
-        <v>282.49</v>
+        <v>282.26</v>
       </c>
       <c r="G377" s="12" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>24480.85</v>
       </c>
       <c r="F378" s="11" t="n">
-        <v>20653</v>
+        <v>20635.63</v>
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>150.72</v>
       </c>
       <c r="F379" s="11" t="n">
-        <v>175.67</v>
+        <v>174.98</v>
       </c>
       <c r="G379" s="12" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>322.81</v>
       </c>
       <c r="F380" s="11" t="n">
-        <v>371.95</v>
+        <v>370.1</v>
       </c>
       <c r="G380" s="12" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>866.39</v>
       </c>
       <c r="F381" s="11" t="n">
-        <v>914.36</v>
+        <v>910.65</v>
       </c>
       <c r="G381" s="12" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>1346.54</v>
       </c>
       <c r="F382" s="11" t="n">
-        <v>1484.59</v>
+        <v>1483.33</v>
       </c>
       <c r="G382" s="12" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>16755.83</v>
       </c>
       <c r="F383" s="11" t="n">
-        <v>16652.71</v>
+        <v>16639.07</v>
       </c>
       <c r="G383" s="14" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>983.91</v>
       </c>
       <c r="F384" s="11" t="n">
-        <v>1032.28</v>
+        <v>1031.12</v>
       </c>
       <c r="G384" s="14" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>2797.91</v>
       </c>
       <c r="F385" s="11" t="n">
-        <v>2835.03</v>
+        <v>2830.3</v>
       </c>
       <c r="G385" s="12" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>299.65</v>
       </c>
       <c r="F386" s="11" t="n">
-        <v>334.83</v>
+        <v>333.94</v>
       </c>
       <c r="G386" s="12" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>1207.06</v>
       </c>
       <c r="F387" s="11" t="n">
-        <v>1305.96</v>
+        <v>1304.21</v>
       </c>
       <c r="G387" s="12" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>1014.6</v>
       </c>
       <c r="F388" s="11" t="n">
-        <v>1032.18</v>
+        <v>1031.37</v>
       </c>
       <c r="G388" s="12" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>386.81</v>
       </c>
       <c r="F389" s="11" t="n">
-        <v>570.1</v>
+        <v>566.86</v>
       </c>
       <c r="G389" s="12" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>850.9400000000001</v>
       </c>
       <c r="F390" s="11" t="n">
-        <v>1047.38</v>
+        <v>1044.69</v>
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>308.49</v>
       </c>
       <c r="F391" s="11" t="n">
-        <v>285.01</v>
+        <v>284.83</v>
       </c>
       <c r="G391" s="12" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>124.63</v>
       </c>
       <c r="F392" s="11" t="n">
-        <v>136.78</v>
+        <v>136.49</v>
       </c>
       <c r="G392" s="12" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>342.11</v>
       </c>
       <c r="F393" s="11" t="n">
-        <v>358.87</v>
+        <v>357.57</v>
       </c>
       <c r="G393" s="12" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>235.04</v>
       </c>
       <c r="F394" s="11" t="n">
-        <v>253.17</v>
+        <v>253.21</v>
       </c>
       <c r="G394" s="12" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>1389.87</v>
       </c>
       <c r="F395" s="11" t="n">
-        <v>1415.34</v>
+        <v>1414.78</v>
       </c>
       <c r="G395" s="12" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>25.93</v>
       </c>
       <c r="F396" s="11" t="n">
-        <v>27.72</v>
+        <v>27.66</v>
       </c>
       <c r="G396" s="12" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>398.31</v>
       </c>
       <c r="F397" s="11" t="n">
-        <v>438.58</v>
+        <v>438.24</v>
       </c>
       <c r="G397" s="12" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>206.71</v>
       </c>
       <c r="F398" s="11" t="n">
-        <v>228.14</v>
+        <v>227.82</v>
       </c>
       <c r="G398" s="12" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>528.79</v>
       </c>
       <c r="F399" s="11" t="n">
-        <v>568.79</v>
+        <v>571.12</v>
       </c>
       <c r="G399" s="12" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>509.85</v>
       </c>
       <c r="F400" s="11" t="n">
-        <v>691.95</v>
+        <v>690.46</v>
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>25.84</v>
       </c>
       <c r="F401" s="11" t="n">
-        <v>35.11</v>
+        <v>35.05</v>
       </c>
       <c r="G401" s="12" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>1405.84</v>
       </c>
       <c r="F402" s="11" t="n">
-        <v>1367.8</v>
+        <v>1366.71</v>
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>31.55</v>
       </c>
       <c r="F403" s="11" t="n">
-        <v>41.17</v>
+        <v>41.06</v>
       </c>
       <c r="G403" s="12" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>288.23</v>
       </c>
       <c r="F404" s="11" t="n">
-        <v>323.56</v>
+        <v>322.82</v>
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>42.89</v>
       </c>
       <c r="F405" s="11" t="n">
-        <v>45.7</v>
+        <v>45.64</v>
       </c>
       <c r="G405" s="12" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>156.44</v>
       </c>
       <c r="F406" s="11" t="n">
-        <v>141.68</v>
+        <v>141.58</v>
       </c>
       <c r="G406" s="12" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>961.13</v>
       </c>
       <c r="F407" s="11" t="n">
-        <v>889.4</v>
+        <v>889</v>
       </c>
       <c r="G407" s="14" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>147.61</v>
       </c>
       <c r="F408" s="11" t="n">
-        <v>145.89</v>
+        <v>145.62</v>
       </c>
       <c r="G408" s="12" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>183.14</v>
       </c>
       <c r="F409" s="11" t="n">
-        <v>241.27</v>
+        <v>240.61</v>
       </c>
       <c r="G409" s="12" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>530.61</v>
       </c>
       <c r="F410" s="11" t="n">
-        <v>513.8</v>
+        <v>513.75</v>
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>337.54</v>
       </c>
       <c r="F411" s="11" t="n">
-        <v>395.91</v>
+        <v>394.92</v>
       </c>
       <c r="G411" s="12" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>92.17</v>
       </c>
       <c r="F412" s="11" t="n">
-        <v>98.81</v>
+        <v>98.83</v>
       </c>
       <c r="G412" s="12" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>716.97</v>
       </c>
       <c r="F413" s="11" t="n">
-        <v>797.49</v>
+        <v>797.14</v>
       </c>
       <c r="G413" s="12" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>1938.58</v>
       </c>
       <c r="F414" s="11" t="n">
-        <v>1897.45</v>
+        <v>1897.88</v>
       </c>
       <c r="G414" s="12" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>1071.75</v>
       </c>
       <c r="F415" s="11" t="n">
-        <v>976.2</v>
+        <v>975.47</v>
       </c>
       <c r="G415" s="12" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>3933.38</v>
       </c>
       <c r="F416" s="11" t="n">
-        <v>3884.64</v>
+        <v>3879.52</v>
       </c>
       <c r="G416" s="12" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>883.87</v>
       </c>
       <c r="F417" s="11" t="n">
-        <v>808.65</v>
+        <v>807.63</v>
       </c>
       <c r="G417" s="12" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>242.25</v>
       </c>
       <c r="F418" s="11" t="n">
-        <v>225.29</v>
+        <v>225.04</v>
       </c>
       <c r="G418" s="12" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>24871.61</v>
       </c>
       <c r="F419" s="11" t="n">
-        <v>26810.22</v>
+        <v>26800.51</v>
       </c>
       <c r="G419" s="12" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>985.01</v>
       </c>
       <c r="F420" s="11" t="n">
-        <v>857.48</v>
+        <v>856.1900000000001</v>
       </c>
       <c r="G420" s="12" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>822.0700000000001</v>
       </c>
       <c r="F421" s="11" t="n">
-        <v>842.6900000000001</v>
+        <v>842.66</v>
       </c>
       <c r="G421" s="12" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>3210.57</v>
       </c>
       <c r="F422" s="11" t="n">
-        <v>3181.54</v>
+        <v>3178.04</v>
       </c>
       <c r="G422" s="12" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>857.48</v>
       </c>
       <c r="F423" s="11" t="n">
-        <v>1012.02</v>
+        <v>1009.55</v>
       </c>
       <c r="G423" s="14" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>71.73999999999999</v>
       </c>
       <c r="F424" s="11" t="n">
-        <v>79.67</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>1663.55</v>
       </c>
       <c r="F425" s="11" t="n">
-        <v>2553.38</v>
+        <v>2550.31</v>
       </c>
       <c r="G425" s="12" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>1338.18</v>
       </c>
       <c r="F426" s="11" t="n">
-        <v>1427.22</v>
+        <v>1426.65</v>
       </c>
       <c r="G426" s="12" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>13642.46</v>
       </c>
       <c r="F427" s="11" t="n">
-        <v>13378.41</v>
+        <v>13373.74</v>
       </c>
       <c r="G427" s="12" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>518.1900000000001</v>
       </c>
       <c r="F428" s="11" t="n">
-        <v>495.97</v>
+        <v>496.13</v>
       </c>
       <c r="G428" s="12" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>263.48</v>
       </c>
       <c r="F429" s="11" t="n">
-        <v>333.22</v>
+        <v>333.24</v>
       </c>
       <c r="G429" s="12" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>2591.02</v>
       </c>
       <c r="F430" s="11" t="n">
-        <v>2797.76</v>
+        <v>2794.6</v>
       </c>
       <c r="G430" s="12" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>464.73</v>
       </c>
       <c r="F431" s="11" t="n">
-        <v>457.96</v>
+        <v>457.46</v>
       </c>
       <c r="G431" s="12" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>407.89</v>
       </c>
       <c r="F432" s="11" t="n">
-        <v>459.31</v>
+        <v>458.34</v>
       </c>
       <c r="G432" s="12" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>4988.59</v>
       </c>
       <c r="F433" s="11" t="n">
-        <v>4915.03</v>
+        <v>4919.56</v>
       </c>
       <c r="G433" s="12" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>838.53</v>
       </c>
       <c r="F434" s="11" t="n">
-        <v>920.79</v>
+        <v>920.08</v>
       </c>
       <c r="G434" s="12" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>1727.68</v>
       </c>
       <c r="F435" s="11" t="n">
-        <v>1711.14</v>
+        <v>1709.35</v>
       </c>
       <c r="G435" s="14" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>590.14</v>
       </c>
       <c r="F436" s="11" t="n">
-        <v>578.34</v>
+        <v>578.39</v>
       </c>
       <c r="G436" s="12" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>3775.3</v>
       </c>
       <c r="F437" s="11" t="n">
-        <v>3846.33</v>
+        <v>3840.88</v>
       </c>
       <c r="G437" s="14" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>44.81</v>
       </c>
       <c r="F438" s="11" t="n">
-        <v>51.05</v>
+        <v>50.95</v>
       </c>
       <c r="G438" s="12" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>297.69</v>
       </c>
       <c r="F440" s="11" t="n">
-        <v>355.9</v>
+        <v>355.23</v>
       </c>
       <c r="G440" s="14" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>183.66</v>
       </c>
       <c r="F441" s="11" t="n">
-        <v>228.03</v>
+        <v>228.42</v>
       </c>
       <c r="G441" s="12" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>440.98</v>
       </c>
       <c r="F442" s="11" t="n">
-        <v>565.3099999999999</v>
+        <v>564.55</v>
       </c>
       <c r="G442" s="12" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>812.45</v>
       </c>
       <c r="F443" s="11" t="n">
-        <v>750.7</v>
+        <v>749.52</v>
       </c>
       <c r="G443" s="12" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>456.3</v>
       </c>
       <c r="F444" s="11" t="n">
-        <v>530.37</v>
+        <v>529.83</v>
       </c>
       <c r="G444" s="12" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>286.48</v>
       </c>
       <c r="F445" s="11" t="n">
-        <v>357.07</v>
+        <v>355.77</v>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>684.76</v>
       </c>
       <c r="F446" s="11" t="n">
-        <v>785.61</v>
+        <v>784.01</v>
       </c>
       <c r="G446" s="12" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>1524.54</v>
       </c>
       <c r="F447" s="11" t="n">
-        <v>1640.1</v>
+        <v>1640.62</v>
       </c>
       <c r="G447" s="12" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>1099.81</v>
       </c>
       <c r="F448" s="11" t="n">
-        <v>1113.06</v>
+        <v>1113.17</v>
       </c>
       <c r="G448" s="12" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>4565.96</v>
       </c>
       <c r="F449" s="11" t="n">
-        <v>5177.09</v>
+        <v>5158.1</v>
       </c>
       <c r="G449" s="12" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>642.3200000000001</v>
       </c>
       <c r="F450" s="11" t="n">
-        <v>679.2</v>
+        <v>678.53</v>
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>389.13</v>
       </c>
       <c r="F452" s="11" t="n">
-        <v>383.46</v>
+        <v>382.99</v>
       </c>
       <c r="G452" s="12" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>197.64</v>
       </c>
       <c r="F453" s="11" t="n">
-        <v>179.35</v>
+        <v>179.24</v>
       </c>
       <c r="G453" s="12" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>576.47</v>
       </c>
       <c r="F454" s="11" t="n">
-        <v>645.9</v>
+        <v>644.15</v>
       </c>
       <c r="G454" s="12" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>1248.59</v>
       </c>
       <c r="F455" s="11" t="n">
-        <v>1414.43</v>
+        <v>1414.36</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>2620.03</v>
       </c>
       <c r="F456" s="11" t="n">
-        <v>2959.51</v>
+        <v>2968.92</v>
       </c>
       <c r="G456" s="12" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>1456.26</v>
       </c>
       <c r="F457" s="11" t="n">
-        <v>1502.6</v>
+        <v>1505.27</v>
       </c>
       <c r="G457" s="12" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>1096.39</v>
       </c>
       <c r="F458" s="11" t="n">
-        <v>1181.58</v>
+        <v>1177.82</v>
       </c>
       <c r="G458" s="12" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>418.18</v>
       </c>
       <c r="F459" s="11" t="n">
-        <v>515.1900000000001</v>
+        <v>513.35</v>
       </c>
       <c r="G459" s="14" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>3300.67</v>
       </c>
       <c r="F460" s="11" t="n">
-        <v>3226.08</v>
+        <v>3220.23</v>
       </c>
       <c r="G460" s="12" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>2607.85</v>
       </c>
       <c r="F461" s="11" t="n">
-        <v>2760.45</v>
+        <v>2755.48</v>
       </c>
       <c r="G461" s="12" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>3298.7</v>
       </c>
       <c r="F462" s="11" t="n">
-        <v>3126.33</v>
+        <v>3124.35</v>
       </c>
       <c r="G462" s="12" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>700.23</v>
       </c>
       <c r="F463" s="11" t="n">
-        <v>798</v>
+        <v>795.75</v>
       </c>
       <c r="G463" s="12" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>4199.9</v>
       </c>
       <c r="F464" s="11" t="n">
-        <v>3907.55</v>
+        <v>3905.51</v>
       </c>
       <c r="G464" s="12" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>4153.44</v>
       </c>
       <c r="F465" s="11" t="n">
-        <v>3834.4</v>
+        <v>3832.37</v>
       </c>
       <c r="G465" s="12" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>1429.32</v>
       </c>
       <c r="F466" s="11" t="n">
-        <v>1371.5</v>
+        <v>1369.09</v>
       </c>
       <c r="G466" s="12" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>3827.65</v>
       </c>
       <c r="F467" s="11" t="n">
-        <v>4424.35</v>
+        <v>4422.71</v>
       </c>
       <c r="G467" s="12" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>25.06</v>
       </c>
       <c r="F468" s="11" t="n">
-        <v>26.98</v>
+        <v>26.94</v>
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>475.52</v>
       </c>
       <c r="F469" s="11" t="n">
-        <v>519.54</v>
+        <v>519.12</v>
       </c>
       <c r="G469" s="12" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>376.63</v>
       </c>
       <c r="F470" s="11" t="n">
-        <v>371.44</v>
+        <v>370.99</v>
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>40.88</v>
       </c>
       <c r="F471" s="11" t="n">
-        <v>49.86</v>
+        <v>49.71</v>
       </c>
       <c r="G471" s="12" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>3631.9</v>
       </c>
       <c r="F472" s="11" t="n">
-        <v>3418.38</v>
+        <v>3416.51</v>
       </c>
       <c r="G472" s="12" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>1558.1</v>
       </c>
       <c r="F473" s="11" t="n">
-        <v>1698.04</v>
+        <v>1698.31</v>
       </c>
       <c r="G473" s="14" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>26.55</v>
       </c>
       <c r="F474" s="11" t="n">
-        <v>29.54</v>
+        <v>29.49</v>
       </c>
       <c r="G474" s="12" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>11666.98</v>
       </c>
       <c r="F475" s="11" t="n">
-        <v>11876.59</v>
+        <v>11859.45</v>
       </c>
       <c r="G475" s="12" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>179.36</v>
       </c>
       <c r="F476" s="11" t="n">
-        <v>158.94</v>
+        <v>158.75</v>
       </c>
       <c r="G476" s="12" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>1313.78</v>
       </c>
       <c r="F477" s="11" t="n">
-        <v>1368.23</v>
+        <v>1366.7</v>
       </c>
       <c r="G477" s="12" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>1113.68</v>
       </c>
       <c r="F478" s="11" t="n">
-        <v>1155.05</v>
+        <v>1156.41</v>
       </c>
       <c r="G478" s="12" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>655.71</v>
       </c>
       <c r="F479" s="11" t="n">
-        <v>682.4400000000001</v>
+        <v>682.59</v>
       </c>
       <c r="G479" s="12" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>419.73</v>
       </c>
       <c r="F480" s="11" t="n">
-        <v>409.37</v>
+        <v>408.64</v>
       </c>
       <c r="G480" s="12" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>997.21</v>
       </c>
       <c r="F481" s="11" t="n">
-        <v>1106.09</v>
+        <v>1105.33</v>
       </c>
       <c r="G481" s="12" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>433.53</v>
       </c>
       <c r="F482" s="11" t="n">
-        <v>466.13</v>
+        <v>465.74</v>
       </c>
       <c r="G482" s="12" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>687.63</v>
       </c>
       <c r="F483" s="11" t="n">
-        <v>575.4400000000001</v>
+        <v>575.16</v>
       </c>
       <c r="G483" s="12" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>322.88</v>
       </c>
       <c r="F484" s="11" t="n">
-        <v>342.29</v>
+        <v>341.59</v>
       </c>
       <c r="G484" s="12" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>961.05</v>
       </c>
       <c r="F485" s="11" t="n">
-        <v>1000.33</v>
+        <v>1001.24</v>
       </c>
       <c r="G485" s="12" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>115.25</v>
       </c>
       <c r="F486" s="11" t="n">
-        <v>125.13</v>
+        <v>125.02</v>
       </c>
       <c r="G486" s="12" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>1381.53</v>
       </c>
       <c r="F487" s="11" t="n">
-        <v>1398.84</v>
+        <v>1396.04</v>
       </c>
       <c r="G487" s="12" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>522.29</v>
       </c>
       <c r="F488" s="11" t="n">
-        <v>474.62</v>
+        <v>474.21</v>
       </c>
       <c r="G488" s="12" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>3039.75</v>
       </c>
       <c r="F489" s="11" t="n">
-        <v>2985.84</v>
+        <v>2984.3</v>
       </c>
       <c r="G489" s="12" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>861.5</v>
       </c>
       <c r="F490" s="11" t="n">
-        <v>836.49</v>
+        <v>835.67</v>
       </c>
       <c r="G490" s="12" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>122.46</v>
       </c>
       <c r="F491" s="11" t="n">
-        <v>127.93</v>
+        <v>127.83</v>
       </c>
       <c r="G491" s="12" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>476.3</v>
       </c>
       <c r="F492" s="11" t="n">
-        <v>570.58</v>
+        <v>569.95</v>
       </c>
       <c r="G492" s="12" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>858.63</v>
       </c>
       <c r="F493" s="11" t="n">
-        <v>1041.36</v>
+        <v>1041.38</v>
       </c>
       <c r="G493" s="12" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>207.88</v>
       </c>
       <c r="F494" s="11" t="n">
-        <v>231.39</v>
+        <v>231.73</v>
       </c>
       <c r="G494" s="12" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>1311.29</v>
       </c>
       <c r="F495" s="11" t="n">
-        <v>1381.83</v>
+        <v>1379.43</v>
       </c>
       <c r="G495" s="12" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>19.67</v>
       </c>
       <c r="F496" s="11" t="n">
-        <v>20.5</v>
+        <v>20.48</v>
       </c>
       <c r="G496" s="12" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>81.55</v>
       </c>
       <c r="F497" s="11" t="n">
-        <v>96.48</v>
+        <v>96.16</v>
       </c>
       <c r="G497" s="12" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>582.84</v>
       </c>
       <c r="F498" s="11" t="n">
-        <v>679.48</v>
+        <v>679.65</v>
       </c>
       <c r="G498" s="12" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>1410.29</v>
       </c>
       <c r="F499" s="11" t="n">
-        <v>1484.36</v>
+        <v>1480.84</v>
       </c>
       <c r="G499" s="12" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>14252.53</v>
       </c>
       <c r="F500" s="11" t="n">
-        <v>13838.87</v>
+        <v>13836.02</v>
       </c>
       <c r="G500" s="12" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>903.72</v>
       </c>
       <c r="F501" s="11" t="n">
-        <v>927.91</v>
+        <v>927.64</v>
       </c>
       <c r="G501" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 24-Apr-2026  16:45:21    |    Closing Price Date: 24-Apr-2026</t>
+          <t>Scan Run: 25-Apr-2026  16:01:21    |    Closing Price Date: 24-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>76.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>68</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>24-Apr-2026  16:45:21</t>
+          <t>25-Apr-2026  16:01:21</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 76.6% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 76.4% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 383 of 500 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 382 of 500 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>1546.59</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1436.01</v>
+        <v>1436.98</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1054.74</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1086.66</v>
+        <v>1086.9</v>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         <v>31862.72</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>32731.81</v>
+        <v>32731.82</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>32487.95</v>
+        <v>32559.42</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>473.48</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>474.43</v>
+        <v>474.36</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>426.81</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>410.31</v>
+        <v>410.7</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>1277.71</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1468.21</v>
+        <v>1468.25</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>6359.58</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5738.37</v>
+        <v>5743.28</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
         <v>25814.33</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>26391.11</v>
+        <v>26391.1</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>28210.03</v>
+        <v>28190.93</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>332.25</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>310.25</v>
+        <v>310.43</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>63.57</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>90.25</v>
+        <v>90.72</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1318.7</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1573.9</v>
+        <v>1577.49</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>944.91</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>843.5</v>
+        <v>843.8099999999999</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1474.21</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1682.99</v>
+        <v>1683.78</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>874.97</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>972.8099999999999</v>
+        <v>975.1</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>262.02</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>248.91</v>
+        <v>249.17</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1083.29</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>969.17</v>
+        <v>969.71</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>2092.06</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2230.06</v>
+        <v>2231.77</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>992.73</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>981.86</v>
+        <v>983.38</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>1471.02</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1424.46</v>
+        <v>1425.4</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>166.22</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>144.74</v>
+        <v>144.86</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>663.41</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>714.0599999999999</v>
+        <v>714.46</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>314.24</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>370.97</v>
+        <v>371.53</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>1453.17</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1628.43</v>
+        <v>1628.48</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>3798.38</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3635.29</v>
+        <v>3637.72</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>477.67</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>508.22</v>
+        <v>508.73</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>2837.74</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2732.14</v>
+        <v>2731.58</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>493.61</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>484.32</v>
+        <v>484.72</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>984.98</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>960.41</v>
+        <v>960.95</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>5461.41</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5404.16</v>
+        <v>5403.31</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>1428.14</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1637.62</v>
+        <v>1637.73</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>13.85</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>15.92</v>
+        <v>15.9</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>7156.08</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7091.61</v>
+        <v>7082.17</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>463.69</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>515.6900000000001</v>
+        <v>516.59</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>3271.23</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2914.6</v>
+        <v>2914.07</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>495.75</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>552.1799999999999</v>
+        <v>551.84</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>263.86</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>251.77</v>
+        <v>251.72</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>10283.48</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>9164.51</v>
+        <v>9153.299999999999</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>2032.87</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1885.18</v>
+        <v>1886.71</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>734.96</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>826.13</v>
+        <v>826.05</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>7504.55</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>7350.2</v>
+        <v>7354.42</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>442.96</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>465.28</v>
+        <v>465.31</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>236.34</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>271.01</v>
+        <v>271.65</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>800.95</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>891.54</v>
+        <v>892.45</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>869.53</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>877.59</v>
+        <v>877.79</v>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>177.22</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>160.85</v>
+        <v>160.88</v>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>2385.93</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2462.66</v>
+        <v>2462.05</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>653.61</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>617.58</v>
+        <v>617.83</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>1583.79</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1507.42</v>
+        <v>1508.54</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>8447.51</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>8582.389999999999</v>
+        <v>8584.549999999999</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>558.67</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>580.8099999999999</v>
+        <v>581.29</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>6386.55</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>6310.72</v>
+        <v>6310.6</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>960.26</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>883.3099999999999</v>
+        <v>884.02</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>1298.3</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1204.76</v>
+        <v>1205.14</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>191.35</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>225.82</v>
+        <v>225.66</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>1302.93</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1240.13</v>
+        <v>1240.62</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>9441.690000000001</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9109.059999999999</v>
+        <v>9109.23</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>1837.01</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1931.66</v>
+        <v>1932.77</v>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>86.48</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>97.88</v>
+        <v>97.86</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>10189.57</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>11230.01</v>
+        <v>11233.8</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>915.9299999999999</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>936.51</v>
+        <v>936.86</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>2281</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2379.35</v>
+        <v>2381.29</v>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>483.45</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>482.01</v>
+        <v>481.91</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>164.88</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>160.43</v>
+        <v>160.56</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>281.58</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>272.87</v>
+        <v>273.16</v>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>151.3</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>140.25</v>
+        <v>140.41</v>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>3569.98</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>4013.24</v>
+        <v>4015.53</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>751.64</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>943.88</v>
+        <v>943.85</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>4680.51</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>4773.71</v>
+        <v>4773.43</v>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>1562.82</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1743.25</v>
+        <v>1743.65</v>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>1321.27</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1406.13</v>
+        <v>1409.03</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>436.13</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>405.97</v>
+        <v>406.32</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>1658.47</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1786.3</v>
+        <v>1788.12</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>455.4</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>495.7</v>
+        <v>495.71</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>1741.69</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1496.92</v>
+        <v>1497.86</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>1878.58</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1921.34</v>
+        <v>1922.32</v>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>1576.02</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1645.59</v>
+        <v>1645.52</v>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>279.2</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>259.68</v>
+        <v>260.05</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>647.21</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>686.34</v>
+        <v>686.78</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>367.23</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>371.51</v>
+        <v>371.98</v>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>275.91</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>311.09</v>
+        <v>311.9</v>
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         <v>5244.7</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>5297.4</v>
+        <v>5297.41</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>5637.52</v>
+        <v>5648.11</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>1791.6</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1820.6</v>
+        <v>1821.31</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>34807.54</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>35163.22</v>
+        <v>35158.54</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>319.25</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>324.41</v>
+        <v>324.4</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>733.64</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>851.22</v>
+        <v>852.6900000000001</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>5749.3</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>5745.72</v>
+        <v>5744.33</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>3042.35</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2692.8</v>
+        <v>2695.8</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>379.76</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>398.29</v>
+        <v>398.52</v>
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>245.33</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>258.93</v>
+        <v>259.12</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>702.39</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>733.58</v>
+        <v>734.76</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>141.06</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>133.4</v>
+        <v>133.51</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>861.87</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>835.62</v>
+        <v>836.24</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>1702.89</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1862.32</v>
+        <v>1862.8</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>847.0599999999999</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>884.22</v>
+        <v>885.03</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>180.71</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>185.49</v>
+        <v>185.54</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>1055.41</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>947.12</v>
+        <v>947.34</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>1294.35</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1409.97</v>
+        <v>1409.98</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>3615.21</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>3600.88</v>
+        <v>3600.34</v>
       </c>
       <c r="G99" s="14" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>35.85</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>37.52</v>
+        <v>37.56</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>736.83</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>755.92</v>
+        <v>756.27</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>5039.11</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>5488.06</v>
+        <v>5491.17</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>161.09</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>159.79</v>
+        <v>159.84</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>175.51</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>177.93</v>
+        <v>178.17</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>717.95</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>685.96</v>
+        <v>686.6799999999999</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>785.2</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>847.92</v>
+        <v>847.01</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>444.87</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>472.27</v>
+        <v>472.75</v>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>967.26</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>852.09</v>
+        <v>852.25</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>1563.82</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1588.67</v>
+        <v>1589.89</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>1579.99</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1717.31</v>
+        <v>1716.4</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>1284.52</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1401.67</v>
+        <v>1401.52</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>753.1900000000001</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>932.59</v>
+        <v>933.6</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>439.57</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>405.07</v>
+        <v>405.24</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>1467.24</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1570</v>
+        <v>1572.13</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>1283.64</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1525.27</v>
+        <v>1526.54</v>
       </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>2034.7</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>2170.97</v>
+        <v>2170.45</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>482.41</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>512.61</v>
+        <v>513.1900000000001</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>1116.52</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1378.68</v>
+        <v>1378.16</v>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>2087.42</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>2169.99</v>
+        <v>2172.14</v>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>7359.4</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>6892.44</v>
+        <v>6893.9</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>1233.07</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1245.43</v>
+        <v>1245.67</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>4195.01</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>4562.66</v>
+        <v>4559.28</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>248.87</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>275.06</v>
+        <v>274.89</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>260.07</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>245.98</v>
+        <v>246.11</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>4759.07</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>4217.61</v>
+        <v>4219.16</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>928.86</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1091.9</v>
+        <v>1093.96</v>
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>458.45</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>488.3</v>
+        <v>488.6</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>1955.49</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>2031.23</v>
+        <v>2031.38</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>3250.35</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>2849.02</v>
+        <v>2851.34</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>105.17</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>130.93</v>
+        <v>131.22</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1129.26</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1153.8</v>
+        <v>1154.62</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>1083.79</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1205.99</v>
+        <v>1207.95</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>1523.46</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1680.09</v>
+        <v>1680.29</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>437.44</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>417.56</v>
+        <v>417.88</v>
       </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>113.09</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>138.04</v>
+        <v>137.65</v>
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>6174.89</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>6231.9</v>
+        <v>6233.59</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>10862.17</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>12964.97</v>
+        <v>12965.81</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>587.16</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>665.3</v>
+        <v>665.5599999999999</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>4152.13</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>4044.67</v>
+        <v>4046.07</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>2339.81</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>2436.97</v>
+        <v>2437.33</v>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>1255.81</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1255.33</v>
+        <v>1253.84</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>1642.46</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1871.52</v>
+        <v>1872.65</v>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>7172.45</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>6817.27</v>
+        <v>6815.82</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>856.4</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>932.46</v>
+        <v>933.92</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>320.35</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>348.76</v>
+        <v>348.8</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>425.23</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>481.45</v>
+        <v>480.63</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>505.83</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>495.33</v>
+        <v>495.74</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>445.8</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>498.82</v>
+        <v>498.76</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>2404.22</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>2493.2</v>
+        <v>2493.07</v>
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>209.16</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>198.48</v>
+        <v>198.46</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>3250.14</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>3423.92</v>
+        <v>3427.14</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>251.24</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>270.96</v>
+        <v>270.87</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>324.59</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>351.82</v>
+        <v>352.07</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>828.34</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>851.55</v>
+        <v>851.98</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>279.86</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>250.98</v>
+        <v>251.04</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>860.4</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>839.28</v>
+        <v>840.26</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>173.25</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>182.98</v>
+        <v>182.97</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>242.3</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>298.32</v>
+        <v>298.69</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>433.28</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>520.12</v>
+        <v>521.42</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>3297.23</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>3449.95</v>
+        <v>3453.74</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>872.29</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>868.16</v>
+        <v>868.6799999999999</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>237.47</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>294.04</v>
+        <v>294.2</v>
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>155.3</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>163.46</v>
+        <v>163.57</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7987,10 +7987,10 @@
         <v>1409.25</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>1362.56</v>
+        <v>1362.57</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>1171.07</v>
+        <v>1174.2</v>
       </c>
       <c r="G166" s="14" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>382.2</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>380.33</v>
+        <v>380.97</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>7956.79</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>8468.139999999999</v>
+        <v>8464.73</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>1738.09</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>1758.32</v>
+        <v>1758.38</v>
       </c>
       <c r="G169" s="14" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>2435.76</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>2542.64</v>
+        <v>2543.09</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>2145.04</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>1973.5</v>
+        <v>1972.83</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>603.76</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>529.22</v>
+        <v>530.6799999999999</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>94.88</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>93.38</v>
+        <v>93.39</v>
       </c>
       <c r="G173" s="14" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>444.83</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>473.65</v>
+        <v>474.4</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>2108.16</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>2420.29</v>
+        <v>2419.06</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>326.36</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>332.8</v>
+        <v>333.05</v>
       </c>
       <c r="G176" s="14" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>590.4299999999999</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>630.0599999999999</v>
+        <v>630.2</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>1101.36</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1145.16</v>
+        <v>1146.05</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>918.35</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>1009.55</v>
+        <v>1008.46</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>1712.29</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>1915.5</v>
+        <v>1917.96</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>274.45</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>247.98</v>
+        <v>248</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>159.28</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>161.96</v>
+        <v>162.05</v>
       </c>
       <c r="G182" s="14" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>617.15</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>571.36</v>
+        <v>571.63</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>655.63</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>599.66</v>
+        <v>599.51</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>2727.42</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>2734.29</v>
+        <v>2735.72</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>1544.51</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>1666.19</v>
+        <v>1669.53</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>2480.1</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>2417.47</v>
+        <v>2419.15</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>269.64</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>293.73</v>
+        <v>293.66</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>365.62</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>402.74</v>
+        <v>402.67</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9043,10 +9043,10 @@
         <v>4072.59</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>3799.38</v>
+        <v>3799.39</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>3143.17</v>
+        <v>3146.85</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>4084.79</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>4260.82</v>
+        <v>4264.89</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>388.26</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>471.11</v>
+        <v>471.03</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>1308.21</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>1405.46</v>
+        <v>1406.81</v>
       </c>
       <c r="G193" s="14" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>734.79</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>744.58</v>
+        <v>745.34</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>1394.33</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>1485.14</v>
+        <v>1483.78</v>
       </c>
       <c r="G195" s="14" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>2576.09</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>2567.11</v>
+        <v>2568.03</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>832.67</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>905.72</v>
+        <v>905.91</v>
       </c>
       <c r="G197" s="14" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>643.29</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>700.29</v>
+        <v>702.33</v>
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>568.3200000000001</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>533.6799999999999</v>
+        <v>533.86</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>5327.62</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>5191.18</v>
+        <v>5189.64</v>
       </c>
       <c r="G200" s="14" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>78.34</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>75.48</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>953.05</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>847.75</v>
+        <v>848.23</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>527.8099999999999</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>430.45</v>
+        <v>430.9</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>383.42</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>409.17</v>
+        <v>408.96</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>2228.12</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>2327.58</v>
+        <v>2326.39</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9718,9 +9718,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I205" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I205" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J205" s="13" t="inlineStr">
@@ -9750,7 +9750,7 @@
         <v>571.4400000000001</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>535.96</v>
+        <v>536.53</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>1076.24</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>1128.47</v>
+        <v>1129.39</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>310.18</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>288.69</v>
+        <v>288.86</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>30478.42</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>33529.97</v>
+        <v>33522.6</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>473.57</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>469.51</v>
+        <v>469.66</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>187.84</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>202.36</v>
+        <v>202.78</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>1956.52</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>2114.22</v>
+        <v>2115.14</v>
       </c>
       <c r="G212" s="14" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>1323.9</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>1351.98</v>
+        <v>1352.45</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>1830.55</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>1881.33</v>
+        <v>1881.9</v>
       </c>
       <c r="G214" s="14" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>575.79</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>609.9400000000001</v>
+        <v>610.73</v>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>83.88</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>91.45</v>
+        <v>91.7</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>9.5</v>
+        <v>9.51</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>69.12</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>72.89</v>
+        <v>72.92</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>126.09</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>138.54</v>
+        <v>138.68</v>
       </c>
       <c r="G219" s="14" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>56.67</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>55.31</v>
+        <v>55.37</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>335.29</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>346.41</v>
+        <v>346.67</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>163.16</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>180.9</v>
+        <v>180.81</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>477.71</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>490.67</v>
+        <v>490.92</v>
       </c>
       <c r="G223" s="14" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>1458.64</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>1560.02</v>
+        <v>1557.61</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>477.58</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>515.95</v>
+        <v>515.5</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>397.06</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>394.34</v>
+        <v>394.36</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>2128.02</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>2240.76</v>
+        <v>2242.01</v>
       </c>
       <c r="G228" s="14" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>907.21</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>808.76</v>
+        <v>809.79</v>
       </c>
       <c r="G229" s="14" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>4551.43</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>4961.35</v>
+        <v>4963.33</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>852.16</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>852.01</v>
+        <v>852.5700000000001</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>428.67</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>409.04</v>
+        <v>409.16</v>
       </c>
       <c r="G232" s="14" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>1334.01</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>1472.58</v>
+        <v>1471.69</v>
       </c>
       <c r="G233" s="14" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>1278.36</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>1180.38</v>
+        <v>1181.38</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>93.67</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>120.98</v>
+        <v>121.07</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>710.21</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>859.29</v>
+        <v>859.24</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>34.4</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>36.99</v>
+        <v>37.01</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>1493.05</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>1452.42</v>
+        <v>1451.76</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>21.21</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>21.7</v>
+        <v>21.73</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>141.52</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>156.88</v>
+        <v>158.16</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>561.38</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>639.9299999999999</v>
+        <v>640.09</v>
       </c>
       <c r="G242" s="14" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>124.64</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>139.16</v>
+        <v>139.18</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>102.44</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>114.14</v>
+        <v>114.37</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>310.29</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>353.63</v>
+        <v>353.45</v>
       </c>
       <c r="G245" s="14" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>280.09</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>296.4</v>
+        <v>296.53</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>118.5</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>108.31</v>
+        <v>108.44</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>1994.67</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>1855.63</v>
+        <v>1856.46</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>580.72</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>610.5</v>
+        <v>609.35</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>200.38</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>196.58</v>
+        <v>196.88</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>1185.57</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>1083.76</v>
+        <v>1084.09</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>247.06</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>272.41</v>
+        <v>272.6</v>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>5495.01</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>5652.54</v>
+        <v>5656.3</v>
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>442.28</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>432.39</v>
+        <v>432.32</v>
       </c>
       <c r="G254" s="14" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>130.18</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>137.73</v>
+        <v>137.8</v>
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>16.49</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>16.79</v>
+        <v>16.81</v>
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>759.26</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>744.8200000000001</v>
+        <v>745.27</v>
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>505.51</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>504.02</v>
+        <v>504.41</v>
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
@@ -12079,10 +12079,10 @@
         <v>13360.19</v>
       </c>
       <c r="E259" s="11" t="n">
-        <v>14682.89</v>
+        <v>14682.9</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>17336.4</v>
+        <v>17366.3</v>
       </c>
       <c r="G259" s="14" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>262.14</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>275.72</v>
+        <v>276.14</v>
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>1201.79</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>1143.04</v>
+        <v>1143.16</v>
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>479.85</v>
       </c>
       <c r="F262" s="11" t="n">
-        <v>555.48</v>
+        <v>555.03</v>
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>630.24</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>661.52</v>
+        <v>661.4</v>
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>898.1799999999999</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>982.35</v>
+        <v>981.42</v>
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>568.58</v>
       </c>
       <c r="F265" s="11" t="n">
-        <v>697.17</v>
+        <v>697.29</v>
       </c>
       <c r="G265" s="14" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>277.64</v>
       </c>
       <c r="F266" s="11" t="n">
-        <v>309.75</v>
+        <v>312.41</v>
       </c>
       <c r="G266" s="12" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>236.08</v>
       </c>
       <c r="F267" s="11" t="n">
-        <v>278.89</v>
+        <v>279.05</v>
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>782.75</v>
       </c>
       <c r="F268" s="11" t="n">
-        <v>897.97</v>
+        <v>899.4400000000001</v>
       </c>
       <c r="G268" s="14" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>1037.23</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>1040.96</v>
+        <v>1041.67</v>
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>414.54</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>459.8</v>
+        <v>459.12</v>
       </c>
       <c r="G270" s="14" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>195.06</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>219.32</v>
+        <v>219.33</v>
       </c>
       <c r="G271" s="12" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>287.74</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>258.21</v>
+        <v>258.5</v>
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>3933.42</v>
       </c>
       <c r="F273" s="11" t="n">
-        <v>4758.56</v>
+        <v>4759.04</v>
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>579.75</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>692.89</v>
+        <v>694.61</v>
       </c>
       <c r="G274" s="12" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>4487.3</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>4222.04</v>
+        <v>4223.81</v>
       </c>
       <c r="G275" s="12" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>955.4</v>
       </c>
       <c r="F276" s="11" t="n">
-        <v>1036.64</v>
+        <v>1036.97</v>
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>661.48</v>
       </c>
       <c r="F277" s="11" t="n">
-        <v>667.36</v>
+        <v>667.13</v>
       </c>
       <c r="G277" s="14" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>1599.24</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>1702.54</v>
+        <v>1704.16</v>
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>1432.83</v>
       </c>
       <c r="F279" s="11" t="n">
-        <v>1183.25</v>
+        <v>1183.15</v>
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>126.81</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>165.02</v>
+        <v>165.13</v>
       </c>
       <c r="G280" s="14" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>386.32</v>
       </c>
       <c r="F281" s="11" t="n">
-        <v>404.36</v>
+        <v>404.49</v>
       </c>
       <c r="G281" s="14" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>1154.66</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>1159.21</v>
+        <v>1160.33</v>
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>777.59</v>
       </c>
       <c r="F283" s="11" t="n">
-        <v>1021.07</v>
+        <v>1020.12</v>
       </c>
       <c r="G283" s="14" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>885.47</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>949.83</v>
+        <v>950.3099999999999</v>
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>1392.09</v>
       </c>
       <c r="F285" s="11" t="n">
-        <v>1436.65</v>
+        <v>1437.55</v>
       </c>
       <c r="G285" s="12" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>320.94</v>
       </c>
       <c r="F286" s="11" t="n">
-        <v>388.07</v>
+        <v>388.1</v>
       </c>
       <c r="G286" s="14" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>1053.29</v>
       </c>
       <c r="F287" s="11" t="n">
-        <v>949.33</v>
+        <v>949.37</v>
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>117.31</v>
       </c>
       <c r="F288" s="11" t="n">
-        <v>136.18</v>
+        <v>136.13</v>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>523.24</v>
       </c>
       <c r="F289" s="11" t="n">
-        <v>539.84</v>
+        <v>540.37</v>
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>811.26</v>
       </c>
       <c r="F290" s="11" t="n">
-        <v>843.4299999999999</v>
+        <v>843.79</v>
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
@@ -13487,10 +13487,10 @@
         <v>7145.28</v>
       </c>
       <c r="E291" s="11" t="n">
-        <v>6914.98</v>
+        <v>6914.97</v>
       </c>
       <c r="F291" s="11" t="n">
-        <v>6480.45</v>
+        <v>6476.03</v>
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>1380.87</v>
       </c>
       <c r="F292" s="11" t="n">
-        <v>1318.36</v>
+        <v>1318.44</v>
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>877.6799999999999</v>
       </c>
       <c r="F293" s="11" t="n">
-        <v>1048.92</v>
+        <v>1049.07</v>
       </c>
       <c r="G293" s="12" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>3902.37</v>
       </c>
       <c r="F294" s="11" t="n">
-        <v>3833.41</v>
+        <v>3833.69</v>
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>277</v>
       </c>
       <c r="F295" s="11" t="n">
-        <v>259.12</v>
+        <v>259.22</v>
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>399.16</v>
       </c>
       <c r="F296" s="11" t="n">
-        <v>403.11</v>
+        <v>403.13</v>
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
@@ -13741,24 +13741,24 @@
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Apr-2026</t>
         </is>
       </c>
       <c r="C297" s="11" t="n">
-        <v>4531.5</v>
+        <v>4282.3</v>
       </c>
       <c r="D297" s="11" t="n">
-        <v>4530.58</v>
+        <v>4506.94</v>
       </c>
       <c r="E297" s="11" t="n">
-        <v>4705.08</v>
+        <v>4688.5</v>
       </c>
       <c r="F297" s="11" t="n">
-        <v>5210.16</v>
-      </c>
-      <c r="G297" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>5206.97</v>
+      </c>
+      <c r="G297" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H297" s="14" t="inlineStr">
@@ -13795,10 +13795,10 @@
         <v>3415.87</v>
       </c>
       <c r="E298" s="11" t="n">
-        <v>3479.7</v>
+        <v>3479.71</v>
       </c>
       <c r="F298" s="11" t="n">
-        <v>3940.13</v>
+        <v>3956.9</v>
       </c>
       <c r="G298" s="14" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>2280.43</v>
       </c>
       <c r="F299" s="11" t="n">
-        <v>2144.87</v>
+        <v>2143.59</v>
       </c>
       <c r="G299" s="14" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>3237.75</v>
       </c>
       <c r="F300" s="11" t="n">
-        <v>3341.4</v>
+        <v>3342.27</v>
       </c>
       <c r="G300" s="14" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>321.92</v>
       </c>
       <c r="F301" s="11" t="n">
-        <v>319.42</v>
+        <v>319.51</v>
       </c>
       <c r="G301" s="14" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>68.76000000000001</v>
       </c>
       <c r="F302" s="11" t="n">
-        <v>61.39</v>
+        <v>61.43</v>
       </c>
       <c r="G302" s="12" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>587.87</v>
       </c>
       <c r="F303" s="11" t="n">
-        <v>589.5</v>
+        <v>589.72</v>
       </c>
       <c r="G303" s="12" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>275.07</v>
       </c>
       <c r="F304" s="11" t="n">
-        <v>271.89</v>
+        <v>272.03</v>
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>2122.98</v>
       </c>
       <c r="F305" s="11" t="n">
-        <v>2250.97</v>
+        <v>2248.78</v>
       </c>
       <c r="G305" s="12" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>421.89</v>
       </c>
       <c r="F306" s="11" t="n">
-        <v>576.89</v>
+        <v>576.4</v>
       </c>
       <c r="G306" s="12" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>1024.91</v>
       </c>
       <c r="F307" s="11" t="n">
-        <v>1391.64</v>
+        <v>1392.38</v>
       </c>
       <c r="G307" s="14" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>758.85</v>
       </c>
       <c r="F308" s="11" t="n">
-        <v>736.14</v>
+        <v>735.83</v>
       </c>
       <c r="G308" s="12" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>13717.03</v>
       </c>
       <c r="F309" s="11" t="n">
-        <v>14314.68</v>
+        <v>14320.88</v>
       </c>
       <c r="G309" s="14" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>1670.28</v>
       </c>
       <c r="F310" s="11" t="n">
-        <v>2001.06</v>
+        <v>2001.41</v>
       </c>
       <c r="G310" s="12" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>1003.57</v>
       </c>
       <c r="F311" s="11" t="n">
-        <v>1068.57</v>
+        <v>1069.04</v>
       </c>
       <c r="G311" s="12" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>2441.26</v>
       </c>
       <c r="F312" s="11" t="n">
-        <v>2542.59</v>
+        <v>2543.4</v>
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>2558.66</v>
       </c>
       <c r="F313" s="11" t="n">
-        <v>2111.19</v>
+        <v>2112.44</v>
       </c>
       <c r="G313" s="12" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>1082.81</v>
       </c>
       <c r="F314" s="11" t="n">
-        <v>1159.3</v>
+        <v>1159.43</v>
       </c>
       <c r="G314" s="12" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>463.31</v>
       </c>
       <c r="F315" s="11" t="n">
-        <v>471.64</v>
+        <v>471.77</v>
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>1650.29</v>
       </c>
       <c r="F316" s="11" t="n">
-        <v>1594.8</v>
+        <v>1596.03</v>
       </c>
       <c r="G316" s="14" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>1067.51</v>
       </c>
       <c r="F317" s="11" t="n">
-        <v>1156.31</v>
+        <v>1156.44</v>
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>532.05</v>
       </c>
       <c r="F318" s="11" t="n">
-        <v>546.9400000000001</v>
+        <v>547.91</v>
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>60.89</v>
       </c>
       <c r="F319" s="11" t="n">
-        <v>62.75</v>
+        <v>62.81</v>
       </c>
       <c r="G319" s="12" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>119.41</v>
       </c>
       <c r="F320" s="11" t="n">
-        <v>112.32</v>
+        <v>112.31</v>
       </c>
       <c r="G320" s="12" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>752.9299999999999</v>
       </c>
       <c r="F321" s="11" t="n">
-        <v>810.04</v>
+        <v>807.33</v>
       </c>
       <c r="G321" s="12" t="inlineStr">
         <is>
@@ -14851,10 +14851,10 @@
         <v>2299.66</v>
       </c>
       <c r="E322" s="11" t="n">
-        <v>2345.68</v>
+        <v>2345.69</v>
       </c>
       <c r="F322" s="11" t="n">
-        <v>2567.98</v>
+        <v>2569.75</v>
       </c>
       <c r="G322" s="14" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>136853.65</v>
       </c>
       <c r="F323" s="11" t="n">
-        <v>140868.32</v>
+        <v>140878.65</v>
       </c>
       <c r="G323" s="14" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>180.1</v>
       </c>
       <c r="F324" s="11" t="n">
-        <v>160.37</v>
+        <v>160.42</v>
       </c>
       <c r="G324" s="12" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>40.36</v>
       </c>
       <c r="F325" s="11" t="n">
-        <v>42.18</v>
+        <v>42.21</v>
       </c>
       <c r="G325" s="12" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>3453.33</v>
       </c>
       <c r="F326" s="11" t="n">
-        <v>3254.14</v>
+        <v>3254.16</v>
       </c>
       <c r="G326" s="12" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>913.63</v>
       </c>
       <c r="F327" s="11" t="n">
-        <v>850.5</v>
+        <v>851.5700000000001</v>
       </c>
       <c r="G327" s="12" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>1000.23</v>
       </c>
       <c r="F328" s="11" t="n">
-        <v>935.11</v>
+        <v>936.16</v>
       </c>
       <c r="G328" s="12" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>389.58</v>
       </c>
       <c r="F329" s="11" t="n">
-        <v>303.85</v>
+        <v>303.99</v>
       </c>
       <c r="G329" s="12" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>1056.4</v>
       </c>
       <c r="F330" s="11" t="n">
-        <v>1229.25</v>
+        <v>1230.74</v>
       </c>
       <c r="G330" s="14" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>596.4400000000001</v>
       </c>
       <c r="F331" s="11" t="n">
-        <v>570.02</v>
+        <v>570.2</v>
       </c>
       <c r="G331" s="12" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>6195.53</v>
       </c>
       <c r="F332" s="11" t="n">
-        <v>5635.43</v>
+        <v>5637.75</v>
       </c>
       <c r="G332" s="12" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>91.44</v>
       </c>
       <c r="F333" s="11" t="n">
-        <v>99.84</v>
+        <v>99.91</v>
       </c>
       <c r="G333" s="12" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>151.2</v>
       </c>
       <c r="F334" s="11" t="n">
-        <v>173.99</v>
+        <v>174.2</v>
       </c>
       <c r="G334" s="12" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>1267.08</v>
       </c>
       <c r="F335" s="11" t="n">
-        <v>1233.98</v>
+        <v>1233.33</v>
       </c>
       <c r="G335" s="12" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>3424.85</v>
       </c>
       <c r="F336" s="11" t="n">
-        <v>3084.95</v>
+        <v>3085.88</v>
       </c>
       <c r="G336" s="12" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>34.33</v>
       </c>
       <c r="F337" s="11" t="n">
-        <v>42.06</v>
+        <v>42.04</v>
       </c>
       <c r="G337" s="12" t="inlineStr">
         <is>
@@ -15555,10 +15555,10 @@
         <v>14169.85</v>
       </c>
       <c r="E338" s="11" t="n">
-        <v>13734.76</v>
+        <v>13734.77</v>
       </c>
       <c r="F338" s="11" t="n">
-        <v>14027.99</v>
+        <v>14038.51</v>
       </c>
       <c r="G338" s="12" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>502.22</v>
       </c>
       <c r="F339" s="11" t="n">
-        <v>756.05</v>
+        <v>750.58</v>
       </c>
       <c r="G339" s="14" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>1756.67</v>
       </c>
       <c r="F340" s="11" t="n">
-        <v>1770.46</v>
+        <v>1771.42</v>
       </c>
       <c r="G340" s="12" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>77.77</v>
       </c>
       <c r="F341" s="11" t="n">
-        <v>78.44</v>
+        <v>78.5</v>
       </c>
       <c r="G341" s="12" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>147.4</v>
       </c>
       <c r="F342" s="11" t="n">
-        <v>160.9</v>
+        <v>161.08</v>
       </c>
       <c r="G342" s="12" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>74.92</v>
       </c>
       <c r="F343" s="11" t="n">
-        <v>76.94</v>
+        <v>77.09</v>
       </c>
       <c r="G343" s="12" t="inlineStr">
         <is>
@@ -15790,9 +15790,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I343" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I343" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J343" s="13" t="inlineStr">
@@ -15822,7 +15822,7 @@
         <v>271.51</v>
       </c>
       <c r="F344" s="11" t="n">
-        <v>253.68</v>
+        <v>253.6</v>
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>82.12</v>
       </c>
       <c r="F345" s="11" t="n">
-        <v>75.84999999999999</v>
+        <v>75.95</v>
       </c>
       <c r="G345" s="12" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>39.61</v>
       </c>
       <c r="F346" s="11" t="n">
-        <v>40.45</v>
+        <v>40.48</v>
       </c>
       <c r="G346" s="12" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>376.62</v>
       </c>
       <c r="F347" s="11" t="n">
-        <v>349.64</v>
+        <v>349.81</v>
       </c>
       <c r="G347" s="12" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>98.88</v>
       </c>
       <c r="F348" s="11" t="n">
-        <v>98.44</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="G348" s="12" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>1285.28</v>
       </c>
       <c r="F349" s="11" t="n">
-        <v>1304.18</v>
+        <v>1303.2</v>
       </c>
       <c r="G349" s="12" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>254.92</v>
       </c>
       <c r="F350" s="11" t="n">
-        <v>242.32</v>
+        <v>242.42</v>
       </c>
       <c r="G350" s="12" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>1582.73</v>
       </c>
       <c r="F351" s="11" t="n">
-        <v>1630.31</v>
+        <v>1628.51</v>
       </c>
       <c r="G351" s="12" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>7340.23</v>
       </c>
       <c r="F352" s="11" t="n">
-        <v>7828.42</v>
+        <v>7813.53</v>
       </c>
       <c r="G352" s="12" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>467.53</v>
       </c>
       <c r="F353" s="11" t="n">
-        <v>440.23</v>
+        <v>440.51</v>
       </c>
       <c r="G353" s="12" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>31.72</v>
       </c>
       <c r="F354" s="11" t="n">
-        <v>39.49</v>
+        <v>39.56</v>
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>1095.59</v>
       </c>
       <c r="F355" s="11" t="n">
-        <v>1198.19</v>
+        <v>1199.99</v>
       </c>
       <c r="G355" s="12" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>274</v>
       </c>
       <c r="F356" s="11" t="n">
-        <v>251.56</v>
+        <v>251.76</v>
       </c>
       <c r="G356" s="12" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>34611.63</v>
       </c>
       <c r="F357" s="11" t="n">
-        <v>37633.15</v>
+        <v>37629.05</v>
       </c>
       <c r="G357" s="12" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>485.47</v>
       </c>
       <c r="F358" s="11" t="n">
-        <v>536.1</v>
+        <v>536.33</v>
       </c>
       <c r="G358" s="14" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>1114.59</v>
       </c>
       <c r="F359" s="11" t="n">
-        <v>1129.4</v>
+        <v>1130.95</v>
       </c>
       <c r="G359" s="12" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>277.58</v>
       </c>
       <c r="F360" s="11" t="n">
-        <v>316.15</v>
+        <v>316.61</v>
       </c>
       <c r="G360" s="12" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>5241.18</v>
       </c>
       <c r="F362" s="11" t="n">
-        <v>5562.43</v>
+        <v>5560.73</v>
       </c>
       <c r="G362" s="14" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>275.94</v>
       </c>
       <c r="F363" s="11" t="n">
-        <v>281.83</v>
+        <v>281.94</v>
       </c>
       <c r="G363" s="12" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>418.95</v>
       </c>
       <c r="F364" s="11" t="n">
-        <v>393.87</v>
+        <v>394.19</v>
       </c>
       <c r="G364" s="12" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>4829.81</v>
       </c>
       <c r="F365" s="11" t="n">
-        <v>4915.04</v>
+        <v>4914.96</v>
       </c>
       <c r="G365" s="14" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>539.34</v>
       </c>
       <c r="F366" s="11" t="n">
-        <v>602.13</v>
+        <v>604.33</v>
       </c>
       <c r="G366" s="12" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>1688.16</v>
       </c>
       <c r="F367" s="11" t="n">
-        <v>1674.63</v>
+        <v>1674.69</v>
       </c>
       <c r="G367" s="12" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>1388.71</v>
       </c>
       <c r="F368" s="11" t="n">
-        <v>1441.81</v>
+        <v>1441.43</v>
       </c>
       <c r="G368" s="12" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>3016.77</v>
       </c>
       <c r="F369" s="11" t="n">
-        <v>3298.08</v>
+        <v>3298.99</v>
       </c>
       <c r="G369" s="12" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>114.76</v>
       </c>
       <c r="F370" s="11" t="n">
-        <v>114.4</v>
+        <v>114.48</v>
       </c>
       <c r="G370" s="12" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>862.8</v>
       </c>
       <c r="F371" s="11" t="n">
-        <v>881.73</v>
+        <v>883.41</v>
       </c>
       <c r="G371" s="12" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>202.01</v>
       </c>
       <c r="F372" s="11" t="n">
-        <v>242</v>
+        <v>242.11</v>
       </c>
       <c r="G372" s="12" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>1544.63</v>
       </c>
       <c r="F373" s="11" t="n">
-        <v>1655.53</v>
+        <v>1657.7</v>
       </c>
       <c r="G373" s="12" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>7620.03</v>
       </c>
       <c r="F374" s="11" t="n">
-        <v>7293.12</v>
+        <v>7302.35</v>
       </c>
       <c r="G374" s="12" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>1413.17</v>
       </c>
       <c r="F375" s="11" t="n">
-        <v>1717.24</v>
+        <v>1716.36</v>
       </c>
       <c r="G375" s="12" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>420.06</v>
       </c>
       <c r="F376" s="11" t="n">
-        <v>431.65</v>
+        <v>431.69</v>
       </c>
       <c r="G376" s="12" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>298.58</v>
       </c>
       <c r="F377" s="11" t="n">
-        <v>284.01</v>
+        <v>283.97</v>
       </c>
       <c r="G377" s="12" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>25628.94</v>
       </c>
       <c r="F378" s="11" t="n">
-        <v>21097.55</v>
+        <v>21114.15</v>
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>151.85</v>
       </c>
       <c r="F379" s="11" t="n">
-        <v>174.48</v>
+        <v>174.64</v>
       </c>
       <c r="G379" s="12" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>333.8</v>
       </c>
       <c r="F380" s="11" t="n">
-        <v>370.77</v>
+        <v>371.98</v>
       </c>
       <c r="G380" s="12" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>890.8099999999999</v>
       </c>
       <c r="F381" s="11" t="n">
-        <v>915.9299999999999</v>
+        <v>916.9400000000001</v>
       </c>
       <c r="G381" s="12" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>1354.01</v>
       </c>
       <c r="F382" s="11" t="n">
-        <v>1476.46</v>
+        <v>1476.92</v>
       </c>
       <c r="G382" s="12" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>16628.73</v>
       </c>
       <c r="F383" s="11" t="n">
-        <v>16616.13</v>
+        <v>16616.09</v>
       </c>
       <c r="G383" s="12" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>983.86</v>
       </c>
       <c r="F384" s="11" t="n">
-        <v>1026.6</v>
+        <v>1026.54</v>
       </c>
       <c r="G384" s="12" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>2878.22</v>
       </c>
       <c r="F385" s="11" t="n">
-        <v>2847.29</v>
+        <v>2846.98</v>
       </c>
       <c r="G385" s="12" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>304.3</v>
       </c>
       <c r="F386" s="11" t="n">
-        <v>333.43</v>
+        <v>334.97</v>
       </c>
       <c r="G386" s="12" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>1217.58</v>
       </c>
       <c r="F387" s="11" t="n">
-        <v>1297.93</v>
+        <v>1298.69</v>
       </c>
       <c r="G387" s="12" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>1009.24</v>
       </c>
       <c r="F388" s="11" t="n">
-        <v>1027.57</v>
+        <v>1027.95</v>
       </c>
       <c r="G388" s="14" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>396.54</v>
       </c>
       <c r="F389" s="11" t="n">
-        <v>560.41</v>
+        <v>560.1900000000001</v>
       </c>
       <c r="G389" s="12" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>841.64</v>
       </c>
       <c r="F390" s="11" t="n">
-        <v>1029.75</v>
+        <v>1031.53</v>
       </c>
       <c r="G390" s="14" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>310.19</v>
       </c>
       <c r="F391" s="11" t="n">
-        <v>286.55</v>
+        <v>286.62</v>
       </c>
       <c r="G391" s="12" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>125.68</v>
       </c>
       <c r="F392" s="11" t="n">
-        <v>135.95</v>
+        <v>136.07</v>
       </c>
       <c r="G392" s="12" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>348.94</v>
       </c>
       <c r="F393" s="11" t="n">
-        <v>359.43</v>
+        <v>359.69</v>
       </c>
       <c r="G393" s="12" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>232.91</v>
       </c>
       <c r="F394" s="11" t="n">
-        <v>251.87</v>
+        <v>252.28</v>
       </c>
       <c r="G394" s="14" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>1382.52</v>
       </c>
       <c r="F395" s="11" t="n">
-        <v>1412.06</v>
+        <v>1412.67</v>
       </c>
       <c r="G395" s="14" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>26.34</v>
       </c>
       <c r="F396" s="11" t="n">
-        <v>27.68</v>
+        <v>27.76</v>
       </c>
       <c r="G396" s="12" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>399.94</v>
       </c>
       <c r="F397" s="11" t="n">
-        <v>436.3</v>
+        <v>436.56</v>
       </c>
       <c r="G397" s="12" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>209.15</v>
       </c>
       <c r="F398" s="11" t="n">
-        <v>227.26</v>
+        <v>227.6</v>
       </c>
       <c r="G398" s="12" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>532.28</v>
       </c>
       <c r="F399" s="11" t="n">
-        <v>569.73</v>
+        <v>571.46</v>
       </c>
       <c r="G399" s="12" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>509.55</v>
       </c>
       <c r="F400" s="11" t="n">
-        <v>680.28</v>
+        <v>680.59</v>
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>26.43</v>
       </c>
       <c r="F401" s="11" t="n">
-        <v>34.77</v>
+        <v>34.86</v>
       </c>
       <c r="G401" s="12" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>1414.26</v>
       </c>
       <c r="F402" s="11" t="n">
-        <v>1368.98</v>
+        <v>1369.01</v>
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>32.17</v>
       </c>
       <c r="F403" s="11" t="n">
-        <v>40.74</v>
+        <v>40.78</v>
       </c>
       <c r="G403" s="12" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>290.87</v>
       </c>
       <c r="F404" s="11" t="n">
-        <v>320.95</v>
+        <v>322.64</v>
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>42.71</v>
       </c>
       <c r="F405" s="11" t="n">
-        <v>45.34</v>
+        <v>45.43</v>
       </c>
       <c r="G405" s="14" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>159.97</v>
       </c>
       <c r="F406" s="11" t="n">
-        <v>143.22</v>
+        <v>143.32</v>
       </c>
       <c r="G406" s="12" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>968.15</v>
       </c>
       <c r="F407" s="11" t="n">
-        <v>893.9400000000001</v>
+        <v>894.23</v>
       </c>
       <c r="G407" s="12" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>147.49</v>
       </c>
       <c r="F408" s="11" t="n">
-        <v>145.39</v>
+        <v>145.93</v>
       </c>
       <c r="G408" s="14" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>181.37</v>
       </c>
       <c r="F409" s="11" t="n">
-        <v>237.45</v>
+        <v>237.11</v>
       </c>
       <c r="G409" s="14" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>540.21</v>
       </c>
       <c r="F410" s="11" t="n">
-        <v>515.29</v>
+        <v>515.3200000000001</v>
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>338.78</v>
       </c>
       <c r="F411" s="11" t="n">
-        <v>392.53</v>
+        <v>391.84</v>
       </c>
       <c r="G411" s="12" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>92.95999999999999</v>
       </c>
       <c r="F412" s="11" t="n">
-        <v>98.61</v>
+        <v>98.62</v>
       </c>
       <c r="G412" s="12" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>709.97</v>
       </c>
       <c r="F413" s="11" t="n">
-        <v>791.88</v>
+        <v>792.64</v>
       </c>
       <c r="G413" s="14" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>1926.34</v>
       </c>
       <c r="F414" s="11" t="n">
-        <v>1896.48</v>
+        <v>1898.24</v>
       </c>
       <c r="G414" s="14" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>1077.5</v>
       </c>
       <c r="F415" s="11" t="n">
-        <v>982.16</v>
+        <v>982.6900000000001</v>
       </c>
       <c r="G415" s="12" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>3954.51</v>
       </c>
       <c r="F416" s="11" t="n">
-        <v>3860.79</v>
+        <v>3863.01</v>
       </c>
       <c r="G416" s="12" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>925.8</v>
       </c>
       <c r="F417" s="11" t="n">
-        <v>822.3200000000001</v>
+        <v>823.3200000000001</v>
       </c>
       <c r="G417" s="12" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>251.92</v>
       </c>
       <c r="F418" s="11" t="n">
-        <v>228.23</v>
+        <v>228.55</v>
       </c>
       <c r="G418" s="12" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>24972.4</v>
       </c>
       <c r="F419" s="11" t="n">
-        <v>26715.63</v>
+        <v>26720.92</v>
       </c>
       <c r="G419" s="12" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>993.22</v>
       </c>
       <c r="F420" s="11" t="n">
-        <v>864.76</v>
+        <v>865.34</v>
       </c>
       <c r="G420" s="12" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>822.92</v>
       </c>
       <c r="F421" s="11" t="n">
-        <v>840.27</v>
+        <v>841.13</v>
       </c>
       <c r="G421" s="14" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>3316.04</v>
       </c>
       <c r="F422" s="11" t="n">
-        <v>3200.54</v>
+        <v>3205.69</v>
       </c>
       <c r="G422" s="12" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>855.6799999999999</v>
       </c>
       <c r="F423" s="11" t="n">
-        <v>995.8099999999999</v>
+        <v>996.59</v>
       </c>
       <c r="G423" s="12" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>72.93000000000001</v>
       </c>
       <c r="F424" s="11" t="n">
-        <v>79.37</v>
+        <v>79.47</v>
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>1676.35</v>
       </c>
       <c r="F425" s="11" t="n">
-        <v>2506.21</v>
+        <v>2507.63</v>
       </c>
       <c r="G425" s="12" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>1346.45</v>
       </c>
       <c r="F426" s="11" t="n">
-        <v>1421.83</v>
+        <v>1421.09</v>
       </c>
       <c r="G426" s="12" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>13923.87</v>
       </c>
       <c r="F427" s="11" t="n">
-        <v>13462.79</v>
+        <v>13467.24</v>
       </c>
       <c r="G427" s="12" t="inlineStr">
         <is>
@@ -19515,10 +19515,10 @@
         <v>551.78</v>
       </c>
       <c r="E428" s="11" t="n">
-        <v>528.83</v>
+        <v>528.84</v>
       </c>
       <c r="F428" s="11" t="n">
-        <v>500.15</v>
+        <v>500.65</v>
       </c>
       <c r="G428" s="12" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>264.07</v>
       </c>
       <c r="F429" s="11" t="n">
-        <v>329.17</v>
+        <v>329</v>
       </c>
       <c r="G429" s="12" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>2573.43</v>
       </c>
       <c r="F430" s="11" t="n">
-        <v>2775.31</v>
+        <v>2779.27</v>
       </c>
       <c r="G430" s="12" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>473.26</v>
       </c>
       <c r="F431" s="11" t="n">
-        <v>460.11</v>
+        <v>460.25</v>
       </c>
       <c r="G431" s="12" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>414.15</v>
       </c>
       <c r="F432" s="11" t="n">
-        <v>457.61</v>
+        <v>457.89</v>
       </c>
       <c r="G432" s="12" t="inlineStr">
         <is>
@@ -19735,10 +19735,10 @@
         <v>4883.66</v>
       </c>
       <c r="E433" s="11" t="n">
-        <v>4972.03</v>
+        <v>4972.02</v>
       </c>
       <c r="F433" s="11" t="n">
-        <v>4919.82</v>
+        <v>4914.65</v>
       </c>
       <c r="G433" s="14" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>836</v>
       </c>
       <c r="F434" s="11" t="n">
-        <v>914.9299999999999</v>
+        <v>915.79</v>
       </c>
       <c r="G434" s="14" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>1715.43</v>
       </c>
       <c r="F435" s="11" t="n">
-        <v>1705.82</v>
+        <v>1706.09</v>
       </c>
       <c r="G435" s="14" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>597.99</v>
       </c>
       <c r="F436" s="11" t="n">
-        <v>580.42</v>
+        <v>580.4</v>
       </c>
       <c r="G436" s="14" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>3758.3</v>
       </c>
       <c r="F437" s="11" t="n">
-        <v>3826.18</v>
+        <v>3823.67</v>
       </c>
       <c r="G437" s="14" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>46.4</v>
       </c>
       <c r="F438" s="11" t="n">
-        <v>51.15</v>
+        <v>51.13</v>
       </c>
       <c r="G438" s="12" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>295.89</v>
       </c>
       <c r="F440" s="11" t="n">
-        <v>351.75</v>
+        <v>351.56</v>
       </c>
       <c r="G440" s="12" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>189.3</v>
       </c>
       <c r="F441" s="11" t="n">
-        <v>226.78</v>
+        <v>228.22</v>
       </c>
       <c r="G441" s="12" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>439.52</v>
       </c>
       <c r="F442" s="11" t="n">
-        <v>556.49</v>
+        <v>556.34</v>
       </c>
       <c r="G442" s="12" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>842.84</v>
       </c>
       <c r="F443" s="11" t="n">
-        <v>759.51</v>
+        <v>759.61</v>
       </c>
       <c r="G443" s="12" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>462.78</v>
       </c>
       <c r="F444" s="11" t="n">
-        <v>527.38</v>
+        <v>527.5700000000001</v>
       </c>
       <c r="G444" s="12" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>292.82</v>
       </c>
       <c r="F445" s="11" t="n">
-        <v>351.02</v>
+        <v>352.07</v>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>688.3099999999999</v>
       </c>
       <c r="F446" s="11" t="n">
-        <v>779.48</v>
+        <v>779.9299999999999</v>
       </c>
       <c r="G446" s="12" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>1525.84</v>
       </c>
       <c r="F447" s="11" t="n">
-        <v>1633.5</v>
+        <v>1634.86</v>
       </c>
       <c r="G447" s="12" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>1110.91</v>
       </c>
       <c r="F448" s="11" t="n">
-        <v>1114.74</v>
+        <v>1113.97</v>
       </c>
       <c r="G448" s="12" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>4532.74</v>
       </c>
       <c r="F449" s="11" t="n">
-        <v>5125.46</v>
+        <v>5128.39</v>
       </c>
       <c r="G449" s="14" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>655.92</v>
       </c>
       <c r="F450" s="11" t="n">
-        <v>679.52</v>
+        <v>679.8200000000001</v>
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>397.29</v>
       </c>
       <c r="F452" s="11" t="n">
-        <v>385.88</v>
+        <v>386.03</v>
       </c>
       <c r="G452" s="12" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>200.15</v>
       </c>
       <c r="F453" s="11" t="n">
-        <v>180.78</v>
+        <v>180.84</v>
       </c>
       <c r="G453" s="12" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>575.9</v>
       </c>
       <c r="F454" s="11" t="n">
-        <v>639.28</v>
+        <v>639.5599999999999</v>
       </c>
       <c r="G454" s="12" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>1251.46</v>
       </c>
       <c r="F455" s="11" t="n">
-        <v>1405.36</v>
+        <v>1405.28</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>2602.95</v>
       </c>
       <c r="F456" s="11" t="n">
-        <v>2946.8</v>
+        <v>2945.02</v>
       </c>
       <c r="G456" s="14" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>1454.5</v>
       </c>
       <c r="F457" s="11" t="n">
-        <v>1501.32</v>
+        <v>1501.82</v>
       </c>
       <c r="G457" s="14" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>1123.69</v>
       </c>
       <c r="F458" s="11" t="n">
-        <v>1175.54</v>
+        <v>1177.8</v>
       </c>
       <c r="G458" s="12" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>416.43</v>
       </c>
       <c r="F459" s="11" t="n">
-        <v>507.62</v>
+        <v>507.8</v>
       </c>
       <c r="G459" s="14" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>3442.42</v>
       </c>
       <c r="F460" s="11" t="n">
-        <v>3273.15</v>
+        <v>3274.47</v>
       </c>
       <c r="G460" s="12" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>2673.63</v>
       </c>
       <c r="F461" s="11" t="n">
-        <v>2759.32</v>
+        <v>2760.37</v>
       </c>
       <c r="G461" s="12" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>3344.89</v>
       </c>
       <c r="F462" s="11" t="n">
-        <v>3142.51</v>
+        <v>3146.05</v>
       </c>
       <c r="G462" s="12" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>707.84</v>
       </c>
       <c r="F463" s="11" t="n">
-        <v>791.96</v>
+        <v>793.75</v>
       </c>
       <c r="G463" s="12" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>4247.22</v>
       </c>
       <c r="F464" s="11" t="n">
-        <v>3927.75</v>
+        <v>3927.46</v>
       </c>
       <c r="G464" s="12" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>4149.93</v>
       </c>
       <c r="F465" s="11" t="n">
-        <v>3844.65</v>
+        <v>3843.1</v>
       </c>
       <c r="G465" s="14" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>1472.36</v>
       </c>
       <c r="F466" s="11" t="n">
-        <v>1386.16</v>
+        <v>1389.18</v>
       </c>
       <c r="G466" s="12" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>3917.45</v>
       </c>
       <c r="F467" s="11" t="n">
-        <v>4409.89</v>
+        <v>4402.16</v>
       </c>
       <c r="G467" s="12" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>25.2</v>
       </c>
       <c r="F468" s="11" t="n">
-        <v>26.9</v>
+        <v>26.91</v>
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>493.23</v>
       </c>
       <c r="F469" s="11" t="n">
-        <v>521.45</v>
+        <v>521.41</v>
       </c>
       <c r="G469" s="12" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>382.32</v>
       </c>
       <c r="F470" s="11" t="n">
-        <v>372.32</v>
+        <v>372.64</v>
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>41.53</v>
       </c>
       <c r="F471" s="11" t="n">
-        <v>49.46</v>
+        <v>49.53</v>
       </c>
       <c r="G471" s="12" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>3631.38</v>
       </c>
       <c r="F472" s="11" t="n">
-        <v>3425.78</v>
+        <v>3426.96</v>
       </c>
       <c r="G472" s="14" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>1546.73</v>
       </c>
       <c r="F473" s="11" t="n">
-        <v>1685.04</v>
+        <v>1684.24</v>
       </c>
       <c r="G473" s="14" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>26.57</v>
       </c>
       <c r="F474" s="11" t="n">
-        <v>29.42</v>
+        <v>29.44</v>
       </c>
       <c r="G474" s="12" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>11739.13</v>
       </c>
       <c r="F475" s="11" t="n">
-        <v>11855.03</v>
+        <v>11859.96</v>
       </c>
       <c r="G475" s="12" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>180.57</v>
       </c>
       <c r="F476" s="11" t="n">
-        <v>160.19</v>
+        <v>160.35</v>
       </c>
       <c r="G476" s="14" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>1323.79</v>
       </c>
       <c r="F477" s="11" t="n">
-        <v>1361.36</v>
+        <v>1361.5</v>
       </c>
       <c r="G477" s="12" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>1117.21</v>
       </c>
       <c r="F478" s="11" t="n">
-        <v>1153.5</v>
+        <v>1155.34</v>
       </c>
       <c r="G478" s="12" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>654.16</v>
       </c>
       <c r="F479" s="11" t="n">
-        <v>680.8099999999999</v>
+        <v>680.78</v>
       </c>
       <c r="G479" s="14" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>424</v>
       </c>
       <c r="F480" s="11" t="n">
-        <v>410.46</v>
+        <v>410.88</v>
       </c>
       <c r="G480" s="12" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>1001.8</v>
       </c>
       <c r="F481" s="11" t="n">
-        <v>1104.2</v>
+        <v>1103.46</v>
       </c>
       <c r="G481" s="14" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>442.79</v>
       </c>
       <c r="F482" s="11" t="n">
-        <v>465.14</v>
+        <v>465.75</v>
       </c>
       <c r="G482" s="12" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>698.8</v>
       </c>
       <c r="F483" s="11" t="n">
-        <v>583.8200000000001</v>
+        <v>584.41</v>
       </c>
       <c r="G483" s="14" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>324.52</v>
       </c>
       <c r="F484" s="11" t="n">
-        <v>340.93</v>
+        <v>340.9</v>
       </c>
       <c r="G484" s="12" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>975.3099999999999</v>
       </c>
       <c r="F485" s="11" t="n">
-        <v>999.15</v>
+        <v>998.35</v>
       </c>
       <c r="G485" s="12" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>116.7</v>
       </c>
       <c r="F486" s="11" t="n">
-        <v>124.79</v>
+        <v>124.97</v>
       </c>
       <c r="G486" s="12" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>1395.31</v>
       </c>
       <c r="F487" s="11" t="n">
-        <v>1397.44</v>
+        <v>1395.82</v>
       </c>
       <c r="G487" s="12" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>530.55</v>
       </c>
       <c r="F488" s="11" t="n">
-        <v>478.87</v>
+        <v>479.37</v>
       </c>
       <c r="G488" s="12" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>3108.37</v>
       </c>
       <c r="F489" s="11" t="n">
-        <v>3007.52</v>
+        <v>3009.19</v>
       </c>
       <c r="G489" s="12" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>913.53</v>
       </c>
       <c r="F490" s="11" t="n">
-        <v>851.0599999999999</v>
+        <v>851.33</v>
       </c>
       <c r="G490" s="12" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>124.08</v>
       </c>
       <c r="F491" s="11" t="n">
-        <v>128.13</v>
+        <v>128.16</v>
       </c>
       <c r="G491" s="12" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>475.72</v>
       </c>
       <c r="F492" s="11" t="n">
-        <v>562.84</v>
+        <v>562.95</v>
       </c>
       <c r="G492" s="14" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>872.6900000000001</v>
       </c>
       <c r="F493" s="11" t="n">
-        <v>1035.54</v>
+        <v>1035.31</v>
       </c>
       <c r="G493" s="12" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>206.93</v>
       </c>
       <c r="F494" s="11" t="n">
-        <v>230</v>
+        <v>229.82</v>
       </c>
       <c r="G494" s="14" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>1331.33</v>
       </c>
       <c r="F495" s="11" t="n">
-        <v>1379.36</v>
+        <v>1380.69</v>
       </c>
       <c r="G495" s="12" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>19.71</v>
       </c>
       <c r="F496" s="11" t="n">
-        <v>20.45</v>
+        <v>20.46</v>
       </c>
       <c r="G496" s="12" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>82.77</v>
       </c>
       <c r="F497" s="11" t="n">
-        <v>95.66</v>
+        <v>95.67</v>
       </c>
       <c r="G497" s="12" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>581.35</v>
       </c>
       <c r="F498" s="11" t="n">
-        <v>674.1900000000001</v>
+        <v>673.75</v>
       </c>
       <c r="G498" s="14" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>1464.47</v>
       </c>
       <c r="F499" s="11" t="n">
-        <v>1478.98</v>
+        <v>1482.72</v>
       </c>
       <c r="G499" s="12" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>14416.6</v>
       </c>
       <c r="F500" s="11" t="n">
-        <v>13904.03</v>
+        <v>13906.2</v>
       </c>
       <c r="G500" s="12" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>909.16</v>
       </c>
       <c r="F501" s="11" t="n">
-        <v>927.13</v>
+        <v>927.27</v>
       </c>
       <c r="G501" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 25-Apr-2026  16:01:21    |    Closing Price Date: 24-Apr-2026</t>
+          <t>Scan Run: 26-Apr-2026  16:03:31    |    Closing Price Date: 24-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>68</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46</v>
+        <v>45.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>500</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>25-Apr-2026  16:01:21</t>
+          <t>26-Apr-2026  16:03:31</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 45.6% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 230 of 500 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 228 of 500 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>1546.59</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1436.98</v>
+        <v>1435.86</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1054.74</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1086.9</v>
+        <v>1086.23</v>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         <v>31862.72</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>32731.82</v>
+        <v>32731.81</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>32559.42</v>
+        <v>32522.78</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>473.48</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>474.36</v>
+        <v>474.44</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>426.81</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>410.7</v>
+        <v>410.87</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>1277.71</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1468.25</v>
+        <v>1468.21</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>6359.58</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5743.28</v>
+        <v>5752.79</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
         <v>25814.33</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>26391.1</v>
+        <v>26391.11</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>28190.93</v>
+        <v>28218.16</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>332.25</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>310.43</v>
+        <v>310.4</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>63.57</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>90.72</v>
+        <v>90.64</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>1318.7</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1577.49</v>
+        <v>1576.11</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>944.91</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>843.8099999999999</v>
+        <v>843.34</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1474.21</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1683.78</v>
+        <v>1684.95</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>874.97</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>975.1</v>
+        <v>974.64</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>262.02</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>249.17</v>
+        <v>248.87</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1083.29</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>969.71</v>
+        <v>970.27</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>2092.06</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2231.77</v>
+        <v>2230.55</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>992.73</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>983.38</v>
+        <v>983.73</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>1471.02</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1425.4</v>
+        <v>1425.96</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>166.22</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>144.86</v>
+        <v>144.76</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>663.41</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>714.46</v>
+        <v>713.14</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>314.24</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>371.53</v>
+        <v>371.36</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>1453.17</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1628.48</v>
+        <v>1627.44</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>3798.38</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3637.72</v>
+        <v>3637.94</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>477.67</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>508.73</v>
+        <v>508.02</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>2837.74</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2731.58</v>
+        <v>2731.45</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>493.61</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>484.72</v>
+        <v>484.87</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>984.98</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>960.95</v>
+        <v>961.22</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>5461.41</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5403.31</v>
+        <v>5406.52</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>1428.14</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1637.73</v>
+        <v>1638.02</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>13.85</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>15.9</v>
+        <v>15.88</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>7156.08</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7082.17</v>
+        <v>7079.62</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>463.69</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>516.59</v>
+        <v>516.42</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>3271.23</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2914.07</v>
+        <v>2914.17</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>495.75</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>551.84</v>
+        <v>552.37</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>263.86</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>251.72</v>
+        <v>251.59</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>10283.48</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>9153.299999999999</v>
+        <v>9154.879999999999</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>2032.87</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1886.71</v>
+        <v>1887.64</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>734.96</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>826.05</v>
+        <v>828.3200000000001</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>7504.55</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>7354.42</v>
+        <v>7356.09</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>442.96</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>465.31</v>
+        <v>465.19</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>236.34</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>271.65</v>
+        <v>271.62</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>800.95</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>892.45</v>
+        <v>892.72</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>869.53</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>877.79</v>
+        <v>877.35</v>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>177.22</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>160.88</v>
+        <v>160.85</v>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>2385.93</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2462.05</v>
+        <v>2464.02</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>653.61</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>617.83</v>
+        <v>617.92</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>1583.79</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1508.54</v>
+        <v>1508.5</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>8447.51</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>8584.549999999999</v>
+        <v>8590.48</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>558.67</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>581.29</v>
+        <v>581.28</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>6386.55</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>6310.6</v>
+        <v>6307.97</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>960.26</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>884.02</v>
+        <v>883.77</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>1298.3</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1205.14</v>
+        <v>1206.11</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>191.35</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>225.66</v>
+        <v>225.58</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>1302.93</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1240.62</v>
+        <v>1238.57</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>9441.690000000001</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9109.23</v>
+        <v>9109.209999999999</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>1837.01</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1932.77</v>
+        <v>1932.04</v>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>86.48</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>97.86</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>10189.57</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>11233.8</v>
+        <v>11227.93</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>915.9299999999999</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>936.86</v>
+        <v>936.53</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>2281</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2381.29</v>
+        <v>2380.44</v>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>483.45</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>481.91</v>
+        <v>482.19</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>281.58</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>273.16</v>
+        <v>273.12</v>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>151.3</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>140.41</v>
+        <v>140.43</v>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>3569.98</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>4015.53</v>
+        <v>4012.12</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>751.64</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>943.85</v>
+        <v>943.98</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>4680.51</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>4773.43</v>
+        <v>4772.08</v>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>1562.82</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1743.65</v>
+        <v>1743.75</v>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>1321.27</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1409.03</v>
+        <v>1412.27</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>436.13</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>406.32</v>
+        <v>406.58</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>1658.47</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1788.12</v>
+        <v>1789.04</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>455.4</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>495.71</v>
+        <v>495.89</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>1741.69</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1497.86</v>
+        <v>1497.96</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>1878.58</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1922.32</v>
+        <v>1922.2</v>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>1576.02</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1645.52</v>
+        <v>1644.2</v>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>279.2</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>260.05</v>
+        <v>260.2</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>647.21</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>686.78</v>
+        <v>686.26</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>367.23</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>371.98</v>
+        <v>372.01</v>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>275.91</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>311.9</v>
+        <v>314.08</v>
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>5297.41</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>5648.11</v>
+        <v>5649.71</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>1791.6</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1821.31</v>
+        <v>1820.84</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>34807.54</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>35158.54</v>
+        <v>35160.5</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>319.25</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>324.4</v>
+        <v>324.67</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>733.64</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>852.6900000000001</v>
+        <v>852.48</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>5749.3</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>5744.33</v>
+        <v>5744.76</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>3042.35</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2695.8</v>
+        <v>2695.86</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>245.33</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>259.12</v>
+        <v>259.08</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>702.39</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>734.76</v>
+        <v>734.53</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>141.06</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>133.51</v>
+        <v>133.53</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>861.87</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>836.24</v>
+        <v>836.41</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>1702.89</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1862.8</v>
+        <v>1861.15</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>847.0599999999999</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>885.03</v>
+        <v>883.84</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>180.71</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>185.54</v>
+        <v>185.57</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>1055.41</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>947.34</v>
+        <v>947.21</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>1294.35</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1409.98</v>
+        <v>1409.75</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>3615.21</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>3600.34</v>
+        <v>3599.5</v>
       </c>
       <c r="G99" s="14" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>35.85</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>37.56</v>
+        <v>37.58</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>736.83</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>756.27</v>
+        <v>756.9299999999999</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>5039.11</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>5491.17</v>
+        <v>5492.73</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>161.09</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>159.84</v>
+        <v>159.92</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>175.51</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>178.17</v>
+        <v>178.14</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>717.95</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>686.6799999999999</v>
+        <v>687.65</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>785.2</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>847.01</v>
+        <v>846.78</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>444.87</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>472.75</v>
+        <v>472.93</v>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>967.26</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>852.25</v>
+        <v>852.79</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>1563.82</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1589.89</v>
+        <v>1588.81</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>1579.99</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1716.4</v>
+        <v>1715.91</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>1284.52</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1401.52</v>
+        <v>1401.46</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>753.1900000000001</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>933.6</v>
+        <v>934.92</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>439.57</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>405.24</v>
+        <v>405.59</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>1467.24</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1572.13</v>
+        <v>1574.15</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>1283.64</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1526.54</v>
+        <v>1525.76</v>
       </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>2034.7</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>2170.45</v>
+        <v>2171.78</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -5846,9 +5846,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I117" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J117" s="13" t="inlineStr">
@@ -5878,7 +5878,7 @@
         <v>482.41</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>513.1900000000001</v>
+        <v>513.0599999999999</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>1116.52</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1378.16</v>
+        <v>1375.43</v>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>2087.42</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>2172.14</v>
+        <v>2172.11</v>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>7359.4</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>6893.9</v>
+        <v>6888.71</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>1233.07</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1245.67</v>
+        <v>1245.88</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>4195.01</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>4559.28</v>
+        <v>4554.35</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>248.87</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>274.89</v>
+        <v>274.96</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>260.07</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>246.11</v>
+        <v>246.12</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>4759.07</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>4219.16</v>
+        <v>4219.6</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>928.86</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1093.96</v>
+        <v>1093.51</v>
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>458.45</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>488.6</v>
+        <v>488.75</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>1955.49</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>2031.38</v>
+        <v>2030.57</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>3250.35</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>2851.34</v>
+        <v>2855.16</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>105.17</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>131.22</v>
+        <v>131.35</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1129.26</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1154.62</v>
+        <v>1156.24</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>1083.79</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1207.95</v>
+        <v>1208.88</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>1523.46</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1680.29</v>
+        <v>1679.98</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>437.44</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>417.88</v>
+        <v>418.16</v>
       </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>113.09</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>137.65</v>
+        <v>137.69</v>
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
@@ -6755,10 +6755,10 @@
         <v>10776.94</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>10862.17</v>
+        <v>10862.18</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>12965.81</v>
+        <v>12978.29</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>587.16</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>665.5599999999999</v>
+        <v>665.91</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>4152.13</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>4046.07</v>
+        <v>4046.93</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>2339.81</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>2437.33</v>
+        <v>2436.95</v>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>1255.81</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1253.84</v>
+        <v>1254.13</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>1642.46</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1872.65</v>
+        <v>1871.24</v>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>7172.45</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>6815.82</v>
+        <v>6814.29</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>856.4</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>933.92</v>
+        <v>933.63</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>320.35</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>348.8</v>
+        <v>348.86</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>425.23</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>480.63</v>
+        <v>480.28</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>505.83</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>495.74</v>
+        <v>495.6</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>2404.22</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>2493.07</v>
+        <v>2494.97</v>
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>209.16</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>198.46</v>
+        <v>198.58</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>1379.48</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>1470.11</v>
+        <v>1469.67</v>
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>3250.14</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>3427.14</v>
+        <v>3429.14</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>251.24</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>270.87</v>
+        <v>271.18</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>324.59</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>352.07</v>
+        <v>352.14</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>828.34</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>851.98</v>
+        <v>853.88</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>279.86</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>251.04</v>
+        <v>250.87</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>860.4</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>840.26</v>
+        <v>840.13</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>173.25</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>182.97</v>
+        <v>182.9</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>242.3</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>298.69</v>
+        <v>298.51</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>433.28</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>521.42</v>
+        <v>520.98</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>3297.23</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>3453.74</v>
+        <v>3451.1</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>872.29</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>868.6799999999999</v>
+        <v>867.86</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>237.47</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>294.2</v>
+        <v>294.51</v>
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>155.3</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>163.57</v>
+        <v>163.58</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>1362.57</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>1174.2</v>
+        <v>1172.68</v>
       </c>
       <c r="G166" s="14" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>382.2</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>380.97</v>
+        <v>381.28</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>7956.79</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>8464.73</v>
+        <v>8465.51</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>1738.09</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>1758.38</v>
+        <v>1758.53</v>
       </c>
       <c r="G169" s="14" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>2435.76</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>2543.09</v>
+        <v>2543.53</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>2145.04</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>1972.83</v>
+        <v>1973.11</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>603.76</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>530.6799999999999</v>
+        <v>530.6900000000001</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>94.88</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>93.39</v>
+        <v>93.45</v>
       </c>
       <c r="G173" s="14" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>444.83</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>474.4</v>
+        <v>474.9</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>2108.16</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>2419.06</v>
+        <v>2419.08</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>326.36</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>333.05</v>
+        <v>333</v>
       </c>
       <c r="G176" s="14" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>590.4299999999999</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>630.2</v>
+        <v>630.21</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>1101.36</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1146.05</v>
+        <v>1147.68</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>918.35</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>1008.46</v>
+        <v>1008.3</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>1712.29</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>1917.96</v>
+        <v>1919.88</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>274.45</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>248</v>
+        <v>248.05</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>159.28</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>162.05</v>
+        <v>162.01</v>
       </c>
       <c r="G182" s="14" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>617.15</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>571.63</v>
+        <v>571.62</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>655.63</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>599.51</v>
+        <v>599.76</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>2727.42</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>2735.72</v>
+        <v>2736.82</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>1544.51</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>1669.53</v>
+        <v>1667.01</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>2480.1</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>2419.15</v>
+        <v>2421.73</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>269.64</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>293.66</v>
+        <v>294.23</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>365.62</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>402.67</v>
+        <v>403.14</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>3799.39</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>3146.85</v>
+        <v>3145.42</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>4084.79</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>4264.89</v>
+        <v>4273.38</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9102,9 +9102,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I191" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I191" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J191" s="13" t="inlineStr">
@@ -9134,7 +9134,7 @@
         <v>388.26</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>471.03</v>
+        <v>470.9</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>1308.21</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>1406.81</v>
+        <v>1407.5</v>
       </c>
       <c r="G193" s="14" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>734.79</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>745.34</v>
+        <v>745.6799999999999</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>1394.33</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>1483.78</v>
+        <v>1484.39</v>
       </c>
       <c r="G195" s="14" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>2576.09</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>2568.03</v>
+        <v>2566.74</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>832.67</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>905.91</v>
+        <v>905.58</v>
       </c>
       <c r="G197" s="14" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>643.29</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>702.33</v>
+        <v>702.37</v>
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>568.3200000000001</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>533.86</v>
+        <v>533.8099999999999</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>5327.62</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>5189.64</v>
+        <v>5190.62</v>
       </c>
       <c r="G200" s="14" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>78.34</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>75.70999999999999</v>
+        <v>75.77</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>953.05</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>848.23</v>
+        <v>848.85</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>527.8099999999999</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>430.9</v>
+        <v>431.61</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>383.42</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>408.96</v>
+        <v>408.99</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>2228.12</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>2326.39</v>
+        <v>2326.78</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>571.4400000000001</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>536.53</v>
+        <v>536.59</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>1076.24</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>1129.39</v>
+        <v>1128.59</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>310.18</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>288.86</v>
+        <v>288.88</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>30478.42</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>33522.6</v>
+        <v>33517.32</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>473.57</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>469.66</v>
+        <v>469.34</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>187.84</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>202.78</v>
+        <v>203.19</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>1956.52</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>2115.14</v>
+        <v>2113.93</v>
       </c>
       <c r="G212" s="14" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>1323.9</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>1352.45</v>
+        <v>1351.42</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>1830.55</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>1881.9</v>
+        <v>1883.67</v>
       </c>
       <c r="G214" s="14" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>575.79</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>610.73</v>
+        <v>610.48</v>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>83.88</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>91.7</v>
+        <v>91.89</v>
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>9.51</v>
+        <v>9.52</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>126.09</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>138.68</v>
+        <v>138.75</v>
       </c>
       <c r="G219" s="14" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>56.67</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>55.37</v>
+        <v>55.45</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>335.29</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>346.67</v>
+        <v>345.45</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>163.16</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>180.81</v>
+        <v>180.97</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>477.71</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>490.92</v>
+        <v>490.93</v>
       </c>
       <c r="G223" s="14" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>1458.64</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>1557.61</v>
+        <v>1558.01</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>477.58</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>515.5</v>
+        <v>515.99</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>643.8</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>698.85</v>
+        <v>698.9400000000001</v>
       </c>
       <c r="G226" s="14" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>397.06</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>394.36</v>
+        <v>394.4</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>2128.02</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>2242.01</v>
+        <v>2243.87</v>
       </c>
       <c r="G228" s="14" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>907.21</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>809.79</v>
+        <v>809.67</v>
       </c>
       <c r="G229" s="14" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>4551.43</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>4963.33</v>
+        <v>4962.39</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>852.16</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>852.5700000000001</v>
+        <v>852.38</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>428.67</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>409.16</v>
+        <v>409.52</v>
       </c>
       <c r="G232" s="14" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>1334.01</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>1471.69</v>
+        <v>1466.89</v>
       </c>
       <c r="G233" s="14" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>1278.36</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>1181.38</v>
+        <v>1181.3</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>93.67</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>121.07</v>
+        <v>121.1</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>710.21</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>859.24</v>
+        <v>858.95</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>34.4</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>37.01</v>
+        <v>37.02</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>150.87</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>149.86</v>
+        <v>149.9</v>
       </c>
       <c r="G238" s="14" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>1493.05</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>1451.76</v>
+        <v>1451.44</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>21.21</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>21.73</v>
+        <v>21.79</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>141.52</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>158.16</v>
+        <v>158.15</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>561.38</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>640.09</v>
+        <v>640.78</v>
       </c>
       <c r="G242" s="14" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>124.64</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>139.18</v>
+        <v>139.31</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>102.44</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>114.37</v>
+        <v>114.5</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>310.29</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>353.45</v>
+        <v>353.75</v>
       </c>
       <c r="G245" s="14" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>280.09</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>296.53</v>
+        <v>295.99</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>118.5</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>108.44</v>
+        <v>108.42</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>1994.67</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>1856.46</v>
+        <v>1854.85</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>580.72</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>609.35</v>
+        <v>609.36</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>200.38</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>196.88</v>
+        <v>196.87</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>1185.57</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>1084.09</v>
+        <v>1084.39</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>247.06</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>272.6</v>
+        <v>272.7</v>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>5495.01</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>5656.3</v>
+        <v>5656.14</v>
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>442.28</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>432.32</v>
+        <v>432.23</v>
       </c>
       <c r="G254" s="14" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>130.18</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>137.8</v>
+        <v>137.71</v>
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>759.26</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>745.27</v>
+        <v>745.66</v>
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>505.51</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>504.41</v>
+        <v>504.3</v>
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>14682.9</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>17366.3</v>
+        <v>17405.35</v>
       </c>
       <c r="G259" s="14" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>262.14</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>276.14</v>
+        <v>276.1</v>
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>1201.79</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>1143.16</v>
+        <v>1143.23</v>
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>479.85</v>
       </c>
       <c r="F262" s="11" t="n">
-        <v>555.03</v>
+        <v>555.17</v>
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>630.24</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>661.4</v>
+        <v>661.48</v>
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>898.1799999999999</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>981.42</v>
+        <v>982.25</v>
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>568.58</v>
       </c>
       <c r="F265" s="11" t="n">
-        <v>697.29</v>
+        <v>698.0599999999999</v>
       </c>
       <c r="G265" s="14" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>277.64</v>
       </c>
       <c r="F266" s="11" t="n">
-        <v>312.41</v>
+        <v>312.19</v>
       </c>
       <c r="G266" s="12" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>236.08</v>
       </c>
       <c r="F267" s="11" t="n">
-        <v>279.05</v>
+        <v>279.26</v>
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>782.75</v>
       </c>
       <c r="F268" s="11" t="n">
-        <v>899.4400000000001</v>
+        <v>899.8</v>
       </c>
       <c r="G268" s="14" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>1037.23</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>1041.67</v>
+        <v>1041.33</v>
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>414.54</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>459.12</v>
+        <v>457.47</v>
       </c>
       <c r="G270" s="14" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>195.06</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>219.33</v>
+        <v>219.37</v>
       </c>
       <c r="G271" s="12" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>287.74</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>258.5</v>
+        <v>258.41</v>
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>3933.42</v>
       </c>
       <c r="F273" s="11" t="n">
-        <v>4759.04</v>
+        <v>4759.2</v>
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>579.75</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>694.61</v>
+        <v>693.64</v>
       </c>
       <c r="G274" s="12" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>4487.3</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>4223.81</v>
+        <v>4223.61</v>
       </c>
       <c r="G275" s="12" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>955.4</v>
       </c>
       <c r="F276" s="11" t="n">
-        <v>1036.97</v>
+        <v>1035.02</v>
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>661.48</v>
       </c>
       <c r="F277" s="11" t="n">
-        <v>667.13</v>
+        <v>666.97</v>
       </c>
       <c r="G277" s="14" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>1599.24</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>1704.16</v>
+        <v>1702.79</v>
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>1432.83</v>
       </c>
       <c r="F279" s="11" t="n">
-        <v>1183.15</v>
+        <v>1182.81</v>
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>126.81</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>165.13</v>
+        <v>165.11</v>
       </c>
       <c r="G280" s="14" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>386.32</v>
       </c>
       <c r="F281" s="11" t="n">
-        <v>404.49</v>
+        <v>404.08</v>
       </c>
       <c r="G281" s="14" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>1154.66</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>1160.33</v>
+        <v>1159.24</v>
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>777.59</v>
       </c>
       <c r="F283" s="11" t="n">
-        <v>1020.12</v>
+        <v>1019.89</v>
       </c>
       <c r="G283" s="14" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>885.47</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>950.3099999999999</v>
+        <v>950.16</v>
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>1392.09</v>
       </c>
       <c r="F285" s="11" t="n">
-        <v>1437.55</v>
+        <v>1437.48</v>
       </c>
       <c r="G285" s="12" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>320.94</v>
       </c>
       <c r="F286" s="11" t="n">
-        <v>388.1</v>
+        <v>388</v>
       </c>
       <c r="G286" s="14" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>1053.29</v>
       </c>
       <c r="F287" s="11" t="n">
-        <v>949.37</v>
+        <v>949.8099999999999</v>
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>117.31</v>
       </c>
       <c r="F288" s="11" t="n">
-        <v>136.13</v>
+        <v>136.11</v>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>523.24</v>
       </c>
       <c r="F289" s="11" t="n">
-        <v>540.37</v>
+        <v>540.25</v>
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>811.26</v>
       </c>
       <c r="F290" s="11" t="n">
-        <v>843.79</v>
+        <v>844.24</v>
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>6914.97</v>
       </c>
       <c r="F291" s="11" t="n">
-        <v>6476.03</v>
+        <v>6472.61</v>
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>1380.87</v>
       </c>
       <c r="F292" s="11" t="n">
-        <v>1318.44</v>
+        <v>1317.96</v>
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>877.6799999999999</v>
       </c>
       <c r="F293" s="11" t="n">
-        <v>1049.07</v>
+        <v>1051.19</v>
       </c>
       <c r="G293" s="12" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>3902.37</v>
       </c>
       <c r="F294" s="11" t="n">
-        <v>3833.69</v>
+        <v>3836.32</v>
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>277</v>
       </c>
       <c r="F295" s="11" t="n">
-        <v>259.22</v>
+        <v>259.25</v>
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>399.16</v>
       </c>
       <c r="F296" s="11" t="n">
-        <v>403.13</v>
+        <v>402.9</v>
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>4688.5</v>
       </c>
       <c r="F297" s="11" t="n">
-        <v>5206.97</v>
+        <v>5203.15</v>
       </c>
       <c r="G297" s="14" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>3479.71</v>
       </c>
       <c r="F298" s="11" t="n">
-        <v>3956.9</v>
+        <v>3962.49</v>
       </c>
       <c r="G298" s="14" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>2280.43</v>
       </c>
       <c r="F299" s="11" t="n">
-        <v>2143.59</v>
+        <v>2144.21</v>
       </c>
       <c r="G299" s="14" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>3237.75</v>
       </c>
       <c r="F300" s="11" t="n">
-        <v>3342.27</v>
+        <v>3339.53</v>
       </c>
       <c r="G300" s="14" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>321.92</v>
       </c>
       <c r="F301" s="11" t="n">
-        <v>319.51</v>
+        <v>319.45</v>
       </c>
       <c r="G301" s="14" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>68.76000000000001</v>
       </c>
       <c r="F302" s="11" t="n">
-        <v>61.43</v>
+        <v>61.4</v>
       </c>
       <c r="G302" s="12" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>587.87</v>
       </c>
       <c r="F303" s="11" t="n">
-        <v>589.72</v>
+        <v>589.28</v>
       </c>
       <c r="G303" s="12" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>275.07</v>
       </c>
       <c r="F304" s="11" t="n">
-        <v>272.03</v>
+        <v>272.49</v>
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>2122.98</v>
       </c>
       <c r="F305" s="11" t="n">
-        <v>2248.78</v>
+        <v>2251.19</v>
       </c>
       <c r="G305" s="12" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>421.89</v>
       </c>
       <c r="F306" s="11" t="n">
-        <v>576.4</v>
+        <v>576.38</v>
       </c>
       <c r="G306" s="12" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>1024.91</v>
       </c>
       <c r="F307" s="11" t="n">
-        <v>1392.38</v>
+        <v>1392.41</v>
       </c>
       <c r="G307" s="14" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>758.85</v>
       </c>
       <c r="F308" s="11" t="n">
-        <v>735.83</v>
+        <v>736.34</v>
       </c>
       <c r="G308" s="12" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>13717.03</v>
       </c>
       <c r="F309" s="11" t="n">
-        <v>14320.88</v>
+        <v>14322.79</v>
       </c>
       <c r="G309" s="14" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>1670.28</v>
       </c>
       <c r="F310" s="11" t="n">
-        <v>2001.41</v>
+        <v>2001.78</v>
       </c>
       <c r="G310" s="12" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>1003.57</v>
       </c>
       <c r="F311" s="11" t="n">
-        <v>1069.04</v>
+        <v>1068.02</v>
       </c>
       <c r="G311" s="12" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>2441.26</v>
       </c>
       <c r="F312" s="11" t="n">
-        <v>2543.4</v>
+        <v>2546.31</v>
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>2558.66</v>
       </c>
       <c r="F313" s="11" t="n">
-        <v>2112.44</v>
+        <v>2111.85</v>
       </c>
       <c r="G313" s="12" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>1082.81</v>
       </c>
       <c r="F314" s="11" t="n">
-        <v>1159.43</v>
+        <v>1159.15</v>
       </c>
       <c r="G314" s="12" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>463.31</v>
       </c>
       <c r="F315" s="11" t="n">
-        <v>471.77</v>
+        <v>471.79</v>
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>1650.29</v>
       </c>
       <c r="F316" s="11" t="n">
-        <v>1596.03</v>
+        <v>1597.13</v>
       </c>
       <c r="G316" s="14" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>1067.51</v>
       </c>
       <c r="F317" s="11" t="n">
-        <v>1156.44</v>
+        <v>1157.59</v>
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>532.05</v>
       </c>
       <c r="F318" s="11" t="n">
-        <v>547.91</v>
+        <v>547.6</v>
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>60.89</v>
       </c>
       <c r="F319" s="11" t="n">
-        <v>62.81</v>
+        <v>62.87</v>
       </c>
       <c r="G319" s="12" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>119.41</v>
       </c>
       <c r="F320" s="11" t="n">
-        <v>112.31</v>
+        <v>112.37</v>
       </c>
       <c r="G320" s="12" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>752.9299999999999</v>
       </c>
       <c r="F321" s="11" t="n">
-        <v>807.33</v>
+        <v>807.17</v>
       </c>
       <c r="G321" s="12" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>2345.69</v>
       </c>
       <c r="F322" s="11" t="n">
-        <v>2569.75</v>
+        <v>2569.57</v>
       </c>
       <c r="G322" s="14" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>136853.65</v>
       </c>
       <c r="F323" s="11" t="n">
-        <v>140878.65</v>
+        <v>140855.94</v>
       </c>
       <c r="G323" s="14" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>180.1</v>
       </c>
       <c r="F324" s="11" t="n">
-        <v>160.42</v>
+        <v>160.5</v>
       </c>
       <c r="G324" s="12" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>3453.33</v>
       </c>
       <c r="F326" s="11" t="n">
-        <v>3254.16</v>
+        <v>3252.86</v>
       </c>
       <c r="G326" s="12" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>913.63</v>
       </c>
       <c r="F327" s="11" t="n">
-        <v>851.5700000000001</v>
+        <v>851.66</v>
       </c>
       <c r="G327" s="12" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>1000.23</v>
       </c>
       <c r="F328" s="11" t="n">
-        <v>936.16</v>
+        <v>935.9</v>
       </c>
       <c r="G328" s="12" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>389.58</v>
       </c>
       <c r="F329" s="11" t="n">
-        <v>303.99</v>
+        <v>304.27</v>
       </c>
       <c r="G329" s="12" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>1056.4</v>
       </c>
       <c r="F330" s="11" t="n">
-        <v>1230.74</v>
+        <v>1231.78</v>
       </c>
       <c r="G330" s="14" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>596.4400000000001</v>
       </c>
       <c r="F331" s="11" t="n">
-        <v>570.2</v>
+        <v>569.89</v>
       </c>
       <c r="G331" s="12" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>6195.53</v>
       </c>
       <c r="F332" s="11" t="n">
-        <v>5637.75</v>
+        <v>5637.19</v>
       </c>
       <c r="G332" s="12" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>91.44</v>
       </c>
       <c r="F333" s="11" t="n">
-        <v>99.91</v>
+        <v>100.23</v>
       </c>
       <c r="G333" s="12" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>151.2</v>
       </c>
       <c r="F334" s="11" t="n">
-        <v>174.2</v>
+        <v>174.43</v>
       </c>
       <c r="G334" s="12" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>1267.08</v>
       </c>
       <c r="F335" s="11" t="n">
-        <v>1233.33</v>
+        <v>1234.36</v>
       </c>
       <c r="G335" s="12" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>3424.85</v>
       </c>
       <c r="F336" s="11" t="n">
-        <v>3085.88</v>
+        <v>3080.83</v>
       </c>
       <c r="G336" s="12" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>34.33</v>
       </c>
       <c r="F337" s="11" t="n">
-        <v>42.04</v>
+        <v>42.03</v>
       </c>
       <c r="G337" s="12" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>13734.77</v>
       </c>
       <c r="F338" s="11" t="n">
-        <v>14038.51</v>
+        <v>14038.16</v>
       </c>
       <c r="G338" s="12" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>502.22</v>
       </c>
       <c r="F339" s="11" t="n">
-        <v>750.58</v>
+        <v>748.72</v>
       </c>
       <c r="G339" s="14" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>1756.67</v>
       </c>
       <c r="F340" s="11" t="n">
-        <v>1771.42</v>
+        <v>1770.96</v>
       </c>
       <c r="G340" s="12" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>77.77</v>
       </c>
       <c r="F341" s="11" t="n">
-        <v>78.5</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="G341" s="12" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>147.4</v>
       </c>
       <c r="F342" s="11" t="n">
-        <v>161.08</v>
+        <v>161.15</v>
       </c>
       <c r="G342" s="12" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>74.92</v>
       </c>
       <c r="F343" s="11" t="n">
-        <v>77.09</v>
+        <v>77.06</v>
       </c>
       <c r="G343" s="12" t="inlineStr">
         <is>
@@ -15790,9 +15790,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I343" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I343" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J343" s="13" t="inlineStr">
@@ -15822,7 +15822,7 @@
         <v>271.51</v>
       </c>
       <c r="F344" s="11" t="n">
-        <v>253.6</v>
+        <v>253.73</v>
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>82.12</v>
       </c>
       <c r="F345" s="11" t="n">
-        <v>75.95</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="G345" s="12" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>376.62</v>
       </c>
       <c r="F347" s="11" t="n">
-        <v>349.81</v>
+        <v>349.84</v>
       </c>
       <c r="G347" s="12" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>98.88</v>
       </c>
       <c r="F348" s="11" t="n">
-        <v>98.56999999999999</v>
+        <v>98.48</v>
       </c>
       <c r="G348" s="12" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>1285.28</v>
       </c>
       <c r="F349" s="11" t="n">
-        <v>1303.2</v>
+        <v>1303.05</v>
       </c>
       <c r="G349" s="12" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>254.92</v>
       </c>
       <c r="F350" s="11" t="n">
-        <v>242.42</v>
+        <v>242.33</v>
       </c>
       <c r="G350" s="12" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>1582.73</v>
       </c>
       <c r="F351" s="11" t="n">
-        <v>1628.51</v>
+        <v>1629.55</v>
       </c>
       <c r="G351" s="12" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>7340.23</v>
       </c>
       <c r="F352" s="11" t="n">
-        <v>7813.53</v>
+        <v>7806.75</v>
       </c>
       <c r="G352" s="12" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>467.53</v>
       </c>
       <c r="F353" s="11" t="n">
-        <v>440.51</v>
+        <v>440.68</v>
       </c>
       <c r="G353" s="12" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>31.72</v>
       </c>
       <c r="F354" s="11" t="n">
-        <v>39.56</v>
+        <v>39.54</v>
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>1095.59</v>
       </c>
       <c r="F355" s="11" t="n">
-        <v>1199.99</v>
+        <v>1199.65</v>
       </c>
       <c r="G355" s="12" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>274</v>
       </c>
       <c r="F356" s="11" t="n">
-        <v>251.76</v>
+        <v>251.9</v>
       </c>
       <c r="G356" s="12" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>34611.63</v>
       </c>
       <c r="F357" s="11" t="n">
-        <v>37629.05</v>
+        <v>37635.81</v>
       </c>
       <c r="G357" s="12" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>485.47</v>
       </c>
       <c r="F358" s="11" t="n">
-        <v>536.33</v>
+        <v>536.3099999999999</v>
       </c>
       <c r="G358" s="14" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>1114.59</v>
       </c>
       <c r="F359" s="11" t="n">
-        <v>1130.95</v>
+        <v>1131.18</v>
       </c>
       <c r="G359" s="12" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>277.58</v>
       </c>
       <c r="F360" s="11" t="n">
-        <v>316.61</v>
+        <v>316.26</v>
       </c>
       <c r="G360" s="12" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>5241.18</v>
       </c>
       <c r="F362" s="11" t="n">
-        <v>5560.73</v>
+        <v>5555.95</v>
       </c>
       <c r="G362" s="14" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>275.94</v>
       </c>
       <c r="F363" s="11" t="n">
-        <v>281.94</v>
+        <v>281.76</v>
       </c>
       <c r="G363" s="12" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>418.95</v>
       </c>
       <c r="F364" s="11" t="n">
-        <v>394.19</v>
+        <v>394.11</v>
       </c>
       <c r="G364" s="12" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>4829.81</v>
       </c>
       <c r="F365" s="11" t="n">
-        <v>4914.96</v>
+        <v>4914.89</v>
       </c>
       <c r="G365" s="14" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>539.34</v>
       </c>
       <c r="F366" s="11" t="n">
-        <v>604.33</v>
+        <v>602.61</v>
       </c>
       <c r="G366" s="12" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>1688.16</v>
       </c>
       <c r="F367" s="11" t="n">
-        <v>1674.69</v>
+        <v>1674.04</v>
       </c>
       <c r="G367" s="12" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>1388.71</v>
       </c>
       <c r="F368" s="11" t="n">
-        <v>1441.43</v>
+        <v>1442.04</v>
       </c>
       <c r="G368" s="12" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>3016.77</v>
       </c>
       <c r="F369" s="11" t="n">
-        <v>3298.99</v>
+        <v>3302.05</v>
       </c>
       <c r="G369" s="12" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>862.8</v>
       </c>
       <c r="F371" s="11" t="n">
-        <v>883.41</v>
+        <v>883.77</v>
       </c>
       <c r="G371" s="12" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>202.01</v>
       </c>
       <c r="F372" s="11" t="n">
-        <v>242.11</v>
+        <v>242.3</v>
       </c>
       <c r="G372" s="12" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>1544.63</v>
       </c>
       <c r="F373" s="11" t="n">
-        <v>1657.7</v>
+        <v>1653.78</v>
       </c>
       <c r="G373" s="12" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>7620.03</v>
       </c>
       <c r="F374" s="11" t="n">
-        <v>7302.35</v>
+        <v>7307.32</v>
       </c>
       <c r="G374" s="12" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>1413.17</v>
       </c>
       <c r="F375" s="11" t="n">
-        <v>1716.36</v>
+        <v>1717.64</v>
       </c>
       <c r="G375" s="12" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>420.06</v>
       </c>
       <c r="F376" s="11" t="n">
-        <v>431.69</v>
+        <v>431.82</v>
       </c>
       <c r="G376" s="12" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>298.58</v>
       </c>
       <c r="F377" s="11" t="n">
-        <v>283.97</v>
+        <v>284.17</v>
       </c>
       <c r="G377" s="12" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>25628.94</v>
       </c>
       <c r="F378" s="11" t="n">
-        <v>21114.15</v>
+        <v>21108.09</v>
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>151.85</v>
       </c>
       <c r="F379" s="11" t="n">
-        <v>174.64</v>
+        <v>174.48</v>
       </c>
       <c r="G379" s="12" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>333.8</v>
       </c>
       <c r="F380" s="11" t="n">
-        <v>371.98</v>
+        <v>373.23</v>
       </c>
       <c r="G380" s="12" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>890.8099999999999</v>
       </c>
       <c r="F381" s="11" t="n">
-        <v>916.9400000000001</v>
+        <v>915.65</v>
       </c>
       <c r="G381" s="12" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>1354.01</v>
       </c>
       <c r="F382" s="11" t="n">
-        <v>1476.92</v>
+        <v>1477.89</v>
       </c>
       <c r="G382" s="12" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>16628.73</v>
       </c>
       <c r="F383" s="11" t="n">
-        <v>16616.09</v>
+        <v>16587.86</v>
       </c>
       <c r="G383" s="12" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>983.86</v>
       </c>
       <c r="F384" s="11" t="n">
-        <v>1026.54</v>
+        <v>1027.38</v>
       </c>
       <c r="G384" s="12" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>2878.22</v>
       </c>
       <c r="F385" s="11" t="n">
-        <v>2846.98</v>
+        <v>2850.68</v>
       </c>
       <c r="G385" s="12" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>304.3</v>
       </c>
       <c r="F386" s="11" t="n">
-        <v>334.97</v>
+        <v>335.04</v>
       </c>
       <c r="G386" s="12" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>1217.58</v>
       </c>
       <c r="F387" s="11" t="n">
-        <v>1298.69</v>
+        <v>1298.24</v>
       </c>
       <c r="G387" s="12" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>1009.24</v>
       </c>
       <c r="F388" s="11" t="n">
-        <v>1027.95</v>
+        <v>1027.78</v>
       </c>
       <c r="G388" s="14" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>396.54</v>
       </c>
       <c r="F389" s="11" t="n">
-        <v>560.1900000000001</v>
+        <v>560.64</v>
       </c>
       <c r="G389" s="12" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>841.64</v>
       </c>
       <c r="F390" s="11" t="n">
-        <v>1031.53</v>
+        <v>1032.06</v>
       </c>
       <c r="G390" s="14" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>310.19</v>
       </c>
       <c r="F391" s="11" t="n">
-        <v>286.62</v>
+        <v>286.48</v>
       </c>
       <c r="G391" s="12" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>125.68</v>
       </c>
       <c r="F392" s="11" t="n">
-        <v>136.07</v>
+        <v>136.28</v>
       </c>
       <c r="G392" s="12" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>348.94</v>
       </c>
       <c r="F393" s="11" t="n">
-        <v>359.69</v>
+        <v>359.58</v>
       </c>
       <c r="G393" s="12" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>232.91</v>
       </c>
       <c r="F394" s="11" t="n">
-        <v>252.28</v>
+        <v>251.97</v>
       </c>
       <c r="G394" s="14" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>1382.52</v>
       </c>
       <c r="F395" s="11" t="n">
-        <v>1412.67</v>
+        <v>1414.23</v>
       </c>
       <c r="G395" s="14" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>26.34</v>
       </c>
       <c r="F396" s="11" t="n">
-        <v>27.76</v>
+        <v>27.74</v>
       </c>
       <c r="G396" s="12" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>399.94</v>
       </c>
       <c r="F397" s="11" t="n">
-        <v>436.56</v>
+        <v>436.81</v>
       </c>
       <c r="G397" s="12" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>209.15</v>
       </c>
       <c r="F398" s="11" t="n">
-        <v>227.6</v>
+        <v>227.75</v>
       </c>
       <c r="G398" s="12" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>532.28</v>
       </c>
       <c r="F399" s="11" t="n">
-        <v>571.46</v>
+        <v>571.2</v>
       </c>
       <c r="G399" s="12" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>509.55</v>
       </c>
       <c r="F400" s="11" t="n">
-        <v>680.59</v>
+        <v>680.6799999999999</v>
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>26.43</v>
       </c>
       <c r="F401" s="11" t="n">
-        <v>34.86</v>
+        <v>34.89</v>
       </c>
       <c r="G401" s="12" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>1414.26</v>
       </c>
       <c r="F402" s="11" t="n">
-        <v>1369.01</v>
+        <v>1367.97</v>
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>32.17</v>
       </c>
       <c r="F403" s="11" t="n">
-        <v>40.78</v>
+        <v>40.79</v>
       </c>
       <c r="G403" s="12" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>290.87</v>
       </c>
       <c r="F404" s="11" t="n">
-        <v>322.64</v>
+        <v>323.3</v>
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>42.71</v>
       </c>
       <c r="F405" s="11" t="n">
-        <v>45.43</v>
+        <v>45.42</v>
       </c>
       <c r="G405" s="14" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>159.97</v>
       </c>
       <c r="F406" s="11" t="n">
-        <v>143.32</v>
+        <v>143.38</v>
       </c>
       <c r="G406" s="12" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>968.15</v>
       </c>
       <c r="F407" s="11" t="n">
-        <v>894.23</v>
+        <v>894.21</v>
       </c>
       <c r="G407" s="12" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>147.49</v>
       </c>
       <c r="F408" s="11" t="n">
-        <v>145.93</v>
+        <v>146.11</v>
       </c>
       <c r="G408" s="14" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>181.37</v>
       </c>
       <c r="F409" s="11" t="n">
-        <v>237.11</v>
+        <v>236.88</v>
       </c>
       <c r="G409" s="14" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>338.78</v>
       </c>
       <c r="F411" s="11" t="n">
-        <v>391.84</v>
+        <v>392.13</v>
       </c>
       <c r="G411" s="12" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>92.95999999999999</v>
       </c>
       <c r="F412" s="11" t="n">
-        <v>98.62</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="G412" s="12" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>709.97</v>
       </c>
       <c r="F413" s="11" t="n">
-        <v>792.64</v>
+        <v>792.12</v>
       </c>
       <c r="G413" s="14" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>1926.34</v>
       </c>
       <c r="F414" s="11" t="n">
-        <v>1898.24</v>
+        <v>1899.41</v>
       </c>
       <c r="G414" s="14" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>1077.5</v>
       </c>
       <c r="F415" s="11" t="n">
-        <v>982.6900000000001</v>
+        <v>982.6</v>
       </c>
       <c r="G415" s="12" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>3954.51</v>
       </c>
       <c r="F416" s="11" t="n">
-        <v>3863.01</v>
+        <v>3860.65</v>
       </c>
       <c r="G416" s="12" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>925.8</v>
       </c>
       <c r="F417" s="11" t="n">
-        <v>823.3200000000001</v>
+        <v>822.6799999999999</v>
       </c>
       <c r="G417" s="12" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>251.92</v>
       </c>
       <c r="F418" s="11" t="n">
-        <v>228.55</v>
+        <v>228.71</v>
       </c>
       <c r="G418" s="12" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>24972.4</v>
       </c>
       <c r="F419" s="11" t="n">
-        <v>26720.92</v>
+        <v>26716.49</v>
       </c>
       <c r="G419" s="12" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>993.22</v>
       </c>
       <c r="F420" s="11" t="n">
-        <v>865.34</v>
+        <v>864.47</v>
       </c>
       <c r="G420" s="12" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>822.92</v>
       </c>
       <c r="F421" s="11" t="n">
-        <v>841.13</v>
+        <v>841.36</v>
       </c>
       <c r="G421" s="14" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>3316.04</v>
       </c>
       <c r="F422" s="11" t="n">
-        <v>3205.69</v>
+        <v>3210.17</v>
       </c>
       <c r="G422" s="12" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>855.6799999999999</v>
       </c>
       <c r="F423" s="11" t="n">
-        <v>996.59</v>
+        <v>996.34</v>
       </c>
       <c r="G423" s="12" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>72.93000000000001</v>
       </c>
       <c r="F424" s="11" t="n">
-        <v>79.47</v>
+        <v>79.62</v>
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>1676.35</v>
       </c>
       <c r="F425" s="11" t="n">
-        <v>2507.63</v>
+        <v>2507.94</v>
       </c>
       <c r="G425" s="12" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>1346.45</v>
       </c>
       <c r="F426" s="11" t="n">
-        <v>1421.09</v>
+        <v>1421.43</v>
       </c>
       <c r="G426" s="12" t="inlineStr">
         <is>
@@ -19471,10 +19471,10 @@
         <v>14422.26</v>
       </c>
       <c r="E427" s="11" t="n">
-        <v>13923.87</v>
+        <v>13923.88</v>
       </c>
       <c r="F427" s="11" t="n">
-        <v>13467.24</v>
+        <v>13470.69</v>
       </c>
       <c r="G427" s="12" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>528.84</v>
       </c>
       <c r="F428" s="11" t="n">
-        <v>500.65</v>
+        <v>500.3</v>
       </c>
       <c r="G428" s="12" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>264.07</v>
       </c>
       <c r="F429" s="11" t="n">
-        <v>329</v>
+        <v>328.37</v>
       </c>
       <c r="G429" s="12" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>2573.43</v>
       </c>
       <c r="F430" s="11" t="n">
-        <v>2779.27</v>
+        <v>2780.26</v>
       </c>
       <c r="G430" s="12" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>473.26</v>
       </c>
       <c r="F431" s="11" t="n">
-        <v>460.25</v>
+        <v>460.07</v>
       </c>
       <c r="G431" s="12" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>414.15</v>
       </c>
       <c r="F432" s="11" t="n">
-        <v>457.89</v>
+        <v>458.4</v>
       </c>
       <c r="G432" s="12" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>4972.02</v>
       </c>
       <c r="F433" s="11" t="n">
-        <v>4914.65</v>
+        <v>4917.84</v>
       </c>
       <c r="G433" s="14" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>836</v>
       </c>
       <c r="F434" s="11" t="n">
-        <v>915.79</v>
+        <v>915.8200000000001</v>
       </c>
       <c r="G434" s="14" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>1715.43</v>
       </c>
       <c r="F435" s="11" t="n">
-        <v>1706.09</v>
+        <v>1707.09</v>
       </c>
       <c r="G435" s="14" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>597.99</v>
       </c>
       <c r="F436" s="11" t="n">
-        <v>580.4</v>
+        <v>580.25</v>
       </c>
       <c r="G436" s="14" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>3758.3</v>
       </c>
       <c r="F437" s="11" t="n">
-        <v>3823.67</v>
+        <v>3818.72</v>
       </c>
       <c r="G437" s="14" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>295.89</v>
       </c>
       <c r="F440" s="11" t="n">
-        <v>351.56</v>
+        <v>351.13</v>
       </c>
       <c r="G440" s="12" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>189.3</v>
       </c>
       <c r="F441" s="11" t="n">
-        <v>228.22</v>
+        <v>226.22</v>
       </c>
       <c r="G441" s="12" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>439.52</v>
       </c>
       <c r="F442" s="11" t="n">
-        <v>556.34</v>
+        <v>556.46</v>
       </c>
       <c r="G442" s="12" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>842.84</v>
       </c>
       <c r="F443" s="11" t="n">
-        <v>759.61</v>
+        <v>759.27</v>
       </c>
       <c r="G443" s="12" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>462.78</v>
       </c>
       <c r="F444" s="11" t="n">
-        <v>527.5700000000001</v>
+        <v>527.65</v>
       </c>
       <c r="G444" s="12" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>292.82</v>
       </c>
       <c r="F445" s="11" t="n">
-        <v>352.07</v>
+        <v>351.98</v>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>688.3099999999999</v>
       </c>
       <c r="F446" s="11" t="n">
-        <v>779.9299999999999</v>
+        <v>780.05</v>
       </c>
       <c r="G446" s="12" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>1525.84</v>
       </c>
       <c r="F447" s="11" t="n">
-        <v>1634.86</v>
+        <v>1634.47</v>
       </c>
       <c r="G447" s="12" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>1110.91</v>
       </c>
       <c r="F448" s="11" t="n">
-        <v>1113.97</v>
+        <v>1114.7</v>
       </c>
       <c r="G448" s="12" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>4532.74</v>
       </c>
       <c r="F449" s="11" t="n">
-        <v>5128.39</v>
+        <v>5129.6</v>
       </c>
       <c r="G449" s="14" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>655.92</v>
       </c>
       <c r="F450" s="11" t="n">
-        <v>679.8200000000001</v>
+        <v>680.13</v>
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>397.29</v>
       </c>
       <c r="F452" s="11" t="n">
-        <v>386.03</v>
+        <v>386.24</v>
       </c>
       <c r="G452" s="12" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>200.15</v>
       </c>
       <c r="F453" s="11" t="n">
-        <v>180.84</v>
+        <v>180.94</v>
       </c>
       <c r="G453" s="12" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>575.9</v>
       </c>
       <c r="F454" s="11" t="n">
-        <v>639.5599999999999</v>
+        <v>639.62</v>
       </c>
       <c r="G454" s="12" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>1251.46</v>
       </c>
       <c r="F455" s="11" t="n">
-        <v>1405.28</v>
+        <v>1403.99</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>2602.95</v>
       </c>
       <c r="F456" s="11" t="n">
-        <v>2945.02</v>
+        <v>2944.76</v>
       </c>
       <c r="G456" s="14" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>1454.5</v>
       </c>
       <c r="F457" s="11" t="n">
-        <v>1501.82</v>
+        <v>1500.65</v>
       </c>
       <c r="G457" s="14" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>1123.69</v>
       </c>
       <c r="F458" s="11" t="n">
-        <v>1177.8</v>
+        <v>1176.59</v>
       </c>
       <c r="G458" s="12" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>416.43</v>
       </c>
       <c r="F459" s="11" t="n">
-        <v>507.8</v>
+        <v>508.19</v>
       </c>
       <c r="G459" s="14" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>3442.42</v>
       </c>
       <c r="F460" s="11" t="n">
-        <v>3274.47</v>
+        <v>3270.9</v>
       </c>
       <c r="G460" s="12" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>2673.63</v>
       </c>
       <c r="F461" s="11" t="n">
-        <v>2760.37</v>
+        <v>2764.15</v>
       </c>
       <c r="G461" s="12" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>3344.89</v>
       </c>
       <c r="F462" s="11" t="n">
-        <v>3146.05</v>
+        <v>3144.35</v>
       </c>
       <c r="G462" s="12" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>707.84</v>
       </c>
       <c r="F463" s="11" t="n">
-        <v>793.75</v>
+        <v>795.01</v>
       </c>
       <c r="G463" s="12" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>4247.22</v>
       </c>
       <c r="F464" s="11" t="n">
-        <v>3927.46</v>
+        <v>3929.23</v>
       </c>
       <c r="G464" s="12" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>4149.93</v>
       </c>
       <c r="F465" s="11" t="n">
-        <v>3843.1</v>
+        <v>3842.94</v>
       </c>
       <c r="G465" s="14" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>1472.36</v>
       </c>
       <c r="F466" s="11" t="n">
-        <v>1389.18</v>
+        <v>1388.51</v>
       </c>
       <c r="G466" s="12" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>3917.45</v>
       </c>
       <c r="F467" s="11" t="n">
-        <v>4402.16</v>
+        <v>4402.38</v>
       </c>
       <c r="G467" s="12" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>25.2</v>
       </c>
       <c r="F468" s="11" t="n">
-        <v>26.91</v>
+        <v>26.92</v>
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>493.23</v>
       </c>
       <c r="F469" s="11" t="n">
-        <v>521.41</v>
+        <v>520.62</v>
       </c>
       <c r="G469" s="12" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>382.32</v>
       </c>
       <c r="F470" s="11" t="n">
-        <v>372.64</v>
+        <v>372.33</v>
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>41.53</v>
       </c>
       <c r="F471" s="11" t="n">
-        <v>49.53</v>
+        <v>49.52</v>
       </c>
       <c r="G471" s="12" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>3631.38</v>
       </c>
       <c r="F472" s="11" t="n">
-        <v>3426.96</v>
+        <v>3427.97</v>
       </c>
       <c r="G472" s="14" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>1546.73</v>
       </c>
       <c r="F473" s="11" t="n">
-        <v>1684.24</v>
+        <v>1685.18</v>
       </c>
       <c r="G473" s="14" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>11739.13</v>
       </c>
       <c r="F475" s="11" t="n">
-        <v>11859.96</v>
+        <v>11857.51</v>
       </c>
       <c r="G475" s="12" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>180.57</v>
       </c>
       <c r="F476" s="11" t="n">
-        <v>160.35</v>
+        <v>160.3</v>
       </c>
       <c r="G476" s="14" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>1323.79</v>
       </c>
       <c r="F477" s="11" t="n">
-        <v>1361.5</v>
+        <v>1362.08</v>
       </c>
       <c r="G477" s="12" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>1117.21</v>
       </c>
       <c r="F478" s="11" t="n">
-        <v>1155.34</v>
+        <v>1154.71</v>
       </c>
       <c r="G478" s="12" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>654.16</v>
       </c>
       <c r="F479" s="11" t="n">
-        <v>680.78</v>
+        <v>681.01</v>
       </c>
       <c r="G479" s="14" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>424</v>
       </c>
       <c r="F480" s="11" t="n">
-        <v>410.88</v>
+        <v>410.55</v>
       </c>
       <c r="G480" s="12" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>1001.8</v>
       </c>
       <c r="F481" s="11" t="n">
-        <v>1103.46</v>
+        <v>1102.33</v>
       </c>
       <c r="G481" s="14" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>442.79</v>
       </c>
       <c r="F482" s="11" t="n">
-        <v>465.75</v>
+        <v>464.95</v>
       </c>
       <c r="G482" s="12" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>698.8</v>
       </c>
       <c r="F483" s="11" t="n">
-        <v>584.41</v>
+        <v>584.58</v>
       </c>
       <c r="G483" s="14" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>324.52</v>
       </c>
       <c r="F484" s="11" t="n">
-        <v>340.9</v>
+        <v>340.55</v>
       </c>
       <c r="G484" s="12" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>975.3099999999999</v>
       </c>
       <c r="F485" s="11" t="n">
-        <v>998.35</v>
+        <v>996.2</v>
       </c>
       <c r="G485" s="12" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>116.7</v>
       </c>
       <c r="F486" s="11" t="n">
-        <v>124.97</v>
+        <v>124.99</v>
       </c>
       <c r="G486" s="12" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>1395.31</v>
       </c>
       <c r="F487" s="11" t="n">
-        <v>1395.82</v>
+        <v>1396.23</v>
       </c>
       <c r="G487" s="12" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>530.55</v>
       </c>
       <c r="F488" s="11" t="n">
-        <v>479.37</v>
+        <v>479.72</v>
       </c>
       <c r="G488" s="12" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>3108.37</v>
       </c>
       <c r="F489" s="11" t="n">
-        <v>3009.19</v>
+        <v>3007.3</v>
       </c>
       <c r="G489" s="12" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>913.53</v>
       </c>
       <c r="F490" s="11" t="n">
-        <v>851.33</v>
+        <v>851.89</v>
       </c>
       <c r="G490" s="12" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>124.08</v>
       </c>
       <c r="F491" s="11" t="n">
-        <v>128.16</v>
+        <v>128.25</v>
       </c>
       <c r="G491" s="12" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>475.72</v>
       </c>
       <c r="F492" s="11" t="n">
-        <v>562.95</v>
+        <v>562.35</v>
       </c>
       <c r="G492" s="14" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>872.6900000000001</v>
       </c>
       <c r="F493" s="11" t="n">
-        <v>1035.31</v>
+        <v>1035.52</v>
       </c>
       <c r="G493" s="12" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>206.93</v>
       </c>
       <c r="F494" s="11" t="n">
-        <v>229.82</v>
+        <v>229.57</v>
       </c>
       <c r="G494" s="14" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>1331.33</v>
       </c>
       <c r="F495" s="11" t="n">
-        <v>1380.69</v>
+        <v>1382.28</v>
       </c>
       <c r="G495" s="12" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>82.77</v>
       </c>
       <c r="F497" s="11" t="n">
-        <v>95.67</v>
+        <v>95.61</v>
       </c>
       <c r="G497" s="12" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>581.35</v>
       </c>
       <c r="F498" s="11" t="n">
-        <v>673.75</v>
+        <v>673.41</v>
       </c>
       <c r="G498" s="14" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>1464.47</v>
       </c>
       <c r="F499" s="11" t="n">
-        <v>1482.72</v>
+        <v>1480.68</v>
       </c>
       <c r="G499" s="12" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>14416.6</v>
       </c>
       <c r="F500" s="11" t="n">
-        <v>13906.2</v>
+        <v>13895.53</v>
       </c>
       <c r="G500" s="12" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>909.16</v>
       </c>
       <c r="F501" s="11" t="n">
-        <v>927.27</v>
+        <v>927.55</v>
       </c>
       <c r="G501" s="12" t="inlineStr">
         <is>
@@ -22742,9 +22742,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I501" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I501" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J501" s="13" t="inlineStr">

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 27-Apr-2026  17:57:02    |    Closing Price Date: 27-Apr-2026</t>
+          <t>Scan Run: 28-Apr-2026  19:16:13    |    Closing Price Date: 27-Apr-2026</t>
         </is>
       </c>
     </row>
@@ -598,20 +598,20 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>84.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>75.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>500</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>27-Apr-2026  17:57:02</t>
+          <t>28-Apr-2026  19:16:13</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONG BULLISH — 84.6% stocks above EMA (market broadly trending up)</t>
+          <t>Short-Term  (20 EMA): STRONG BULLISH — 84.4% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONG BULLISH — 75.4% stocks above EMA (market broadly trending up)</t>
+          <t>Medium-Term (50 EMA): STRONG BULLISH — 75.2% stocks above EMA (market broadly trending up)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 49.8% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 423 of 500 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 422 of 500 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 377 of 500 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 376 of 500 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 249 of 500 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 250 of 500 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1638</v>
+        <v>1608.2</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1598.09</v>
+        <v>1599.05</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1550.17</v>
+        <v>1552.45</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1439.05</v>
+        <v>1440.73</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1435.8</v>
+        <v>1435.45</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>1205.85</v>
+        <v>1227.72</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>1097.12</v>
+        <v>1110.38</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>975.37</v>
+        <v>979.95</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>722.45</v>
+        <v>711.45</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>671.75</v>
+        <v>675.53</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>665.72</v>
+        <v>667.51</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>712.9299999999999</v>
+        <v>712.92</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1666,9 +1666,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>487.85</v>
+        <v>488.6</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>466.34</v>
+        <v>468.46</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>478.07</v>
+        <v>478.49</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>508.99</v>
+        <v>508.79</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>531.3</v>
+        <v>533.2</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>516.71</v>
+        <v>518.28</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>495.09</v>
+        <v>496.58</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>485.06</v>
+        <v>485.54</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,24 +1949,24 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1044.95</v>
+        <v>1007.65</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1032.35</v>
+        <v>1030</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>987.33</v>
+        <v>988.13</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>962.95</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>963.4</v>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>878.1</v>
+        <v>897.85</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>800.89</v>
+        <v>810.12</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>803.97</v>
+        <v>807.66</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>893.98</v>
+        <v>894.02</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2634,9 +2634,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J44" s="13" t="inlineStr">
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>432.1</v>
+        <v>493.3</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>352.21</v>
+        <v>365.65</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>353.12</v>
+        <v>358.62</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>579.41</v>
+        <v>578.55</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>255.49</v>
+        <v>253.07</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>248.58</v>
+        <v>249</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>251.41</v>
+        <v>251.47</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>270.62</v>
+        <v>270.45</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>809.6</v>
+        <v>800.35</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>753.29</v>
+        <v>757.77</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>737.73</v>
+        <v>740.1799999999999</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>746.67</v>
+        <v>747.2</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -10397,20 +10397,20 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>355.85</v>
+        <v>357.3</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>346.27</v>
+        <v>347.32</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>336.1</v>
+        <v>336.93</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>345.72</v>
+        <v>345.84</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -11761,20 +11761,20 @@
       </c>
       <c r="B252" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C252" s="11" t="n">
-        <v>253.64</v>
+        <v>250.81</v>
       </c>
       <c r="D252" s="11" t="n">
-        <v>241.68</v>
+        <v>242.55</v>
       </c>
       <c r="E252" s="11" t="n">
-        <v>247.32</v>
+        <v>247.45</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>272.37</v>
+        <v>272.15</v>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
@@ -12113,20 +12113,20 @@
       </c>
       <c r="B260" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C260" s="11" t="n">
-        <v>284.51</v>
+        <v>284.94</v>
       </c>
       <c r="D260" s="11" t="n">
-        <v>267.31</v>
+        <v>268.99</v>
       </c>
       <c r="E260" s="11" t="n">
-        <v>263.02</v>
+        <v>263.88</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>276.1</v>
+        <v>276.18</v>
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
@@ -13081,20 +13081,20 @@
       </c>
       <c r="B282" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C282" s="11" t="n">
-        <v>1261.6</v>
+        <v>1254.2</v>
       </c>
       <c r="D282" s="11" t="n">
-        <v>1192.44</v>
+        <v>1198.32</v>
       </c>
       <c r="E282" s="11" t="n">
-        <v>1158.86</v>
+        <v>1162.59</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>1160.76</v>
+        <v>1161.69</v>
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
@@ -13697,20 +13697,20 @@
       </c>
       <c r="B296" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C296" s="11" t="n">
-        <v>428.8</v>
+        <v>425</v>
       </c>
       <c r="D296" s="11" t="n">
-        <v>408.99</v>
+        <v>410.51</v>
       </c>
       <c r="E296" s="11" t="n">
-        <v>400.32</v>
+        <v>401.29</v>
       </c>
       <c r="F296" s="11" t="n">
-        <v>403.29</v>
+        <v>403.5</v>
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
@@ -13741,20 +13741,20 @@
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>24-Apr-2026</t>
+          <t>27-Apr-2026</t>
         </is>
       </c>
       <c r="C297" s="11" t="n">
-        <v>4282.3</v>
+        <v>4346</v>
       </c>
       <c r="D297" s="11" t="n">
-        <v>4506.94</v>
+        <v>4491.61</v>
       </c>
       <c r="E297" s="11" t="n">
-        <v>4688.5</v>
+        <v>4675.07</v>
       </c>
       <c r="F297" s="11" t="n">
-        <v>5200.31</v>
+        <v>5191.81</v>
       </c>
       <c r="G297" s="14" t="inlineStr">
         <is>
@@ -16029,20 +16029,20 @@
       </c>
       <c r="B349" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C349" s="11" t="n">
-        <v>1359.6</v>
+        <v>1378.3</v>
       </c>
       <c r="D349" s="11" t="n">
-        <v>1308.64</v>
+        <v>1315.27</v>
       </c>
       <c r="E349" s="11" t="n">
-        <v>1288.19</v>
+        <v>1291.73</v>
       </c>
       <c r="F349" s="11" t="n">
-        <v>1304.56</v>
+        <v>1305.3</v>
       </c>
       <c r="G349" s="12" t="inlineStr">
         <is>
@@ -16557,20 +16557,20 @@
       </c>
       <c r="B361" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C361" s="11" t="n">
-        <v>1843.1</v>
+        <v>2008.8</v>
       </c>
       <c r="D361" s="11" t="n">
-        <v>1774.54</v>
+        <v>1796.85</v>
       </c>
       <c r="E361" s="11" t="n">
-        <v>1760.42</v>
+        <v>1770.16</v>
       </c>
       <c r="F361" s="11" t="n">
-        <v>1597.45</v>
+        <v>1601.54</v>
       </c>
       <c r="G361" s="12" t="inlineStr">
         <is>
@@ -17569,20 +17569,20 @@
       </c>
       <c r="B384" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C384" s="11" t="n">
-        <v>1018.9</v>
+        <v>1051.75</v>
       </c>
       <c r="D384" s="11" t="n">
-        <v>972.83</v>
+        <v>980.34</v>
       </c>
       <c r="E384" s="11" t="n">
-        <v>985.24</v>
+        <v>987.84</v>
       </c>
       <c r="F384" s="11" t="n">
-        <v>1026.87</v>
+        <v>1027.11</v>
       </c>
       <c r="G384" s="12" t="inlineStr">
         <is>
@@ -17594,9 +17594,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I384" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I384" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J384" s="13" t="inlineStr">
@@ -17833,20 +17833,20 @@
       </c>
       <c r="B390" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C390" s="11" t="n">
-        <v>812</v>
+        <v>810.45</v>
       </c>
       <c r="D390" s="11" t="n">
-        <v>801.46</v>
+        <v>802.3099999999999</v>
       </c>
       <c r="E390" s="11" t="n">
-        <v>840.48</v>
+        <v>839.3</v>
       </c>
       <c r="F390" s="11" t="n">
-        <v>1032.98</v>
+        <v>1030.77</v>
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
@@ -18361,20 +18361,20 @@
       </c>
       <c r="B402" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C402" s="11" t="n">
-        <v>1508.5</v>
+        <v>1609</v>
       </c>
       <c r="D402" s="11" t="n">
-        <v>1424.91</v>
+        <v>1442.44</v>
       </c>
       <c r="E402" s="11" t="n">
-        <v>1417.96</v>
+        <v>1425.45</v>
       </c>
       <c r="F402" s="11" t="n">
-        <v>1368.78</v>
+        <v>1371.17</v>
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
@@ -18801,20 +18801,20 @@
       </c>
       <c r="B412" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C412" s="11" t="n">
-        <v>94.93000000000001</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="D412" s="11" t="n">
-        <v>93.03</v>
+        <v>93.17</v>
       </c>
       <c r="E412" s="11" t="n">
-        <v>93.04000000000001</v>
+        <v>93.09</v>
       </c>
       <c r="F412" s="11" t="n">
-        <v>98.8</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="G412" s="12" t="inlineStr">
         <is>
@@ -19989,20 +19989,20 @@
       </c>
       <c r="B439" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C439" s="11" t="n">
-        <v>1858.2</v>
+        <v>1878.2</v>
       </c>
       <c r="D439" s="11" t="n">
-        <v>1848.3</v>
+        <v>1851.15</v>
       </c>
       <c r="E439" s="11" t="n">
-        <v>1700.48</v>
+        <v>1707.45</v>
       </c>
       <c r="F439" s="11" t="n">
-        <v>884.73</v>
+        <v>894.62</v>
       </c>
       <c r="G439" s="12" t="inlineStr">
         <is>
@@ -20253,20 +20253,20 @@
       </c>
       <c r="B445" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C445" s="11" t="n">
-        <v>342.65</v>
+        <v>337.8</v>
       </c>
       <c r="D445" s="11" t="n">
-        <v>305.67</v>
+        <v>308.73</v>
       </c>
       <c r="E445" s="11" t="n">
-        <v>294.77</v>
+        <v>296.46</v>
       </c>
       <c r="F445" s="11" t="n">
-        <v>352.98</v>
+        <v>352.83</v>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
@@ -20517,20 +20517,20 @@
       </c>
       <c r="B451" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C451" s="11" t="n">
-        <v>354.35</v>
+        <v>350.8</v>
       </c>
       <c r="D451" s="11" t="n">
-        <v>343.58</v>
+        <v>344.26</v>
       </c>
       <c r="E451" s="11" t="n">
-        <v>344.01</v>
+        <v>344.27</v>
       </c>
       <c r="F451" s="11" t="n">
-        <v>364.37</v>
+        <v>364.23</v>
       </c>
       <c r="G451" s="12" t="inlineStr">
         <is>
@@ -20649,29 +20649,29 @@
       </c>
       <c r="B454" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C454" s="11" t="n">
-        <v>592.8</v>
+        <v>569.8</v>
       </c>
       <c r="D454" s="11" t="n">
-        <v>567.6900000000001</v>
+        <v>567.89</v>
       </c>
       <c r="E454" s="11" t="n">
-        <v>576.5599999999999</v>
+        <v>576.3</v>
       </c>
       <c r="F454" s="11" t="n">
-        <v>639.36</v>
+        <v>638.66</v>
       </c>
       <c r="G454" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H454" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H454" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I454" s="14" t="inlineStr">
@@ -21661,20 +21661,20 @@
       </c>
       <c r="B477" s="11" t="inlineStr">
         <is>
-          <t>27-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="C477" s="11" t="n">
-        <v>1391.6</v>
+        <v>1374.4</v>
       </c>
       <c r="D477" s="11" t="n">
-        <v>1320.61</v>
+        <v>1325.73</v>
       </c>
       <c r="E477" s="11" t="n">
-        <v>1326.45</v>
+        <v>1328.33</v>
       </c>
       <c r="F477" s="11" t="n">
-        <v>1363.7</v>
+        <v>1363.8</v>
       </c>
       <c r="G477" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 27-May-2026  14:28:44    |    Closing Price Date: 27-May-2026</t>
+          <t>Scan Run: 28-May-2026  14:38:50    |    Closing Price Date: 27-May-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>64.59999999999999</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>55</v>
+        <v>54.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>500</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>27-May-2026  14:28:44</t>
+          <t>28-May-2026  14:38:50</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 55.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 54.8% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 275 of 500 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 274 of 500 stocks</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
         <v>1637.17</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1473.65</v>
+        <v>1474.77</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1076.49</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1070.89</v>
+        <v>1070.38</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>32513.97</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>32382.76</v>
+        <v>32371.71</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>479.68</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>476.57</v>
+        <v>476.51</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>460.98</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>425.03</v>
+        <v>424.66</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>1343.34</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1453.41</v>
+        <v>1453.16</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>6612.03</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5907.52</v>
+        <v>5903.21</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>26784.43</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>27972.83</v>
+        <v>28005.43</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>345.54</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>318.33</v>
+        <v>318.34</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>524.48</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>507.07</v>
+        <v>506.72</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>64.2</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>84.48999999999999</v>
+        <v>84.27</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1341.37</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1538.01</v>
+        <v>1536.02</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>999.26</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>879.28</v>
+        <v>879.02</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>1421.87</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1620.11</v>
+        <v>1618.76</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>885.85</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>952.92</v>
+        <v>950.91</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>279.97</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>256.06</v>
+        <v>256.23</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>1259.51</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1049.35</v>
+        <v>1048.26</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>2420.31</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2300.48</v>
+        <v>2300.33</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>1213.7</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>1051.29</v>
+        <v>1051.61</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>1641.65</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1488.44</v>
+        <v>1488.54</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>201.79</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>160.71</v>
+        <v>160.66</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>688.17</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>706.99</v>
+        <v>705.92</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>320</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>358.59</v>
+        <v>358.77</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1464.69</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1594.02</v>
+        <v>1591.21</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>3902.99</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3700.13</v>
+        <v>3697.43</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>487.35</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>503.96</v>
+        <v>503.32</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>2974.01</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2788.2</v>
+        <v>2792.38</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>5460.51</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5401.18</v>
+        <v>5398.03</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
         <v>7701.87</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>7589.88</v>
+        <v>7589.87</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7216.8</v>
+        <v>7205.19</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>450.52</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>499.28</v>
+        <v>499.21</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>3448.27</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3034.18</v>
+        <v>3036.51</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>502.14</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>528.64</v>
+        <v>528.27</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>298.63</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>264.71</v>
+        <v>264.72</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>1326.29</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1213.89</v>
+        <v>1213.53</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>11672.8</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>9718.309999999999</v>
+        <v>9704.76</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>1951.45</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1881.39</v>
+        <v>1881.01</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         <v>8067.18</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>7830.52</v>
+        <v>7830.53</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>7468.04</v>
+        <v>7471.38</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>414.6</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>450.12</v>
+        <v>449.94</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>252.15</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>268.43</v>
+        <v>268.6</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>835.52</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>881.12</v>
+        <v>880.38</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>854.95</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>870.39</v>
+        <v>871.17</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>166.68</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>161.08</v>
+        <v>161.05</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>2498.6</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2483.13</v>
+        <v>2482.55</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>706.39</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>639.13</v>
+        <v>639.0599999999999</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>1557.69</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1510.46</v>
+        <v>1509.52</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>612.3200000000001</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>590.34</v>
+        <v>590.55</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>6738.83</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>6390.29</v>
+        <v>6389.95</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>985.39</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>905.47</v>
+        <v>904.61</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>1401.53</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1258.99</v>
+        <v>1258.72</v>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>196.35</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>219.06</v>
+        <v>219.96</v>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>1285.23</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1245.89</v>
+        <v>1245.94</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>9990.530000000001</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>9351.719999999999</v>
+        <v>9347.860000000001</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>1799.33</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1908.08</v>
+        <v>1908.03</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>85.78</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>95.17</v>
+        <v>95.12</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>10328.31</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>11105.72</v>
+        <v>11104.87</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>924.1900000000001</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>940.0700000000001</v>
+        <v>940.24</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>2224.01</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2340.38</v>
+        <v>2339.39</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>512.36</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>490.01</v>
+        <v>489.48</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>184.53</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>167.39</v>
+        <v>167.28</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>272.08</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>270.81</v>
+        <v>270.77</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>145.56</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>140.6</v>
+        <v>140.47</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>722.84</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>894.46</v>
+        <v>893.96</v>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>4567.25</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>4698.5</v>
+        <v>4703.29</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>1538.87</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1692.7</v>
+        <v>1691.22</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>1338.3</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1392.69</v>
+        <v>1389.99</v>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>430.28</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>409.55</v>
+        <v>409.38</v>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>1769.06</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1781.31</v>
+        <v>1779.04</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>482.46</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>496.67</v>
+        <v>497.03</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>1844.73</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1577.94</v>
+        <v>1577.8</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>1865.72</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1910.15</v>
+        <v>1909.86</v>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>1550.2</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1620.48</v>
+        <v>1620.93</v>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>349.7</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>286.56</v>
+        <v>286.26</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>656.42</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>677.11</v>
+        <v>676.5700000000001</v>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>390.97</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>376.18</v>
+        <v>375.77</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>273.08</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>300.49</v>
+        <v>300.83</v>
       </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>5202.62</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>5536.42</v>
+        <v>5536.68</v>
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>434.8</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>521.48</v>
+        <v>521.37</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>1737.86</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1800.32</v>
+        <v>1796.99</v>
       </c>
       <c r="G85" s="14" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>35862.77</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>35283.46</v>
+        <v>35286.35</v>
       </c>
       <c r="G86" s="14" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>306.83</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>318.82</v>
+        <v>318.84</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>723.23</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>820.61</v>
+        <v>820.02</v>
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>5585.87</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>5699.79</v>
+        <v>5696.67</v>
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>3624.42</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2946.24</v>
+        <v>2945.91</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>354.88</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>384.65</v>
+        <v>384.45</v>
       </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>748.89</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>736.1900000000001</v>
+        <v>735.3</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>135.46</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>132.76</v>
+        <v>132.75</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>857.8</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>837.72</v>
+        <v>837.28</v>
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>1833.58</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1861.17</v>
+        <v>1858.76</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>957.23</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>902.74</v>
+        <v>899.79</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>1827.6</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2084.32</v>
+        <v>2082.74</v>
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>182.34</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>186.05</v>
+        <v>186.03</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>1256.43</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1359.56</v>
+        <v>1358.59</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>3417.97</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3524.3</v>
+        <v>3525.96</v>
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>34.52</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>36.21</v>
+        <v>36.16</v>
       </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>174.62</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>163.9</v>
+        <v>163.98</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>183.59</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>179.85</v>
+        <v>179.58</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>797.03</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>717.53</v>
+        <v>717.34</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>783.28</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>827.52</v>
+        <v>827.23</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>448.59</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>469.85</v>
+        <v>469.6</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>1012.04</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>888.63</v>
+        <v>888.4</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>685.3200000000001</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>712.77</v>
+        <v>712.79</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>1571.12</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1590.88</v>
+        <v>1590.59</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>1625.43</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1703.89</v>
+        <v>1705.67</v>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>1338.68</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1395.75</v>
+        <v>1396.07</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>777.6900000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>902.29</v>
+        <v>901.78</v>
       </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>453.89</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>416.84</v>
+        <v>416.88</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>1558.75</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1575.91</v>
+        <v>1576.72</v>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>1306.27</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1473.05</v>
+        <v>1473.13</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>409.31</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>553.04</v>
+        <v>557.24</v>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>2098.72</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>2156.37</v>
+        <v>2155.84</v>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>498.64</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>510.71</v>
+        <v>509.86</v>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>1131.64</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1306.71</v>
+        <v>1310.01</v>
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>1974.32</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>2112.11</v>
+        <v>2112.22</v>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>7979.06</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>7151.2</v>
+        <v>7149.3</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>1296.15</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1269.33</v>
+        <v>1267.03</v>
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>4155.66</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>4445.52</v>
+        <v>4442.51</v>
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>271.73</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>275.93</v>
+        <v>275.87</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>258.16</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>248.2</v>
+        <v>248.06</v>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>5124.99</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>4443.97</v>
+        <v>4443.78</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>908.02</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1040.78</v>
+        <v>1042.09</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>457.27</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>481.98</v>
+        <v>481.75</v>
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>1874.65</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1993.97</v>
+        <v>1993.61</v>
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>3717.42</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>3067.05</v>
+        <v>3062.93</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>1145.83</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1156.18</v>
+        <v>1155.2</v>
       </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>1233.84</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1222.96</v>
+        <v>1222.08</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>1675.49</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1681.05</v>
+        <v>1681.08</v>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>453.31</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>424.85</v>
+        <v>424.86</v>
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>115.81</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>132.64</v>
+        <v>132.7</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>6510.27</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>6332.07</v>
+        <v>6328.37</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6887,10 +6887,10 @@
         <v>11235.27</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>11075.26</v>
+        <v>11075.25</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>12498.89</v>
+        <v>12490.46</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>587.98</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>647.13</v>
+        <v>647.01</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>4240.76</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>4104.28</v>
+        <v>4106.69</v>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>2299.2</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>2407.08</v>
+        <v>2407.67</v>
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>1290.17</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1262.03</v>
+        <v>1261.96</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>1578.22</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1796.96</v>
+        <v>1797.57</v>
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>7153</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>6869.12</v>
+        <v>6868.01</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>826.1900000000001</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>903.9400000000001</v>
+        <v>903.9299999999999</v>
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>321.71</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>340.46</v>
+        <v>340.17</v>
       </c>
       <c r="G149" s="14" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>479.29</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>481.69</v>
+        <v>481.67</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>532.99</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>504.77</v>
+        <v>504.18</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>436.45</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>483.81</v>
+        <v>484.55</v>
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>2496.06</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>2490.45</v>
+        <v>2490.53</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>230.04</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>207.5</v>
+        <v>207.56</v>
       </c>
       <c r="G155" s="14" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>1369.06</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>1446.84</v>
+        <v>1446.7</v>
       </c>
       <c r="G157" s="14" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>3126.62</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>3331.34</v>
+        <v>3332.36</v>
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>249.09</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>265.35</v>
+        <v>265.56</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>342.46</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>351.57</v>
+        <v>351.52</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>865.39</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>853.3</v>
+        <v>851.5700000000001</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>284.75</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>258.16</v>
+        <v>258.12</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>981.4400000000001</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>880.09</v>
+        <v>879.41</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>236.64</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>281.07</v>
+        <v>280.62</v>
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>451.59</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>510.87</v>
+        <v>511.42</v>
       </c>
       <c r="G165" s="14" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>3546.36</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>3499.79</v>
+        <v>3497.67</v>
       </c>
       <c r="G166" s="14" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>20550.88</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>18897.59</v>
+        <v>18898.77</v>
       </c>
       <c r="G167" s="14" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>924.02</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>884.87</v>
+        <v>884.45</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>242.68</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>282.24</v>
+        <v>282.45</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>1030.1</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>972.99</v>
+        <v>972.48</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>160.02</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>162.98</v>
+        <v>163.14</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>721.59</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>619.76</v>
+        <v>619.42</v>
       </c>
       <c r="G172" s="14" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>1490.83</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>1246.83</v>
+        <v>1246.48</v>
       </c>
       <c r="G173" s="14" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>387.8</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>380.59</v>
+        <v>381.29</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>7923.35</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>8276.059999999999</v>
+        <v>8312.01</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>1918.8</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>1800.06</v>
+        <v>1799.74</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>2398.1</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>2521.69</v>
+        <v>2530.17</v>
       </c>
       <c r="G177" s="14" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>2272.12</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>2048.45</v>
+        <v>2048.69</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>648.12</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>559.16</v>
+        <v>558.84</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>96.06999999999999</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>93.95</v>
+        <v>93.97</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>2234.39</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>2433.62</v>
+        <v>2430.81</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>316.26</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>328.73</v>
+        <v>328.66</v>
       </c>
       <c r="G182" s="14" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>1062.44</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>1116.29</v>
+        <v>1115.28</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>1027.71</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1020.97</v>
+        <v>1021.69</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>1750.86</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>1874.94</v>
+        <v>1875.02</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>285.75</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>257.08</v>
+        <v>257.33</v>
       </c>
       <c r="G186" s="14" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>691.48</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>603.16</v>
+        <v>603</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>706.4</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>623.71</v>
+        <v>623.23</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>2881.22</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>2785.72</v>
+        <v>2785.69</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>1623.37</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>1650.79</v>
+        <v>1649.09</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>2663.71</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>2492.34</v>
+        <v>2489.2</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>4280.74</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>3420.18</v>
+        <v>3418.79</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>4316.66</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>4290.63</v>
+        <v>4286.05</v>
       </c>
       <c r="G195" s="14" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>1250.98</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>1362.07</v>
+        <v>1361.14</v>
       </c>
       <c r="G196" s="14" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>769.92</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>753.0599999999999</v>
+        <v>752.1799999999999</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>1260.64</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>1418.04</v>
+        <v>1418.69</v>
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>2667.4</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>2595.02</v>
+        <v>2595.17</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>795.52</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>879.62</v>
+        <v>879.74</v>
       </c>
       <c r="G201" s="14" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>622.0700000000001</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>682</v>
+        <v>681.8099999999999</v>
       </c>
       <c r="G202" s="14" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>588.22</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>544.79</v>
+        <v>544.9299999999999</v>
       </c>
       <c r="G203" s="14" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>5169.25</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>5161.31</v>
+        <v>5159.79</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>117.08</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>88.25</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>1026.01</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>894.2</v>
+        <v>894.22</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>547.3</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>456.64</v>
+        <v>456.56</v>
       </c>
       <c r="G208" s="14" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>383.62</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>402.03</v>
+        <v>402.11</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>2241.55</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>2311.4</v>
+        <v>2309.96</v>
       </c>
       <c r="G210" s="14" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>604.0700000000001</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>546.5599999999999</v>
+        <v>546.28</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>1100.37</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>1124.84</v>
+        <v>1123.88</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>341.43</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>302.39</v>
+        <v>302.25</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>31097.25</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>32795.28</v>
+        <v>32775.51</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>548.61</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>490.86</v>
+        <v>490.74</v>
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>203.37</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>203.7</v>
+        <v>203.56</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>1888.68</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>2060.54</v>
+        <v>2059.11</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>1286.92</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>1334.3</v>
+        <v>1333.95</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>1820.45</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>1859.71</v>
+        <v>1860.29</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>548.45</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>591.51</v>
+        <v>591.42</v>
       </c>
       <c r="G221" s="14" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>87.69</v>
+        <v>87.66</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>11.37</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>69.14</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>72.11</v>
+        <v>72.02</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>125.47</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>134.29</v>
+        <v>134.18</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>60.01</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>56.33</v>
+        <v>56.26</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>345.35</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>342.83</v>
+        <v>342.58</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>161.81</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>176.51</v>
+        <v>176.6</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>467.8</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>481.17</v>
+        <v>480.78</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>1567.12</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>1567.54</v>
+        <v>1567.57</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>501.53</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>513.27</v>
+        <v>512.89</v>
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>649.85</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>685.87</v>
+        <v>685.89</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>400.09</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>392.35</v>
+        <v>392.09</v>
       </c>
       <c r="G233" s="14" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>2071.96</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>2195.79</v>
+        <v>2194.35</v>
       </c>
       <c r="G234" s="14" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>865.4299999999999</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>815.84</v>
+        <v>815.89</v>
       </c>
       <c r="G235" s="14" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>4449.69</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>4853.93</v>
+        <v>4855.8</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>888.58</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>867.79</v>
+        <v>866.74</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>423.83</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>410.41</v>
+        <v>410.31</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>1231.03</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>1405.17</v>
+        <v>1405.58</v>
       </c>
       <c r="G239" s="14" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>96.63</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>116.82</v>
+        <v>116.51</v>
       </c>
       <c r="G240" s="14" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>717.99</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>824.11</v>
+        <v>823.79</v>
       </c>
       <c r="G241" s="14" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>34.23</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>36.26</v>
+        <v>36.22</v>
       </c>
       <c r="G242" s="14" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>144.98</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>147.78</v>
+        <v>147.81</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>1542.71</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>1473.57</v>
+        <v>1473.4</v>
       </c>
       <c r="G244" s="14" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>21.25</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>21.51</v>
+        <v>21.47</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>144.79</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>153.6</v>
+        <v>153.45</v>
       </c>
       <c r="G246" s="14" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>549.11</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>618.39</v>
+        <v>618.12</v>
       </c>
       <c r="G247" s="14" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>128.36</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>136.04</v>
+        <v>135.84</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>101.7</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>110.92</v>
+        <v>110.82</v>
       </c>
       <c r="G249" s="14" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>300.07</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>334.12</v>
+        <v>333.98</v>
       </c>
       <c r="G250" s="14" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>159.16</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>180.32</v>
+        <v>180.21</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>288.38</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>291.01</v>
+        <v>290.45</v>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>128.72</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>113.93</v>
+        <v>113.89</v>
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>2084.53</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>1908.28</v>
+        <v>1907.17</v>
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>615.73</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>608.48</v>
+        <v>607.58</v>
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>216.89</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>201.22</v>
+        <v>201.16</v>
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>1213.76</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>1112.27</v>
+        <v>1112.68</v>
       </c>
       <c r="G258" s="14" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>243.38</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>264.18</v>
+        <v>264.12</v>
       </c>
       <c r="G259" s="12" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>5458.85</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>5613.41</v>
+        <v>5608.16</v>
       </c>
       <c r="G260" s="14" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>410.08</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>420.73</v>
+        <v>420.75</v>
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>133.31</v>
       </c>
       <c r="F262" s="11" t="n">
-        <v>136.75</v>
+        <v>136.63</v>
       </c>
       <c r="G262" s="14" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>18.1</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>17.17</v>
+        <v>17.15</v>
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>752.01</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>744.85</v>
+        <v>744.52</v>
       </c>
       <c r="G264" s="14" t="inlineStr">
         <is>
@@ -12384,13 +12384,13 @@
         <v>2905.6</v>
       </c>
       <c r="D266" s="11" t="n">
-        <v>2936.68</v>
+        <v>2934.59</v>
       </c>
       <c r="E266" s="11" t="n">
-        <v>2955.34</v>
+        <v>2949.18</v>
       </c>
       <c r="F266" s="11" t="n">
-        <v/>
+        <v>3088.58</v>
       </c>
       <c r="G266" s="14" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>533.71</v>
       </c>
       <c r="F267" s="11" t="n">
-        <v>508.98</v>
+        <v>509.37</v>
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>269.17</v>
       </c>
       <c r="F268" s="11" t="n">
-        <v>272.75</v>
+        <v>272.73</v>
       </c>
       <c r="G268" s="12" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>1249.42</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>1173.71</v>
+        <v>1173.94</v>
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>466.47</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>535.34</v>
+        <v>535.84</v>
       </c>
       <c r="G270" s="14" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>686.97</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>671.9400000000001</v>
+        <v>671.92</v>
       </c>
       <c r="G271" s="14" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>949.92</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>984.42</v>
+        <v>984.73</v>
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>282.28</v>
       </c>
       <c r="F273" s="11" t="n">
-        <v>299.78</v>
+        <v>299.46</v>
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>739.89</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>851.79</v>
+        <v>849.27</v>
       </c>
       <c r="G274" s="14" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>1070.49</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>1047.13</v>
+        <v>1046.28</v>
       </c>
       <c r="G275" s="14" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>390.25</v>
       </c>
       <c r="F276" s="11" t="n">
-        <v>441.62</v>
+        <v>440.62</v>
       </c>
       <c r="G276" s="14" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>291.36</v>
       </c>
       <c r="F277" s="11" t="n">
-        <v>265.73</v>
+        <v>265.71</v>
       </c>
       <c r="G277" s="12" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>3774.46</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>4456.62</v>
+        <v>4452.34</v>
       </c>
       <c r="G278" s="14" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>552.0700000000001</v>
       </c>
       <c r="F279" s="11" t="n">
-        <v>653.1</v>
+        <v>652.54</v>
       </c>
       <c r="G279" s="14" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>4869.55</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>4376.68</v>
+        <v>4374.77</v>
       </c>
       <c r="G280" s="12" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>898.52</v>
       </c>
       <c r="F281" s="11" t="n">
-        <v>985.36</v>
+        <v>984.3200000000001</v>
       </c>
       <c r="G281" s="14" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>706.42</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>677.64</v>
+        <v>676.9299999999999</v>
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>1590.34</v>
       </c>
       <c r="F283" s="11" t="n">
-        <v>1275.71</v>
+        <v>1274.75</v>
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>384.15</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>400.9</v>
+        <v>401.06</v>
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>1219.35</v>
       </c>
       <c r="F285" s="11" t="n">
-        <v>1170.38</v>
+        <v>1169.49</v>
       </c>
       <c r="G285" s="12" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>756.5700000000001</v>
       </c>
       <c r="F286" s="11" t="n">
-        <v>962.1799999999999</v>
+        <v>963</v>
       </c>
       <c r="G286" s="12" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>918.16</v>
       </c>
       <c r="F287" s="11" t="n">
-        <v>942.78</v>
+        <v>942.53</v>
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>1509.23</v>
       </c>
       <c r="F288" s="11" t="n">
-        <v>1461.64</v>
+        <v>1461.59</v>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>313.37</v>
       </c>
       <c r="F289" s="11" t="n">
-        <v>369.25</v>
+        <v>369.08</v>
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>1186.3</v>
       </c>
       <c r="F290" s="11" t="n">
-        <v>1011.34</v>
+        <v>1010.93</v>
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>116.34</v>
       </c>
       <c r="F291" s="11" t="n">
-        <v>131.54</v>
+        <v>131.32</v>
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>543.1799999999999</v>
       </c>
       <c r="F294" s="11" t="n">
-        <v>542.75</v>
+        <v>542.41</v>
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
@@ -13657,16 +13657,16 @@
         </is>
       </c>
       <c r="C295" s="11" t="n">
-        <v>830</v>
+        <v>415</v>
       </c>
       <c r="D295" s="11" t="n">
-        <v>811.8</v>
+        <v>405.9</v>
       </c>
       <c r="E295" s="11" t="n">
-        <v>809.89</v>
+        <v>404.95</v>
       </c>
       <c r="F295" s="11" t="n">
-        <v>833.17</v>
+        <v>416.45</v>
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>7193.33</v>
       </c>
       <c r="F296" s="11" t="n">
-        <v>6650.48</v>
+        <v>6647.84</v>
       </c>
       <c r="G296" s="14" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>1604.27</v>
       </c>
       <c r="F297" s="11" t="n">
-        <v>1395.67</v>
+        <v>1396.03</v>
       </c>
       <c r="G297" s="12" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>890.83</v>
       </c>
       <c r="F298" s="11" t="n">
-        <v>1019.82</v>
+        <v>1019.6</v>
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>3915.91</v>
       </c>
       <c r="F299" s="11" t="n">
-        <v>3817.29</v>
+        <v>3817.21</v>
       </c>
       <c r="G299" s="12" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>278.22</v>
       </c>
       <c r="F300" s="11" t="n">
-        <v>261.44</v>
+        <v>261.28</v>
       </c>
       <c r="G300" s="12" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>408.09</v>
       </c>
       <c r="F301" s="11" t="n">
-        <v>404.68</v>
+        <v>404.05</v>
       </c>
       <c r="G301" s="14" t="inlineStr">
         <is>
@@ -13968,13 +13968,13 @@
         <v>3988.6</v>
       </c>
       <c r="D302" s="11" t="n">
-        <v>4102.9</v>
+        <v>4103.65</v>
       </c>
       <c r="E302" s="11" t="n">
-        <v>4257.1</v>
+        <v>4310</v>
       </c>
       <c r="F302" s="11" t="n">
-        <v/>
+        <v>4917.31</v>
       </c>
       <c r="G302" s="14" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>3512.53</v>
       </c>
       <c r="F303" s="11" t="n">
-        <v>3823.07</v>
+        <v>3827.88</v>
       </c>
       <c r="G303" s="14" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>2290.85</v>
       </c>
       <c r="F304" s="11" t="n">
-        <v>2173.18</v>
+        <v>2172.6</v>
       </c>
       <c r="G304" s="14" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>3184.02</v>
       </c>
       <c r="F305" s="11" t="n">
-        <v>3296.77</v>
+        <v>3294.95</v>
       </c>
       <c r="G305" s="14" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>317.75</v>
       </c>
       <c r="F306" s="11" t="n">
-        <v>318.95</v>
+        <v>318.78</v>
       </c>
       <c r="G306" s="14" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>75.48999999999999</v>
       </c>
       <c r="F307" s="11" t="n">
-        <v>65.12</v>
+        <v>65.13</v>
       </c>
       <c r="G307" s="12" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>297.17</v>
       </c>
       <c r="F308" s="11" t="n">
-        <v>279.8</v>
+        <v>279.63</v>
       </c>
       <c r="G308" s="12" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>2297.69</v>
       </c>
       <c r="F309" s="11" t="n">
-        <v>2271.84</v>
+        <v>2273.56</v>
       </c>
       <c r="G309" s="12" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>972.8200000000001</v>
       </c>
       <c r="F310" s="11" t="n">
-        <v>1303.27</v>
+        <v>1303.76</v>
       </c>
       <c r="G310" s="14" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>796.6</v>
       </c>
       <c r="F311" s="11" t="n">
-        <v>751.6799999999999</v>
+        <v>751.74</v>
       </c>
       <c r="G311" s="12" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>13428.29</v>
       </c>
       <c r="F312" s="11" t="n">
-        <v>14127.12</v>
+        <v>14128.13</v>
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>1017.26</v>
       </c>
       <c r="F313" s="11" t="n">
-        <v>1058.22</v>
+        <v>1059.25</v>
       </c>
       <c r="G313" s="14" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>2499.84</v>
       </c>
       <c r="F314" s="11" t="n">
-        <v>2539.02</v>
+        <v>2533.75</v>
       </c>
       <c r="G314" s="14" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>2937.86</v>
       </c>
       <c r="F315" s="11" t="n">
-        <v>2323.41</v>
+        <v>2322.44</v>
       </c>
       <c r="G315" s="14" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>1157.47</v>
       </c>
       <c r="F316" s="11" t="n">
-        <v>1172.52</v>
+        <v>1172.08</v>
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>1648.05</v>
       </c>
       <c r="F318" s="11" t="n">
-        <v>1605.41</v>
+        <v>1605.26</v>
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>1084.96</v>
       </c>
       <c r="F319" s="11" t="n">
-        <v>1145.36</v>
+        <v>1146.39</v>
       </c>
       <c r="G319" s="12" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>537.11</v>
       </c>
       <c r="F320" s="11" t="n">
-        <v>542.79</v>
+        <v>542.09</v>
       </c>
       <c r="G320" s="12" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>63.34</v>
       </c>
       <c r="F321" s="11" t="n">
-        <v>62.7</v>
+        <v>62.61</v>
       </c>
       <c r="G321" s="12" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>125.93</v>
       </c>
       <c r="F322" s="11" t="n">
-        <v>115.16</v>
+        <v>115.26</v>
       </c>
       <c r="G322" s="12" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>810.42</v>
       </c>
       <c r="F323" s="11" t="n">
-        <v>808.34</v>
+        <v>808.4</v>
       </c>
       <c r="G323" s="12" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>2265</v>
       </c>
       <c r="F324" s="11" t="n">
-        <v>2486.86</v>
+        <v>2486.33</v>
       </c>
       <c r="G324" s="12" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>131653.43</v>
       </c>
       <c r="F325" s="11" t="n">
-        <v>138147.03</v>
+        <v>138104.55</v>
       </c>
       <c r="G325" s="14" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>165.27</v>
       </c>
       <c r="F326" s="11" t="n">
-        <v>158.61</v>
+        <v>158.58</v>
       </c>
       <c r="G326" s="14" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>40.29</v>
       </c>
       <c r="F327" s="11" t="n">
-        <v>41.63</v>
+        <v>41.6</v>
       </c>
       <c r="G327" s="14" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>3417.85</v>
       </c>
       <c r="F328" s="11" t="n">
-        <v>3288.27</v>
+        <v>3288.29</v>
       </c>
       <c r="G328" s="14" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>1008.97</v>
       </c>
       <c r="F329" s="11" t="n">
-        <v>889.6900000000001</v>
+        <v>889.4</v>
       </c>
       <c r="G329" s="12" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>1095.25</v>
       </c>
       <c r="F330" s="11" t="n">
-        <v>965.02</v>
+        <v>963.53</v>
       </c>
       <c r="G330" s="12" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>400.41</v>
       </c>
       <c r="F331" s="11" t="n">
-        <v>323.84</v>
+        <v>323.8</v>
       </c>
       <c r="G331" s="12" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>997.9</v>
       </c>
       <c r="F332" s="11" t="n">
-        <v>1172.89</v>
+        <v>1174.8</v>
       </c>
       <c r="G332" s="12" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>629.87</v>
       </c>
       <c r="F333" s="11" t="n">
-        <v>586.3200000000001</v>
+        <v>585.64</v>
       </c>
       <c r="G333" s="14" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>6700.33</v>
       </c>
       <c r="F334" s="11" t="n">
-        <v>5930.91</v>
+        <v>5929.89</v>
       </c>
       <c r="G334" s="12" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>93.39</v>
       </c>
       <c r="F335" s="11" t="n">
-        <v>98.53</v>
+        <v>98.37</v>
       </c>
       <c r="G335" s="12" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>155.21</v>
       </c>
       <c r="F336" s="11" t="n">
-        <v>168.86</v>
+        <v>168.66</v>
       </c>
       <c r="G336" s="14" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>1373.82</v>
       </c>
       <c r="F337" s="11" t="n">
-        <v>1278.38</v>
+        <v>1278.51</v>
       </c>
       <c r="G337" s="12" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>3759.55</v>
       </c>
       <c r="F338" s="11" t="n">
-        <v>3232.61</v>
+        <v>3231.32</v>
       </c>
       <c r="G338" s="12" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>15397.04</v>
       </c>
       <c r="F339" s="11" t="n">
-        <v>14429.69</v>
+        <v>14407.57</v>
       </c>
       <c r="G339" s="12" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>481.04</v>
       </c>
       <c r="F340" s="11" t="n">
-        <v>669.0700000000001</v>
+        <v>669.54</v>
       </c>
       <c r="G340" s="14" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>1814.8</v>
       </c>
       <c r="F341" s="11" t="n">
-        <v>1786.77</v>
+        <v>1788.56</v>
       </c>
       <c r="G341" s="12" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>79.15000000000001</v>
       </c>
       <c r="F342" s="11" t="n">
-        <v>78.73999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="G342" s="12" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>157.13</v>
       </c>
       <c r="F343" s="11" t="n">
-        <v>160.05</v>
+        <v>160.08</v>
       </c>
       <c r="G343" s="14" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>78.81</v>
       </c>
       <c r="F344" s="11" t="n">
-        <v>77.7</v>
+        <v>77.62</v>
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>311.02</v>
       </c>
       <c r="F345" s="11" t="n">
-        <v>269.6</v>
+        <v>270.4</v>
       </c>
       <c r="G345" s="12" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>86.73999999999999</v>
       </c>
       <c r="F346" s="11" t="n">
-        <v>78.68000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="G346" s="12" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>42.06</v>
       </c>
       <c r="F347" s="11" t="n">
-        <v>40.87</v>
+        <v>40.84</v>
       </c>
       <c r="G347" s="12" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>387.53</v>
       </c>
       <c r="F348" s="11" t="n">
-        <v>358.4</v>
+        <v>358.78</v>
       </c>
       <c r="G348" s="12" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>1386.55</v>
       </c>
       <c r="F350" s="11" t="n">
-        <v>1334.93</v>
+        <v>1334.67</v>
       </c>
       <c r="G350" s="12" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>314.77</v>
       </c>
       <c r="F351" s="11" t="n">
-        <v>339.74</v>
+        <v>339.4</v>
       </c>
       <c r="G351" s="12" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>263.8</v>
       </c>
       <c r="F352" s="11" t="n">
-        <v>247.96</v>
+        <v>247.84</v>
       </c>
       <c r="G352" s="14" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>1627.79</v>
       </c>
       <c r="F353" s="11" t="n">
-        <v>1619.03</v>
+        <v>1619.04</v>
       </c>
       <c r="G353" s="12" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>8543.790000000001</v>
       </c>
       <c r="F354" s="11" t="n">
-        <v>7925.66</v>
+        <v>7924.02</v>
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>480.95</v>
       </c>
       <c r="F355" s="11" t="n">
-        <v>448.14</v>
+        <v>448.06</v>
       </c>
       <c r="G355" s="14" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>34.51</v>
       </c>
       <c r="F356" s="11" t="n">
-        <v>38.33</v>
+        <v>38.29</v>
       </c>
       <c r="G356" s="12" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>1187.36</v>
       </c>
       <c r="F357" s="11" t="n">
-        <v>1200.09</v>
+        <v>1198.22</v>
       </c>
       <c r="G357" s="14" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>1677.39</v>
       </c>
       <c r="F358" s="11" t="n">
-        <v>1624.31</v>
+        <v>1625.44</v>
       </c>
       <c r="G358" s="12" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>284.4</v>
       </c>
       <c r="F359" s="11" t="n">
-        <v>259.04</v>
+        <v>259.16</v>
       </c>
       <c r="G359" s="14" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>36172.76</v>
       </c>
       <c r="F360" s="11" t="n">
-        <v>37239.87</v>
+        <v>37226.57</v>
       </c>
       <c r="G360" s="12" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>125.05</v>
       </c>
       <c r="F361" s="11" t="n">
-        <v>137.98</v>
+        <v>137.78</v>
       </c>
       <c r="G361" s="12" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>470.09</v>
       </c>
       <c r="F362" s="11" t="n">
-        <v>519.6</v>
+        <v>520.09</v>
       </c>
       <c r="G362" s="14" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>1124.68</v>
       </c>
       <c r="F363" s="11" t="n">
-        <v>1124.83</v>
+        <v>1124.17</v>
       </c>
       <c r="G363" s="14" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>285.14</v>
       </c>
       <c r="F364" s="11" t="n">
-        <v>311.39</v>
+        <v>311.47</v>
       </c>
       <c r="G364" s="14" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>5061.96</v>
       </c>
       <c r="F365" s="11" t="n">
-        <v>5408.79</v>
+        <v>5420.34</v>
       </c>
       <c r="G365" s="12" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>275.22</v>
       </c>
       <c r="F366" s="11" t="n">
-        <v>278.86</v>
+        <v>279</v>
       </c>
       <c r="G366" s="12" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>434.34</v>
       </c>
       <c r="F367" s="11" t="n">
-        <v>402.71</v>
+        <v>402.84</v>
       </c>
       <c r="G367" s="14" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>4772.16</v>
       </c>
       <c r="F368" s="11" t="n">
-        <v>4849.59</v>
+        <v>4848.41</v>
       </c>
       <c r="G368" s="14" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>514.1</v>
       </c>
       <c r="F369" s="11" t="n">
-        <v>579.5</v>
+        <v>577.73</v>
       </c>
       <c r="G369" s="14" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>1739.77</v>
       </c>
       <c r="F370" s="11" t="n">
-        <v>1690.46</v>
+        <v>1692.91</v>
       </c>
       <c r="G370" s="12" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>1422.91</v>
       </c>
       <c r="F371" s="11" t="n">
-        <v>1440.54</v>
+        <v>1440.21</v>
       </c>
       <c r="G371" s="12" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>3000.24</v>
       </c>
       <c r="F372" s="11" t="n">
-        <v>3223.57</v>
+        <v>3225.62</v>
       </c>
       <c r="G372" s="14" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>109.18</v>
       </c>
       <c r="F375" s="11" t="n">
-        <v>112.45</v>
+        <v>112.4</v>
       </c>
       <c r="G375" s="12" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>983.49</v>
       </c>
       <c r="F376" s="11" t="n">
-        <v>915.34</v>
+        <v>916.17</v>
       </c>
       <c r="G376" s="12" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>1652.49</v>
       </c>
       <c r="F377" s="11" t="n">
-        <v>1656.49</v>
+        <v>1657.9</v>
       </c>
       <c r="G377" s="12" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>8441.25</v>
       </c>
       <c r="F378" s="11" t="n">
-        <v>7582.01</v>
+        <v>7583</v>
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>1484.65</v>
       </c>
       <c r="F379" s="11" t="n">
-        <v>1664.73</v>
+        <v>1665.08</v>
       </c>
       <c r="G379" s="14" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>418.06</v>
       </c>
       <c r="F380" s="11" t="n">
-        <v>428.01</v>
+        <v>428.24</v>
       </c>
       <c r="G380" s="14" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>302.77</v>
       </c>
       <c r="F381" s="11" t="n">
-        <v>287.57</v>
+        <v>287.73</v>
       </c>
       <c r="G381" s="14" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>30770.28</v>
       </c>
       <c r="F382" s="11" t="n">
-        <v>23671.01</v>
+        <v>23654.79</v>
       </c>
       <c r="G382" s="12" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>164.87</v>
       </c>
       <c r="F383" s="11" t="n">
-        <v>172.81</v>
+        <v>172.71</v>
       </c>
       <c r="G383" s="12" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>959.37</v>
       </c>
       <c r="F384" s="11" t="n">
-        <v>927.53</v>
+        <v>927.99</v>
       </c>
       <c r="G384" s="12" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>1384.09</v>
       </c>
       <c r="F385" s="11" t="n">
-        <v>1454.55</v>
+        <v>1453.54</v>
       </c>
       <c r="G385" s="12" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>16504.69</v>
       </c>
       <c r="F386" s="11" t="n">
-        <v>16368.84</v>
+        <v>16316.18</v>
       </c>
       <c r="G386" s="12" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>1004.45</v>
       </c>
       <c r="F387" s="11" t="n">
-        <v>1022.68</v>
+        <v>1021.88</v>
       </c>
       <c r="G387" s="14" t="inlineStr">
         <is>
@@ -17799,10 +17799,10 @@
         <v>3445.31</v>
       </c>
       <c r="E389" s="11" t="n">
-        <v>3239.14</v>
+        <v>3239.13</v>
       </c>
       <c r="F389" s="11" t="n">
-        <v>2963.24</v>
+        <v>2960.61</v>
       </c>
       <c r="G389" s="14" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>317.81</v>
       </c>
       <c r="F390" s="11" t="n">
-        <v>329.2</v>
+        <v>328.68</v>
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>1276.61</v>
       </c>
       <c r="F391" s="11" t="n">
-        <v>1293.75</v>
+        <v>1292.8</v>
       </c>
       <c r="G391" s="12" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>955.9</v>
       </c>
       <c r="F392" s="11" t="n">
-        <v>1005.48</v>
+        <v>1005.01</v>
       </c>
       <c r="G392" s="14" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>324.82</v>
       </c>
       <c r="F393" s="11" t="n">
-        <v>296.21</v>
+        <v>295.99</v>
       </c>
       <c r="G393" s="12" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>347.68</v>
       </c>
       <c r="F394" s="11" t="n">
-        <v>354.16</v>
+        <v>354.01</v>
       </c>
       <c r="G394" s="14" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>225.06</v>
       </c>
       <c r="F395" s="11" t="n">
-        <v>246.63</v>
+        <v>245.98</v>
       </c>
       <c r="G395" s="12" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>1380.14</v>
       </c>
       <c r="F396" s="11" t="n">
-        <v>1405.14</v>
+        <v>1405.16</v>
       </c>
       <c r="G396" s="14" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>399.52</v>
       </c>
       <c r="F397" s="11" t="n">
-        <v>425.58</v>
+        <v>424.84</v>
       </c>
       <c r="G397" s="12" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>211.59</v>
       </c>
       <c r="F398" s="11" t="n">
-        <v>222.6</v>
+        <v>222.45</v>
       </c>
       <c r="G398" s="14" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>562.42</v>
       </c>
       <c r="F399" s="11" t="n">
-        <v>560.58</v>
+        <v>560.75</v>
       </c>
       <c r="G399" s="14" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>27.23</v>
       </c>
       <c r="F400" s="11" t="n">
-        <v>33.26</v>
+        <v>33.25</v>
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>1696.25</v>
       </c>
       <c r="F401" s="11" t="n">
-        <v>1463.09</v>
+        <v>1462.3</v>
       </c>
       <c r="G401" s="12" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>286.25</v>
       </c>
       <c r="F402" s="11" t="n">
-        <v>312.25</v>
+        <v>311.85</v>
       </c>
       <c r="G402" s="14" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>42.35</v>
       </c>
       <c r="F403" s="11" t="n">
-        <v>44.71</v>
+        <v>44.65</v>
       </c>
       <c r="G403" s="14" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>179.95</v>
       </c>
       <c r="F404" s="11" t="n">
-        <v>153.21</v>
+        <v>153.17</v>
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>1052.74</v>
       </c>
       <c r="F405" s="11" t="n">
-        <v>935.29</v>
+        <v>935.47</v>
       </c>
       <c r="G405" s="12" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>149.06</v>
       </c>
       <c r="F406" s="11" t="n">
-        <v>145.16</v>
+        <v>145.01</v>
       </c>
       <c r="G406" s="12" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>182.9</v>
       </c>
       <c r="F407" s="11" t="n">
-        <v>225.36</v>
+        <v>225.75</v>
       </c>
       <c r="G407" s="12" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>554.8200000000001</v>
       </c>
       <c r="F408" s="11" t="n">
-        <v>528.45</v>
+        <v>528.0700000000001</v>
       </c>
       <c r="G408" s="14" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>361.85</v>
       </c>
       <c r="F409" s="11" t="n">
-        <v>386.46</v>
+        <v>386.21</v>
       </c>
       <c r="G409" s="12" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>92.83</v>
       </c>
       <c r="F410" s="11" t="n">
-        <v>97.26000000000001</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="G410" s="14" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>664.27</v>
       </c>
       <c r="F411" s="11" t="n">
-        <v>764.4400000000001</v>
+        <v>764.97</v>
       </c>
       <c r="G411" s="14" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>1884.86</v>
       </c>
       <c r="F412" s="11" t="n">
-        <v>1887.86</v>
+        <v>1887.82</v>
       </c>
       <c r="G412" s="14" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>1016.82</v>
       </c>
       <c r="F413" s="11" t="n">
-        <v>970.42</v>
+        <v>970.34</v>
       </c>
       <c r="G413" s="14" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>4058.95</v>
       </c>
       <c r="F414" s="11" t="n">
-        <v>3905.67</v>
+        <v>3912.36</v>
       </c>
       <c r="G414" s="12" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>1148.28</v>
       </c>
       <c r="F415" s="11" t="n">
-        <v>914.11</v>
+        <v>913.8099999999999</v>
       </c>
       <c r="G415" s="12" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>292.91</v>
       </c>
       <c r="F416" s="11" t="n">
-        <v>245.46</v>
+        <v>245.24</v>
       </c>
       <c r="G416" s="14" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>24929.63</v>
       </c>
       <c r="F417" s="11" t="n">
-        <v>26456.35</v>
+        <v>26458.61</v>
       </c>
       <c r="G417" s="12" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>967.9299999999999</v>
       </c>
       <c r="F418" s="11" t="n">
-        <v>883.62</v>
+        <v>883.75</v>
       </c>
       <c r="G418" s="12" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>874.3099999999999</v>
       </c>
       <c r="F419" s="11" t="n">
-        <v>852.0599999999999</v>
+        <v>852.08</v>
       </c>
       <c r="G419" s="12" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>3559.25</v>
       </c>
       <c r="F420" s="11" t="n">
-        <v>3285.96</v>
+        <v>3285.56</v>
       </c>
       <c r="G420" s="12" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>851.89</v>
       </c>
       <c r="F421" s="11" t="n">
-        <v>967.62</v>
+        <v>966.91</v>
       </c>
       <c r="G421" s="14" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>75.01000000000001</v>
       </c>
       <c r="F422" s="11" t="n">
-        <v>78.59</v>
+        <v>78.63</v>
       </c>
       <c r="G422" s="12" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>1383.72</v>
       </c>
       <c r="F423" s="11" t="n">
-        <v>1413.18</v>
+        <v>1414.32</v>
       </c>
       <c r="G423" s="12" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>15776.84</v>
       </c>
       <c r="F424" s="11" t="n">
-        <v>14102.84</v>
+        <v>14102.39</v>
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>565.6900000000001</v>
       </c>
       <c r="F425" s="11" t="n">
-        <v>515.45</v>
+        <v>516.29</v>
       </c>
       <c r="G425" s="12" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>266.69</v>
       </c>
       <c r="F426" s="11" t="n">
-        <v>310.05</v>
+        <v>309.65</v>
       </c>
       <c r="G426" s="14" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>709.34</v>
       </c>
       <c r="F427" s="11" t="n">
-        <v>690.63</v>
+        <v>689.86</v>
       </c>
       <c r="G427" s="14" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>2627.11</v>
       </c>
       <c r="F428" s="11" t="n">
-        <v>2759.12</v>
+        <v>2758.83</v>
       </c>
       <c r="G428" s="12" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>500.24</v>
       </c>
       <c r="F429" s="11" t="n">
-        <v>469.29</v>
+        <v>469.2</v>
       </c>
       <c r="G429" s="12" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>444.8</v>
       </c>
       <c r="F430" s="11" t="n">
-        <v>458.29</v>
+        <v>458.41</v>
       </c>
       <c r="G430" s="12" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>4717.48</v>
       </c>
       <c r="F431" s="11" t="n">
-        <v>4846.08</v>
+        <v>4852.09</v>
       </c>
       <c r="G431" s="14" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>1793.25</v>
       </c>
       <c r="F432" s="11" t="n">
-        <v>1731.95</v>
+        <v>1731.41</v>
       </c>
       <c r="G432" s="12" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>563.76</v>
       </c>
       <c r="F433" s="11" t="n">
-        <v>571.26</v>
+        <v>571.01</v>
       </c>
       <c r="G433" s="14" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>3647.77</v>
       </c>
       <c r="F434" s="11" t="n">
-        <v>3748.14</v>
+        <v>3749.65</v>
       </c>
       <c r="G434" s="12" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>51.18</v>
       </c>
       <c r="F435" s="11" t="n">
-        <v>51.6</v>
+        <v>51.57</v>
       </c>
       <c r="G435" s="12" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>339.07</v>
       </c>
       <c r="F436" s="11" t="n">
-        <v>392.74</v>
+        <v>391.46</v>
       </c>
       <c r="G436" s="14" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>276.23</v>
       </c>
       <c r="F437" s="11" t="n">
-        <v>328.12</v>
+        <v>328.55</v>
       </c>
       <c r="G437" s="12" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>453.61</v>
       </c>
       <c r="F438" s="11" t="n">
-        <v>532.46</v>
+        <v>532.4400000000001</v>
       </c>
       <c r="G438" s="12" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>955.88</v>
       </c>
       <c r="F439" s="11" t="n">
-        <v>811.03</v>
+        <v>810.27</v>
       </c>
       <c r="G439" s="12" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>306.03</v>
       </c>
       <c r="F440" s="11" t="n">
-        <v>339.07</v>
+        <v>338.4</v>
       </c>
       <c r="G440" s="12" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>737.27</v>
       </c>
       <c r="F442" s="11" t="n">
-        <v>773.63</v>
+        <v>773.73</v>
       </c>
       <c r="G442" s="12" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>1641.49</v>
       </c>
       <c r="F443" s="11" t="n">
-        <v>1638.91</v>
+        <v>1638.09</v>
       </c>
       <c r="G443" s="12" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>1153.36</v>
       </c>
       <c r="F444" s="11" t="n">
-        <v>1124.01</v>
+        <v>1124.17</v>
       </c>
       <c r="G444" s="12" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>4338.02</v>
       </c>
       <c r="F445" s="11" t="n">
-        <v>4935.66</v>
+        <v>4933.52</v>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>676.3200000000001</v>
       </c>
       <c r="F446" s="11" t="n">
-        <v>678.47</v>
+        <v>678.53</v>
       </c>
       <c r="G446" s="14" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>413.54</v>
       </c>
       <c r="F447" s="11" t="n">
-        <v>393.16</v>
+        <v>393.27</v>
       </c>
       <c r="G447" s="12" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>207.68</v>
       </c>
       <c r="F448" s="11" t="n">
-        <v>187.66</v>
+        <v>187.67</v>
       </c>
       <c r="G448" s="12" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>615.4</v>
       </c>
       <c r="F449" s="11" t="n">
-        <v>634.87</v>
+        <v>634.88</v>
       </c>
       <c r="G449" s="12" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>1229.11</v>
       </c>
       <c r="F450" s="11" t="n">
-        <v>1361.6</v>
+        <v>1358.37</v>
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>2419.04</v>
       </c>
       <c r="F451" s="11" t="n">
-        <v>2778.79</v>
+        <v>2777.49</v>
       </c>
       <c r="G451" s="14" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>1441.58</v>
       </c>
       <c r="F452" s="11" t="n">
-        <v>1486.98</v>
+        <v>1488.68</v>
       </c>
       <c r="G452" s="12" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>1195.68</v>
       </c>
       <c r="F453" s="11" t="n">
-        <v>1177.03</v>
+        <v>1176.44</v>
       </c>
       <c r="G453" s="14" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>1659.44</v>
       </c>
       <c r="F454" s="11" t="n">
-        <v>1727.36</v>
+        <v>1729.44</v>
       </c>
       <c r="G454" s="14" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>443.64</v>
       </c>
       <c r="F455" s="11" t="n">
-        <v>487.09</v>
+        <v>486.57</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>4009.41</v>
       </c>
       <c r="F458" s="11" t="n">
-        <v>3455.8</v>
+        <v>3464.61</v>
       </c>
       <c r="G458" s="12" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>2853.28</v>
       </c>
       <c r="F459" s="11" t="n">
-        <v>2773.93</v>
+        <v>2774.2</v>
       </c>
       <c r="G459" s="12" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>3476.46</v>
       </c>
       <c r="F460" s="11" t="n">
-        <v>3216.89</v>
+        <v>3214.5</v>
       </c>
       <c r="G460" s="12" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>757.58</v>
       </c>
       <c r="F461" s="11" t="n">
-        <v>781.99</v>
+        <v>782.3099999999999</v>
       </c>
       <c r="G461" s="12" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>4225.94</v>
       </c>
       <c r="F462" s="11" t="n">
-        <v>3986.4</v>
+        <v>3985.91</v>
       </c>
       <c r="G462" s="14" t="inlineStr">
         <is>
@@ -21099,10 +21099,10 @@
         <v>360.94</v>
       </c>
       <c r="E464" s="11" t="n">
-        <v>352.34</v>
+        <v>352.99</v>
       </c>
       <c r="F464" s="11" t="n">
-        <v>362.59</v>
+        <v>425.52</v>
       </c>
       <c r="G464" s="12" t="inlineStr">
         <is>
@@ -21114,9 +21114,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I464" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I464" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J464" s="13" t="inlineStr">
@@ -21146,7 +21146,7 @@
         <v>4296.48</v>
       </c>
       <c r="F465" s="11" t="n">
-        <v>3948.64</v>
+        <v>3947.07</v>
       </c>
       <c r="G465" s="12" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>1533.76</v>
       </c>
       <c r="F466" s="11" t="n">
-        <v>1422.44</v>
+        <v>1422.26</v>
       </c>
       <c r="G466" s="14" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>4075.85</v>
       </c>
       <c r="F468" s="11" t="n">
-        <v>4313.73</v>
+        <v>4309.42</v>
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>24.77</v>
       </c>
       <c r="F469" s="11" t="n">
-        <v>25.91</v>
+        <v>25.89</v>
       </c>
       <c r="G469" s="12" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>571.17</v>
       </c>
       <c r="F470" s="11" t="n">
-        <v>534.48</v>
+        <v>535.34</v>
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>3537.66</v>
       </c>
       <c r="F472" s="11" t="n">
-        <v>3441.77</v>
+        <v>3441.25</v>
       </c>
       <c r="G472" s="14" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>1449.98</v>
       </c>
       <c r="F473" s="11" t="n">
-        <v>1628.02</v>
+        <v>1627.79</v>
       </c>
       <c r="G473" s="14" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>25.83</v>
       </c>
       <c r="F474" s="11" t="n">
-        <v>28.12</v>
+        <v>28.07</v>
       </c>
       <c r="G474" s="12" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>11703.11</v>
       </c>
       <c r="F475" s="11" t="n">
-        <v>11858.45</v>
+        <v>11850.58</v>
       </c>
       <c r="G475" s="12" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>170.92</v>
       </c>
       <c r="F476" s="11" t="n">
-        <v>161.21</v>
+        <v>161.24</v>
       </c>
       <c r="G476" s="12" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>1308.28</v>
       </c>
       <c r="F477" s="11" t="n">
-        <v>1346.07</v>
+        <v>1345.44</v>
       </c>
       <c r="G477" s="12" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>1114.57</v>
       </c>
       <c r="F478" s="11" t="n">
-        <v>1139.2</v>
+        <v>1138.1</v>
       </c>
       <c r="G478" s="12" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>647.16</v>
       </c>
       <c r="F479" s="11" t="n">
-        <v>676.21</v>
+        <v>676.15</v>
       </c>
       <c r="G479" s="12" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>452.13</v>
       </c>
       <c r="F481" s="11" t="n">
-        <v>420.85</v>
+        <v>420.28</v>
       </c>
       <c r="G481" s="12" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>975.79</v>
       </c>
       <c r="F482" s="11" t="n">
-        <v>1062.12</v>
+        <v>1061.98</v>
       </c>
       <c r="G482" s="14" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>486.19</v>
       </c>
       <c r="F483" s="11" t="n">
-        <v>471.27</v>
+        <v>471.03</v>
       </c>
       <c r="G483" s="12" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>493.93</v>
       </c>
       <c r="F484" s="11" t="n">
-        <v>538.96</v>
+        <v>539.09</v>
       </c>
       <c r="G484" s="14" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>1133.99</v>
       </c>
       <c r="F485" s="11" t="n">
-        <v>1036.99</v>
+        <v>1036.71</v>
       </c>
       <c r="G485" s="12" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>119.94</v>
       </c>
       <c r="F486" s="11" t="n">
-        <v>124.14</v>
+        <v>124.07</v>
       </c>
       <c r="G486" s="12" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>1350.92</v>
       </c>
       <c r="F487" s="11" t="n">
-        <v>1370.23</v>
+        <v>1369.59</v>
       </c>
       <c r="G487" s="14" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>576.5599999999999</v>
       </c>
       <c r="F488" s="11" t="n">
-        <v>503.59</v>
+        <v>503.27</v>
       </c>
       <c r="G488" s="14" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>3114.39</v>
       </c>
       <c r="F489" s="11" t="n">
-        <v>3017.87</v>
+        <v>3017.48</v>
       </c>
       <c r="G489" s="12" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>1147.1</v>
       </c>
       <c r="F490" s="11" t="n">
-        <v>941.5</v>
+        <v>940.41</v>
       </c>
       <c r="G490" s="12" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>131.47</v>
       </c>
       <c r="F491" s="11" t="n">
-        <v>128.48</v>
+        <v>128.32</v>
       </c>
       <c r="G491" s="12" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>888.0700000000001</v>
       </c>
       <c r="F492" s="11" t="n">
-        <v>983.34</v>
+        <v>982.61</v>
       </c>
       <c r="G492" s="14" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>201.6</v>
       </c>
       <c r="F493" s="11" t="n">
-        <v>224.02</v>
+        <v>224.31</v>
       </c>
       <c r="G493" s="12" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>1481.73</v>
       </c>
       <c r="F494" s="11" t="n">
-        <v>1419.94</v>
+        <v>1417.6</v>
       </c>
       <c r="G494" s="12" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>20.95</v>
       </c>
       <c r="F495" s="11" t="n">
-        <v>20.67</v>
+        <v>20.66</v>
       </c>
       <c r="G495" s="12" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>85.94</v>
       </c>
       <c r="F496" s="11" t="n">
-        <v>93.23</v>
+        <v>93.3</v>
       </c>
       <c r="G496" s="12" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>533.8099999999999</v>
       </c>
       <c r="F497" s="11" t="n">
-        <v>640.91</v>
+        <v>640.23</v>
       </c>
       <c r="G497" s="14" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>1550.48</v>
       </c>
       <c r="F498" s="11" t="n">
-        <v>1463.25</v>
+        <v>1458.53</v>
       </c>
       <c r="G498" s="12" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>14552.84</v>
       </c>
       <c r="F499" s="11" t="n">
-        <v>14034.82</v>
+        <v>13997.99</v>
       </c>
       <c r="G499" s="12" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>956.8</v>
       </c>
       <c r="F500" s="11" t="n">
-        <v>934.88</v>
+        <v>934.46</v>
       </c>
       <c r="G500" s="12" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>481.35</v>
       </c>
       <c r="F501" s="11" t="n">
-        <v>443.18</v>
+        <v>442.79</v>
       </c>
       <c r="G501" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Jun-2026  10:29:25    |    Closing Price Date: 08-Jun-2026</t>
+          <t>Scan Run: 08-Jun-2026  10:50:11    |    Closing Price Date: 08-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Jun-2026  10:29:25</t>
+          <t>08-Jun-2026  10:50:11</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Jun-2026  10:50:11    |    Closing Price Date: 08-Jun-2026</t>
+          <t>Scan Run: 08-Jun-2026  14:50:00    |    Closing Price Date: 08-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Jun-2026  10:50:11</t>
+          <t>08-Jun-2026  14:50:00</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Jun-2026  05:48:14    |    Closing Price Date: 09-Jun-2026</t>
+          <t>Scan Run: 09-Jun-2026  06:05:02    |    Closing Price Date: 09-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         <v>36.8</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>42.8</v>
+        <v>42.2</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>49</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Jun-2026  05:48:14</t>
+          <t>09-Jun-2026  06:05:02</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 42.8% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 42.2% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 214 of 500 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 211 of 500 stocks</t>
         </is>
       </c>
     </row>
@@ -765,16 +765,16 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1774.9</v>
+        <v>1779.1</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1715</v>
+        <v>1715.4</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1664.4</v>
+        <v>1664.56</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1495.11</v>
+        <v>1495.16</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1065.4</v>
+        <v>1060.9</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1084.56</v>
+        <v>1084.13</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1077.18</v>
+        <v>1077</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1074.93</v>
+        <v>1074.89</v>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>31720</v>
+        <v>31790</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>32277.13</v>
+        <v>32283.79</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>32450.77</v>
+        <v>32453.52</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>32351.3</v>
+        <v>32352</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>7010</v>
+        <v>7004.5</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>6966.63</v>
+        <v>6966.11</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>6765.45</v>
+        <v>6765.24</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>6005.79</v>
+        <v>6005.74</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -941,16 +941,16 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1315.8</v>
+        <v>1315.5</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1365.12</v>
+        <v>1365.09</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1401.58</v>
+        <v>1401.56</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1593.98</v>
+        <v>1593.97</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -985,16 +985,16 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>352.6</v>
+        <v>349.4</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>318.36</v>
+        <v>318.05</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>296.47</v>
+        <v>296.34</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>263.06</v>
+        <v>263.03</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4469.7</v>
+        <v>4463.5</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>4313.56</v>
+        <v>4312.97</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>4093.26</v>
+        <v>4093.02</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>3758.8</v>
+        <v>3758.74</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1807</v>
+        <v>1803.3</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1849.04</v>
+        <v>1848.69</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1909.39</v>
+        <v>1909.24</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1879.22</v>
+        <v>1879.18</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>972</v>
+        <v>970.15</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>981.72</v>
+        <v>981.55</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>981.73</v>
+        <v>981.66</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>912.86</v>
+        <v>912.84</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>188.02</v>
+        <v>187.45</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>192.55</v>
+        <v>192.5</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>194.34</v>
+        <v>194.32</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>216.78</v>
@@ -1205,16 +1205,16 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>462.55</v>
+        <v>461.55</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>472.28</v>
+        <v>472.19</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>475.96</v>
+        <v>475.92</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>475.19</v>
+        <v>475.18</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1249,16 +1249,16 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>437.9</v>
+        <v>436.45</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>466.45</v>
+        <v>466.31</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>461.1</v>
+        <v>461.04</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>426.73</v>
+        <v>426.72</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1255.7</v>
+        <v>1256.8</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1329.36</v>
+        <v>1329.46</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1331.45</v>
+        <v>1331.5</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1440.42</v>
+        <v>1440.43</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>25950</v>
+        <v>25910</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>26636.34</v>
+        <v>26632.53</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>26651.83</v>
+        <v>26650.26</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>27944.05</v>
+        <v>27943.65</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>892.4</v>
+        <v>890.95</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>886.8200000000001</v>
+        <v>886.6799999999999</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>885.26</v>
+        <v>885.2</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>940.99</v>
+        <v>940.98</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1425,16 +1425,16 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>3229</v>
+        <v>3224.4</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>3023.84</v>
+        <v>3023.4</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>2748.97</v>
+        <v>2748.79</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>2101.6</v>
+        <v>2101.56</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1572.1</v>
+        <v>1572.7</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>1468.64</v>
+        <v>1468.7</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>1343.44</v>
+        <v>1343.46</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>1089.23</v>
+        <v>1089.24</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2962.5</v>
+        <v>2976.8</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>2835.49</v>
+        <v>2836.85</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>2584.85</v>
+        <v>2585.41</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>2353.18</v>
+        <v>2353.33</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1496</v>
+        <v>1494.9</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1422.25</v>
+        <v>1422.14</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1291.31</v>
+        <v>1291.26</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1083.73</v>
+        <v>1083.72</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1797.7</v>
+        <v>1796</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>1780.44</v>
+        <v>1780.28</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>1691.1</v>
+        <v>1691.04</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1514.44</v>
+        <v>1514.42</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>226.23</v>
+        <v>226.3</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>228.68</v>
+        <v>228.69</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>211.39</v>
+        <v>211.4</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>166.96</v>
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>740.6</v>
+        <v>743.7</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>707.67</v>
+        <v>707.97</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>653.62</v>
+        <v>653.74</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>603.08</v>
+        <v>603.11</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>348.45</v>
+        <v>347.9</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>352.92</v>
+        <v>352.87</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>347.83</v>
+        <v>347.81</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>321.31</v>
+        <v>321.3</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>59.84</v>
+        <v>59.66</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>62.48</v>
+        <v>62.46</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>63.35</v>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>98.45</v>
+        <v>98.48</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>101.14</v>
+        <v>101.15</v>
       </c>
       <c r="E26" s="11" t="n">
         <v>102.72</v>
@@ -1865,16 +1865,16 @@
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>1232</v>
+        <v>1226.6</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>1273</v>
+        <v>1272.49</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>1310.77</v>
+        <v>1310.56</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1507.7</v>
+        <v>1507.64</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1909,16 +1909,16 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1060.2</v>
+        <v>1059.6</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1035.71</v>
+        <v>1035.65</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1011.72</v>
+        <v>1011.7</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>891.55</v>
+        <v>891.54</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>3509.8</v>
+        <v>3487</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>2957.75</v>
+        <v>2955.58</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>2531.32</v>
+        <v>2530.43</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1841.2</v>
+        <v>1840.97</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>772.45</v>
+        <v>773.7</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>736.47</v>
+        <v>736.58</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>709.47</v>
+        <v>709.52</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>714.4400000000001</v>
+        <v>714.45</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>187.6</v>
+        <v>187.67</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>195.85</v>
+        <v>195.86</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>198.01</v>
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>315.3</v>
+        <v>314.85</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>321.18</v>
+        <v>321.13</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>320.94</v>
+        <v>320.92</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>354.48</v>
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1481.2</v>
+        <v>1476.7</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1473.8</v>
+        <v>1473.37</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>1468.34</v>
+        <v>1468.16</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1577.88</v>
+        <v>1577.84</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>3010</v>
+        <v>3029.5</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>3003.25</v>
+        <v>3005.11</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>2969.59</v>
+        <v>2970.35</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>2793.61</v>
+        <v>2793.8</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2217,20 +2217,20 @@
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>5397.5</v>
+        <v>5379</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>5383.67</v>
+        <v>5381.91</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>5423.16</v>
+        <v>5422.43</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5387.92</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>5387.74</v>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
@@ -2238,9 +2238,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J35" s="13" t="inlineStr">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>582</v>
+        <v>581.7</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>556.16</v>
+        <v>556.13</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>536.62</v>
+        <v>536.61</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>510.99</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>828.3</v>
+        <v>829.05</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>853.26</v>
+        <v>853.33</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>842.6</v>
+        <v>842.63</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>878.51</v>
@@ -2349,16 +2349,16 @@
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>7736</v>
+        <v>7728.5</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>7677.75</v>
+        <v>7677.04</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>7607.98</v>
+        <v>7607.69</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>7248.13</v>
+        <v>7248.06</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>413.65</v>
+        <v>413.7</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>433.6</v>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1732.7</v>
+        <v>1730</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1766.03</v>
+        <v>1765.78</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1735.55</v>
+        <v>1735.44</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1546.41</v>
+        <v>1546.38</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>540.55</v>
+        <v>537.85</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>529.26</v>
+        <v>529</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>515.26</v>
+        <v>515.15</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>527.0700000000001</v>
+        <v>527.05</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>329.2</v>
+        <v>329.55</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>328.87</v>
+        <v>328.91</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>309.44</v>
+        <v>309.45</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>269.73</v>
@@ -2569,16 +2569,16 @@
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>770.4</v>
+        <v>772.65</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>764.33</v>
+        <v>764.55</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>746.9400000000001</v>
+        <v>747.03</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>716.24</v>
+        <v>716.27</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2613,16 +2613,16 @@
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1292.2</v>
+        <v>1290.4</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1335.49</v>
+        <v>1335.31</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1325.14</v>
+        <v>1325.07</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1226.15</v>
+        <v>1226.13</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2657,16 +2657,16 @@
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>13632</v>
+        <v>13630</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>13057.84</v>
+        <v>13057.65</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>12201.85</v>
+        <v>12201.77</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>10008.31</v>
+        <v>10008.29</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2701,16 +2701,16 @@
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>8457</v>
+        <v>8443.5</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>8192.379999999999</v>
+        <v>8191.1</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>7961.8</v>
+        <v>7961.27</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>7530.53</v>
+        <v>7530.4</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>387.4</v>
+        <v>386.7</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>393.16</v>
+        <v>393.1</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>407.67</v>
+        <v>407.65</v>
       </c>
       <c r="F47" s="11" t="n">
         <v>443.92</v>
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>250.35</v>
+        <v>249.85</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>259.68</v>
+        <v>259.63</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>254.32</v>
+        <v>254.3</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>268.06</v>
+        <v>268.05</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>879.35</v>
+        <v>878.95</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>876.33</v>
+        <v>876.3</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>867.34</v>
+        <v>867.3200000000001</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>870.61</v>
+        <v>870.6</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2877,16 +2877,16 @@
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>142.57</v>
+        <v>142.68</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>150.88</v>
+        <v>150.89</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>158.75</v>
+        <v>158.76</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>157.11</v>
+        <v>157.12</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2965,16 +2965,16 @@
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>794.95</v>
+        <v>798.9</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>745.04</v>
+        <v>745.42</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>718.5</v>
+        <v>718.65</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>647.73</v>
+        <v>647.77</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3009,16 +3009,16 @@
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>1522.8</v>
+        <v>1520.2</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>1540.1</v>
+        <v>1539.85</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>1552.19</v>
+        <v>1552.09</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1511.56</v>
+        <v>1511.54</v>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
@@ -3053,16 +3053,16 @@
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>1009.95</v>
+        <v>1012.5</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>961.36</v>
+        <v>961.6</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>903.6799999999999</v>
+        <v>903.78</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>719.36</v>
+        <v>719.39</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3097,16 +3097,16 @@
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>6626.5</v>
+        <v>6606.5</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>6796.14</v>
+        <v>6794.24</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>6730.13</v>
+        <v>6729.34</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>6423.23</v>
+        <v>6423.04</v>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
@@ -3141,16 +3141,16 @@
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>1460.1</v>
+        <v>1461.9</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>1454.33</v>
+        <v>1454.5</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>1414.97</v>
+        <v>1415.05</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1270.56</v>
+        <v>1270.58</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>466.85</v>
+        <v>467.2</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>475.39</v>
+        <v>475.42</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>480.17</v>
+        <v>480.19</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>500.39</v>
+        <v>500.4</v>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
@@ -3229,16 +3229,16 @@
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>4103.5</v>
+        <v>4099.9</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>4166.9</v>
+        <v>4166.55</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>4199.31</v>
+        <v>4199.16</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4097.06</v>
+        <v>4097.02</v>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
@@ -3273,16 +3273,16 @@
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>1278.9</v>
+        <v>1277</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>1274.07</v>
+        <v>1273.89</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>1280.95</v>
+        <v>1280.87</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1248.66</v>
+        <v>1248.64</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3317,16 +3317,16 @@
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1753.2</v>
+        <v>1751.4</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1775.6</v>
+        <v>1775.43</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1760.51</v>
+        <v>1760.44</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1770.38</v>
+        <v>1770.36</v>
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>263.65</v>
+        <v>263.5</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>266.44</v>
+        <v>266.43</v>
       </c>
       <c r="E61" s="11" t="n">
         <v>270.36</v>
@@ -3405,16 +3405,16 @@
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>4002.2</v>
+        <v>3999.4</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>4004.75</v>
+        <v>4004.48</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>3741.89</v>
+        <v>3741.78</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3026.13</v>
+        <v>3026.1</v>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
@@ -3449,16 +3449,16 @@
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>10338</v>
+        <v>10309</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>10288.4</v>
+        <v>10285.64</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>10005.25</v>
+        <v>10004.12</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>9286.620000000001</v>
+        <v>9286.34</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>878.3</v>
+        <v>878.15</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>901.6799999999999</v>
+        <v>901.67</v>
       </c>
       <c r="E64" s="11" t="n">
         <v>913.1</v>
@@ -3537,16 +3537,16 @@
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>1682.6</v>
+        <v>1687.5</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>1744.91</v>
+        <v>1745.38</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>1778</v>
+        <v>1778.19</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1890.53</v>
+        <v>1890.58</v>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
@@ -3581,16 +3581,16 @@
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>10130</v>
+        <v>10137</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>10271.78</v>
+        <v>10272.45</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>10289.7</v>
+        <v>10289.98</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>11000.31</v>
+        <v>11000.38</v>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
@@ -3625,13 +3625,13 @@
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>82.73</v>
+        <v>82.98</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>84.18000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>85.17</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="F67" s="11" t="n">
         <v>94.20999999999999</v>
@@ -3669,16 +3669,16 @@
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>2121.6</v>
+        <v>2132.1</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>2170.08</v>
+        <v>2171.08</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>2204.76</v>
+        <v>2205.17</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2321.22</v>
+        <v>2321.32</v>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
@@ -3713,16 +3713,16 @@
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>533.45</v>
+        <v>532.4</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>532.16</v>
+        <v>532.0599999999999</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>518.62</v>
+        <v>518.58</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>493.74</v>
+        <v>493.72</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3757,16 +3757,16 @@
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>205.1</v>
+        <v>204.19</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>201.26</v>
+        <v>201.17</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>191.01</v>
+        <v>190.97</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>171.02</v>
+        <v>171.01</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>267.5</v>
+        <v>267.6</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>260.41</v>
+        <v>260.42</v>
       </c>
       <c r="E71" s="11" t="n">
         <v>262.87</v>
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>144.28</v>
+        <v>144.18</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>139.54</v>
+        <v>139.53</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>140.76</v>
+        <v>140.75</v>
       </c>
       <c r="F72" s="11" t="n">
         <v>136.36</v>
@@ -3889,13 +3889,13 @@
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>82.69</v>
+        <v>83.44</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>78.68000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>75.76000000000001</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
         <v>65.25</v>
@@ -3933,16 +3933,16 @@
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>663.8</v>
+        <v>661.65</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>680.5</v>
+        <v>680.29</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>705.86</v>
+        <v>705.78</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>872.42</v>
+        <v>872.4</v>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
@@ -3977,16 +3977,16 @@
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>4286.9</v>
+        <v>4281.6</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>4437.58</v>
+        <v>4437.08</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>4521.58</v>
+        <v>4521.37</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>4679.22</v>
+        <v>4679.16</v>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
@@ -4021,16 +4021,16 @@
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>231.21</v>
+        <v>231.97</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>216.56</v>
+        <v>216.64</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>209.86</v>
+        <v>209.89</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>178.34</v>
+        <v>178.35</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>502.2</v>
+        <v>502.05</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>500.74</v>
+        <v>500.73</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>488.31</v>
+        <v>488.3</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>497.34</v>
+        <v>497.33</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>1194.4</v>
+        <v>1194.2</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>1261.03</v>
+        <v>1261.01</v>
       </c>
       <c r="E78" s="11" t="n">
         <v>1300.18</v>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>411.45</v>
+        <v>411.6</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>416.66</v>
+        <v>416.67</v>
       </c>
       <c r="E79" s="11" t="n">
         <v>424.26</v>
@@ -4197,16 +4197,16 @@
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>1937.4</v>
+        <v>1941.1</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>1917.59</v>
+        <v>1917.94</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1869.84</v>
+        <v>1869.98</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1606.01</v>
+        <v>1606.05</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>388.55</v>
+        <v>389.4</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>395.97</v>
+        <v>396.05</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>364.93</v>
+        <v>364.96</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>296.07</v>
+        <v>296.08</v>
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
@@ -4285,13 +4285,13 @@
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>288</v>
+        <v>287.65</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>295.73</v>
+        <v>295.69</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>302.99</v>
+        <v>302.98</v>
       </c>
       <c r="F82" s="11" t="n">
         <v>316.33</v>
@@ -4329,16 +4329,16 @@
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>1833.16</v>
+        <v>1833.35</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>1850.84</v>
+        <v>1850.92</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1898.89</v>
+        <v>1898.91</v>
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
@@ -4373,16 +4373,16 @@
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>1472.5</v>
+        <v>1482.3</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>1509.13</v>
+        <v>1510.06</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>1531.98</v>
+        <v>1532.36</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1608.03</v>
+        <v>1608.12</v>
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
@@ -4417,16 +4417,16 @@
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>651.2</v>
+        <v>652.35</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>654.7</v>
+        <v>654.8099999999999</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>655.27</v>
+        <v>655.3099999999999</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>678.02</v>
+        <v>678.03</v>
       </c>
       <c r="G85" s="14" t="inlineStr">
         <is>
@@ -4461,13 +4461,13 @@
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>191.56</v>
+        <v>191.33</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>191.16</v>
+        <v>191.14</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>189.19</v>
+        <v>189.18</v>
       </c>
       <c r="F86" s="11" t="n">
         <v>167.03</v>
@@ -4505,20 +4505,20 @@
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>414.9</v>
+        <v>413.85</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>414.35</v>
+        <v>414.25</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>399.15</v>
+        <v>399.11</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>378.07</v>
-      </c>
-      <c r="G87" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>378.06</v>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
@@ -4549,13 +4549,13 @@
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>322.35</v>
+        <v>322.2</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>330.97</v>
+        <v>330.95</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>346.55</v>
+        <v>346.54</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>377.36</v>
@@ -4593,16 +4593,16 @@
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>4679.7</v>
+        <v>4655</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>4849.39</v>
+        <v>4847.03</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>5053.21</v>
+        <v>5052.24</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>5462.97</v>
+        <v>5462.73</v>
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>457.9</v>
+        <v>458.85</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>455.18</v>
+        <v>455.27</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>441.62</v>
+        <v>441.65</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>516.6</v>
+        <v>516.61</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4681,16 +4681,16 @@
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>1562.9</v>
+        <v>1562</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>1625.21</v>
+        <v>1625.13</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>1690.83</v>
+        <v>1690.79</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1785.42</v>
+        <v>1785.41</v>
       </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
@@ -4725,16 +4725,16 @@
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>1486.6</v>
+        <v>1483.1</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>1510.1</v>
+        <v>1509.77</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>1527.96</v>
+        <v>1527.82</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1669.71</v>
+        <v>1669.68</v>
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
@@ -4769,16 +4769,16 @@
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>37675</v>
+        <v>37770</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>36795.53</v>
+        <v>36804.58</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>36211.85</v>
+        <v>36215.58</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>35420.67</v>
+        <v>35421.62</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4813,16 +4813,16 @@
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>219.04</v>
+        <v>218.61</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>226.14</v>
+        <v>226.1</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>232.25</v>
+        <v>232.23</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>275.59</v>
+        <v>275.58</v>
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
@@ -4857,16 +4857,16 @@
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>648.95</v>
+        <v>645.05</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>672.0700000000001</v>
+        <v>671.7</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>701.63</v>
+        <v>701.48</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>804.05</v>
+        <v>804.01</v>
       </c>
       <c r="G95" s="14" t="inlineStr">
         <is>
@@ -4901,16 +4901,16 @@
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>5085</v>
+        <v>5078</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>5256.14</v>
+        <v>5255.47</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>5448.88</v>
+        <v>5448.6</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>5636.27</v>
+        <v>5636.2</v>
       </c>
       <c r="G96" s="14" t="inlineStr">
         <is>
@@ -4945,16 +4945,16 @@
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>849.8</v>
+        <v>850.2</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>872.1799999999999</v>
+        <v>872.21</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>931.58</v>
+        <v>931.6</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1264.24</v>
+        <v>1264.25</v>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
@@ -4989,16 +4989,16 @@
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>1147.4</v>
+        <v>1149.8</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>1097.45</v>
+        <v>1097.68</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>1089.11</v>
+        <v>1089.21</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>988.58</v>
+        <v>988.61</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5033,13 +5033,13 @@
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>172.58</v>
+        <v>172.4</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>179.28</v>
+        <v>179.27</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>175.78</v>
+        <v>175.77</v>
       </c>
       <c r="F99" s="11" t="n">
         <v>165.42</v>
@@ -5077,16 +5077,16 @@
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>917.45</v>
+        <v>913.4</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>889.13</v>
+        <v>888.74</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>833.47</v>
+        <v>833.3099999999999</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>734.88</v>
+        <v>734.84</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>440.4</v>
+        <v>440.45</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>453.38</v>
@@ -5165,16 +5165,16 @@
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>3854</v>
+        <v>3848.4</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>3975.16</v>
+        <v>3974.63</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>4075.4</v>
+        <v>4075.18</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>4378.11</v>
+        <v>4378.05</v>
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>824.2</v>
+        <v>824.55</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>834.1799999999999</v>
+        <v>834.22</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>847.5</v>
+        <v>847.51</v>
       </c>
       <c r="F103" s="11" t="n">
         <v>835.3200000000001</v>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>135.26</v>
+        <v>135.27</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>132.32</v>
+        <v>132.33</v>
       </c>
       <c r="E104" s="11" t="n">
         <v>134.52</v>
@@ -5297,13 +5297,13 @@
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>141.1</v>
+        <v>140.85</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>138.79</v>
+        <v>138.77</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>140.45</v>
+        <v>140.44</v>
       </c>
       <c r="F105" s="11" t="n">
         <v>134.22</v>
@@ -5341,16 +5341,16 @@
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>2205.2</v>
+        <v>2210.7</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>2004.54</v>
+        <v>2005.06</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>1895.43</v>
+        <v>1895.65</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1862.01</v>
+        <v>1862.06</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5385,16 +5385,16 @@
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>202.2</v>
+        <v>201.52</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>194.92</v>
+        <v>194.85</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>188.39</v>
+        <v>188.36</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>181.3</v>
+        <v>181.29</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>1057.7</v>
+        <v>1054.9</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>1032.08</v>
+        <v>1031.81</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>980.85</v>
+        <v>980.74</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>908.5700000000001</v>
+        <v>908.54</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5473,16 +5473,16 @@
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>2149.1</v>
+        <v>2141.9</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1871.78</v>
+        <v>1871.1</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>1853.01</v>
+        <v>1852.73</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>2067.56</v>
+        <v>2067.49</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>183.2</v>
+        <v>183.14</v>
       </c>
       <c r="D110" s="11" t="n">
         <v>183.35</v>
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>3120.9</v>
+        <v>3115.6</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>3233.06</v>
+        <v>3232.56</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>3350.23</v>
+        <v>3350.03</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>3484.08</v>
+        <v>3484.03</v>
       </c>
       <c r="G111" s="14" t="inlineStr">
         <is>
@@ -5605,16 +5605,16 @@
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>1173.5</v>
+        <v>1172</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>999.91</v>
+        <v>999.77</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>868.4</v>
+        <v>868.34</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>746.53</v>
+        <v>746.52</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>30.87</v>
+        <v>30.91</v>
       </c>
       <c r="D113" s="11" t="n">
         <v>31.7</v>
@@ -5693,16 +5693,16 @@
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>1202.9</v>
+        <v>1201.8</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>1222.23</v>
+        <v>1222.13</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>1244.96</v>
+        <v>1244.91</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1343.13</v>
+        <v>1343.12</v>
       </c>
       <c r="G114" s="14" t="inlineStr">
         <is>
@@ -5737,16 +5737,16 @@
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>751.25</v>
+        <v>750.8</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>776.76</v>
+        <v>776.72</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>780.33</v>
+        <v>780.3200000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>826.0700000000001</v>
+        <v>826.0599999999999</v>
       </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
@@ -5781,13 +5781,13 @@
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>449.8</v>
+        <v>450.05</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>458.42</v>
+        <v>458.44</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>452.94</v>
+        <v>452.95</v>
       </c>
       <c r="F116" s="11" t="n">
         <v>469.4</v>
@@ -5825,13 +5825,13 @@
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>1203.3</v>
+        <v>1203.2</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>1106.15</v>
+        <v>1106.14</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>1053.89</v>
+        <v>1053.88</v>
       </c>
       <c r="F117" s="11" t="n">
         <v>909.45</v>
@@ -5869,16 +5869,16 @@
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>652.4</v>
+        <v>651.35</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>669.8099999999999</v>
+        <v>669.71</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>679.55</v>
+        <v>679.51</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>707.75</v>
+        <v>707.74</v>
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
@@ -5913,16 +5913,16 @@
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1420.1</v>
+        <v>1422.4</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1542.02</v>
+        <v>1542.24</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>1582.31</v>
+        <v>1582.4</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1690.4</v>
+        <v>1690.42</v>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
@@ -5957,16 +5957,16 @@
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>1467.2</v>
+        <v>1466.7</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>1520.75</v>
+        <v>1520.7</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>1547.92</v>
+        <v>1547.9</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1585.38</v>
+        <v>1585.37</v>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
@@ -6001,16 +6001,16 @@
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>1388.9</v>
+        <v>1390.1</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>1375.36</v>
+        <v>1375.47</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>1343.95</v>
+        <v>1344</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1380.15</v>
+        <v>1380.16</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6089,13 +6089,13 @@
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>768.7</v>
+        <v>768</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>780</v>
+        <v>779.9299999999999</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>778.89</v>
+        <v>778.86</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>885.05</v>
@@ -6133,16 +6133,16 @@
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>464.3</v>
+        <v>464.9</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>465.55</v>
+        <v>465.6</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>458.5</v>
+        <v>458.52</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>421.33</v>
+        <v>421.34</v>
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>1412.5</v>
+        <v>1411.7</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>1499.54</v>
+        <v>1499.46</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>1525.91</v>
+        <v>1525.88</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1565.07</v>
+        <v>1565.06</v>
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
@@ -6221,16 +6221,16 @@
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>1423.5</v>
+        <v>1424.6</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>1394.9</v>
+        <v>1395</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>1345.62</v>
+        <v>1345.66</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1467.15</v>
+        <v>1467.17</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6265,16 +6265,16 @@
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>430.2</v>
+        <v>430.85</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>429.73</v>
+        <v>429.79</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>415.02</v>
+        <v>415.05</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>547.6900000000001</v>
+        <v>547.7</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6309,16 +6309,16 @@
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>2011</v>
+        <v>2010.3</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>2047.77</v>
+        <v>2047.7</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>2055.72</v>
+        <v>2055.7</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>2119.91</v>
+        <v>2119.9</v>
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
@@ -6353,16 +6353,16 @@
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>744.9</v>
+        <v>746.2</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>765.59</v>
+        <v>765.71</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>753.0700000000001</v>
+        <v>753.12</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>736.5</v>
+        <v>736.51</v>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
@@ -6397,16 +6397,16 @@
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>1217.6</v>
+        <v>1220.8</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>1156.05</v>
+        <v>1156.35</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>1141.98</v>
+        <v>1142.1</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1287.43</v>
+        <v>1287.46</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6441,16 +6441,16 @@
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>447.6</v>
+        <v>446.25</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>474.41</v>
+        <v>474.28</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>485.69</v>
+        <v>485.64</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>503.57</v>
+        <v>503.56</v>
       </c>
       <c r="G131" s="14" t="inlineStr">
         <is>
@@ -6529,16 +6529,16 @@
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>8940.5</v>
+        <v>8919.5</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>8732.940000000001</v>
+        <v>8730.940000000001</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>8275.129999999999</v>
+        <v>8274.299999999999</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>7326.53</v>
+        <v>7326.32</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>1265</v>
+        <v>1265.1</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>1292.95</v>
+        <v>1292.96</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>1291.01</v>
+        <v>1291.02</v>
       </c>
       <c r="F134" s="11" t="n">
         <v>1265.55</v>
@@ -6617,16 +6617,16 @@
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>261.45</v>
+        <v>260.1</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>275.7</v>
+        <v>275.58</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>271.39</v>
+        <v>271.33</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>275.33</v>
+        <v>275.32</v>
       </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
@@ -6661,16 +6661,16 @@
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>5573.5</v>
+        <v>5578</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>5578.44</v>
+        <v>5578.87</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>5310.69</v>
+        <v>5310.87</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>4560.34</v>
+        <v>4560.38</v>
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
@@ -6705,16 +6705,16 @@
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>864.95</v>
+        <v>865.25</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>894.4400000000001</v>
+        <v>894.47</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>903.6900000000001</v>
+        <v>903.7</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1019.6</v>
+        <v>1019.61</v>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
@@ -6749,13 +6749,13 @@
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1016.1</v>
+        <v>1016.6</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1072.34</v>
+        <v>1072.39</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1110.75</v>
+        <v>1110.77</v>
       </c>
       <c r="F138" s="11" t="n">
         <v>1140.36</v>
@@ -6793,13 +6793,13 @@
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>569.55</v>
+        <v>568.85</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>581.58</v>
+        <v>581.52</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>585.4400000000001</v>
+        <v>585.41</v>
       </c>
       <c r="F139" s="11" t="n">
         <v>640.21</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>2089.9</v>
+        <v>2090</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>2186.96</v>
+        <v>2186.97</v>
       </c>
       <c r="E140" s="11" t="n">
         <v>2250.88</v>
@@ -6881,16 +6881,16 @@
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>424.5</v>
+        <v>424.1</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>437.38</v>
+        <v>437.34</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>448.14</v>
+        <v>448.13</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>476.12</v>
+        <v>476.11</v>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
@@ -6925,16 +6925,16 @@
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>1662.4</v>
+        <v>1660</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>1753.03</v>
+        <v>1752.8</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>1827.36</v>
+        <v>1827.27</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1966.52</v>
+        <v>1966.5</v>
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
@@ -6969,16 +6969,16 @@
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>4342.1</v>
+        <v>4380</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>4060.47</v>
+        <v>4064.08</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>3836.78</v>
+        <v>3838.26</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>3152.69</v>
+        <v>3153.07</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7013,16 +7013,16 @@
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>1392.35</v>
+        <v>1392.64</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>1292.92</v>
+        <v>1293.03</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1237.99</v>
+        <v>1238.02</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7057,16 +7057,16 @@
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>1660.9</v>
+        <v>1667.9</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>1708.56</v>
+        <v>1709.22</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1677.01</v>
+        <v>1677.28</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1678.97</v>
+        <v>1679.04</v>
       </c>
       <c r="G145" s="14" t="inlineStr">
         <is>
@@ -7101,16 +7101,16 @@
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>440</v>
+        <v>438.95</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>449.74</v>
+        <v>449.64</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>450.1</v>
+        <v>450.06</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>425.82</v>
+        <v>425.81</v>
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
@@ -7145,13 +7145,13 @@
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>110.01</v>
+        <v>109.82</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>114.14</v>
+        <v>114.12</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>114.97</v>
+        <v>114.96</v>
       </c>
       <c r="F147" s="11" t="n">
         <v>131.22</v>
@@ -7189,16 +7189,16 @@
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>6725.5</v>
+        <v>6735</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>6655.97</v>
+        <v>6656.88</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>6543.29</v>
+        <v>6543.66</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>6340.82</v>
+        <v>6340.91</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7233,16 +7233,16 @@
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>11577</v>
+        <v>11556</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>11383.06</v>
+        <v>11381.06</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>11200.83</v>
+        <v>11200</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>12406.61</v>
+        <v>12406.4</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7277,16 +7277,16 @@
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>1561.2</v>
+        <v>1563.1</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>1574.34</v>
+        <v>1574.52</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>1527.22</v>
+        <v>1527.29</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1465.18</v>
+        <v>1465.2</v>
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
@@ -7321,16 +7321,16 @@
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>1282.9</v>
+        <v>1278.4</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>1292.41</v>
+        <v>1291.99</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>1287.92</v>
+        <v>1287.75</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>1260.63</v>
+        <v>1260.58</v>
       </c>
       <c r="G151" s="14" t="inlineStr">
         <is>
@@ -7365,13 +7365,13 @@
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>727</v>
+        <v>726.8</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>764.73</v>
+        <v>764.71</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>800.78</v>
+        <v>800.77</v>
       </c>
       <c r="F152" s="11" t="n">
         <v>887.5599999999999</v>
@@ -7409,16 +7409,16 @@
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>286.55</v>
+        <v>287.75</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>303.43</v>
+        <v>303.55</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>312.76</v>
+        <v>312.8</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>336.34</v>
+        <v>336.36</v>
       </c>
       <c r="G153" s="14" t="inlineStr">
         <is>
@@ -7453,25 +7453,25 @@
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>7153</v>
+        <v>7150</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>7137.13</v>
+        <v>7136.85</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>7150.15</v>
+        <v>7150.03</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>6899.59</v>
+        <v>6899.56</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H154" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H154" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I154" s="12" t="inlineStr">
@@ -7497,16 +7497,16 @@
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>531.8</v>
+        <v>530.7</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>514.11</v>
+        <v>514</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>490.77</v>
+        <v>490.73</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>482.22</v>
+        <v>482.21</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7541,13 +7541,13 @@
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>600.15</v>
+        <v>600</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>578.21</v>
+        <v>578.1900000000001</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>551.96</v>
+        <v>551.95</v>
       </c>
       <c r="F156" s="11" t="n">
         <v>509.79</v>
@@ -7585,10 +7585,10 @@
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>385.45</v>
+        <v>385.4</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>404.37</v>
+        <v>404.36</v>
       </c>
       <c r="E157" s="11" t="n">
         <v>422.76</v>
@@ -7629,16 +7629,16 @@
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>329.75</v>
+        <v>332.1</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>302.53</v>
+        <v>302.76</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>274.55</v>
+        <v>274.64</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>235.62</v>
+        <v>235.64</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7673,16 +7673,16 @@
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>2525.8</v>
+        <v>2520</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>2598.46</v>
+        <v>2597.91</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>2534.7</v>
+        <v>2534.47</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>2497.84</v>
+        <v>2497.78</v>
       </c>
       <c r="G159" s="14" t="inlineStr">
         <is>
@@ -7717,16 +7717,16 @@
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>237.63</v>
+        <v>237.09</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>235.8</v>
+        <v>235.75</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>231.09</v>
+        <v>231.06</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>209.29</v>
+        <v>209.28</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7761,13 +7761,13 @@
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>1365.3</v>
+        <v>1365</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>1365.32</v>
+        <v>1365.29</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>1364.63</v>
+        <v>1364.62</v>
       </c>
       <c r="F161" s="11" t="n">
         <v>1430.19</v>
@@ -7805,16 +7805,16 @@
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>2802.5</v>
+        <v>2782</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>2882.73</v>
+        <v>2880.78</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>3025.69</v>
+        <v>3024.89</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>3284.01</v>
+        <v>3283.81</v>
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
@@ -7849,10 +7849,10 @@
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>244.75</v>
+        <v>244.85</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>249.15</v>
+        <v>249.16</v>
       </c>
       <c r="E163" s="11" t="n">
         <v>249.55</v>
@@ -7893,16 +7893,16 @@
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>391.9</v>
+        <v>390.75</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>377.67</v>
+        <v>377.56</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>358.47</v>
+        <v>358.42</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>354.68</v>
+        <v>354.67</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>264.8</v>
+        <v>264.85</v>
       </c>
       <c r="D165" s="11" t="n">
         <v>266.42</v>
@@ -7981,16 +7981,16 @@
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>311.35</v>
+        <v>311.85</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>294.78</v>
+        <v>294.83</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>288.94</v>
+        <v>288.96</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>261.5</v>
+        <v>261.51</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8025,16 +8025,16 @@
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>868.35</v>
+        <v>869.45</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>877.9400000000001</v>
+        <v>878.05</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>868.04</v>
+        <v>868.09</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>850.45</v>
+        <v>850.46</v>
       </c>
       <c r="G167" s="14" t="inlineStr">
         <is>
@@ -8069,16 +8069,16 @@
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>1030.7</v>
+        <v>1032.1</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>1045.14</v>
+        <v>1045.27</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>1000.43</v>
+        <v>1000.48</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>889.79</v>
+        <v>889.8</v>
       </c>
       <c r="G168" s="14" t="inlineStr">
         <is>
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>254.25</v>
+        <v>254.2</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>257.34</v>
+        <v>257.33</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>248.92</v>
+        <v>248.91</v>
       </c>
       <c r="F169" s="11" t="n">
         <v>281.06</v>
@@ -8157,16 +8157,16 @@
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>423</v>
+        <v>426.8</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>444.08</v>
+        <v>444.44</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>446.95</v>
+        <v>447.1</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>505.93</v>
+        <v>505.96</v>
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
@@ -8201,16 +8201,16 @@
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>17313</v>
+        <v>17326</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>18917.28</v>
+        <v>18918.52</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>19857.77</v>
+        <v>19858.28</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>18863.77</v>
+        <v>18863.9</v>
       </c>
       <c r="G171" s="14" t="inlineStr">
         <is>
@@ -8245,16 +8245,16 @@
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>991.15</v>
+        <v>989.65</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>955.09</v>
+        <v>954.95</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>933.02</v>
+        <v>932.96</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>891.37</v>
+        <v>891.36</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8289,13 +8289,13 @@
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>166.97</v>
+        <v>167.08</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>164.81</v>
+        <v>164.82</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>161.93</v>
+        <v>161.94</v>
       </c>
       <c r="F173" s="11" t="n">
         <v>163</v>
@@ -8333,16 +8333,16 @@
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>4912.5</v>
+        <v>4929</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>4799.74</v>
+        <v>4801.32</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>4481.98</v>
+        <v>4482.63</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>3546.09</v>
+        <v>3546.25</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>101.77</v>
+        <v>101.57</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>98.65000000000001</v>
+        <v>98.63</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>97.23999999999999</v>
+        <v>97.23</v>
       </c>
       <c r="F175" s="11" t="n">
         <v>94.43000000000001</v>
@@ -8421,16 +8421,16 @@
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>1020.6</v>
+        <v>1021.4</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>1058.26</v>
+        <v>1058.33</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>1035.32</v>
+        <v>1035.35</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>979.28</v>
+        <v>979.29</v>
       </c>
       <c r="G176" s="14" t="inlineStr">
         <is>
@@ -8465,16 +8465,16 @@
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>634.25</v>
+        <v>638.8</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>685.97</v>
+        <v>686.4</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>700.21</v>
+        <v>700.39</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>622.15</v>
+        <v>622.2</v>
       </c>
       <c r="G177" s="14" t="inlineStr">
         <is>
@@ -8509,16 +8509,16 @@
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>2623.2</v>
+        <v>2629</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>2670.93</v>
+        <v>2671.48</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>2654.45</v>
+        <v>2654.68</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>2500.98</v>
+        <v>2501.03</v>
       </c>
       <c r="G178" s="14" t="inlineStr">
         <is>
@@ -8553,16 +8553,16 @@
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>384.55</v>
+        <v>383.85</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>386.93</v>
+        <v>386.86</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>386.78</v>
+        <v>386.75</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>380.9</v>
+        <v>380.89</v>
       </c>
       <c r="G179" s="14" t="inlineStr">
         <is>
@@ -8597,16 +8597,16 @@
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>7694</v>
+        <v>7689.5</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>7821.9</v>
+        <v>7821.47</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>7886.79</v>
+        <v>7886.62</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>8251.65</v>
+        <v>8251.610000000001</v>
       </c>
       <c r="G180" s="14" t="inlineStr">
         <is>
@@ -8641,16 +8641,16 @@
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>2277</v>
+        <v>2285</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>2188.38</v>
+        <v>2189.14</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>2023.07</v>
+        <v>2023.38</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>1842.42</v>
+        <v>1842.5</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8685,16 +8685,16 @@
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>2197.3</v>
+        <v>2198.4</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>2236.79</v>
+        <v>2236.9</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>2294.06</v>
+        <v>2294.1</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>2442.95</v>
+        <v>2442.97</v>
       </c>
       <c r="G182" s="14" t="inlineStr">
         <is>
@@ -8729,16 +8729,16 @@
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>2205.6</v>
+        <v>2199.6</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>2259.69</v>
+        <v>2259.12</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>2253.91</v>
+        <v>2253.68</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>2060.34</v>
+        <v>2060.29</v>
       </c>
       <c r="G183" s="14" t="inlineStr">
         <is>
@@ -8773,16 +8773,16 @@
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>1222.6</v>
+        <v>1221.4</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1207.8</v>
+        <v>1207.68</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1173.1</v>
+        <v>1173.05</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1179</v>
+        <v>1178.99</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8817,16 +8817,16 @@
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>300.85</v>
+        <v>301.5</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>306.67</v>
+        <v>306.73</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>312.67</v>
+        <v>312.69</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>326.22</v>
+        <v>326.23</v>
       </c>
       <c r="G185" s="14" t="inlineStr">
         <is>
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>277.1</v>
+        <v>277.25</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>285.82</v>
+        <v>285.84</v>
       </c>
       <c r="E186" s="11" t="n">
         <v>284.82</v>
@@ -8905,16 +8905,16 @@
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>2230.9</v>
+        <v>2221.1</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>2265.17</v>
+        <v>2264.24</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>2237.76</v>
+        <v>2237.38</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>2391.28</v>
+        <v>2391.18</v>
       </c>
       <c r="G187" s="14" t="inlineStr">
         <is>
@@ -8949,16 +8949,16 @@
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>1006</v>
+        <v>1006.6</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>1018.66</v>
+        <v>1018.72</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>1045.38</v>
+        <v>1045.41</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>1105.14</v>
+        <v>1105.15</v>
       </c>
       <c r="G188" s="14" t="inlineStr">
         <is>
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>1018.5</v>
+        <v>1018.6</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>1072.78</v>
+        <v>1072.79</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>1038.06</v>
+        <v>1038.07</v>
       </c>
       <c r="F189" s="11" t="n">
         <v>1036.08</v>
@@ -9037,16 +9037,16 @@
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>1673</v>
+        <v>1667.5</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>1726.58</v>
+        <v>1726.06</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>1738.45</v>
+        <v>1738.24</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>1862.12</v>
+        <v>1862.07</v>
       </c>
       <c r="G190" s="14" t="inlineStr">
         <is>
@@ -9081,16 +9081,16 @@
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>773.65</v>
+        <v>772.95</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>763.1900000000001</v>
+        <v>763.12</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>718.48</v>
+        <v>718.45</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>616.34</v>
+        <v>616.33</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9125,16 +9125,16 @@
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>669</v>
+        <v>667.55</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>718.5700000000001</v>
+        <v>718.4299999999999</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>707.3</v>
+        <v>707.25</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>630.11</v>
+        <v>630.09</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9169,16 +9169,16 @@
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>3099</v>
+        <v>3097</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>3056.65</v>
+        <v>3056.46</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>2947.84</v>
+        <v>2947.76</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>2809.53</v>
+        <v>2809.51</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9213,16 +9213,16 @@
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>1586.7</v>
+        <v>1585.1</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>1630.36</v>
+        <v>1630.21</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>1620.9</v>
+        <v>1620.83</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>1641.53</v>
+        <v>1641.52</v>
       </c>
       <c r="G194" s="14" t="inlineStr">
         <is>
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>1436.9</v>
+        <v>1436.8</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>1511.29</v>
+        <v>1511.28</v>
       </c>
       <c r="E195" s="11" t="n">
         <v>1483.81</v>
@@ -9301,16 +9301,16 @@
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>3472.1</v>
+        <v>3469.3</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>3623.2</v>
+        <v>3622.93</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>3558.56</v>
+        <v>3558.45</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>3495.94</v>
+        <v>3495.91</v>
       </c>
       <c r="G196" s="14" t="inlineStr">
         <is>
@@ -9345,16 +9345,16 @@
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>622.4</v>
+        <v>620.95</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>660.14</v>
+        <v>660</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>651.01</v>
+        <v>650.95</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>566.76</v>
+        <v>566.75</v>
       </c>
       <c r="G197" s="14" t="inlineStr">
         <is>
@@ -9389,16 +9389,16 @@
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>518.5</v>
+        <v>517.85</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>565.64</v>
+        <v>565.5700000000001</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>575.76</v>
+        <v>575.73</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>545.52</v>
+        <v>545.51</v>
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
@@ -9433,16 +9433,16 @@
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>774.45</v>
+        <v>774.3</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>788.97</v>
+        <v>788.96</v>
       </c>
       <c r="E199" s="11" t="n">
         <v>777.1900000000001</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>754.4299999999999</v>
+        <v>754.42</v>
       </c>
       <c r="G199" s="14" t="inlineStr">
         <is>
@@ -9477,13 +9477,13 @@
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>1143.2</v>
+        <v>1143</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>1177.58</v>
+        <v>1177.56</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>1234.57</v>
+        <v>1234.56</v>
       </c>
       <c r="F200" s="11" t="n">
         <v>1391.68</v>
@@ -9521,16 +9521,16 @@
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>626.1</v>
+        <v>625.75</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>655.3200000000001</v>
+        <v>655.29</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>662.23</v>
+        <v>662.21</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>709.83</v>
+        <v>709.8200000000001</v>
       </c>
       <c r="G201" s="14" t="inlineStr">
         <is>
@@ -9565,16 +9565,16 @@
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>2454.5</v>
+        <v>2461.6</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>2564.99</v>
+        <v>2565.67</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>2581.1</v>
+        <v>2581.37</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>2537.25</v>
+        <v>2537.32</v>
       </c>
       <c r="G202" s="14" t="inlineStr">
         <is>
@@ -9609,16 +9609,16 @@
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>734.7</v>
+        <v>735</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>756.5599999999999</v>
+        <v>756.59</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>780.6900000000001</v>
+        <v>780.71</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>867.87</v>
+        <v>867.88</v>
       </c>
       <c r="G203" s="14" t="inlineStr">
         <is>
@@ -9653,10 +9653,10 @@
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>561.3</v>
+        <v>561.45</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>590.39</v>
+        <v>590.4</v>
       </c>
       <c r="E204" s="11" t="n">
         <v>608.9400000000001</v>
@@ -9697,16 +9697,16 @@
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>180.66</v>
+        <v>179.27</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>167.76</v>
+        <v>167.63</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>137.77</v>
+        <v>137.71</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>96.29000000000001</v>
+        <v>96.28</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9741,16 +9741,16 @@
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>1149.9</v>
+        <v>1147.8</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>1183.15</v>
+        <v>1182.95</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>1223.99</v>
+        <v>1223.91</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>1340.61</v>
+        <v>1340.59</v>
       </c>
       <c r="G206" s="14" t="inlineStr">
         <is>
@@ -9785,13 +9785,13 @@
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>4818.5</v>
+        <v>4818.7</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>4938.64</v>
+        <v>4938.66</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>5076.81</v>
+        <v>5076.82</v>
       </c>
       <c r="F207" s="11" t="n">
         <v>5125.94</v>
@@ -9829,16 +9829,16 @@
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>528.1</v>
+        <v>527.45</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>511.15</v>
+        <v>511.08</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>499.08</v>
+        <v>499.06</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>588.9299999999999</v>
+        <v>588.92</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9873,13 +9873,13 @@
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>662.2</v>
+        <v>662.1</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>617.12</v>
+        <v>617.11</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>574.46</v>
+        <v>574.45</v>
       </c>
       <c r="F209" s="11" t="n">
         <v>502.15</v>
@@ -9961,16 +9961,16 @@
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>4229.8</v>
+        <v>4254</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>4321.98</v>
+        <v>4324.28</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>4299.76</v>
+        <v>4300.71</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>4277.56</v>
+        <v>4277.8</v>
       </c>
       <c r="G211" s="14" t="inlineStr">
         <is>
@@ -10005,16 +10005,16 @@
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>518.3</v>
+        <v>517.7</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>542.5</v>
+        <v>542.4400000000001</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>543.29</v>
+        <v>543.27</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>462.87</v>
+        <v>462.86</v>
       </c>
       <c r="G212" s="14" t="inlineStr">
         <is>
@@ -10049,16 +10049,16 @@
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>379.1</v>
+        <v>378.85</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>384.39</v>
+        <v>384.36</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>384.23</v>
+        <v>384.22</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>399.83</v>
+        <v>399.82</v>
       </c>
       <c r="G213" s="14" t="inlineStr">
         <is>
@@ -10093,16 +10093,16 @@
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>2112.6</v>
+        <v>2121.5</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>2161.85</v>
+        <v>2162.7</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>2203.07</v>
+        <v>2203.42</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>2288.33</v>
+        <v>2288.42</v>
       </c>
       <c r="G214" s="14" t="inlineStr">
         <is>
@@ -10137,16 +10137,16 @@
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>562.85</v>
+        <v>562.4</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>609.0700000000001</v>
+        <v>609.03</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>603</v>
+        <v>602.98</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>550.25</v>
+        <v>550.24</v>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
@@ -10181,16 +10181,16 @@
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>34760</v>
+        <v>34610</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>35176.59</v>
+        <v>35162.3</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>32387.87</v>
+        <v>32381.99</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>24784.98</v>
+        <v>24783.49</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10225,13 +10225,13 @@
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>1080</v>
+        <v>1079.6</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>1081.88</v>
+        <v>1081.84</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>1088.14</v>
+        <v>1088.12</v>
       </c>
       <c r="F217" s="11" t="n">
         <v>1117.52</v>
@@ -10269,16 +10269,16 @@
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>412.6</v>
+        <v>413.75</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>392.6</v>
+        <v>392.71</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>362.51</v>
+        <v>362.56</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>311.16</v>
+        <v>311.17</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10313,16 +10313,16 @@
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>35090</v>
+        <v>35040</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>33734.7</v>
+        <v>33729.94</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>32274.15</v>
+        <v>32272.19</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>32987.35</v>
+        <v>32986.85</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>204.74</v>
+        <v>204.64</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>206.23</v>
+        <v>206.22</v>
       </c>
       <c r="E220" s="11" t="n">
         <v>203.61</v>
@@ -10401,16 +10401,16 @@
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1902.8</v>
+        <v>1904</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1879.29</v>
+        <v>1879.4</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1892.16</v>
+        <v>1892.2</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>2040.5</v>
+        <v>2040.52</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10445,16 +10445,16 @@
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>1260.2</v>
+        <v>1262.4</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>1258.12</v>
+        <v>1258.33</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>1276.16</v>
+        <v>1276.25</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>1325.29</v>
+        <v>1325.32</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10489,13 +10489,13 @@
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>1787</v>
+        <v>1786.3</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>1782.95</v>
+        <v>1782.89</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>1798.49</v>
+        <v>1798.46</v>
       </c>
       <c r="F223" s="11" t="n">
         <v>1842.51</v>
@@ -10533,16 +10533,16 @@
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>3241.1</v>
+        <v>3247.9</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>3290.78</v>
+        <v>3291.43</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>3223.88</v>
+        <v>3224.15</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>2934.21</v>
+        <v>2934.28</v>
       </c>
       <c r="G224" s="14" t="inlineStr">
         <is>
@@ -10577,10 +10577,10 @@
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>478.2</v>
+        <v>478.1</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>501.85</v>
+        <v>501.84</v>
       </c>
       <c r="E225" s="11" t="n">
         <v>528.05</v>
@@ -10665,13 +10665,13 @@
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>73.62</v>
+        <v>73.55</v>
       </c>
       <c r="D227" s="11" t="n">
         <v>70.75</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>69.98999999999999</v>
+        <v>69.98</v>
       </c>
       <c r="F227" s="11" t="n">
         <v>71.93000000000001</v>
@@ -10709,13 +10709,13 @@
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>76.7</v>
+        <v>76.13</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>69.88</v>
+        <v>69.83</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>64.43000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F228" s="11" t="n">
         <v>57.7</v>
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>499</v>
+        <v>499.05</v>
       </c>
       <c r="D229" s="11" t="n">
         <v>482.4</v>
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>20.8</v>
+        <v>20.75</v>
       </c>
       <c r="D230" s="11" t="n">
         <v>21.26</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>135.34</v>
+        <v>134.82</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>139.3</v>
+        <v>139.25</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>142.09</v>
+        <v>142.07</v>
       </c>
       <c r="F231" s="11" t="n">
         <v>151.48</v>
@@ -10885,10 +10885,10 @@
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>150.07</v>
+        <v>150.06</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>154.16</v>
+        <v>154.15</v>
       </c>
       <c r="E232" s="11" t="n">
         <v>157.3</v>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>279.55</v>
+        <v>279.6</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>287.91</v>
+        <v>287.92</v>
       </c>
       <c r="E233" s="11" t="n">
         <v>294.54</v>
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>296.9</v>
+        <v>297.45</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>295.98</v>
+        <v>296.03</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>291.49</v>
+        <v>291.51</v>
       </c>
       <c r="F234" s="11" t="n">
         <v>291.39</v>
@@ -11017,13 +11017,13 @@
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>521.4</v>
+        <v>521.5</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>516.27</v>
+        <v>516.28</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>506.56</v>
+        <v>506.57</v>
       </c>
       <c r="F235" s="11" t="n">
         <v>511.77</v>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>371.2</v>
+        <v>370.6</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>388.88</v>
+        <v>388.82</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>394.47</v>
+        <v>394.45</v>
       </c>
       <c r="F236" s="11" t="n">
         <v>390.67</v>
@@ -11105,20 +11105,20 @@
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>2014.8</v>
+        <v>2011.1</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>2013.28</v>
+        <v>2012.93</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>2049.83</v>
+        <v>2049.69</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>2172.88</v>
-      </c>
-      <c r="G237" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2172.84</v>
+      </c>
+      <c r="G237" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H237" s="14" t="inlineStr">
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>861.35</v>
+        <v>861.45</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>840.3200000000001</v>
+        <v>840.33</v>
       </c>
       <c r="E238" s="11" t="n">
         <v>857.14</v>
@@ -11193,13 +11193,13 @@
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>119.36</v>
+        <v>119.1</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>124.34</v>
+        <v>124.32</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>124.86</v>
+        <v>124.85</v>
       </c>
       <c r="F239" s="11" t="n">
         <v>132.86</v>
@@ -11237,16 +11237,16 @@
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>659.7</v>
+        <v>661.3</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>655.83</v>
+        <v>655.98</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>652.15</v>
+        <v>652.21</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>683.61</v>
+        <v>683.62</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>136.72</v>
+        <v>136.7</v>
       </c>
       <c r="D241" s="11" t="n">
         <v>139.46</v>
@@ -11413,13 +11413,13 @@
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>95.47</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>97.88</v>
+        <v>97.86</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>100.08</v>
+        <v>100.07</v>
       </c>
       <c r="F244" s="11" t="n">
         <v>109.23</v>
@@ -11457,13 +11457,13 @@
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>121.84</v>
+        <v>121.57</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>126.43</v>
+        <v>126.41</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>127.28</v>
+        <v>127.27</v>
       </c>
       <c r="F245" s="11" t="n">
         <v>134.3</v>
@@ -11501,10 +11501,10 @@
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>162.55</v>
+        <v>162.64</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>161.75</v>
+        <v>161.76</v>
       </c>
       <c r="E246" s="11" t="n">
         <v>162.09</v>
@@ -11545,16 +11545,16 @@
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>422.1</v>
+        <v>423</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>427.44</v>
+        <v>427.52</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>425.77</v>
+        <v>425.8</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>411.61</v>
+        <v>411.62</v>
       </c>
       <c r="G247" s="14" t="inlineStr">
         <is>
@@ -11589,13 +11589,13 @@
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>906.25</v>
+        <v>906.15</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>906.05</v>
+        <v>906.04</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>894.16</v>
+        <v>894.15</v>
       </c>
       <c r="F248" s="11" t="n">
         <v>868.49</v>
@@ -11633,16 +11633,16 @@
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>990.75</v>
+        <v>989.5</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>985.5700000000001</v>
+        <v>985.45</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>998.88</v>
+        <v>998.83</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>1154.85</v>
+        <v>1154.84</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11677,16 +11677,16 @@
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>1175.7</v>
+        <v>1174.8</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>1188.54</v>
+        <v>1188.46</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>1220.99</v>
+        <v>1220.95</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>1381.88</v>
+        <v>1381.87</v>
       </c>
       <c r="G250" s="14" t="inlineStr">
         <is>
@@ -11721,13 +11721,13 @@
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>85.12</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>90.65000000000001</v>
+        <v>90.61</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>93.61</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F251" s="11" t="n">
         <v>113.09</v>
@@ -11765,16 +11765,16 @@
         </is>
       </c>
       <c r="C252" s="11" t="n">
-        <v>733.15</v>
+        <v>734.1</v>
       </c>
       <c r="D252" s="11" t="n">
-        <v>724.4400000000001</v>
+        <v>724.53</v>
       </c>
       <c r="E252" s="11" t="n">
-        <v>722.25</v>
+        <v>722.29</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>813.8099999999999</v>
+        <v>813.8200000000001</v>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
@@ -11809,16 +11809,16 @@
         </is>
       </c>
       <c r="C253" s="11" t="n">
+        <v>4449.4</v>
+      </c>
+      <c r="D253" s="11" t="n">
         <v>4437.5</v>
       </c>
-      <c r="D253" s="11" t="n">
-        <v>4436.37</v>
-      </c>
       <c r="E253" s="11" t="n">
-        <v>4453.85</v>
+        <v>4454.31</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>4827.03</v>
+        <v>4827.15</v>
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
@@ -11853,16 +11853,16 @@
         </is>
       </c>
       <c r="C254" s="11" t="n">
-        <v>362.8</v>
+        <v>363.5</v>
       </c>
       <c r="D254" s="11" t="n">
-        <v>360.35</v>
+        <v>360.42</v>
       </c>
       <c r="E254" s="11" t="n">
-        <v>351.26</v>
+        <v>351.28</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>342.05</v>
+        <v>342.06</v>
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
@@ -11897,16 +11897,16 @@
         </is>
       </c>
       <c r="C255" s="11" t="n">
-        <v>1670.2</v>
+        <v>1670.6</v>
       </c>
       <c r="D255" s="11" t="n">
-        <v>1648.2</v>
+        <v>1648.24</v>
       </c>
       <c r="E255" s="11" t="n">
-        <v>1597.64</v>
+        <v>1597.65</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>1580.03</v>
+        <v>1580.04</v>
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
@@ -11941,16 +11941,16 @@
         </is>
       </c>
       <c r="C256" s="11" t="n">
-        <v>1643.5</v>
+        <v>1644.1</v>
       </c>
       <c r="D256" s="11" t="n">
-        <v>1583.92</v>
+        <v>1583.98</v>
       </c>
       <c r="E256" s="11" t="n">
-        <v>1554.72</v>
+        <v>1554.74</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>1477.46</v>
+        <v>1477.47</v>
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
@@ -11985,16 +11985,16 @@
         </is>
       </c>
       <c r="C257" s="11" t="n">
-        <v>2200</v>
+        <v>2206.6</v>
       </c>
       <c r="D257" s="11" t="n">
-        <v>2151.78</v>
+        <v>2152.41</v>
       </c>
       <c r="E257" s="11" t="n">
-        <v>2101.65</v>
+        <v>2101.91</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>1920.97</v>
+        <v>1921.04</v>
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
@@ -12029,16 +12029,16 @@
         </is>
       </c>
       <c r="C258" s="11" t="n">
-        <v>4778</v>
+        <v>4780</v>
       </c>
       <c r="D258" s="11" t="n">
-        <v>5154.53</v>
+        <v>5154.72</v>
       </c>
       <c r="E258" s="11" t="n">
-        <v>5315.55</v>
+        <v>5315.63</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>5552.54</v>
+        <v>5552.56</v>
       </c>
       <c r="G258" s="14" t="inlineStr">
         <is>
@@ -12073,16 +12073,16 @@
         </is>
       </c>
       <c r="C259" s="11" t="n">
-        <v>658.7</v>
+        <v>658.25</v>
       </c>
       <c r="D259" s="11" t="n">
-        <v>649.47</v>
+        <v>649.4299999999999</v>
       </c>
       <c r="E259" s="11" t="n">
-        <v>628.45</v>
+        <v>628.4299999999999</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>609.66</v>
+        <v>609.65</v>
       </c>
       <c r="G259" s="12" t="inlineStr">
         <is>
@@ -12117,13 +12117,13 @@
         </is>
       </c>
       <c r="C260" s="11" t="n">
-        <v>369.2</v>
+        <v>368.85</v>
       </c>
       <c r="D260" s="11" t="n">
-        <v>386.13</v>
+        <v>386.1</v>
       </c>
       <c r="E260" s="11" t="n">
-        <v>402.74</v>
+        <v>402.73</v>
       </c>
       <c r="F260" s="11" t="n">
         <v>416.56</v>
@@ -12161,13 +12161,13 @@
         </is>
       </c>
       <c r="C261" s="11" t="n">
-        <v>119.16</v>
+        <v>119.4</v>
       </c>
       <c r="D261" s="11" t="n">
-        <v>127.08</v>
+        <v>127.1</v>
       </c>
       <c r="E261" s="11" t="n">
-        <v>130.24</v>
+        <v>130.25</v>
       </c>
       <c r="F261" s="11" t="n">
         <v>135.2</v>
@@ -12205,13 +12205,13 @@
         </is>
       </c>
       <c r="C262" s="11" t="n">
-        <v>126.27</v>
+        <v>126.16</v>
       </c>
       <c r="D262" s="11" t="n">
-        <v>127.36</v>
+        <v>127.35</v>
       </c>
       <c r="E262" s="11" t="n">
-        <v>125.46</v>
+        <v>125.45</v>
       </c>
       <c r="F262" s="11" t="n">
         <v>127.69</v>
@@ -12249,16 +12249,16 @@
         </is>
       </c>
       <c r="C263" s="11" t="n">
-        <v>3111.9</v>
+        <v>3119</v>
       </c>
       <c r="D263" s="11" t="n">
-        <v>3039.07</v>
+        <v>3039.75</v>
       </c>
       <c r="E263" s="11" t="n">
-        <v>2996.75</v>
+        <v>2997.03</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>3081.32</v>
+        <v>3081.39</v>
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
@@ -12293,16 +12293,16 @@
         </is>
       </c>
       <c r="C264" s="11" t="n">
-        <v>570.9</v>
+        <v>571.65</v>
       </c>
       <c r="D264" s="11" t="n">
-        <v>568.22</v>
+        <v>568.29</v>
       </c>
       <c r="E264" s="11" t="n">
-        <v>547.33</v>
+        <v>547.36</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>515.52</v>
+        <v>515.53</v>
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
@@ -12337,13 +12337,13 @@
         </is>
       </c>
       <c r="C265" s="11" t="n">
-        <v>275.6</v>
+        <v>275.35</v>
       </c>
       <c r="D265" s="11" t="n">
-        <v>273.57</v>
+        <v>273.54</v>
       </c>
       <c r="E265" s="11" t="n">
-        <v>270.72</v>
+        <v>270.71</v>
       </c>
       <c r="F265" s="11" t="n">
         <v>273.74</v>
@@ -12381,13 +12381,13 @@
         </is>
       </c>
       <c r="C266" s="11" t="n">
-        <v>1269.4</v>
+        <v>1269.1</v>
       </c>
       <c r="D266" s="11" t="n">
-        <v>1284.28</v>
+        <v>1284.25</v>
       </c>
       <c r="E266" s="11" t="n">
-        <v>1261.86</v>
+        <v>1261.85</v>
       </c>
       <c r="F266" s="11" t="n">
         <v>1183.96</v>
@@ -12425,16 +12425,16 @@
         </is>
       </c>
       <c r="C267" s="11" t="n">
-        <v>366.6</v>
+        <v>362.45</v>
       </c>
       <c r="D267" s="11" t="n">
-        <v>394.09</v>
+        <v>393.69</v>
       </c>
       <c r="E267" s="11" t="n">
-        <v>418.88</v>
+        <v>418.71</v>
       </c>
       <c r="F267" s="11" t="n">
-        <v>396.63</v>
+        <v>396.59</v>
       </c>
       <c r="G267" s="14" t="inlineStr">
         <is>
@@ -12469,13 +12469,13 @@
         </is>
       </c>
       <c r="C268" s="11" t="n">
-        <v>18.56</v>
+        <v>18.49</v>
       </c>
       <c r="D268" s="11" t="n">
-        <v>19.27</v>
+        <v>19.26</v>
       </c>
       <c r="E268" s="11" t="n">
-        <v>18.54</v>
+        <v>18.53</v>
       </c>
       <c r="F268" s="11" t="n">
         <v>17.36</v>
@@ -12485,9 +12485,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H268" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H268" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I268" s="12" t="inlineStr">
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="C269" s="11" t="n">
-        <v>154.82</v>
+        <v>154.67</v>
       </c>
       <c r="D269" s="11" t="n">
-        <v>142.32</v>
+        <v>142.3</v>
       </c>
       <c r="E269" s="11" t="n">
         <v>134.08</v>
@@ -12557,13 +12557,13 @@
         </is>
       </c>
       <c r="C270" s="11" t="n">
-        <v>239.46</v>
+        <v>239.28</v>
       </c>
       <c r="D270" s="11" t="n">
-        <v>238.04</v>
+        <v>238.02</v>
       </c>
       <c r="E270" s="11" t="n">
-        <v>225.6</v>
+        <v>225.59</v>
       </c>
       <c r="F270" s="11" t="n">
         <v>205.03</v>
@@ -12601,16 +12601,16 @@
         </is>
       </c>
       <c r="C271" s="11" t="n">
-        <v>670.05</v>
+        <v>668.2</v>
       </c>
       <c r="D271" s="11" t="n">
-        <v>709.0599999999999</v>
+        <v>708.89</v>
       </c>
       <c r="E271" s="11" t="n">
-        <v>732.37</v>
+        <v>732.3</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>740.1</v>
+        <v>740.08</v>
       </c>
       <c r="G271" s="14" t="inlineStr">
         <is>
@@ -12645,16 +12645,16 @@
         </is>
       </c>
       <c r="C272" s="11" t="n">
-        <v>1161.5</v>
+        <v>1160</v>
       </c>
       <c r="D272" s="11" t="n">
-        <v>1204.52</v>
+        <v>1204.38</v>
       </c>
       <c r="E272" s="11" t="n">
-        <v>1207.26</v>
+        <v>1207.2</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>1119.93</v>
+        <v>1119.91</v>
       </c>
       <c r="G272" s="14" t="inlineStr">
         <is>
@@ -12689,13 +12689,13 @@
         </is>
       </c>
       <c r="C273" s="11" t="n">
-        <v>233.05</v>
+        <v>233</v>
       </c>
       <c r="D273" s="11" t="n">
-        <v>237.09</v>
+        <v>237.08</v>
       </c>
       <c r="E273" s="11" t="n">
-        <v>241.06</v>
+        <v>241.05</v>
       </c>
       <c r="F273" s="11" t="n">
         <v>260.81</v>
@@ -12733,16 +12733,16 @@
         </is>
       </c>
       <c r="C274" s="11" t="n">
-        <v>418.8</v>
+        <v>417.3</v>
       </c>
       <c r="D274" s="11" t="n">
-        <v>436.45</v>
+        <v>436.31</v>
       </c>
       <c r="E274" s="11" t="n">
-        <v>454.09</v>
+        <v>454.03</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>523.8200000000001</v>
+        <v>523.8</v>
       </c>
       <c r="G274" s="14" t="inlineStr">
         <is>
@@ -12777,13 +12777,13 @@
         </is>
       </c>
       <c r="C275" s="11" t="n">
-        <v>626.15</v>
+        <v>625.8</v>
       </c>
       <c r="D275" s="11" t="n">
-        <v>666.2</v>
+        <v>666.17</v>
       </c>
       <c r="E275" s="11" t="n">
-        <v>671.15</v>
+        <v>671.14</v>
       </c>
       <c r="F275" s="11" t="n">
         <v>665.99</v>
@@ -12821,13 +12821,13 @@
         </is>
       </c>
       <c r="C276" s="11" t="n">
-        <v>959.5</v>
+        <v>959.3</v>
       </c>
       <c r="D276" s="11" t="n">
-        <v>977.04</v>
+        <v>977.02</v>
       </c>
       <c r="E276" s="11" t="n">
-        <v>957.62</v>
+        <v>957.61</v>
       </c>
       <c r="F276" s="11" t="n">
         <v>979.6799999999999</v>
@@ -12865,13 +12865,13 @@
         </is>
       </c>
       <c r="C277" s="11" t="n">
-        <v>276.2</v>
+        <v>276.7</v>
       </c>
       <c r="D277" s="11" t="n">
-        <v>281.92</v>
+        <v>281.97</v>
       </c>
       <c r="E277" s="11" t="n">
-        <v>282.01</v>
+        <v>282.03</v>
       </c>
       <c r="F277" s="11" t="n">
         <v>297.24</v>
@@ -12909,16 +12909,16 @@
         </is>
       </c>
       <c r="C278" s="11" t="n">
-        <v>636.8</v>
+        <v>626.85</v>
       </c>
       <c r="D278" s="11" t="n">
-        <v>649.5700000000001</v>
+        <v>648.62</v>
       </c>
       <c r="E278" s="11" t="n">
-        <v>701.39</v>
+        <v>701</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>823.41</v>
+        <v>823.3099999999999</v>
       </c>
       <c r="G278" s="14" t="inlineStr">
         <is>
@@ -12953,13 +12953,13 @@
         </is>
       </c>
       <c r="C279" s="11" t="n">
-        <v>1030</v>
+        <v>1030.4</v>
       </c>
       <c r="D279" s="11" t="n">
-        <v>994.62</v>
+        <v>994.66</v>
       </c>
       <c r="E279" s="11" t="n">
-        <v>952.05</v>
+        <v>952.0700000000001</v>
       </c>
       <c r="F279" s="11" t="n">
         <v>948.0599999999999</v>
@@ -12997,16 +12997,16 @@
         </is>
       </c>
       <c r="C280" s="11" t="n">
-        <v>5257</v>
+        <v>5254.5</v>
       </c>
       <c r="D280" s="11" t="n">
-        <v>5200.28</v>
+        <v>5200.04</v>
       </c>
       <c r="E280" s="11" t="n">
-        <v>4988.91</v>
+        <v>4988.81</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>4439.64</v>
+        <v>4439.62</v>
       </c>
       <c r="G280" s="12" t="inlineStr">
         <is>
@@ -13041,16 +13041,16 @@
         </is>
       </c>
       <c r="C281" s="11" t="n">
-        <v>751.55</v>
+        <v>750.8</v>
       </c>
       <c r="D281" s="11" t="n">
-        <v>760.45</v>
+        <v>760.38</v>
       </c>
       <c r="E281" s="11" t="n">
-        <v>761.75</v>
+        <v>761.72</v>
       </c>
       <c r="F281" s="11" t="n">
-        <v>941.55</v>
+        <v>941.54</v>
       </c>
       <c r="G281" s="14" t="inlineStr">
         <is>
@@ -13085,16 +13085,16 @@
         </is>
       </c>
       <c r="C282" s="11" t="n">
-        <v>1078.9</v>
+        <v>1077.2</v>
       </c>
       <c r="D282" s="11" t="n">
-        <v>1086.69</v>
+        <v>1086.52</v>
       </c>
       <c r="E282" s="11" t="n">
-        <v>1076.46</v>
+        <v>1076.4</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>1049.58</v>
+        <v>1049.56</v>
       </c>
       <c r="G282" s="14" t="inlineStr">
         <is>
@@ -13129,16 +13129,16 @@
         </is>
       </c>
       <c r="C283" s="11" t="n">
-        <v>1278.4</v>
+        <v>1275.9</v>
       </c>
       <c r="D283" s="11" t="n">
-        <v>1273.76</v>
+        <v>1273.52</v>
       </c>
       <c r="E283" s="11" t="n">
-        <v>1239.75</v>
+        <v>1239.66</v>
       </c>
       <c r="F283" s="11" t="n">
-        <v>1176.89</v>
+        <v>1176.87</v>
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
@@ -13173,16 +13173,16 @@
         </is>
       </c>
       <c r="C284" s="11" t="n">
-        <v>353.75</v>
+        <v>351.7</v>
       </c>
       <c r="D284" s="11" t="n">
-        <v>362.19</v>
+        <v>361.99</v>
       </c>
       <c r="E284" s="11" t="n">
-        <v>379.89</v>
+        <v>379.81</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>431.45</v>
+        <v>431.43</v>
       </c>
       <c r="G284" s="14" t="inlineStr">
         <is>
@@ -13217,16 +13217,16 @@
         </is>
       </c>
       <c r="C285" s="11" t="n">
-        <v>282.9</v>
+        <v>284.8</v>
       </c>
       <c r="D285" s="11" t="n">
-        <v>288.25</v>
+        <v>288.44</v>
       </c>
       <c r="E285" s="11" t="n">
-        <v>289.79</v>
+        <v>289.86</v>
       </c>
       <c r="F285" s="11" t="n">
-        <v>266.86</v>
+        <v>266.88</v>
       </c>
       <c r="G285" s="14" t="inlineStr">
         <is>
@@ -13261,16 +13261,16 @@
         </is>
       </c>
       <c r="C286" s="11" t="n">
-        <v>3070.8</v>
+        <v>3064.9</v>
       </c>
       <c r="D286" s="11" t="n">
-        <v>3310.7</v>
+        <v>3310.13</v>
       </c>
       <c r="E286" s="11" t="n">
-        <v>3581.33</v>
+        <v>3581.1</v>
       </c>
       <c r="F286" s="11" t="n">
-        <v>4346.31</v>
+        <v>4346.25</v>
       </c>
       <c r="G286" s="14" t="inlineStr">
         <is>
@@ -13305,10 +13305,10 @@
         </is>
       </c>
       <c r="C287" s="11" t="n">
-        <v>487</v>
+        <v>487.2</v>
       </c>
       <c r="D287" s="11" t="n">
-        <v>507.73</v>
+        <v>507.75</v>
       </c>
       <c r="E287" s="11" t="n">
         <v>535.1900000000001</v>
@@ -13349,16 +13349,16 @@
         </is>
       </c>
       <c r="C288" s="11" t="n">
-        <v>834</v>
+        <v>836.2</v>
       </c>
       <c r="D288" s="11" t="n">
-        <v>852.1900000000001</v>
+        <v>852.4</v>
       </c>
       <c r="E288" s="11" t="n">
-        <v>883.4400000000001</v>
+        <v>883.53</v>
       </c>
       <c r="F288" s="11" t="n">
-        <v>975.47</v>
+        <v>975.49</v>
       </c>
       <c r="G288" s="14" t="inlineStr">
         <is>
@@ -13393,16 +13393,16 @@
         </is>
       </c>
       <c r="C289" s="11" t="n">
-        <v>1845.8</v>
+        <v>1849.9</v>
       </c>
       <c r="D289" s="11" t="n">
-        <v>1803.56</v>
+        <v>1803.96</v>
       </c>
       <c r="E289" s="11" t="n">
-        <v>1680</v>
+        <v>1680.16</v>
       </c>
       <c r="F289" s="11" t="n">
-        <v>1325.82</v>
+        <v>1325.86</v>
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
@@ -13437,13 +13437,13 @@
         </is>
       </c>
       <c r="C290" s="11" t="n">
-        <v>378.15</v>
+        <v>379</v>
       </c>
       <c r="D290" s="11" t="n">
-        <v>381.24</v>
+        <v>381.32</v>
       </c>
       <c r="E290" s="11" t="n">
-        <v>382.97</v>
+        <v>383</v>
       </c>
       <c r="F290" s="11" t="n">
         <v>398.87</v>
@@ -13481,16 +13481,16 @@
         </is>
       </c>
       <c r="C291" s="11" t="n">
-        <v>799.4</v>
+        <v>795</v>
       </c>
       <c r="D291" s="11" t="n">
-        <v>759.9299999999999</v>
+        <v>759.51</v>
       </c>
       <c r="E291" s="11" t="n">
-        <v>726.22</v>
+        <v>726.05</v>
       </c>
       <c r="F291" s="11" t="n">
-        <v>683.92</v>
+        <v>683.87</v>
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
@@ -13525,13 +13525,13 @@
         </is>
       </c>
       <c r="C292" s="11" t="n">
-        <v>263.45</v>
+        <v>262.85</v>
       </c>
       <c r="D292" s="11" t="n">
-        <v>273.29</v>
+        <v>273.24</v>
       </c>
       <c r="E292" s="11" t="n">
-        <v>275.82</v>
+        <v>275.79</v>
       </c>
       <c r="F292" s="11" t="n">
         <v>262.33</v>
@@ -13569,16 +13569,16 @@
         </is>
       </c>
       <c r="C293" s="11" t="n">
-        <v>3329.9</v>
+        <v>3331.1</v>
       </c>
       <c r="D293" s="11" t="n">
-        <v>3405.18</v>
+        <v>3405.3</v>
       </c>
       <c r="E293" s="11" t="n">
-        <v>3458.91</v>
+        <v>3458.96</v>
       </c>
       <c r="F293" s="11" t="n">
-        <v>3770.85</v>
+        <v>3770.86</v>
       </c>
       <c r="G293" s="14" t="inlineStr">
         <is>
@@ -13613,16 +13613,16 @@
         </is>
       </c>
       <c r="C294" s="11" t="n">
-        <v>1513.5</v>
+        <v>1512.2</v>
       </c>
       <c r="D294" s="11" t="n">
-        <v>1524.74</v>
+        <v>1524.61</v>
       </c>
       <c r="E294" s="11" t="n">
-        <v>1528.83</v>
+        <v>1528.78</v>
       </c>
       <c r="F294" s="11" t="n">
-        <v>1564.45</v>
+        <v>1564.43</v>
       </c>
       <c r="G294" s="14" t="inlineStr">
         <is>
@@ -13657,13 +13657,13 @@
         </is>
       </c>
       <c r="C295" s="11" t="n">
-        <v>547.6</v>
+        <v>547.4</v>
       </c>
       <c r="D295" s="11" t="n">
-        <v>546.61</v>
+        <v>546.59</v>
       </c>
       <c r="E295" s="11" t="n">
-        <v>543.17</v>
+        <v>543.16</v>
       </c>
       <c r="F295" s="11" t="n">
         <v>541.21</v>
@@ -13701,13 +13701,13 @@
         </is>
       </c>
       <c r="C296" s="11" t="n">
-        <v>374.95</v>
+        <v>374.55</v>
       </c>
       <c r="D296" s="11" t="n">
-        <v>394.42</v>
+        <v>394.38</v>
       </c>
       <c r="E296" s="11" t="n">
-        <v>401</v>
+        <v>400.99</v>
       </c>
       <c r="F296" s="11" t="n">
         <v>401.23</v>
@@ -13745,16 +13745,16 @@
         </is>
       </c>
       <c r="C297" s="11" t="n">
-        <v>3995</v>
+        <v>4000.9</v>
       </c>
       <c r="D297" s="11" t="n">
-        <v>4082.37</v>
+        <v>4082.93</v>
       </c>
       <c r="E297" s="11" t="n">
-        <v>4238.85</v>
+        <v>4239.08</v>
       </c>
       <c r="F297" s="11" t="n">
-        <v>4811.5</v>
+        <v>4811.56</v>
       </c>
       <c r="G297" s="14" t="inlineStr">
         <is>
@@ -13789,16 +13789,16 @@
         </is>
       </c>
       <c r="C298" s="11" t="n">
-        <v>3901.4</v>
+        <v>3903.9</v>
       </c>
       <c r="D298" s="11" t="n">
-        <v>3952.99</v>
+        <v>3953.23</v>
       </c>
       <c r="E298" s="11" t="n">
-        <v>3931.49</v>
+        <v>3931.59</v>
       </c>
       <c r="F298" s="11" t="n">
-        <v>3829.49</v>
+        <v>3829.51</v>
       </c>
       <c r="G298" s="14" t="inlineStr">
         <is>
@@ -13877,13 +13877,13 @@
         </is>
       </c>
       <c r="C300" s="11" t="n">
-        <v>1426.7</v>
+        <v>1427.3</v>
       </c>
       <c r="D300" s="11" t="n">
-        <v>1357.17</v>
+        <v>1357.23</v>
       </c>
       <c r="E300" s="11" t="n">
-        <v>1252.02</v>
+        <v>1252.05</v>
       </c>
       <c r="F300" s="11" t="n">
         <v>1043.88</v>
@@ -13921,16 +13921,16 @@
         </is>
       </c>
       <c r="C301" s="11" t="n">
-        <v>412.35</v>
+        <v>413.1</v>
       </c>
       <c r="D301" s="11" t="n">
-        <v>415.18</v>
+        <v>415.26</v>
       </c>
       <c r="E301" s="11" t="n">
-        <v>418.46</v>
+        <v>418.49</v>
       </c>
       <c r="F301" s="11" t="n">
-        <v>423.85</v>
+        <v>423.86</v>
       </c>
       <c r="G301" s="14" t="inlineStr">
         <is>
@@ -13965,13 +13965,13 @@
         </is>
       </c>
       <c r="C302" s="11" t="n">
-        <v>108.19</v>
+        <v>108.18</v>
       </c>
       <c r="D302" s="11" t="n">
         <v>112.54</v>
       </c>
       <c r="E302" s="11" t="n">
-        <v>114.79</v>
+        <v>114.78</v>
       </c>
       <c r="F302" s="11" t="n">
         <v>129.67</v>
@@ -14009,16 +14009,16 @@
         </is>
       </c>
       <c r="C303" s="11" t="n">
-        <v>505.4</v>
+        <v>502.85</v>
       </c>
       <c r="D303" s="11" t="n">
-        <v>508.42</v>
+        <v>508.18</v>
       </c>
       <c r="E303" s="11" t="n">
-        <v>505.64</v>
+        <v>505.54</v>
       </c>
       <c r="F303" s="11" t="n">
-        <v>468.34</v>
+        <v>468.32</v>
       </c>
       <c r="G303" s="14" t="inlineStr">
         <is>
@@ -14053,16 +14053,16 @@
         </is>
       </c>
       <c r="C304" s="11" t="n">
-        <v>399.95</v>
+        <v>399.05</v>
       </c>
       <c r="D304" s="11" t="n">
-        <v>403.56</v>
+        <v>403.47</v>
       </c>
       <c r="E304" s="11" t="n">
-        <v>404.26</v>
+        <v>404.23</v>
       </c>
       <c r="F304" s="11" t="n">
-        <v>414.66</v>
+        <v>414.65</v>
       </c>
       <c r="G304" s="14" t="inlineStr">
         <is>
@@ -14097,16 +14097,16 @@
         </is>
       </c>
       <c r="C305" s="11" t="n">
-        <v>6885.5</v>
+        <v>6893.5</v>
       </c>
       <c r="D305" s="11" t="n">
-        <v>7135.72</v>
+        <v>7136.48</v>
       </c>
       <c r="E305" s="11" t="n">
-        <v>7140.37</v>
+        <v>7140.68</v>
       </c>
       <c r="F305" s="11" t="n">
-        <v>6691.2</v>
+        <v>6691.28</v>
       </c>
       <c r="G305" s="14" t="inlineStr">
         <is>
@@ -14141,16 +14141,16 @@
         </is>
       </c>
       <c r="C306" s="11" t="n">
-        <v>1723.6</v>
+        <v>1719.1</v>
       </c>
       <c r="D306" s="11" t="n">
-        <v>1758.98</v>
+        <v>1758.55</v>
       </c>
       <c r="E306" s="11" t="n">
-        <v>1658.21</v>
+        <v>1658.04</v>
       </c>
       <c r="F306" s="11" t="n">
-        <v>1422.91</v>
+        <v>1422.86</v>
       </c>
       <c r="G306" s="14" t="inlineStr">
         <is>
@@ -14185,16 +14185,16 @@
         </is>
       </c>
       <c r="C307" s="11" t="n">
-        <v>889.9</v>
+        <v>885.15</v>
       </c>
       <c r="D307" s="11" t="n">
-        <v>892.66</v>
+        <v>892.21</v>
       </c>
       <c r="E307" s="11" t="n">
-        <v>892.29</v>
+        <v>892.1</v>
       </c>
       <c r="F307" s="11" t="n">
-        <v>1007.16</v>
+        <v>1007.11</v>
       </c>
       <c r="G307" s="14" t="inlineStr">
         <is>
@@ -14229,16 +14229,16 @@
         </is>
       </c>
       <c r="C308" s="11" t="n">
-        <v>2259</v>
+        <v>2261.3</v>
       </c>
       <c r="D308" s="11" t="n">
-        <v>2272.84</v>
+        <v>2273.05</v>
       </c>
       <c r="E308" s="11" t="n">
-        <v>2281.69</v>
+        <v>2281.78</v>
       </c>
       <c r="F308" s="11" t="n">
-        <v>2177.86</v>
+        <v>2177.88</v>
       </c>
       <c r="G308" s="14" t="inlineStr">
         <is>
@@ -14273,10 +14273,10 @@
         </is>
       </c>
       <c r="C309" s="11" t="n">
-        <v>65.87</v>
+        <v>65.92</v>
       </c>
       <c r="D309" s="11" t="n">
-        <v>65.38</v>
+        <v>65.39</v>
       </c>
       <c r="E309" s="11" t="n">
         <v>64.11</v>
@@ -14317,16 +14317,16 @@
         </is>
       </c>
       <c r="C310" s="11" t="n">
-        <v>122905</v>
+        <v>122920</v>
       </c>
       <c r="D310" s="11" t="n">
-        <v>125863.76</v>
+        <v>125865.19</v>
       </c>
       <c r="E310" s="11" t="n">
-        <v>129390.09</v>
+        <v>129390.68</v>
       </c>
       <c r="F310" s="11" t="n">
-        <v>136745.88</v>
+        <v>136746.03</v>
       </c>
       <c r="G310" s="14" t="inlineStr">
         <is>
@@ -14361,16 +14361,16 @@
         </is>
       </c>
       <c r="C311" s="11" t="n">
-        <v>1049.6</v>
+        <v>1048.4</v>
       </c>
       <c r="D311" s="11" t="n">
-        <v>1081.89</v>
+        <v>1081.78</v>
       </c>
       <c r="E311" s="11" t="n">
-        <v>1083.45</v>
+        <v>1083.41</v>
       </c>
       <c r="F311" s="11" t="n">
-        <v>1137.92</v>
+        <v>1137.91</v>
       </c>
       <c r="G311" s="14" t="inlineStr">
         <is>
@@ -14405,16 +14405,16 @@
         </is>
       </c>
       <c r="C312" s="11" t="n">
-        <v>282.9</v>
+        <v>282.8</v>
       </c>
       <c r="D312" s="11" t="n">
-        <v>299.24</v>
+        <v>299.23</v>
       </c>
       <c r="E312" s="11" t="n">
-        <v>309.85</v>
+        <v>309.84</v>
       </c>
       <c r="F312" s="11" t="n">
-        <v>316.39</v>
+        <v>316.38</v>
       </c>
       <c r="G312" s="14" t="inlineStr">
         <is>
@@ -14449,16 +14449,16 @@
         </is>
       </c>
       <c r="C313" s="11" t="n">
-        <v>3006.1</v>
+        <v>3010.7</v>
       </c>
       <c r="D313" s="11" t="n">
-        <v>3065.05</v>
+        <v>3065.49</v>
       </c>
       <c r="E313" s="11" t="n">
-        <v>3133.58</v>
+        <v>3133.76</v>
       </c>
       <c r="F313" s="11" t="n">
-        <v>3263.74</v>
+        <v>3263.78</v>
       </c>
       <c r="G313" s="14" t="inlineStr">
         <is>
@@ -14493,13 +14493,13 @@
         </is>
       </c>
       <c r="C314" s="11" t="n">
-        <v>302.35</v>
+        <v>302.4</v>
       </c>
       <c r="D314" s="11" t="n">
         <v>311.13</v>
       </c>
       <c r="E314" s="11" t="n">
-        <v>301.66</v>
+        <v>301.67</v>
       </c>
       <c r="F314" s="11" t="n">
         <v>282.89</v>
@@ -14537,10 +14537,10 @@
         </is>
       </c>
       <c r="C315" s="11" t="n">
-        <v>155.71</v>
+        <v>155.65</v>
       </c>
       <c r="D315" s="11" t="n">
-        <v>153.74</v>
+        <v>153.73</v>
       </c>
       <c r="E315" s="11" t="n">
         <v>161.16</v>
@@ -14581,20 +14581,20 @@
         </is>
       </c>
       <c r="C316" s="11" t="n">
-        <v>2374.7</v>
+        <v>2380.4</v>
       </c>
       <c r="D316" s="11" t="n">
-        <v>2376.75</v>
+        <v>2377.29</v>
       </c>
       <c r="E316" s="11" t="n">
-        <v>2315.22</v>
+        <v>2315.44</v>
       </c>
       <c r="F316" s="11" t="n">
-        <v>2278.39</v>
-      </c>
-      <c r="G316" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2278.44</v>
+      </c>
+      <c r="G316" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H316" s="12" t="inlineStr">
@@ -14625,16 +14625,16 @@
         </is>
       </c>
       <c r="C317" s="11" t="n">
-        <v>807.55</v>
+        <v>806.5</v>
       </c>
       <c r="D317" s="11" t="n">
-        <v>815.66</v>
+        <v>815.5599999999999</v>
       </c>
       <c r="E317" s="11" t="n">
-        <v>801.74</v>
+        <v>801.7</v>
       </c>
       <c r="F317" s="11" t="n">
-        <v>755.74</v>
+        <v>755.73</v>
       </c>
       <c r="G317" s="14" t="inlineStr">
         <is>
@@ -14669,16 +14669,16 @@
         </is>
       </c>
       <c r="C318" s="11" t="n">
-        <v>12906</v>
+        <v>12931</v>
       </c>
       <c r="D318" s="11" t="n">
-        <v>13098.93</v>
+        <v>13101.31</v>
       </c>
       <c r="E318" s="11" t="n">
-        <v>13310.47</v>
+        <v>13311.45</v>
       </c>
       <c r="F318" s="11" t="n">
-        <v>13992.92</v>
+        <v>13993.16</v>
       </c>
       <c r="G318" s="14" t="inlineStr">
         <is>
@@ -14713,16 +14713,16 @@
         </is>
       </c>
       <c r="C319" s="11" t="n">
-        <v>1591.5</v>
+        <v>1589.1</v>
       </c>
       <c r="D319" s="11" t="n">
-        <v>1623.17</v>
+        <v>1622.94</v>
       </c>
       <c r="E319" s="11" t="n">
-        <v>1635.64</v>
+        <v>1635.55</v>
       </c>
       <c r="F319" s="11" t="n">
-        <v>1602.42</v>
+        <v>1602.4</v>
       </c>
       <c r="G319" s="14" t="inlineStr">
         <is>
@@ -14757,16 +14757,16 @@
         </is>
       </c>
       <c r="C320" s="11" t="n">
-        <v>1008.8</v>
+        <v>1007.1</v>
       </c>
       <c r="D320" s="11" t="n">
-        <v>996.72</v>
+        <v>996.5599999999999</v>
       </c>
       <c r="E320" s="11" t="n">
-        <v>1004.75</v>
+        <v>1004.68</v>
       </c>
       <c r="F320" s="11" t="n">
-        <v>1049.29</v>
+        <v>1049.27</v>
       </c>
       <c r="G320" s="12" t="inlineStr">
         <is>
@@ -14801,16 +14801,16 @@
         </is>
       </c>
       <c r="C321" s="11" t="n">
-        <v>2423</v>
+        <v>2417.8</v>
       </c>
       <c r="D321" s="11" t="n">
-        <v>2461.28</v>
+        <v>2460.79</v>
       </c>
       <c r="E321" s="11" t="n">
-        <v>2479.34</v>
+        <v>2479.14</v>
       </c>
       <c r="F321" s="11" t="n">
-        <v>2532.81</v>
+        <v>2532.76</v>
       </c>
       <c r="G321" s="14" t="inlineStr">
         <is>
@@ -14845,13 +14845,13 @@
         </is>
       </c>
       <c r="C322" s="11" t="n">
-        <v>164.59</v>
+        <v>164.36</v>
       </c>
       <c r="D322" s="11" t="n">
-        <v>179.46</v>
+        <v>179.44</v>
       </c>
       <c r="E322" s="11" t="n">
-        <v>177.48</v>
+        <v>177.47</v>
       </c>
       <c r="F322" s="11" t="n">
         <v>170.9</v>
@@ -14889,16 +14889,16 @@
         </is>
       </c>
       <c r="C323" s="11" t="n">
-        <v>639.85</v>
+        <v>642.1</v>
       </c>
       <c r="D323" s="11" t="n">
-        <v>598.3</v>
+        <v>598.51</v>
       </c>
       <c r="E323" s="11" t="n">
-        <v>565.92</v>
+        <v>566.01</v>
       </c>
       <c r="F323" s="11" t="n">
-        <v>549.25</v>
+        <v>549.28</v>
       </c>
       <c r="G323" s="12" t="inlineStr">
         <is>
@@ -14933,13 +14933,13 @@
         </is>
       </c>
       <c r="C324" s="11" t="n">
-        <v>37.98</v>
+        <v>37.8</v>
       </c>
       <c r="D324" s="11" t="n">
-        <v>38.94</v>
+        <v>38.92</v>
       </c>
       <c r="E324" s="11" t="n">
-        <v>39.69</v>
+        <v>39.68</v>
       </c>
       <c r="F324" s="11" t="n">
         <v>41.32</v>
@@ -14977,16 +14977,16 @@
         </is>
       </c>
       <c r="C325" s="11" t="n">
-        <v>856.1</v>
+        <v>856.8</v>
       </c>
       <c r="D325" s="11" t="n">
-        <v>852.05</v>
+        <v>852.11</v>
       </c>
       <c r="E325" s="11" t="n">
-        <v>825</v>
+        <v>825.03</v>
       </c>
       <c r="F325" s="11" t="n">
-        <v>811.21</v>
+        <v>811.22</v>
       </c>
       <c r="G325" s="12" t="inlineStr">
         <is>
@@ -15021,16 +15021,16 @@
         </is>
       </c>
       <c r="C326" s="11" t="n">
-        <v>2338.9</v>
+        <v>2341</v>
       </c>
       <c r="D326" s="11" t="n">
-        <v>2278.45</v>
+        <v>2278.65</v>
       </c>
       <c r="E326" s="11" t="n">
-        <v>2280.03</v>
+        <v>2280.11</v>
       </c>
       <c r="F326" s="11" t="n">
-        <v>2458.37</v>
+        <v>2458.39</v>
       </c>
       <c r="G326" s="12" t="inlineStr">
         <is>
@@ -15065,16 +15065,16 @@
         </is>
       </c>
       <c r="C327" s="11" t="n">
-        <v>2845</v>
+        <v>2838</v>
       </c>
       <c r="D327" s="11" t="n">
-        <v>3001.52</v>
+        <v>3000.85</v>
       </c>
       <c r="E327" s="11" t="n">
-        <v>2923.14</v>
+        <v>2922.87</v>
       </c>
       <c r="F327" s="11" t="n">
-        <v>2365.46</v>
+        <v>2365.39</v>
       </c>
       <c r="G327" s="14" t="inlineStr">
         <is>
@@ -15109,16 +15109,16 @@
         </is>
       </c>
       <c r="C328" s="11" t="n">
-        <v>2948</v>
+        <v>2953.1</v>
       </c>
       <c r="D328" s="11" t="n">
-        <v>3240.78</v>
+        <v>3241.26</v>
       </c>
       <c r="E328" s="11" t="n">
-        <v>3341.8</v>
+        <v>3342</v>
       </c>
       <c r="F328" s="11" t="n">
-        <v>3274.56</v>
+        <v>3274.61</v>
       </c>
       <c r="G328" s="14" t="inlineStr">
         <is>
@@ -15153,16 +15153,16 @@
         </is>
       </c>
       <c r="C329" s="11" t="n">
-        <v>864.7</v>
+        <v>865.9</v>
       </c>
       <c r="D329" s="11" t="n">
-        <v>1021.68</v>
+        <v>1021.8</v>
       </c>
       <c r="E329" s="11" t="n">
-        <v>1048.78</v>
+        <v>1048.82</v>
       </c>
       <c r="F329" s="11" t="n">
-        <v>960.55</v>
+        <v>960.5599999999999</v>
       </c>
       <c r="G329" s="14" t="inlineStr">
         <is>
@@ -15197,13 +15197,13 @@
         </is>
       </c>
       <c r="C330" s="11" t="n">
-        <v>104.05</v>
+        <v>104.02</v>
       </c>
       <c r="D330" s="11" t="n">
         <v>99.8</v>
       </c>
       <c r="E330" s="11" t="n">
-        <v>96.38</v>
+        <v>96.37</v>
       </c>
       <c r="F330" s="11" t="n">
         <v>98.59999999999999</v>
@@ -15241,16 +15241,16 @@
         </is>
       </c>
       <c r="C331" s="11" t="n">
-        <v>144.7</v>
+        <v>144.06</v>
       </c>
       <c r="D331" s="11" t="n">
-        <v>150.54</v>
+        <v>150.48</v>
       </c>
       <c r="E331" s="11" t="n">
-        <v>152.97</v>
+        <v>152.94</v>
       </c>
       <c r="F331" s="11" t="n">
-        <v>166.48</v>
+        <v>166.47</v>
       </c>
       <c r="G331" s="14" t="inlineStr">
         <is>
@@ -15285,10 +15285,10 @@
         </is>
       </c>
       <c r="C332" s="11" t="n">
-        <v>73.45</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="D332" s="11" t="n">
-        <v>77.03</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="E332" s="11" t="n">
         <v>78.08</v>
@@ -15329,16 +15329,16 @@
         </is>
       </c>
       <c r="C333" s="11" t="n">
-        <v>321.8</v>
+        <v>323.15</v>
       </c>
       <c r="D333" s="11" t="n">
-        <v>337.27</v>
+        <v>337.4</v>
       </c>
       <c r="E333" s="11" t="n">
-        <v>319.62</v>
+        <v>319.67</v>
       </c>
       <c r="F333" s="11" t="n">
-        <v>275.46</v>
+        <v>275.48</v>
       </c>
       <c r="G333" s="14" t="inlineStr">
         <is>
@@ -15373,13 +15373,13 @@
         </is>
       </c>
       <c r="C334" s="11" t="n">
-        <v>89.61</v>
+        <v>89.52</v>
       </c>
       <c r="D334" s="11" t="n">
-        <v>91.05</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="E334" s="11" t="n">
-        <v>88.42</v>
+        <v>88.41</v>
       </c>
       <c r="F334" s="11" t="n">
         <v>79.86</v>
@@ -15417,7 +15417,7 @@
         </is>
       </c>
       <c r="C335" s="11" t="n">
-        <v>48.98</v>
+        <v>48.94</v>
       </c>
       <c r="D335" s="11" t="n">
         <v>47.12</v>
@@ -15461,10 +15461,10 @@
         </is>
       </c>
       <c r="C336" s="11" t="n">
-        <v>99.78</v>
+        <v>99.69</v>
       </c>
       <c r="D336" s="11" t="n">
-        <v>103.15</v>
+        <v>103.14</v>
       </c>
       <c r="E336" s="11" t="n">
         <v>103.22</v>
@@ -15505,16 +15505,16 @@
         </is>
       </c>
       <c r="C337" s="11" t="n">
-        <v>357.65</v>
+        <v>356.75</v>
       </c>
       <c r="D337" s="11" t="n">
-        <v>378.67</v>
+        <v>378.58</v>
       </c>
       <c r="E337" s="11" t="n">
-        <v>382.41</v>
+        <v>382.38</v>
       </c>
       <c r="F337" s="11" t="n">
-        <v>359.99</v>
+        <v>359.98</v>
       </c>
       <c r="G337" s="14" t="inlineStr">
         <is>
@@ -15549,16 +15549,16 @@
         </is>
       </c>
       <c r="C338" s="11" t="n">
-        <v>1950.1</v>
+        <v>1946</v>
       </c>
       <c r="D338" s="11" t="n">
-        <v>1906.64</v>
+        <v>1906.25</v>
       </c>
       <c r="E338" s="11" t="n">
-        <v>1851.88</v>
+        <v>1851.72</v>
       </c>
       <c r="F338" s="11" t="n">
-        <v>1811.81</v>
+        <v>1811.77</v>
       </c>
       <c r="G338" s="12" t="inlineStr">
         <is>
@@ -15593,13 +15593,13 @@
         </is>
       </c>
       <c r="C339" s="11" t="n">
-        <v>377.85</v>
+        <v>377.3</v>
       </c>
       <c r="D339" s="11" t="n">
-        <v>409.28</v>
+        <v>409.23</v>
       </c>
       <c r="E339" s="11" t="n">
-        <v>403.99</v>
+        <v>403.97</v>
       </c>
       <c r="F339" s="11" t="n">
         <v>331.51</v>
@@ -15637,10 +15637,10 @@
         </is>
       </c>
       <c r="C340" s="11" t="n">
-        <v>588.2</v>
+        <v>588</v>
       </c>
       <c r="D340" s="11" t="n">
-        <v>614.23</v>
+        <v>614.21</v>
       </c>
       <c r="E340" s="11" t="n">
         <v>620.15</v>
@@ -15681,16 +15681,16 @@
         </is>
       </c>
       <c r="C341" s="11" t="n">
-        <v>6884.5</v>
+        <v>6832.5</v>
       </c>
       <c r="D341" s="11" t="n">
-        <v>7012.5</v>
+        <v>7007.54</v>
       </c>
       <c r="E341" s="11" t="n">
-        <v>6799.19</v>
+        <v>6797.15</v>
       </c>
       <c r="F341" s="11" t="n">
-        <v>6014.21</v>
+        <v>6013.7</v>
       </c>
       <c r="G341" s="14" t="inlineStr">
         <is>
@@ -15725,16 +15725,16 @@
         </is>
       </c>
       <c r="C342" s="11" t="n">
-        <v>1405.5</v>
+        <v>1403.6</v>
       </c>
       <c r="D342" s="11" t="n">
-        <v>1408.91</v>
+        <v>1408.73</v>
       </c>
       <c r="E342" s="11" t="n">
-        <v>1381.65</v>
+        <v>1381.58</v>
       </c>
       <c r="F342" s="11" t="n">
-        <v>1288.2</v>
+        <v>1288.18</v>
       </c>
       <c r="G342" s="14" t="inlineStr">
         <is>
@@ -15769,16 +15769,16 @@
         </is>
       </c>
       <c r="C343" s="11" t="n">
-        <v>4328.3</v>
+        <v>4375.8</v>
       </c>
       <c r="D343" s="11" t="n">
-        <v>4293.32</v>
+        <v>4297.84</v>
       </c>
       <c r="E343" s="11" t="n">
-        <v>4001.45</v>
+        <v>4003.31</v>
       </c>
       <c r="F343" s="11" t="n">
-        <v>3348.54</v>
+        <v>3349.01</v>
       </c>
       <c r="G343" s="12" t="inlineStr">
         <is>
@@ -15813,16 +15813,16 @@
         </is>
       </c>
       <c r="C344" s="11" t="n">
-        <v>17200</v>
+        <v>17202</v>
       </c>
       <c r="D344" s="11" t="n">
-        <v>16744.74</v>
+        <v>16744.93</v>
       </c>
       <c r="E344" s="11" t="n">
-        <v>15875.52</v>
+        <v>15875.59</v>
       </c>
       <c r="F344" s="11" t="n">
-        <v>14605</v>
+        <v>14605.02</v>
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
@@ -15857,13 +15857,13 @@
         </is>
       </c>
       <c r="C345" s="11" t="n">
-        <v>481</v>
+        <v>480.95</v>
       </c>
       <c r="D345" s="11" t="n">
-        <v>472.54</v>
+        <v>472.53</v>
       </c>
       <c r="E345" s="11" t="n">
-        <v>480.62</v>
+        <v>480.61</v>
       </c>
       <c r="F345" s="11" t="n">
         <v>651.67</v>
@@ -15901,16 +15901,16 @@
         </is>
       </c>
       <c r="C346" s="11" t="n">
-        <v>1069</v>
+        <v>1070.7</v>
       </c>
       <c r="D346" s="11" t="n">
-        <v>1079.94</v>
+        <v>1080.1</v>
       </c>
       <c r="E346" s="11" t="n">
-        <v>1033.48</v>
+        <v>1033.55</v>
       </c>
       <c r="F346" s="11" t="n">
-        <v>906.66</v>
+        <v>906.6799999999999</v>
       </c>
       <c r="G346" s="14" t="inlineStr">
         <is>
@@ -15989,16 +15989,16 @@
         </is>
       </c>
       <c r="C348" s="11" t="n">
-        <v>1550.2</v>
+        <v>1551.6</v>
       </c>
       <c r="D348" s="11" t="n">
-        <v>1517.57</v>
+        <v>1517.7</v>
       </c>
       <c r="E348" s="11" t="n">
-        <v>1438.06</v>
+        <v>1438.12</v>
       </c>
       <c r="F348" s="11" t="n">
-        <v>1352.15</v>
+        <v>1352.16</v>
       </c>
       <c r="G348" s="12" t="inlineStr">
         <is>
@@ -16033,16 +16033,16 @@
         </is>
       </c>
       <c r="C349" s="11" t="n">
-        <v>305.6</v>
+        <v>306.35</v>
       </c>
       <c r="D349" s="11" t="n">
-        <v>321.83</v>
+        <v>321.9</v>
       </c>
       <c r="E349" s="11" t="n">
-        <v>318.16</v>
+        <v>318.19</v>
       </c>
       <c r="F349" s="11" t="n">
-        <v>337.83</v>
+        <v>337.84</v>
       </c>
       <c r="G349" s="14" t="inlineStr">
         <is>
@@ -16077,16 +16077,16 @@
         </is>
       </c>
       <c r="C350" s="11" t="n">
-        <v>1629.7</v>
+        <v>1627.5</v>
       </c>
       <c r="D350" s="11" t="n">
-        <v>1649.61</v>
+        <v>1649.4</v>
       </c>
       <c r="E350" s="11" t="n">
-        <v>1633.87</v>
+        <v>1633.78</v>
       </c>
       <c r="F350" s="11" t="n">
-        <v>1618.14</v>
+        <v>1618.12</v>
       </c>
       <c r="G350" s="14" t="inlineStr">
         <is>
@@ -16121,13 +16121,13 @@
         </is>
       </c>
       <c r="C351" s="11" t="n">
-        <v>263.05</v>
+        <v>263.3</v>
       </c>
       <c r="D351" s="11" t="n">
-        <v>275.46</v>
+        <v>275.49</v>
       </c>
       <c r="E351" s="11" t="n">
-        <v>278.87</v>
+        <v>278.88</v>
       </c>
       <c r="F351" s="11" t="n">
         <v>259.3</v>
@@ -16165,16 +16165,16 @@
         </is>
       </c>
       <c r="C352" s="11" t="n">
-        <v>475.5</v>
+        <v>475.75</v>
       </c>
       <c r="D352" s="11" t="n">
-        <v>485.87</v>
+        <v>485.89</v>
       </c>
       <c r="E352" s="11" t="n">
-        <v>481.65</v>
+        <v>481.66</v>
       </c>
       <c r="F352" s="11" t="n">
-        <v>448.75</v>
+        <v>448.76</v>
       </c>
       <c r="G352" s="14" t="inlineStr">
         <is>
@@ -16209,10 +16209,10 @@
         </is>
       </c>
       <c r="C353" s="11" t="n">
-        <v>47.96</v>
+        <v>48.05</v>
       </c>
       <c r="D353" s="11" t="n">
-        <v>40.52</v>
+        <v>40.53</v>
       </c>
       <c r="E353" s="11" t="n">
         <v>37.07</v>
@@ -16253,16 +16253,16 @@
         </is>
       </c>
       <c r="C354" s="11" t="n">
-        <v>1270</v>
+        <v>1272.6</v>
       </c>
       <c r="D354" s="11" t="n">
-        <v>1252.82</v>
+        <v>1253.07</v>
       </c>
       <c r="E354" s="11" t="n">
-        <v>1210.87</v>
+        <v>1210.97</v>
       </c>
       <c r="F354" s="11" t="n">
-        <v>1201.24</v>
+        <v>1201.27</v>
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
@@ -16297,16 +16297,16 @@
         </is>
       </c>
       <c r="C355" s="11" t="n">
-        <v>1053.2</v>
+        <v>1055.7</v>
       </c>
       <c r="D355" s="11" t="n">
-        <v>1093.62</v>
+        <v>1093.86</v>
       </c>
       <c r="E355" s="11" t="n">
-        <v>1109.13</v>
+        <v>1109.23</v>
       </c>
       <c r="F355" s="11" t="n">
-        <v>1120.26</v>
+        <v>1120.29</v>
       </c>
       <c r="G355" s="14" t="inlineStr">
         <is>
@@ -16341,25 +16341,25 @@
         </is>
       </c>
       <c r="C356" s="11" t="n">
-        <v>1713.9</v>
+        <v>1709.1</v>
       </c>
       <c r="D356" s="11" t="n">
-        <v>1787.89</v>
+        <v>1787.44</v>
       </c>
       <c r="E356" s="11" t="n">
-        <v>1712.6</v>
+        <v>1712.41</v>
       </c>
       <c r="F356" s="11" t="n">
-        <v>1638.9</v>
+        <v>1638.85</v>
       </c>
       <c r="G356" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H356" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H356" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I356" s="12" t="inlineStr">
@@ -16385,16 +16385,16 @@
         </is>
       </c>
       <c r="C357" s="11" t="n">
-        <v>9611</v>
+        <v>9592.5</v>
       </c>
       <c r="D357" s="11" t="n">
-        <v>9719.549999999999</v>
+        <v>9717.780000000001</v>
       </c>
       <c r="E357" s="11" t="n">
-        <v>8985.07</v>
+        <v>8984.35</v>
       </c>
       <c r="F357" s="11" t="n">
-        <v>8068.46</v>
+        <v>8068.27</v>
       </c>
       <c r="G357" s="14" t="inlineStr">
         <is>
@@ -16429,16 +16429,16 @@
         </is>
       </c>
       <c r="C358" s="11" t="n">
-        <v>1494</v>
+        <v>1498.5</v>
       </c>
       <c r="D358" s="11" t="n">
-        <v>1641.12</v>
+        <v>1641.55</v>
       </c>
       <c r="E358" s="11" t="n">
-        <v>1635.75</v>
+        <v>1635.92</v>
       </c>
       <c r="F358" s="11" t="n">
-        <v>1650.05</v>
+        <v>1650.09</v>
       </c>
       <c r="G358" s="14" t="inlineStr">
         <is>
@@ -16473,13 +16473,13 @@
         </is>
       </c>
       <c r="C359" s="11" t="n">
-        <v>281.6</v>
+        <v>281.05</v>
       </c>
       <c r="D359" s="11" t="n">
-        <v>287.35</v>
+        <v>287.3</v>
       </c>
       <c r="E359" s="11" t="n">
-        <v>285.87</v>
+        <v>285.84</v>
       </c>
       <c r="F359" s="11" t="n">
         <v>308.77</v>
@@ -16517,13 +16517,13 @@
         </is>
       </c>
       <c r="C360" s="11" t="n">
-        <v>476.3</v>
+        <v>476.85</v>
       </c>
       <c r="D360" s="11" t="n">
-        <v>483.55</v>
+        <v>483.61</v>
       </c>
       <c r="E360" s="11" t="n">
-        <v>503.32</v>
+        <v>503.34</v>
       </c>
       <c r="F360" s="11" t="n">
         <v>571.76</v>
@@ -16561,16 +16561,16 @@
         </is>
       </c>
       <c r="C361" s="11" t="n">
-        <v>2702</v>
+        <v>2740</v>
       </c>
       <c r="D361" s="11" t="n">
-        <v>2820</v>
+        <v>2823.62</v>
       </c>
       <c r="E361" s="11" t="n">
-        <v>2918.78</v>
+        <v>2920.27</v>
       </c>
       <c r="F361" s="11" t="n">
-        <v>3175.76</v>
+        <v>3176.14</v>
       </c>
       <c r="G361" s="14" t="inlineStr">
         <is>
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="C362" s="11" t="n">
-        <v>986</v>
+        <v>985.9</v>
       </c>
       <c r="D362" s="11" t="n">
-        <v>1020.42</v>
+        <v>1020.41</v>
       </c>
       <c r="E362" s="11" t="n">
         <v>989.5700000000001</v>
@@ -16649,16 +16649,16 @@
         </is>
       </c>
       <c r="C363" s="11" t="n">
-        <v>18820</v>
+        <v>18902</v>
       </c>
       <c r="D363" s="11" t="n">
-        <v>17548</v>
+        <v>17555.81</v>
       </c>
       <c r="E363" s="11" t="n">
-        <v>17041.17</v>
+        <v>17044.39</v>
       </c>
       <c r="F363" s="11" t="n">
-        <v>16462.98</v>
+        <v>16463.8</v>
       </c>
       <c r="G363" s="12" t="inlineStr">
         <is>
@@ -16693,16 +16693,16 @@
         </is>
       </c>
       <c r="C364" s="11" t="n">
-        <v>968.5</v>
+        <v>967.2</v>
       </c>
       <c r="D364" s="11" t="n">
-        <v>984.41</v>
+        <v>984.29</v>
       </c>
       <c r="E364" s="11" t="n">
-        <v>994.8099999999999</v>
+        <v>994.76</v>
       </c>
       <c r="F364" s="11" t="n">
-        <v>1013.65</v>
+        <v>1013.64</v>
       </c>
       <c r="G364" s="14" t="inlineStr">
         <is>
@@ -16737,16 +16737,16 @@
         </is>
       </c>
       <c r="C365" s="11" t="n">
-        <v>38845</v>
+        <v>38825</v>
       </c>
       <c r="D365" s="11" t="n">
-        <v>37879.76</v>
+        <v>37877.85</v>
       </c>
       <c r="E365" s="11" t="n">
-        <v>36771.71</v>
+        <v>36770.92</v>
       </c>
       <c r="F365" s="11" t="n">
-        <v>37299.62</v>
+        <v>37299.42</v>
       </c>
       <c r="G365" s="12" t="inlineStr">
         <is>
@@ -16781,13 +16781,13 @@
         </is>
       </c>
       <c r="C366" s="11" t="n">
-        <v>125.24</v>
+        <v>125.3</v>
       </c>
       <c r="D366" s="11" t="n">
         <v>125.57</v>
       </c>
       <c r="E366" s="11" t="n">
-        <v>125.19</v>
+        <v>125.2</v>
       </c>
       <c r="F366" s="11" t="n">
         <v>136.54</v>
@@ -16825,13 +16825,13 @@
         </is>
       </c>
       <c r="C367" s="11" t="n">
-        <v>421.55</v>
+        <v>421.4</v>
       </c>
       <c r="D367" s="11" t="n">
-        <v>445.4</v>
+        <v>445.38</v>
       </c>
       <c r="E367" s="11" t="n">
-        <v>459.98</v>
+        <v>459.97</v>
       </c>
       <c r="F367" s="11" t="n">
         <v>512.04</v>
@@ -16869,16 +16869,16 @@
         </is>
       </c>
       <c r="C368" s="11" t="n">
-        <v>5055.5</v>
+        <v>5070</v>
       </c>
       <c r="D368" s="11" t="n">
-        <v>5087</v>
+        <v>5088.38</v>
       </c>
       <c r="E368" s="11" t="n">
-        <v>5092.8</v>
+        <v>5093.36</v>
       </c>
       <c r="F368" s="11" t="n">
-        <v>5377.53</v>
+        <v>5377.68</v>
       </c>
       <c r="G368" s="14" t="inlineStr">
         <is>
@@ -16913,10 +16913,10 @@
         </is>
       </c>
       <c r="C369" s="11" t="n">
-        <v>268.9</v>
+        <v>269.15</v>
       </c>
       <c r="D369" s="11" t="n">
-        <v>271.58</v>
+        <v>271.6</v>
       </c>
       <c r="E369" s="11" t="n">
         <v>273.71</v>
@@ -16957,16 +16957,16 @@
         </is>
       </c>
       <c r="C370" s="11" t="n">
-        <v>4543.9</v>
+        <v>4552.9</v>
       </c>
       <c r="D370" s="11" t="n">
-        <v>4599.53</v>
+        <v>4600.39</v>
       </c>
       <c r="E370" s="11" t="n">
-        <v>4694.55</v>
+        <v>4694.91</v>
       </c>
       <c r="F370" s="11" t="n">
-        <v>4812.18</v>
+        <v>4812.27</v>
       </c>
       <c r="G370" s="14" t="inlineStr">
         <is>
@@ -17001,25 +17001,25 @@
         </is>
       </c>
       <c r="C371" s="11" t="n">
-        <v>1743.2</v>
+        <v>1738.6</v>
       </c>
       <c r="D371" s="11" t="n">
-        <v>1751.41</v>
+        <v>1750.98</v>
       </c>
       <c r="E371" s="11" t="n">
-        <v>1740.07</v>
+        <v>1739.89</v>
       </c>
       <c r="F371" s="11" t="n">
-        <v>1694.91</v>
+        <v>1694.86</v>
       </c>
       <c r="G371" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H371" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H371" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I371" s="12" t="inlineStr">
@@ -17045,13 +17045,13 @@
         </is>
       </c>
       <c r="C372" s="11" t="n">
-        <v>103.98</v>
+        <v>103.89</v>
       </c>
       <c r="D372" s="11" t="n">
         <v>105.72</v>
       </c>
       <c r="E372" s="11" t="n">
-        <v>105.57</v>
+        <v>105.56</v>
       </c>
       <c r="F372" s="11" t="n">
         <v>120.13</v>
@@ -17089,16 +17089,16 @@
         </is>
       </c>
       <c r="C373" s="11" t="n">
-        <v>1476.1</v>
+        <v>1486.1</v>
       </c>
       <c r="D373" s="11" t="n">
-        <v>1460.74</v>
+        <v>1461.7</v>
       </c>
       <c r="E373" s="11" t="n">
-        <v>1437.05</v>
+        <v>1437.44</v>
       </c>
       <c r="F373" s="11" t="n">
-        <v>1440.96</v>
+        <v>1441.06</v>
       </c>
       <c r="G373" s="12" t="inlineStr">
         <is>
@@ -17133,13 +17133,13 @@
         </is>
       </c>
       <c r="C374" s="11" t="n">
-        <v>146.65</v>
+        <v>146.87</v>
       </c>
       <c r="D374" s="11" t="n">
-        <v>151.54</v>
+        <v>151.56</v>
       </c>
       <c r="E374" s="11" t="n">
-        <v>166.1</v>
+        <v>166.11</v>
       </c>
       <c r="F374" s="11" t="n">
         <v>203.75</v>
@@ -17177,16 +17177,16 @@
         </is>
       </c>
       <c r="C375" s="11" t="n">
-        <v>1985</v>
+        <v>1965.6</v>
       </c>
       <c r="D375" s="11" t="n">
-        <v>1943.08</v>
+        <v>1941.23</v>
       </c>
       <c r="E375" s="11" t="n">
-        <v>1893.98</v>
+        <v>1893.22</v>
       </c>
       <c r="F375" s="11" t="n">
-        <v>1692.58</v>
+        <v>1692.38</v>
       </c>
       <c r="G375" s="12" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         </is>
       </c>
       <c r="C376" s="11" t="n">
-        <v>168.63</v>
+        <v>168.67</v>
       </c>
       <c r="D376" s="11" t="n">
         <v>170.15</v>
@@ -17265,16 +17265,16 @@
         </is>
       </c>
       <c r="C377" s="11" t="n">
-        <v>1411.2</v>
+        <v>1410</v>
       </c>
       <c r="D377" s="11" t="n">
-        <v>1427.02</v>
+        <v>1426.91</v>
       </c>
       <c r="E377" s="11" t="n">
-        <v>1449.67</v>
+        <v>1449.62</v>
       </c>
       <c r="F377" s="11" t="n">
-        <v>1636.32</v>
+        <v>1636.31</v>
       </c>
       <c r="G377" s="14" t="inlineStr">
         <is>
@@ -17309,16 +17309,16 @@
         </is>
       </c>
       <c r="C378" s="11" t="n">
-        <v>9649</v>
+        <v>9648</v>
       </c>
       <c r="D378" s="11" t="n">
-        <v>9353.24</v>
+        <v>9353.139999999999</v>
       </c>
       <c r="E378" s="11" t="n">
-        <v>8788.6</v>
+        <v>8788.559999999999</v>
       </c>
       <c r="F378" s="11" t="n">
-        <v>7731.17</v>
+        <v>7731.16</v>
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
@@ -17353,16 +17353,16 @@
         </is>
       </c>
       <c r="C379" s="11" t="n">
-        <v>385.35</v>
+        <v>383.5</v>
       </c>
       <c r="D379" s="11" t="n">
-        <v>398.76</v>
+        <v>398.58</v>
       </c>
       <c r="E379" s="11" t="n">
-        <v>409.71</v>
+        <v>409.64</v>
       </c>
       <c r="F379" s="11" t="n">
-        <v>424.3</v>
+        <v>424.28</v>
       </c>
       <c r="G379" s="14" t="inlineStr">
         <is>
@@ -17397,16 +17397,16 @@
         </is>
       </c>
       <c r="C380" s="11" t="n">
-        <v>435.25</v>
+        <v>434.7</v>
       </c>
       <c r="D380" s="11" t="n">
-        <v>432.23</v>
+        <v>432.18</v>
       </c>
       <c r="E380" s="11" t="n">
-        <v>431.84</v>
+        <v>431.82</v>
       </c>
       <c r="F380" s="11" t="n">
-        <v>405.12</v>
+        <v>405.11</v>
       </c>
       <c r="G380" s="12" t="inlineStr">
         <is>
@@ -17441,16 +17441,16 @@
         </is>
       </c>
       <c r="C381" s="11" t="n">
-        <v>286.15</v>
+        <v>286.25</v>
       </c>
       <c r="D381" s="11" t="n">
-        <v>293.72</v>
+        <v>293.73</v>
       </c>
       <c r="E381" s="11" t="n">
-        <v>298.19</v>
+        <v>298.2</v>
       </c>
       <c r="F381" s="11" t="n">
-        <v>287.15</v>
+        <v>287.16</v>
       </c>
       <c r="G381" s="14" t="inlineStr">
         <is>
@@ -17485,16 +17485,16 @@
         </is>
       </c>
       <c r="C382" s="11" t="n">
-        <v>1093.2</v>
+        <v>1091.3</v>
       </c>
       <c r="D382" s="11" t="n">
-        <v>1045.51</v>
+        <v>1045.33</v>
       </c>
       <c r="E382" s="11" t="n">
-        <v>994.4299999999999</v>
+        <v>994.36</v>
       </c>
       <c r="F382" s="11" t="n">
-        <v>935.3099999999999</v>
+        <v>935.29</v>
       </c>
       <c r="G382" s="12" t="inlineStr">
         <is>
@@ -17529,16 +17529,16 @@
         </is>
       </c>
       <c r="C383" s="11" t="n">
-        <v>1342.4</v>
+        <v>1344.9</v>
       </c>
       <c r="D383" s="11" t="n">
-        <v>1372.71</v>
+        <v>1372.95</v>
       </c>
       <c r="E383" s="11" t="n">
-        <v>1377.54</v>
+        <v>1377.64</v>
       </c>
       <c r="F383" s="11" t="n">
-        <v>1444.44</v>
+        <v>1444.46</v>
       </c>
       <c r="G383" s="14" t="inlineStr">
         <is>
@@ -17573,13 +17573,13 @@
         </is>
       </c>
       <c r="C384" s="11" t="n">
-        <v>107.91</v>
+        <v>108.14</v>
       </c>
       <c r="D384" s="11" t="n">
-        <v>105.8</v>
+        <v>105.83</v>
       </c>
       <c r="E384" s="11" t="n">
-        <v>108.18</v>
+        <v>108.19</v>
       </c>
       <c r="F384" s="11" t="n">
         <v>111.64</v>
@@ -17617,16 +17617,16 @@
         </is>
       </c>
       <c r="C385" s="11" t="n">
-        <v>2149.5</v>
+        <v>2145.5</v>
       </c>
       <c r="D385" s="11" t="n">
-        <v>2020.8</v>
+        <v>2020.42</v>
       </c>
       <c r="E385" s="11" t="n">
-        <v>1822.73</v>
+        <v>1822.58</v>
       </c>
       <c r="F385" s="11" t="n">
-        <v>1508.49</v>
+        <v>1508.45</v>
       </c>
       <c r="G385" s="12" t="inlineStr">
         <is>
@@ -17661,13 +17661,13 @@
         </is>
       </c>
       <c r="C386" s="11" t="n">
-        <v>352.1</v>
+        <v>352.5</v>
       </c>
       <c r="D386" s="11" t="n">
-        <v>342.07</v>
+        <v>342.1</v>
       </c>
       <c r="E386" s="11" t="n">
-        <v>331.71</v>
+        <v>331.73</v>
       </c>
       <c r="F386" s="11" t="n">
         <v>300.58</v>
@@ -17705,13 +17705,13 @@
         </is>
       </c>
       <c r="C387" s="11" t="n">
-        <v>349.65</v>
+        <v>350.05</v>
       </c>
       <c r="D387" s="11" t="n">
-        <v>340.75</v>
+        <v>340.79</v>
       </c>
       <c r="E387" s="11" t="n">
-        <v>344.53</v>
+        <v>344.55</v>
       </c>
       <c r="F387" s="11" t="n">
         <v>352.23</v>
@@ -17749,16 +17749,16 @@
         </is>
       </c>
       <c r="C388" s="11" t="n">
-        <v>375.55</v>
+        <v>375.25</v>
       </c>
       <c r="D388" s="11" t="n">
-        <v>389.47</v>
+        <v>389.45</v>
       </c>
       <c r="E388" s="11" t="n">
-        <v>394.88</v>
+        <v>394.86</v>
       </c>
       <c r="F388" s="11" t="n">
-        <v>421.65</v>
+        <v>421.64</v>
       </c>
       <c r="G388" s="14" t="inlineStr">
         <is>
@@ -17793,13 +17793,13 @@
         </is>
       </c>
       <c r="C389" s="11" t="n">
-        <v>204.31</v>
+        <v>204.11</v>
       </c>
       <c r="D389" s="11" t="n">
-        <v>206.4</v>
+        <v>206.38</v>
       </c>
       <c r="E389" s="11" t="n">
-        <v>209.13</v>
+        <v>209.12</v>
       </c>
       <c r="F389" s="11" t="n">
         <v>220.53</v>
@@ -17837,16 +17837,16 @@
         </is>
       </c>
       <c r="C390" s="11" t="n">
-        <v>3490</v>
+        <v>3494</v>
       </c>
       <c r="D390" s="11" t="n">
-        <v>3470.56</v>
+        <v>3470.94</v>
       </c>
       <c r="E390" s="11" t="n">
-        <v>3314.21</v>
+        <v>3314.36</v>
       </c>
       <c r="F390" s="11" t="n">
-        <v>3013</v>
+        <v>3013.04</v>
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
@@ -17881,10 +17881,10 @@
         </is>
       </c>
       <c r="C391" s="11" t="n">
-        <v>232.62</v>
+        <v>232.4</v>
       </c>
       <c r="D391" s="11" t="n">
-        <v>254.16</v>
+        <v>254.14</v>
       </c>
       <c r="E391" s="11" t="n">
         <v>271.8</v>
@@ -17925,13 +17925,13 @@
         </is>
       </c>
       <c r="C392" s="11" t="n">
-        <v>308.35</v>
+        <v>308.9</v>
       </c>
       <c r="D392" s="11" t="n">
-        <v>317.04</v>
+        <v>317.09</v>
       </c>
       <c r="E392" s="11" t="n">
-        <v>316.45</v>
+        <v>316.47</v>
       </c>
       <c r="F392" s="11" t="n">
         <v>326.71</v>
@@ -17969,16 +17969,16 @@
         </is>
       </c>
       <c r="C393" s="11" t="n">
-        <v>1334.6</v>
+        <v>1335.5</v>
       </c>
       <c r="D393" s="11" t="n">
-        <v>1338.62</v>
+        <v>1338.7</v>
       </c>
       <c r="E393" s="11" t="n">
-        <v>1299.73</v>
+        <v>1299.76</v>
       </c>
       <c r="F393" s="11" t="n">
-        <v>1296.72</v>
+        <v>1296.73</v>
       </c>
       <c r="G393" s="14" t="inlineStr">
         <is>
@@ -18013,13 +18013,13 @@
         </is>
       </c>
       <c r="C394" s="11" t="n">
-        <v>534.9</v>
+        <v>535.3</v>
       </c>
       <c r="D394" s="11" t="n">
-        <v>561.99</v>
+        <v>562.03</v>
       </c>
       <c r="E394" s="11" t="n">
-        <v>560.58</v>
+        <v>560.6</v>
       </c>
       <c r="F394" s="11" t="n">
         <v>559.95</v>
@@ -18057,16 +18057,16 @@
         </is>
       </c>
       <c r="C395" s="11" t="n">
-        <v>239.46</v>
+        <v>239.7</v>
       </c>
       <c r="D395" s="11" t="n">
-        <v>229.9</v>
+        <v>229.92</v>
       </c>
       <c r="E395" s="11" t="n">
         <v>228.25</v>
       </c>
       <c r="F395" s="11" t="n">
-        <v>245.19</v>
+        <v>245.2</v>
       </c>
       <c r="G395" s="12" t="inlineStr">
         <is>
@@ -18101,16 +18101,16 @@
         </is>
       </c>
       <c r="C396" s="11" t="n">
-        <v>1263.4</v>
+        <v>1266.2</v>
       </c>
       <c r="D396" s="11" t="n">
-        <v>1321.47</v>
+        <v>1321.73</v>
       </c>
       <c r="E396" s="11" t="n">
-        <v>1350.91</v>
+        <v>1351.02</v>
       </c>
       <c r="F396" s="11" t="n">
-        <v>1387.89</v>
+        <v>1387.92</v>
       </c>
       <c r="G396" s="14" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="C397" s="11" t="n">
-        <v>27.07</v>
+        <v>27.02</v>
       </c>
       <c r="D397" s="11" t="n">
         <v>27.39</v>
@@ -18189,16 +18189,16 @@
         </is>
       </c>
       <c r="C398" s="11" t="n">
-        <v>91.28</v>
+        <v>91.58</v>
       </c>
       <c r="D398" s="11" t="n">
-        <v>92.31999999999999</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="E398" s="11" t="n">
-        <v>92.68000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="F398" s="11" t="n">
-        <v>97.04000000000001</v>
+        <v>97.05</v>
       </c>
       <c r="G398" s="14" t="inlineStr">
         <is>
@@ -18233,13 +18233,13 @@
         </is>
       </c>
       <c r="C399" s="11" t="n">
-        <v>577.35</v>
+        <v>577.65</v>
       </c>
       <c r="D399" s="11" t="n">
-        <v>611.6900000000001</v>
+        <v>611.72</v>
       </c>
       <c r="E399" s="11" t="n">
-        <v>644.24</v>
+        <v>644.26</v>
       </c>
       <c r="F399" s="11" t="n">
         <v>749.27</v>
@@ -18277,10 +18277,10 @@
         </is>
       </c>
       <c r="C400" s="11" t="n">
-        <v>1777</v>
+        <v>1777.1</v>
       </c>
       <c r="D400" s="11" t="n">
-        <v>1822.01</v>
+        <v>1822.02</v>
       </c>
       <c r="E400" s="11" t="n">
         <v>1857.76</v>
@@ -18321,16 +18321,16 @@
         </is>
       </c>
       <c r="C401" s="11" t="n">
-        <v>72.22</v>
+        <v>72</v>
       </c>
       <c r="D401" s="11" t="n">
-        <v>74.12</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E401" s="11" t="n">
-        <v>74.51000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="F401" s="11" t="n">
-        <v>77.91</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G401" s="14" t="inlineStr">
         <is>
@@ -18365,16 +18365,16 @@
         </is>
       </c>
       <c r="C402" s="11" t="n">
-        <v>2714</v>
+        <v>2721.7</v>
       </c>
       <c r="D402" s="11" t="n">
-        <v>2690.25</v>
+        <v>2690.98</v>
       </c>
       <c r="E402" s="11" t="n">
-        <v>2653.3</v>
+        <v>2653.6</v>
       </c>
       <c r="F402" s="11" t="n">
-        <v>2758.58</v>
+        <v>2758.66</v>
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         </is>
       </c>
       <c r="C403" s="11" t="n">
-        <v>39.87</v>
+        <v>39.86</v>
       </c>
       <c r="D403" s="11" t="n">
         <v>40.95</v>
@@ -18453,16 +18453,16 @@
         </is>
       </c>
       <c r="C404" s="11" t="n">
-        <v>1201.9</v>
+        <v>1205.6</v>
       </c>
       <c r="D404" s="11" t="n">
-        <v>1141.52</v>
+        <v>1141.87</v>
       </c>
       <c r="E404" s="11" t="n">
-        <v>1086.01</v>
+        <v>1086.15</v>
       </c>
       <c r="F404" s="11" t="n">
-        <v>956.27</v>
+        <v>956.3099999999999</v>
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
@@ -18497,16 +18497,16 @@
         </is>
       </c>
       <c r="C405" s="11" t="n">
-        <v>177.18</v>
+        <v>177.84</v>
       </c>
       <c r="D405" s="11" t="n">
-        <v>168.09</v>
+        <v>168.15</v>
       </c>
       <c r="E405" s="11" t="n">
-        <v>157.98</v>
+        <v>158.01</v>
       </c>
       <c r="F405" s="11" t="n">
-        <v>147.5</v>
+        <v>147.51</v>
       </c>
       <c r="G405" s="12" t="inlineStr">
         <is>
@@ -18541,16 +18541,16 @@
         </is>
       </c>
       <c r="C406" s="11" t="n">
-        <v>142.32</v>
+        <v>143.03</v>
       </c>
       <c r="D406" s="11" t="n">
-        <v>138.18</v>
+        <v>138.25</v>
       </c>
       <c r="E406" s="11" t="n">
-        <v>131.15</v>
+        <v>131.18</v>
       </c>
       <c r="F406" s="11" t="n">
-        <v>117.42</v>
+        <v>117.43</v>
       </c>
       <c r="G406" s="12" t="inlineStr">
         <is>
@@ -18585,13 +18585,13 @@
         </is>
       </c>
       <c r="C407" s="11" t="n">
-        <v>175.42</v>
+        <v>175.11</v>
       </c>
       <c r="D407" s="11" t="n">
-        <v>179.3</v>
+        <v>179.27</v>
       </c>
       <c r="E407" s="11" t="n">
-        <v>181.36</v>
+        <v>181.35</v>
       </c>
       <c r="F407" s="11" t="n">
         <v>222.43</v>
@@ -18629,16 +18629,16 @@
         </is>
       </c>
       <c r="C408" s="11" t="n">
-        <v>531.85</v>
+        <v>531.2</v>
       </c>
       <c r="D408" s="11" t="n">
-        <v>540.53</v>
+        <v>540.47</v>
       </c>
       <c r="E408" s="11" t="n">
-        <v>546.7</v>
+        <v>546.6799999999999</v>
       </c>
       <c r="F408" s="11" t="n">
-        <v>527.03</v>
+        <v>527.02</v>
       </c>
       <c r="G408" s="14" t="inlineStr">
         <is>
@@ -18673,16 +18673,16 @@
         </is>
       </c>
       <c r="C409" s="11" t="n">
-        <v>455.75</v>
+        <v>454.45</v>
       </c>
       <c r="D409" s="11" t="n">
-        <v>424.38</v>
+        <v>424.26</v>
       </c>
       <c r="E409" s="11" t="n">
-        <v>389.28</v>
+        <v>389.23</v>
       </c>
       <c r="F409" s="11" t="n">
-        <v>390.8</v>
+        <v>390.78</v>
       </c>
       <c r="G409" s="12" t="inlineStr">
         <is>
@@ -18717,16 +18717,16 @@
         </is>
       </c>
       <c r="C410" s="11" t="n">
-        <v>4125.1</v>
+        <v>4133.9</v>
       </c>
       <c r="D410" s="11" t="n">
-        <v>4081.47</v>
+        <v>4082.31</v>
       </c>
       <c r="E410" s="11" t="n">
-        <v>4062.19</v>
+        <v>4062.53</v>
       </c>
       <c r="F410" s="11" t="n">
-        <v>3925.62</v>
+        <v>3925.7</v>
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
@@ -18761,16 +18761,16 @@
         </is>
       </c>
       <c r="C411" s="11" t="n">
-        <v>1146.2</v>
+        <v>1141.1</v>
       </c>
       <c r="D411" s="11" t="n">
-        <v>1222.69</v>
+        <v>1222.2</v>
       </c>
       <c r="E411" s="11" t="n">
-        <v>1161.94</v>
+        <v>1161.74</v>
       </c>
       <c r="F411" s="11" t="n">
-        <v>937.88</v>
+        <v>937.83</v>
       </c>
       <c r="G411" s="14" t="inlineStr">
         <is>
@@ -18805,16 +18805,16 @@
         </is>
       </c>
       <c r="C412" s="11" t="n">
-        <v>292.2</v>
+        <v>293.55</v>
       </c>
       <c r="D412" s="11" t="n">
-        <v>304.57</v>
+        <v>304.7</v>
       </c>
       <c r="E412" s="11" t="n">
-        <v>294.41</v>
+        <v>294.46</v>
       </c>
       <c r="F412" s="11" t="n">
-        <v>249.51</v>
+        <v>249.53</v>
       </c>
       <c r="G412" s="14" t="inlineStr">
         <is>
@@ -18849,16 +18849,16 @@
         </is>
       </c>
       <c r="C413" s="11" t="n">
-        <v>23490</v>
+        <v>23450</v>
       </c>
       <c r="D413" s="11" t="n">
-        <v>24605.76</v>
+        <v>24601.95</v>
       </c>
       <c r="E413" s="11" t="n">
-        <v>24799.17</v>
+        <v>24797.6</v>
       </c>
       <c r="F413" s="11" t="n">
-        <v>26265.31</v>
+        <v>26264.91</v>
       </c>
       <c r="G413" s="14" t="inlineStr">
         <is>
@@ -18893,10 +18893,10 @@
         </is>
       </c>
       <c r="C414" s="11" t="n">
-        <v>899.05</v>
+        <v>898.95</v>
       </c>
       <c r="D414" s="11" t="n">
-        <v>931.9</v>
+        <v>931.89</v>
       </c>
       <c r="E414" s="11" t="n">
         <v>953.21</v>
@@ -18937,16 +18937,16 @@
         </is>
       </c>
       <c r="C415" s="11" t="n">
-        <v>970.05</v>
+        <v>969.7</v>
       </c>
       <c r="D415" s="11" t="n">
-        <v>952.5</v>
+        <v>952.46</v>
       </c>
       <c r="E415" s="11" t="n">
-        <v>906.52</v>
+        <v>906.51</v>
       </c>
       <c r="F415" s="11" t="n">
-        <v>862.28</v>
+        <v>862.27</v>
       </c>
       <c r="G415" s="12" t="inlineStr">
         <is>
@@ -18981,16 +18981,16 @@
         </is>
       </c>
       <c r="C416" s="11" t="n">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="D416" s="11" t="n">
-        <v>3516.34</v>
+        <v>3516.15</v>
       </c>
       <c r="E416" s="11" t="n">
-        <v>3287.28</v>
+        <v>3287.2</v>
       </c>
       <c r="F416" s="11" t="n">
-        <v>3017.41</v>
+        <v>3017.39</v>
       </c>
       <c r="G416" s="12" t="inlineStr">
         <is>
@@ -19025,16 +19025,16 @@
         </is>
       </c>
       <c r="C417" s="11" t="n">
-        <v>3604</v>
+        <v>3602.3</v>
       </c>
       <c r="D417" s="11" t="n">
-        <v>3696.61</v>
+        <v>3696.45</v>
       </c>
       <c r="E417" s="11" t="n">
-        <v>3605.73</v>
+        <v>3605.66</v>
       </c>
       <c r="F417" s="11" t="n">
-        <v>3322.68</v>
+        <v>3322.67</v>
       </c>
       <c r="G417" s="14" t="inlineStr">
         <is>
@@ -19069,16 +19069,16 @@
         </is>
       </c>
       <c r="C418" s="11" t="n">
-        <v>816.55</v>
+        <v>815.7</v>
       </c>
       <c r="D418" s="11" t="n">
-        <v>825.48</v>
+        <v>825.4</v>
       </c>
       <c r="E418" s="11" t="n">
-        <v>841.6799999999999</v>
+        <v>841.65</v>
       </c>
       <c r="F418" s="11" t="n">
-        <v>951.39</v>
+        <v>951.38</v>
       </c>
       <c r="G418" s="14" t="inlineStr">
         <is>
@@ -19113,16 +19113,16 @@
         </is>
       </c>
       <c r="C419" s="11" t="n">
-        <v>1294.7</v>
+        <v>1286.5</v>
       </c>
       <c r="D419" s="11" t="n">
-        <v>1367.8</v>
+        <v>1367.01</v>
       </c>
       <c r="E419" s="11" t="n">
-        <v>1375.21</v>
+        <v>1374.89</v>
       </c>
       <c r="F419" s="11" t="n">
-        <v>1410.28</v>
+        <v>1410.2</v>
       </c>
       <c r="G419" s="14" t="inlineStr">
         <is>
@@ -19157,16 +19157,16 @@
         </is>
       </c>
       <c r="C420" s="11" t="n">
-        <v>18306</v>
+        <v>18270</v>
       </c>
       <c r="D420" s="11" t="n">
-        <v>17854.21</v>
+        <v>17850.78</v>
       </c>
       <c r="E420" s="11" t="n">
-        <v>16555.33</v>
+        <v>16553.92</v>
       </c>
       <c r="F420" s="11" t="n">
-        <v>14484</v>
+        <v>14483.64</v>
       </c>
       <c r="G420" s="12" t="inlineStr">
         <is>
@@ -19201,20 +19201,20 @@
         </is>
       </c>
       <c r="C421" s="11" t="n">
-        <v>595</v>
+        <v>599.9</v>
       </c>
       <c r="D421" s="11" t="n">
-        <v>595.83</v>
+        <v>596.3</v>
       </c>
       <c r="E421" s="11" t="n">
-        <v>576.79</v>
+        <v>576.98</v>
       </c>
       <c r="F421" s="11" t="n">
-        <v>522.86</v>
-      </c>
-      <c r="G421" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>522.91</v>
+      </c>
+      <c r="G421" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H421" s="12" t="inlineStr">
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="C422" s="11" t="n">
-        <v>262.45</v>
+        <v>262.5</v>
       </c>
       <c r="D422" s="11" t="n">
-        <v>266.47</v>
+        <v>266.48</v>
       </c>
       <c r="E422" s="11" t="n">
         <v>266.52</v>
@@ -19289,13 +19289,13 @@
         </is>
       </c>
       <c r="C423" s="11" t="n">
-        <v>519.55</v>
+        <v>520.05</v>
       </c>
       <c r="D423" s="11" t="n">
-        <v>521.6</v>
+        <v>521.65</v>
       </c>
       <c r="E423" s="11" t="n">
-        <v>508.13</v>
+        <v>508.15</v>
       </c>
       <c r="F423" s="11" t="n">
         <v>473.02</v>
@@ -19333,16 +19333,16 @@
         </is>
       </c>
       <c r="C424" s="11" t="n">
-        <v>989.9</v>
+        <v>990.9</v>
       </c>
       <c r="D424" s="11" t="n">
-        <v>978.16</v>
+        <v>978.26</v>
       </c>
       <c r="E424" s="11" t="n">
-        <v>1003.36</v>
+        <v>1003.4</v>
       </c>
       <c r="F424" s="11" t="n">
-        <v>969.21</v>
+        <v>969.22</v>
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         </is>
       </c>
       <c r="C425" s="11" t="n">
-        <v>185.4</v>
+        <v>185.37</v>
       </c>
       <c r="D425" s="11" t="n">
         <v>194.61</v>
@@ -19421,13 +19421,13 @@
         </is>
       </c>
       <c r="C426" s="11" t="n">
-        <v>459.2</v>
+        <v>458.9</v>
       </c>
       <c r="D426" s="11" t="n">
-        <v>471.34</v>
+        <v>471.31</v>
       </c>
       <c r="E426" s="11" t="n">
-        <v>454.82</v>
+        <v>454.81</v>
       </c>
       <c r="F426" s="11" t="n">
         <v>459.57</v>
@@ -19465,16 +19465,16 @@
         </is>
       </c>
       <c r="C427" s="11" t="n">
-        <v>1791.6</v>
+        <v>1788.6</v>
       </c>
       <c r="D427" s="11" t="n">
-        <v>1810.43</v>
+        <v>1810.14</v>
       </c>
       <c r="E427" s="11" t="n">
-        <v>1793.63</v>
+        <v>1793.51</v>
       </c>
       <c r="F427" s="11" t="n">
-        <v>1732.1</v>
+        <v>1732.07</v>
       </c>
       <c r="G427" s="14" t="inlineStr">
         <is>
@@ -19509,10 +19509,10 @@
         </is>
       </c>
       <c r="C428" s="11" t="n">
-        <v>510.05</v>
+        <v>509.95</v>
       </c>
       <c r="D428" s="11" t="n">
-        <v>522.35</v>
+        <v>522.34</v>
       </c>
       <c r="E428" s="11" t="n">
         <v>548.2</v>
@@ -19553,16 +19553,16 @@
         </is>
       </c>
       <c r="C429" s="11" t="n">
-        <v>4142.3</v>
+        <v>4136.2</v>
       </c>
       <c r="D429" s="11" t="n">
-        <v>4319.62</v>
+        <v>4319.04</v>
       </c>
       <c r="E429" s="11" t="n">
-        <v>4552.09</v>
+        <v>4551.85</v>
       </c>
       <c r="F429" s="11" t="n">
-        <v>4784.53</v>
+        <v>4784.47</v>
       </c>
       <c r="G429" s="14" t="inlineStr">
         <is>
@@ -19597,16 +19597,16 @@
         </is>
       </c>
       <c r="C430" s="11" t="n">
-        <v>3497.2</v>
+        <v>3495.8</v>
       </c>
       <c r="D430" s="11" t="n">
-        <v>3566.84</v>
+        <v>3566.71</v>
       </c>
       <c r="E430" s="11" t="n">
-        <v>3621.36</v>
+        <v>3621.31</v>
       </c>
       <c r="F430" s="11" t="n">
-        <v>3728.12</v>
+        <v>3728.1</v>
       </c>
       <c r="G430" s="14" t="inlineStr">
         <is>
@@ -19641,13 +19641,13 @@
         </is>
       </c>
       <c r="C431" s="11" t="n">
-        <v>684.85</v>
+        <v>684.6</v>
       </c>
       <c r="D431" s="11" t="n">
-        <v>694.25</v>
+        <v>694.23</v>
       </c>
       <c r="E431" s="11" t="n">
-        <v>702.38</v>
+        <v>702.37</v>
       </c>
       <c r="F431" s="11" t="n">
         <v>688.55</v>
@@ -19685,7 +19685,7 @@
         </is>
       </c>
       <c r="C432" s="11" t="n">
-        <v>54.73</v>
+        <v>54.72</v>
       </c>
       <c r="D432" s="11" t="n">
         <v>54.52</v>
@@ -19729,16 +19729,16 @@
         </is>
       </c>
       <c r="C433" s="11" t="n">
-        <v>308.6</v>
+        <v>309.15</v>
       </c>
       <c r="D433" s="11" t="n">
-        <v>319.78</v>
+        <v>319.83</v>
       </c>
       <c r="E433" s="11" t="n">
-        <v>332.18</v>
+        <v>332.2</v>
       </c>
       <c r="F433" s="11" t="n">
-        <v>384.78</v>
+        <v>384.79</v>
       </c>
       <c r="G433" s="14" t="inlineStr">
         <is>
@@ -19773,13 +19773,13 @@
         </is>
       </c>
       <c r="C434" s="11" t="n">
-        <v>243.7</v>
+        <v>243.95</v>
       </c>
       <c r="D434" s="11" t="n">
-        <v>255.67</v>
+        <v>255.69</v>
       </c>
       <c r="E434" s="11" t="n">
-        <v>268.88</v>
+        <v>268.89</v>
       </c>
       <c r="F434" s="11" t="n">
         <v>321.03</v>
@@ -19817,16 +19817,16 @@
         </is>
       </c>
       <c r="C435" s="11" t="n">
-        <v>448</v>
+        <v>446.6</v>
       </c>
       <c r="D435" s="11" t="n">
-        <v>450.07</v>
+        <v>449.94</v>
       </c>
       <c r="E435" s="11" t="n">
-        <v>450.65</v>
+        <v>450.6</v>
       </c>
       <c r="F435" s="11" t="n">
-        <v>522.74</v>
+        <v>522.73</v>
       </c>
       <c r="G435" s="14" t="inlineStr">
         <is>
@@ -19861,10 +19861,10 @@
         </is>
       </c>
       <c r="C436" s="11" t="n">
-        <v>1255.7</v>
+        <v>1255.6</v>
       </c>
       <c r="D436" s="11" t="n">
-        <v>1117.6</v>
+        <v>1117.59</v>
       </c>
       <c r="E436" s="11" t="n">
         <v>1022.09</v>
@@ -19905,16 +19905,16 @@
         </is>
       </c>
       <c r="C437" s="11" t="n">
-        <v>1187.3</v>
+        <v>1191</v>
       </c>
       <c r="D437" s="11" t="n">
-        <v>1209.68</v>
+        <v>1210.03</v>
       </c>
       <c r="E437" s="11" t="n">
-        <v>1224.29</v>
+        <v>1224.44</v>
       </c>
       <c r="F437" s="11" t="n">
-        <v>1333.86</v>
+        <v>1333.89</v>
       </c>
       <c r="G437" s="14" t="inlineStr">
         <is>
@@ -19949,16 +19949,16 @@
         </is>
       </c>
       <c r="C438" s="11" t="n">
-        <v>3350.8</v>
+        <v>3350.2</v>
       </c>
       <c r="D438" s="11" t="n">
-        <v>3399.9</v>
+        <v>3399.84</v>
       </c>
       <c r="E438" s="11" t="n">
-        <v>3481.81</v>
+        <v>3481.79</v>
       </c>
       <c r="F438" s="11" t="n">
-        <v>3432.45</v>
+        <v>3432.44</v>
       </c>
       <c r="G438" s="14" t="inlineStr">
         <is>
@@ -19993,16 +19993,16 @@
         </is>
       </c>
       <c r="C439" s="11" t="n">
-        <v>314.85</v>
+        <v>316</v>
       </c>
       <c r="D439" s="11" t="n">
-        <v>310.95</v>
+        <v>311.06</v>
       </c>
       <c r="E439" s="11" t="n">
-        <v>316.6</v>
+        <v>316.64</v>
       </c>
       <c r="F439" s="11" t="n">
-        <v>326.77</v>
+        <v>326.78</v>
       </c>
       <c r="G439" s="12" t="inlineStr">
         <is>
@@ -20037,16 +20037,16 @@
         </is>
       </c>
       <c r="C440" s="11" t="n">
-        <v>714.9</v>
+        <v>713.8</v>
       </c>
       <c r="D440" s="11" t="n">
-        <v>740.4</v>
+        <v>740.29</v>
       </c>
       <c r="E440" s="11" t="n">
-        <v>735.45</v>
+        <v>735.4</v>
       </c>
       <c r="F440" s="11" t="n">
-        <v>767.3099999999999</v>
+        <v>767.3</v>
       </c>
       <c r="G440" s="14" t="inlineStr">
         <is>
@@ -20081,16 +20081,16 @@
         </is>
       </c>
       <c r="C441" s="11" t="n">
-        <v>1986</v>
+        <v>1982.8</v>
       </c>
       <c r="D441" s="11" t="n">
-        <v>1868.3</v>
+        <v>1868</v>
       </c>
       <c r="E441" s="11" t="n">
-        <v>1735.32</v>
+        <v>1735.2</v>
       </c>
       <c r="F441" s="11" t="n">
-        <v>1658.24</v>
+        <v>1658.2</v>
       </c>
       <c r="G441" s="12" t="inlineStr">
         <is>
@@ -20125,16 +20125,16 @@
         </is>
       </c>
       <c r="C442" s="11" t="n">
-        <v>2146.5</v>
+        <v>2150</v>
       </c>
       <c r="D442" s="11" t="n">
-        <v>2271.32</v>
+        <v>2271.65</v>
       </c>
       <c r="E442" s="11" t="n">
-        <v>2366.74</v>
+        <v>2366.87</v>
       </c>
       <c r="F442" s="11" t="n">
-        <v>2716.98</v>
+        <v>2717.02</v>
       </c>
       <c r="G442" s="14" t="inlineStr">
         <is>
@@ -20169,16 +20169,16 @@
         </is>
       </c>
       <c r="C443" s="11" t="n">
-        <v>1096.5</v>
+        <v>1098.1</v>
       </c>
       <c r="D443" s="11" t="n">
-        <v>1156.65</v>
+        <v>1156.81</v>
       </c>
       <c r="E443" s="11" t="n">
-        <v>1150.05</v>
+        <v>1150.11</v>
       </c>
       <c r="F443" s="11" t="n">
-        <v>1122.89</v>
+        <v>1122.91</v>
       </c>
       <c r="G443" s="14" t="inlineStr">
         <is>
@@ -20213,16 +20213,16 @@
         </is>
       </c>
       <c r="C444" s="11" t="n">
-        <v>4233</v>
+        <v>4240.8</v>
       </c>
       <c r="D444" s="11" t="n">
-        <v>4283.31</v>
+        <v>4284.05</v>
       </c>
       <c r="E444" s="11" t="n">
-        <v>4331.6</v>
+        <v>4331.9</v>
       </c>
       <c r="F444" s="11" t="n">
-        <v>4854.12</v>
+        <v>4854.19</v>
       </c>
       <c r="G444" s="14" t="inlineStr">
         <is>
@@ -20257,16 +20257,16 @@
         </is>
       </c>
       <c r="C445" s="11" t="n">
-        <v>655.8</v>
+        <v>656.9</v>
       </c>
       <c r="D445" s="11" t="n">
-        <v>673.12</v>
+        <v>673.22</v>
       </c>
       <c r="E445" s="11" t="n">
-        <v>673.79</v>
+        <v>673.83</v>
       </c>
       <c r="F445" s="11" t="n">
-        <v>680.48</v>
+        <v>680.49</v>
       </c>
       <c r="G445" s="14" t="inlineStr">
         <is>
@@ -20301,13 +20301,13 @@
         </is>
       </c>
       <c r="C446" s="11" t="n">
-        <v>364.8</v>
+        <v>364.5</v>
       </c>
       <c r="D446" s="11" t="n">
-        <v>380.98</v>
+        <v>380.95</v>
       </c>
       <c r="E446" s="11" t="n">
-        <v>399.56</v>
+        <v>399.54</v>
       </c>
       <c r="F446" s="11" t="n">
         <v>394.53</v>
@@ -20345,16 +20345,16 @@
         </is>
       </c>
       <c r="C447" s="11" t="n">
-        <v>388.7</v>
+        <v>389</v>
       </c>
       <c r="D447" s="11" t="n">
-        <v>380.19</v>
+        <v>380.22</v>
       </c>
       <c r="E447" s="11" t="n">
-        <v>365.26</v>
+        <v>365.27</v>
       </c>
       <c r="F447" s="11" t="n">
-        <v>420.2</v>
+        <v>420.21</v>
       </c>
       <c r="G447" s="12" t="inlineStr">
         <is>
@@ -20389,16 +20389,16 @@
         </is>
       </c>
       <c r="C448" s="11" t="n">
-        <v>399.5</v>
+        <v>399.9</v>
       </c>
       <c r="D448" s="11" t="n">
-        <v>414.46</v>
+        <v>414.5</v>
       </c>
       <c r="E448" s="11" t="n">
-        <v>413.12</v>
+        <v>413.13</v>
       </c>
       <c r="F448" s="11" t="n">
-        <v>395.05</v>
+        <v>395.06</v>
       </c>
       <c r="G448" s="14" t="inlineStr">
         <is>
@@ -20433,10 +20433,10 @@
         </is>
       </c>
       <c r="C449" s="11" t="n">
-        <v>202.36</v>
+        <v>202.39</v>
       </c>
       <c r="D449" s="11" t="n">
-        <v>209.35</v>
+        <v>209.36</v>
       </c>
       <c r="E449" s="11" t="n">
         <v>207.89</v>
@@ -20477,16 +20477,16 @@
         </is>
       </c>
       <c r="C450" s="11" t="n">
-        <v>750.1</v>
+        <v>750.8</v>
       </c>
       <c r="D450" s="11" t="n">
-        <v>704.9299999999999</v>
+        <v>705</v>
       </c>
       <c r="E450" s="11" t="n">
-        <v>653.63</v>
+        <v>653.66</v>
       </c>
       <c r="F450" s="11" t="n">
-        <v>641.6</v>
+        <v>641.61</v>
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
@@ -20521,16 +20521,16 @@
         </is>
       </c>
       <c r="C451" s="11" t="n">
-        <v>42.75</v>
+        <v>42.68</v>
       </c>
       <c r="D451" s="11" t="n">
-        <v>43.18</v>
+        <v>43.17</v>
       </c>
       <c r="E451" s="11" t="n">
         <v>42.66</v>
       </c>
       <c r="F451" s="11" t="n">
-        <v>47.13</v>
+        <v>47.12</v>
       </c>
       <c r="G451" s="14" t="inlineStr">
         <is>
@@ -20565,16 +20565,16 @@
         </is>
       </c>
       <c r="C452" s="11" t="n">
-        <v>1486.3</v>
+        <v>1487.4</v>
       </c>
       <c r="D452" s="11" t="n">
-        <v>1471.87</v>
+        <v>1471.97</v>
       </c>
       <c r="E452" s="11" t="n">
-        <v>1458.75</v>
+        <v>1458.79</v>
       </c>
       <c r="F452" s="11" t="n">
-        <v>1480.88</v>
+        <v>1480.89</v>
       </c>
       <c r="G452" s="12" t="inlineStr">
         <is>
@@ -20609,16 +20609,16 @@
         </is>
       </c>
       <c r="C453" s="11" t="n">
-        <v>1008.7</v>
+        <v>1000.1</v>
       </c>
       <c r="D453" s="11" t="n">
-        <v>1112.95</v>
+        <v>1112.13</v>
       </c>
       <c r="E453" s="11" t="n">
-        <v>1147.94</v>
+        <v>1147.6</v>
       </c>
       <c r="F453" s="11" t="n">
-        <v>1165.39</v>
+        <v>1165.3</v>
       </c>
       <c r="G453" s="14" t="inlineStr">
         <is>
@@ -20653,16 +20653,16 @@
         </is>
       </c>
       <c r="C454" s="11" t="n">
-        <v>1793.6</v>
+        <v>1794.2</v>
       </c>
       <c r="D454" s="11" t="n">
-        <v>1723.53</v>
+        <v>1723.59</v>
       </c>
       <c r="E454" s="11" t="n">
-        <v>1700.09</v>
+        <v>1700.11</v>
       </c>
       <c r="F454" s="11" t="n">
-        <v>1729.74</v>
+        <v>1729.75</v>
       </c>
       <c r="G454" s="12" t="inlineStr">
         <is>
@@ -20697,16 +20697,16 @@
         </is>
       </c>
       <c r="C455" s="11" t="n">
-        <v>529</v>
+        <v>533.5</v>
       </c>
       <c r="D455" s="11" t="n">
-        <v>513.24</v>
+        <v>513.67</v>
       </c>
       <c r="E455" s="11" t="n">
-        <v>474.48</v>
+        <v>474.66</v>
       </c>
       <c r="F455" s="11" t="n">
-        <v>489.44</v>
+        <v>489.49</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20741,16 +20741,16 @@
         </is>
       </c>
       <c r="C456" s="11" t="n">
-        <v>582.25</v>
+        <v>582.95</v>
       </c>
       <c r="D456" s="11" t="n">
-        <v>590.79</v>
+        <v>590.85</v>
       </c>
       <c r="E456" s="11" t="n">
-        <v>585.3099999999999</v>
+        <v>585.34</v>
       </c>
       <c r="F456" s="11" t="n">
-        <v>542.46</v>
+        <v>542.47</v>
       </c>
       <c r="G456" s="14" t="inlineStr">
         <is>
@@ -20785,16 +20785,16 @@
         </is>
       </c>
       <c r="C457" s="11" t="n">
-        <v>150</v>
+        <v>150.29</v>
       </c>
       <c r="D457" s="11" t="n">
-        <v>156.24</v>
+        <v>156.26</v>
       </c>
       <c r="E457" s="11" t="n">
-        <v>155.69</v>
+        <v>155.7</v>
       </c>
       <c r="F457" s="11" t="n">
-        <v>158.96</v>
+        <v>158.97</v>
       </c>
       <c r="G457" s="14" t="inlineStr">
         <is>
@@ -20829,16 +20829,16 @@
         </is>
       </c>
       <c r="C458" s="11" t="n">
-        <v>849.2</v>
+        <v>851.15</v>
       </c>
       <c r="D458" s="11" t="n">
-        <v>888.47</v>
+        <v>888.66</v>
       </c>
       <c r="E458" s="11" t="n">
-        <v>929.26</v>
+        <v>929.34</v>
       </c>
       <c r="F458" s="11" t="n">
-        <v>992.88</v>
+        <v>992.9</v>
       </c>
       <c r="G458" s="14" t="inlineStr">
         <is>
@@ -20873,16 +20873,16 @@
         </is>
       </c>
       <c r="C459" s="11" t="n">
-        <v>4731.9</v>
+        <v>4741</v>
       </c>
       <c r="D459" s="11" t="n">
-        <v>4633.7</v>
+        <v>4634.57</v>
       </c>
       <c r="E459" s="11" t="n">
-        <v>4256.01</v>
+        <v>4256.36</v>
       </c>
       <c r="F459" s="11" t="n">
-        <v>3581.31</v>
+        <v>3581.4</v>
       </c>
       <c r="G459" s="12" t="inlineStr">
         <is>
@@ -20917,20 +20917,20 @@
         </is>
       </c>
       <c r="C460" s="11" t="n">
-        <v>3565</v>
+        <v>3577.2</v>
       </c>
       <c r="D460" s="11" t="n">
-        <v>3574.66</v>
+        <v>3575.82</v>
       </c>
       <c r="E460" s="11" t="n">
-        <v>3506.57</v>
+        <v>3507.05</v>
       </c>
       <c r="F460" s="11" t="n">
-        <v>3244.02</v>
-      </c>
-      <c r="G460" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3244.14</v>
+      </c>
+      <c r="G460" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H460" s="12" t="inlineStr">
@@ -20961,16 +20961,16 @@
         </is>
       </c>
       <c r="C461" s="11" t="n">
-        <v>840.05</v>
+        <v>842.85</v>
       </c>
       <c r="D461" s="11" t="n">
-        <v>816.22</v>
+        <v>816.49</v>
       </c>
       <c r="E461" s="11" t="n">
-        <v>782.0599999999999</v>
+        <v>782.17</v>
       </c>
       <c r="F461" s="11" t="n">
-        <v>782.67</v>
+        <v>782.7</v>
       </c>
       <c r="G461" s="12" t="inlineStr">
         <is>
@@ -21005,16 +21005,16 @@
         </is>
       </c>
       <c r="C462" s="11" t="n">
-        <v>4121.6</v>
+        <v>4124.8</v>
       </c>
       <c r="D462" s="11" t="n">
-        <v>4163.92</v>
+        <v>4164.23</v>
       </c>
       <c r="E462" s="11" t="n">
-        <v>4199.47</v>
+        <v>4199.6</v>
       </c>
       <c r="F462" s="11" t="n">
-        <v>3992.87</v>
+        <v>3992.9</v>
       </c>
       <c r="G462" s="14" t="inlineStr">
         <is>
@@ -21049,16 +21049,16 @@
         </is>
       </c>
       <c r="C463" s="11" t="n">
-        <v>4457.2</v>
+        <v>4479.3</v>
       </c>
       <c r="D463" s="11" t="n">
-        <v>4397.24</v>
+        <v>4399.35</v>
       </c>
       <c r="E463" s="11" t="n">
-        <v>4321.9</v>
+        <v>4322.77</v>
       </c>
       <c r="F463" s="11" t="n">
-        <v>3975.42</v>
+        <v>3975.64</v>
       </c>
       <c r="G463" s="12" t="inlineStr">
         <is>
@@ -21093,10 +21093,10 @@
         </is>
       </c>
       <c r="C464" s="11" t="n">
-        <v>1442</v>
+        <v>1442.1</v>
       </c>
       <c r="D464" s="11" t="n">
-        <v>1478.85</v>
+        <v>1478.86</v>
       </c>
       <c r="E464" s="11" t="n">
         <v>1504.71</v>
@@ -21137,16 +21137,16 @@
         </is>
       </c>
       <c r="C465" s="11" t="n">
-        <v>309.25</v>
+        <v>311.95</v>
       </c>
       <c r="D465" s="11" t="n">
-        <v>313.38</v>
+        <v>313.63</v>
       </c>
       <c r="E465" s="11" t="n">
-        <v>308.68</v>
+        <v>308.79</v>
       </c>
       <c r="F465" s="11" t="n">
-        <v>336.05</v>
+        <v>336.07</v>
       </c>
       <c r="G465" s="14" t="inlineStr">
         <is>
@@ -21181,16 +21181,16 @@
         </is>
       </c>
       <c r="C466" s="11" t="n">
-        <v>1209</v>
+        <v>1202.4</v>
       </c>
       <c r="D466" s="11" t="n">
-        <v>1211.94</v>
+        <v>1211.31</v>
       </c>
       <c r="E466" s="11" t="n">
-        <v>1210.52</v>
+        <v>1210.26</v>
       </c>
       <c r="F466" s="11" t="n">
-        <v>1202.04</v>
+        <v>1201.97</v>
       </c>
       <c r="G466" s="14" t="inlineStr">
         <is>
@@ -21225,16 +21225,16 @@
         </is>
       </c>
       <c r="C467" s="11" t="n">
-        <v>2754</v>
+        <v>2757</v>
       </c>
       <c r="D467" s="11" t="n">
-        <v>2784.55</v>
+        <v>2784.83</v>
       </c>
       <c r="E467" s="11" t="n">
-        <v>2759.32</v>
+        <v>2759.43</v>
       </c>
       <c r="F467" s="11" t="n">
-        <v>3413.8</v>
+        <v>3413.83</v>
       </c>
       <c r="G467" s="14" t="inlineStr">
         <is>
@@ -21313,16 +21313,16 @@
         </is>
       </c>
       <c r="C469" s="11" t="n">
-        <v>666.45</v>
+        <v>667.2</v>
       </c>
       <c r="D469" s="11" t="n">
-        <v>663.1</v>
+        <v>663.17</v>
       </c>
       <c r="E469" s="11" t="n">
-        <v>606.95</v>
+        <v>606.98</v>
       </c>
       <c r="F469" s="11" t="n">
-        <v>544.99</v>
+        <v>545</v>
       </c>
       <c r="G469" s="12" t="inlineStr">
         <is>
@@ -21357,16 +21357,16 @@
         </is>
       </c>
       <c r="C470" s="11" t="n">
-        <v>3143.4</v>
+        <v>3147.8</v>
       </c>
       <c r="D470" s="11" t="n">
-        <v>3051.71</v>
+        <v>3052.13</v>
       </c>
       <c r="E470" s="11" t="n">
-        <v>2931.3</v>
+        <v>2931.47</v>
       </c>
       <c r="F470" s="11" t="n">
-        <v>2804.58</v>
+        <v>2804.62</v>
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
@@ -21401,13 +21401,13 @@
         </is>
       </c>
       <c r="C471" s="11" t="n">
-        <v>25.6</v>
+        <v>25.64</v>
       </c>
       <c r="D471" s="11" t="n">
         <v>25.3</v>
       </c>
       <c r="E471" s="11" t="n">
-        <v>25.63</v>
+        <v>25.64</v>
       </c>
       <c r="F471" s="11" t="n">
         <v>27.71</v>
@@ -21417,9 +21417,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H471" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H471" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I471" s="14" t="inlineStr">
@@ -21445,16 +21445,16 @@
         </is>
       </c>
       <c r="C472" s="11" t="n">
-        <v>1062.7</v>
+        <v>1063.7</v>
       </c>
       <c r="D472" s="11" t="n">
-        <v>1091.6</v>
+        <v>1091.69</v>
       </c>
       <c r="E472" s="11" t="n">
-        <v>1104.11</v>
+        <v>1104.15</v>
       </c>
       <c r="F472" s="11" t="n">
-        <v>1130.41</v>
+        <v>1130.42</v>
       </c>
       <c r="G472" s="14" t="inlineStr">
         <is>
@@ -21489,16 +21489,16 @@
         </is>
       </c>
       <c r="C473" s="11" t="n">
-        <v>622.55</v>
+        <v>624</v>
       </c>
       <c r="D473" s="11" t="n">
-        <v>639.45</v>
+        <v>639.58</v>
       </c>
       <c r="E473" s="11" t="n">
-        <v>644.64</v>
+        <v>644.6900000000001</v>
       </c>
       <c r="F473" s="11" t="n">
-        <v>672.36</v>
+        <v>672.37</v>
       </c>
       <c r="G473" s="14" t="inlineStr">
         <is>
@@ -21533,13 +21533,13 @@
         </is>
       </c>
       <c r="C474" s="11" t="n">
-        <v>915.4</v>
+        <v>916</v>
       </c>
       <c r="D474" s="11" t="n">
-        <v>940.47</v>
+        <v>940.53</v>
       </c>
       <c r="E474" s="11" t="n">
-        <v>961.5</v>
+        <v>961.52</v>
       </c>
       <c r="F474" s="11" t="n">
         <v>1051.06</v>
@@ -21577,16 +21577,16 @@
         </is>
       </c>
       <c r="C475" s="11" t="n">
-        <v>10826</v>
+        <v>10831</v>
       </c>
       <c r="D475" s="11" t="n">
-        <v>11302.01</v>
+        <v>11302.49</v>
       </c>
       <c r="E475" s="11" t="n">
-        <v>11522.42</v>
+        <v>11522.61</v>
       </c>
       <c r="F475" s="11" t="n">
-        <v>11747.8</v>
+        <v>11747.85</v>
       </c>
       <c r="G475" s="14" t="inlineStr">
         <is>
@@ -21621,13 +21621,13 @@
         </is>
       </c>
       <c r="C476" s="11" t="n">
-        <v>167.71</v>
+        <v>168</v>
       </c>
       <c r="D476" s="11" t="n">
-        <v>166.15</v>
+        <v>166.18</v>
       </c>
       <c r="E476" s="11" t="n">
-        <v>169.46</v>
+        <v>169.48</v>
       </c>
       <c r="F476" s="11" t="n">
         <v>161.62</v>
@@ -21665,10 +21665,10 @@
         </is>
       </c>
       <c r="C477" s="11" t="n">
-        <v>1332.5</v>
+        <v>1332.4</v>
       </c>
       <c r="D477" s="11" t="n">
-        <v>1348.78</v>
+        <v>1348.77</v>
       </c>
       <c r="E477" s="11" t="n">
         <v>1412.31</v>
@@ -21709,13 +21709,13 @@
         </is>
       </c>
       <c r="C478" s="11" t="n">
-        <v>1250.3</v>
+        <v>1250.4</v>
       </c>
       <c r="D478" s="11" t="n">
-        <v>1272.6</v>
+        <v>1272.61</v>
       </c>
       <c r="E478" s="11" t="n">
-        <v>1293.39</v>
+        <v>1293.4</v>
       </c>
       <c r="F478" s="11" t="n">
         <v>1336.89</v>
@@ -21753,10 +21753,10 @@
         </is>
       </c>
       <c r="C479" s="11" t="n">
-        <v>121.61</v>
+        <v>121.63</v>
       </c>
       <c r="D479" s="11" t="n">
-        <v>124.32</v>
+        <v>124.33</v>
       </c>
       <c r="E479" s="11" t="n">
         <v>126.56</v>
@@ -21797,16 +21797,16 @@
         </is>
       </c>
       <c r="C480" s="11" t="n">
-        <v>497.75</v>
+        <v>498.45</v>
       </c>
       <c r="D480" s="11" t="n">
-        <v>488.94</v>
+        <v>489.01</v>
       </c>
       <c r="E480" s="11" t="n">
-        <v>467.31</v>
+        <v>467.34</v>
       </c>
       <c r="F480" s="11" t="n">
-        <v>427.69</v>
+        <v>427.7</v>
       </c>
       <c r="G480" s="12" t="inlineStr">
         <is>
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="C481" s="11" t="n">
-        <v>622.5</v>
+        <v>623.35</v>
       </c>
       <c r="D481" s="11" t="n">
-        <v>609.55</v>
+        <v>609.64</v>
       </c>
       <c r="E481" s="11" t="n">
-        <v>587.78</v>
+        <v>587.8099999999999</v>
       </c>
       <c r="F481" s="11" t="n">
         <v>510.63</v>
@@ -21885,13 +21885,13 @@
         </is>
       </c>
       <c r="C482" s="11" t="n">
-        <v>525.6</v>
+        <v>525.85</v>
       </c>
       <c r="D482" s="11" t="n">
-        <v>521.13</v>
+        <v>521.15</v>
       </c>
       <c r="E482" s="11" t="n">
-        <v>498.94</v>
+        <v>498.95</v>
       </c>
       <c r="F482" s="11" t="n">
         <v>475.46</v>
@@ -21929,13 +21929,13 @@
         </is>
       </c>
       <c r="C483" s="11" t="n">
-        <v>305.5</v>
+        <v>306.4</v>
       </c>
       <c r="D483" s="11" t="n">
-        <v>348.28</v>
+        <v>348.37</v>
       </c>
       <c r="E483" s="11" t="n">
-        <v>443.47</v>
+        <v>443.51</v>
       </c>
       <c r="F483" s="11" t="n">
         <v>520.59</v>
@@ -21973,16 +21973,16 @@
         </is>
       </c>
       <c r="C484" s="11" t="n">
-        <v>1303.7</v>
+        <v>1298.2</v>
       </c>
       <c r="D484" s="11" t="n">
-        <v>1275.78</v>
+        <v>1275.26</v>
       </c>
       <c r="E484" s="11" t="n">
-        <v>1186.49</v>
+        <v>1186.27</v>
       </c>
       <c r="F484" s="11" t="n">
-        <v>1061.13</v>
+        <v>1061.07</v>
       </c>
       <c r="G484" s="12" t="inlineStr">
         <is>
@@ -22017,13 +22017,13 @@
         </is>
       </c>
       <c r="C485" s="11" t="n">
-        <v>117.21</v>
+        <v>117.44</v>
       </c>
       <c r="D485" s="11" t="n">
-        <v>119.84</v>
+        <v>119.86</v>
       </c>
       <c r="E485" s="11" t="n">
-        <v>119.67</v>
+        <v>119.68</v>
       </c>
       <c r="F485" s="11" t="n">
         <v>123.64</v>
@@ -22061,10 +22061,10 @@
         </is>
       </c>
       <c r="C486" s="11" t="n">
-        <v>14.42</v>
+        <v>14.37</v>
       </c>
       <c r="D486" s="11" t="n">
-        <v>13.72</v>
+        <v>13.71</v>
       </c>
       <c r="E486" s="11" t="n">
         <v>12.3</v>
@@ -22105,16 +22105,16 @@
         </is>
       </c>
       <c r="C487" s="11" t="n">
-        <v>1302.1</v>
+        <v>1303.6</v>
       </c>
       <c r="D487" s="11" t="n">
-        <v>1285.24</v>
+        <v>1285.38</v>
       </c>
       <c r="E487" s="11" t="n">
-        <v>1325.19</v>
+        <v>1325.25</v>
       </c>
       <c r="F487" s="11" t="n">
-        <v>1366.34</v>
+        <v>1366.36</v>
       </c>
       <c r="G487" s="12" t="inlineStr">
         <is>
@@ -22149,16 +22149,16 @@
         </is>
       </c>
       <c r="C488" s="11" t="n">
-        <v>3019.3</v>
+        <v>3024</v>
       </c>
       <c r="D488" s="11" t="n">
-        <v>3083.14</v>
+        <v>3083.59</v>
       </c>
       <c r="E488" s="11" t="n">
-        <v>3101.95</v>
+        <v>3102.14</v>
       </c>
       <c r="F488" s="11" t="n">
-        <v>3020.24</v>
+        <v>3020.29</v>
       </c>
       <c r="G488" s="14" t="inlineStr">
         <is>
@@ -22170,9 +22170,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I488" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I488" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J488" s="13" t="inlineStr">
@@ -22193,16 +22193,16 @@
         </is>
       </c>
       <c r="C489" s="11" t="n">
-        <v>1395.9</v>
+        <v>1398.2</v>
       </c>
       <c r="D489" s="11" t="n">
-        <v>1342.46</v>
+        <v>1342.68</v>
       </c>
       <c r="E489" s="11" t="n">
-        <v>1218.96</v>
+        <v>1219.05</v>
       </c>
       <c r="F489" s="11" t="n">
-        <v>978.01</v>
+        <v>978.03</v>
       </c>
       <c r="G489" s="12" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         </is>
       </c>
       <c r="C490" s="11" t="n">
-        <v>144.5</v>
+        <v>144.51</v>
       </c>
       <c r="D490" s="11" t="n">
         <v>140.42</v>
@@ -22281,16 +22281,16 @@
         </is>
       </c>
       <c r="C491" s="11" t="n">
-        <v>773.9</v>
+        <v>771.95</v>
       </c>
       <c r="D491" s="11" t="n">
-        <v>836.55</v>
+        <v>836.37</v>
       </c>
       <c r="E491" s="11" t="n">
-        <v>864.55</v>
+        <v>864.47</v>
       </c>
       <c r="F491" s="11" t="n">
-        <v>965.33</v>
+        <v>965.3099999999999</v>
       </c>
       <c r="G491" s="14" t="inlineStr">
         <is>
@@ -22325,16 +22325,16 @@
         </is>
       </c>
       <c r="C492" s="11" t="n">
-        <v>181.27</v>
+        <v>181.37</v>
       </c>
       <c r="D492" s="11" t="n">
-        <v>197.78</v>
+        <v>197.79</v>
       </c>
       <c r="E492" s="11" t="n">
         <v>200.61</v>
       </c>
       <c r="F492" s="11" t="n">
-        <v>220.97</v>
+        <v>220.98</v>
       </c>
       <c r="G492" s="14" t="inlineStr">
         <is>
@@ -22369,16 +22369,16 @@
         </is>
       </c>
       <c r="C493" s="11" t="n">
-        <v>1885</v>
+        <v>1887.5</v>
       </c>
       <c r="D493" s="11" t="n">
-        <v>1811.62</v>
+        <v>1811.85</v>
       </c>
       <c r="E493" s="11" t="n">
-        <v>1630.07</v>
+        <v>1630.17</v>
       </c>
       <c r="F493" s="11" t="n">
-        <v>1458.94</v>
+        <v>1458.97</v>
       </c>
       <c r="G493" s="12" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         </is>
       </c>
       <c r="C494" s="11" t="n">
-        <v>23.3</v>
+        <v>23.32</v>
       </c>
       <c r="D494" s="11" t="n">
         <v>22.51</v>
@@ -22422,7 +22422,7 @@
         <v>21.58</v>
       </c>
       <c r="F494" s="11" t="n">
-        <v>20.81</v>
+        <v>20.82</v>
       </c>
       <c r="G494" s="12" t="inlineStr">
         <is>
@@ -22457,16 +22457,16 @@
         </is>
       </c>
       <c r="C495" s="11" t="n">
-        <v>14279</v>
+        <v>14270</v>
       </c>
       <c r="D495" s="11" t="n">
-        <v>14522.84</v>
+        <v>14521.98</v>
       </c>
       <c r="E495" s="11" t="n">
-        <v>14523.62</v>
+        <v>14523.27</v>
       </c>
       <c r="F495" s="11" t="n">
-        <v>14064.36</v>
+        <v>14064.27</v>
       </c>
       <c r="G495" s="14" t="inlineStr">
         <is>
@@ -22501,16 +22501,16 @@
         </is>
       </c>
       <c r="C496" s="11" t="n">
-        <v>107.6</v>
+        <v>108.2</v>
       </c>
       <c r="D496" s="11" t="n">
-        <v>95.92</v>
+        <v>95.98</v>
       </c>
       <c r="E496" s="11" t="n">
-        <v>90.56</v>
+        <v>90.59</v>
       </c>
       <c r="F496" s="11" t="n">
-        <v>93.59</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G496" s="12" t="inlineStr">
         <is>
@@ -22545,16 +22545,16 @@
         </is>
       </c>
       <c r="C497" s="11" t="n">
-        <v>1790.4</v>
+        <v>1797.2</v>
       </c>
       <c r="D497" s="11" t="n">
-        <v>1681.48</v>
+        <v>1682.13</v>
       </c>
       <c r="E497" s="11" t="n">
-        <v>1604.27</v>
+        <v>1604.53</v>
       </c>
       <c r="F497" s="11" t="n">
-        <v>1484.06</v>
+        <v>1484.13</v>
       </c>
       <c r="G497" s="12" t="inlineStr">
         <is>
@@ -22589,13 +22589,13 @@
         </is>
       </c>
       <c r="C498" s="11" t="n">
-        <v>467.65</v>
+        <v>468</v>
       </c>
       <c r="D498" s="11" t="n">
-        <v>494.94</v>
+        <v>494.97</v>
       </c>
       <c r="E498" s="11" t="n">
-        <v>520.58</v>
+        <v>520.59</v>
       </c>
       <c r="F498" s="11" t="n">
         <v>623.15</v>
@@ -22633,16 +22633,16 @@
         </is>
       </c>
       <c r="C499" s="11" t="n">
-        <v>1108.5</v>
+        <v>1107.9</v>
       </c>
       <c r="D499" s="11" t="n">
-        <v>1052.82</v>
+        <v>1052.76</v>
       </c>
       <c r="E499" s="11" t="n">
-        <v>996.21</v>
+        <v>996.1900000000001</v>
       </c>
       <c r="F499" s="11" t="n">
-        <v>945.78</v>
+        <v>945.77</v>
       </c>
       <c r="G499" s="12" t="inlineStr">
         <is>
@@ -22677,13 +22677,13 @@
         </is>
       </c>
       <c r="C500" s="11" t="n">
-        <v>514.85</v>
+        <v>515.5</v>
       </c>
       <c r="D500" s="11" t="n">
-        <v>501.56</v>
+        <v>501.62</v>
       </c>
       <c r="E500" s="11" t="n">
-        <v>488.2</v>
+        <v>488.23</v>
       </c>
       <c r="F500" s="11" t="n">
         <v>447.21</v>
@@ -22721,16 +22721,16 @@
         </is>
       </c>
       <c r="C501" s="11" t="n">
-        <v>1380.6</v>
+        <v>1387.8</v>
       </c>
       <c r="D501" s="11" t="n">
-        <v>1477.84</v>
+        <v>1478.52</v>
       </c>
       <c r="E501" s="11" t="n">
-        <v>1537.12</v>
+        <v>1537.4</v>
       </c>
       <c r="F501" s="11" t="n">
-        <v>1758.59</v>
+        <v>1758.66</v>
       </c>
       <c r="G501" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Jun-2026  10:20:07    |    Closing Price Date: 09-Jun-2026</t>
+          <t>Scan Run: 09-Jun-2026  10:45:55    |    Closing Price Date: 09-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Jun-2026  10:20:07</t>
+          <t>09-Jun-2026  10:45:55</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Jun-2026  10:45:55    |    Closing Price Date: 09-Jun-2026</t>
+          <t>Scan Run: 09-Jun-2026  13:46:46    |    Closing Price Date: 09-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Jun-2026  10:45:55</t>
+          <t>09-Jun-2026  13:46:46</t>
         </is>
       </c>
     </row>
@@ -21929,13 +21929,13 @@
         <v>306.25</v>
       </c>
       <c r="D483" s="10" t="n">
-        <v>348.35</v>
+        <v/>
       </c>
       <c r="E483" s="10" t="n">
-        <v>443.5</v>
+        <v/>
       </c>
       <c r="F483" s="10" t="n">
-        <v>520.59</v>
+        <v/>
       </c>
       <c r="G483" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 25-Jun-2026  13:17:26    |    Closing Price Date: 25-Jun-2026</t>
+          <t>Scan Run: 26-Jun-2026  13:12:22    |    Closing Price Date: 25-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>66.2</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>58.2</v>
+        <v>58</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>500</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>25-Jun-2026  13:17:26</t>
+          <t>26-Jun-2026  13:12:22</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 58.2% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 58.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 291 of 500 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 290 of 500 stocks</t>
         </is>
       </c>
     </row>
@@ -771,10 +771,10 @@
         <v>1761.35</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1704.54</v>
+        <v>1704.55</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1524.23</v>
+        <v>1524.54</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>1091.11</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1074.24</v>
+        <v>1077.19</v>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         <v>32707.57</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>32561.9</v>
+        <v>32561.91</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>32424.81</v>
+        <v>32470.18</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>6866.59</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>6124.05</v>
+        <v>6136.24</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>1373.19</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1559.34</v>
+        <v>1560.06</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>314.39</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>272.4</v>
+        <v>272.76</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>4296.65</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>3856.7</v>
+        <v>3857.36</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>1878.48</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1872.58</v>
+        <v>1876.06</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>997.87</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>922.5</v>
+        <v>923.96</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>191.06</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>212.56</v>
+        <v>212.98</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>482.11</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>478.46</v>
+        <v>479.6</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>465.02</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>431.77</v>
+        <v>432.4</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>1370.34</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1448.54</v>
+        <v>1448.89</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>26403.77</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>27687.36</v>
+        <v>27694.66</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>914.76</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>948.03</v>
+        <v>950.52</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>2912.36</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>2223.29</v>
+        <v>2226.75</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>1404.56</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>1141.71</v>
+        <v>1142.52</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>2738.25</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>2428.97</v>
+        <v>2431.8</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>1372.14</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1134.77</v>
+        <v>1135.41</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>1734</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1546.13</v>
+        <v>1547.67</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>217.11</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>173.85</v>
+        <v>173.94</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>679.35</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>618.33</v>
+        <v>619.16</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>357.83</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>327.44</v>
+        <v>327.82</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>62.27</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>79.48999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>1298.95</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1471.97</v>
+        <v>1478.91</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>1063.19</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>919.36</v>
+        <v>921.02</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>824.14</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>746.51</v>
+        <v>747.75</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>320.37</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>352.28</v>
+        <v>352.5</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>1467.99</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1566.32</v>
+        <v>1568.72</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>3031.59</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>2836.72</v>
+        <v>2838.68</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>5400.04</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5393.27</v>
+        <v>5394.71</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>565.37</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>519.25</v>
+        <v>519.49</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>841.13</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>874.7</v>
+        <v>878.53</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>7657.55</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>7335.36</v>
+        <v>7351.31</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>434.66</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>483.33</v>
+        <v>484.03</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>1774.17</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1571.3</v>
+        <v>1571.31</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>519.96</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>528.73</v>
+        <v>530.14</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>322.76</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>278.14</v>
+        <v>279.12</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>1305.07</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1233.51</v>
+        <v>1234.08</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>13608.25</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>10646.55</v>
+        <v>10667.03</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>8163.36</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>7638.26</v>
+        <v>7649.84</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>411.28</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>441.32</v>
+        <v>442.28</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>259.17</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>267.06</v>
+        <v>267.54</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>869.37</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>869.8200000000001</v>
+        <v>871.1799999999999</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>157.17</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>156.58</v>
+        <v>156.73</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>2589.8</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2500.62</v>
+        <v>2503.19</v>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>744.54</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>664.8</v>
+        <v>665.04</v>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>1544.81</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1509.5</v>
+        <v>1510.48</v>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>6662.26</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>6449.87</v>
+        <v>6443.86</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>1438.59</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1295.43</v>
+        <v>1297.67</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>499.69</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>502.54</v>
+        <v>503.52</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>4210.64</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4125.75</v>
+        <v>4126.61</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>1310.77</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1262.08</v>
+        <v>1262.85</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>1761.85</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1771.7</v>
+        <v>1776.48</v>
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>267.2</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>292.09</v>
+        <v>292.63</v>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>3835.82</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3130.01</v>
+        <v>3136.13</v>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
@@ -3455,10 +3455,10 @@
         <v>10077.81</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>10002.38</v>
+        <v>10002.39</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>9359.09</v>
+        <v>9368.799999999999</v>
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>927.58</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>937.67</v>
+        <v>938.3099999999999</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>1767.28</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1875.69</v>
+        <v>1874.44</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>10364.42</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>10948.45</v>
+        <v>10961.36</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>85.69</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>93.52</v>
+        <v>93.8</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>2198.86</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2303.45</v>
+        <v>2307.35</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>527.55</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>500.53</v>
+        <v>503.21</v>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>197.46</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>175.08</v>
+        <v>175.21</v>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>268.84</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>264</v>
+        <v>264.33</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>142.61</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>137.38</v>
+        <v>137.72</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>80.53</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>67.81999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>706.96</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>852.35</v>
+        <v>855.04</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>4409.84</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>4632.94</v>
+        <v>4637.67</v>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>503.12</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>501.15</v>
+        <v>501.1</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>1302.49</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1369.9</v>
+        <v>1373.78</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>421.01</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>411.54</v>
+        <v>411.96</v>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>1938.37</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1657.18</v>
+        <v>1659.75</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>376.65</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>307.6</v>
+        <v>308.04</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>304.82</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>315.99</v>
+        <v>316.15</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>1854.81</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1895.97</v>
+        <v>1895.88</v>
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>1510.75</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1595.28</v>
+        <v>1593.93</v>
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>657.73</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>677.47</v>
+        <v>678.33</v>
       </c>
       <c r="G85" s="14" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>406.07</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>383.61</v>
+        <v>383.98</v>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>334.88</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>369.15</v>
+        <v>369.42</v>
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>4993.59</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>5389.21</v>
+        <v>5395.44</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>468.02</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>520.47</v>
+        <v>521.58</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>1671.89</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1767.86</v>
+        <v>1776.23</v>
       </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>1534.55</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1652.35</v>
+        <v>1656.18</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>37491.51</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>35865.1</v>
+        <v>35916.83</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>227.23</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>268.82</v>
+        <v>269.11</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>527.35</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>594.39</v>
+        <v>594.77</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>5359.24</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>5591.02</v>
+        <v>5592.38</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>908.4299999999999</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1216.03</v>
+        <v>1216.91</v>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>1110.5</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1005.25</v>
+        <v>1005.22</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>173.51</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>166.2</v>
+        <v>166.51</v>
       </c>
       <c r="G99" s="14" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>873.77</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>758.75</v>
+        <v>761.02</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>458.46</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>438.78</v>
+        <v>439.38</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>4074.16</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>4340.51</v>
+        <v>4339.97</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>858.34</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>841.6</v>
+        <v>843.0599999999999</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>130.89</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>128.78</v>
+        <v>128.9</v>
       </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>2100.33</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1930.66</v>
+        <v>1934.23</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>198.51</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>184.91</v>
+        <v>185.1</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>1038.4</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>938.33</v>
+        <v>938.34</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>2110.91</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>2122.22</v>
+        <v>2126.89</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>183.59</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>187.1</v>
+        <v>186.39</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>3376.44</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>3485.72</v>
+        <v>3489.67</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>995.88</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>797.77</v>
+        <v>797.74</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>32.89</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>35.09</v>
+        <v>35.2</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>1266.66</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1335.94</v>
+        <v>1340.83</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>781.72</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>821.36</v>
+        <v>822.74</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>462.92</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>471.81</v>
+        <v>472.15</v>
       </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>1086.65</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>940.13</v>
+        <v>940.61</v>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>688.29</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>707.4299999999999</v>
+        <v>708.36</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>1579.15</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1675.79</v>
+        <v>1679.05</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>1596.65</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1595.94</v>
+        <v>1598.4</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>1362.57</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1384.69</v>
+        <v>1384.97</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>194.57</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>187.52</v>
+        <v>187.6</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>780.33</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>875.5700000000001</v>
+        <v>876.34</v>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>454.09</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>425.21</v>
+        <v>425.61</v>
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>1498.84</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1555.38</v>
+        <v>1562.24</v>
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>1387.07</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1465.21</v>
+        <v>1466.78</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>421.5</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>534.23</v>
+        <v>535.27</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>2042.57</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>2107.09</v>
+        <v>2108.35</v>
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>768.48</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>744.98</v>
+        <v>748.28</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>1215.77</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1295.66</v>
+        <v>1298.13</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>477.87</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>499.56</v>
+        <v>500.93</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>1942.24</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>2079.57</v>
+        <v>2083.39</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>8684.24</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>7565.04</v>
+        <v>7562.78</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>1328.86</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1279.87</v>
+        <v>1280.91</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>270.65</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>275.57</v>
+        <v>275.89</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>5464.9</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>4692.23</v>
+        <v>4698.15</v>
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>894.0700000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1002.43</v>
+        <v>1004.54</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>1084.43</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1131.58</v>
+        <v>1133.06</v>
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>595.9299999999999</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>637.26</v>
+        <v>639.05</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>2261.56</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2383.14</v>
+        <v>2387.44</v>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>439.64</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>470.57</v>
+        <v>470.6</v>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>1773.55</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1928.45</v>
+        <v>1931.16</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>4140.18</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>3327.08</v>
+        <v>3330.44</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>1393.22</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1280.73</v>
+        <v>1280.07</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>1665.33</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1680.36</v>
+        <v>1682.45</v>
       </c>
       <c r="G145" s="14" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>453.58</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>428.97</v>
+        <v>429.76</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>114.44</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>128.46</v>
+        <v>128.64</v>
       </c>
       <c r="G147" s="14" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>6606.8</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>6387.53</v>
+        <v>6393.88</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>11547.5</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>12332.06</v>
+        <v>12365.36</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>1568.06</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1485.28</v>
+        <v>1485.63</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>1288.73</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>1264.99</v>
+        <v>1265.9</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>769.53</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>871.04</v>
+        <v>872.78</v>
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>313.66</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>335.49</v>
+        <v>335.43</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>7290.89</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>6974.08</v>
+        <v>6976.22</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>508.48</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>487.54</v>
+        <v>489.26</v>
       </c>
       <c r="G155" s="14" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>572.9</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>524.24</v>
+        <v>524.38</v>
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>414.17</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>468.08</v>
+        <v>468.54</v>
       </c>
       <c r="G157" s="14" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>2567.07</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>2518.88</v>
+        <v>2520.81</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>236.65</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>213.76</v>
+        <v>213.99</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>1386.8</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1432.23</v>
+        <v>1435.61</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>2959.22</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>3234.73</v>
+        <v>3244.36</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>251.34</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>262.27</v>
+        <v>263.12</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>369.59</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>357.9</v>
+        <v>358.58</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>300.9</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>268.02</v>
+        <v>268.4</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>886.1799999999999</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>856.21</v>
+        <v>858.1900000000001</v>
       </c>
       <c r="G167" s="14" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>1040.7</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>912.89</v>
+        <v>916.4299999999999</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>247.16</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>273.96</v>
+        <v>274.63</v>
       </c>
       <c r="G169" s="14" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>460.35</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>500.89</v>
+        <v>501.86</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>19238.77</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>18795.17</v>
+        <v>18831.24</v>
       </c>
       <c r="G171" s="14" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>947.55</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>899.1799999999999</v>
+        <v>899.6799999999999</v>
       </c>
       <c r="G172" s="14" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>166.4</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>164.28</v>
+        <v>164.67</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>4724.73</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>3730.87</v>
+        <v>3729.98</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>100.96</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>96</v>
+        <v>96.11</v>
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>1081.92</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>1000.88</v>
+        <v>1003.92</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>700.58</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>630.88</v>
+        <v>631.37</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>2687.25</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>2533.43</v>
+        <v>2545.07</v>
       </c>
       <c r="G178" s="14" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>379.46</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>380.56</v>
+        <v>381.68</v>
       </c>
       <c r="G179" s="14" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>7844.09</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>8210.77</v>
+        <v>8207.799999999999</v>
       </c>
       <c r="G180" s="14" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>2109.07</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>1888.78</v>
+        <v>1889.89</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8691,10 +8691,10 @@
         <v>2268.77</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>2282.35</v>
+        <v>2282.36</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>2428.04</v>
+        <v>2434.01</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>2220.83</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>2076.93</v>
+        <v>2079.37</v>
       </c>
       <c r="G183" s="14" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>1209.23</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1187.33</v>
+        <v>1189.39</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>309.86</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>324.06</v>
+        <v>324.22</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>280.27</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>260.9</v>
+        <v>261.16</v>
       </c>
       <c r="G186" s="14" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>2244.33</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>2387.38</v>
+        <v>2389.35</v>
       </c>
       <c r="G187" s="14" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>1036.66</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>1097.95</v>
+        <v>1098.87</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>1059.97</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1043.79</v>
+        <v>1044.96</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>1751.49</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>1850.06</v>
+        <v>1855.67</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9058,9 +9058,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I190" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I190" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J190" s="13" t="inlineStr">
@@ -9090,7 +9090,7 @@
         <v>736.97</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>633.92</v>
+        <v>634.25</v>
       </c>
       <c r="G191" s="14" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>680.8099999999999</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>633.8</v>
+        <v>634.54</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>3018.92</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>2846.94</v>
+        <v>2849.46</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>1641.53</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>1646.63</v>
+        <v>1652.67</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>1465.13</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>1284.29</v>
+        <v>1285.84</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>3647.17</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>3544.33</v>
+        <v>3543.87</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>634.22</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>571.65</v>
+        <v>572.36</v>
       </c>
       <c r="G197" s="14" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>558.99</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>546.11</v>
+        <v>546.64</v>
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>786.39</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>758.66</v>
+        <v>761.91</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>1194.04</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>1360.93</v>
+        <v>1360.9</v>
       </c>
       <c r="G200" s="14" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>2599</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>2547.33</v>
+        <v>2552.05</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>770.22</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>844.71</v>
+        <v>845.41</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>596.36</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>660.5700000000001</v>
+        <v>662.05</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>159.23</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>107.08</v>
+        <v>107.26</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>1205.2</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>1323</v>
+        <v>1327.06</v>
       </c>
       <c r="G206" s="14" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>5032</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>5101.62</v>
+        <v>5103.44</v>
       </c>
       <c r="G207" s="14" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>498.52</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>576.36</v>
+        <v>575.6799999999999</v>
       </c>
       <c r="G208" s="14" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>613.04</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>521.98</v>
+        <v>523.23</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>1033</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>926.1</v>
+        <v>926.85</v>
       </c>
       <c r="G210" s="14" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>4322.75</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>4295.76</v>
+        <v>4308.5</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>529.4299999999999</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>468.36</v>
+        <v>468.67</v>
       </c>
       <c r="G212" s="14" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>388.93</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>400.38</v>
+        <v>400.48</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10099,10 +10099,10 @@
         <v>2157.04</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>2174.07</v>
+        <v>2174.08</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>2253.34</v>
+        <v>2254.54</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>584.6799999999999</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>552.6799999999999</v>
+        <v>553.46</v>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>33409.84</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>25977.68</v>
+        <v>25940.7</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>1104.52</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>1118.78</v>
+        <v>1118.29</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>381.51</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>322.42</v>
+        <v>322.98</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10319,10 +10319,10 @@
         <v>36430.67</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>34205.52</v>
+        <v>34205.53</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>33452.16</v>
+        <v>33494.85</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>205.8</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>204.64</v>
+        <v>205.18</v>
       </c>
       <c r="G220" s="14" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>1921.42</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>2028.34</v>
+        <v>2029.06</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>1302.27</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>1329.82</v>
+        <v>1331.69</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>1797.51</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>1839.23</v>
+        <v>1840.55</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>514.33</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>569.45</v>
+        <v>570.0599999999999</v>
       </c>
       <c r="G225" s="14" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>78.64</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>85.95</v>
+        <v>86.06</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>72.95999999999999</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>72.38</v>
+        <v>72.48</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>71.2</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>60.44</v>
+        <v>60.6</v>
       </c>
       <c r="G228" s="14" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>493.61</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>486.41</v>
+        <v>487.4</v>
       </c>
       <c r="G229" s="14" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>21.22</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>21.35</v>
+        <v>21.41</v>
       </c>
       <c r="G230" s="14" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>140.01</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>149.68</v>
+        <v>150.41</v>
       </c>
       <c r="G231" s="14" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>160.38</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>176.41</v>
+        <v>177.12</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>292.51</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>325.09</v>
+        <v>324.85</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>296.49</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>292.71</v>
+        <v>293.33</v>
       </c>
       <c r="G234" s="14" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>512.36</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>512.64</v>
+        <v>513.16</v>
       </c>
       <c r="G235" s="14" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>390.57</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>390.31</v>
+        <v>390.65</v>
       </c>
       <c r="G236" s="14" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>1996.32</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>2099.48</v>
+        <v>2104.78</v>
       </c>
       <c r="G237" s="14" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>844.23</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>805.76</v>
+        <v>806.8099999999999</v>
       </c>
       <c r="G238" s="14" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>124.23</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>132.06</v>
+        <v>132.28</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>669.8200000000001</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>683.9299999999999</v>
+        <v>686.36</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>143.12</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>146.76</v>
+        <v>146.91</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>34.11</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>35.61</v>
+        <v>35.73</v>
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>531.86</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>598.33</v>
+        <v>599.47</v>
       </c>
       <c r="G243" s="14" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>98.87</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>108.13</v>
+        <v>108.52</v>
       </c>
       <c r="G244" s="14" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>126.78</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>132.96</v>
+        <v>133.54</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>164.29</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>174.34</v>
+        <v>174.58</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>419.28</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>411.51</v>
+        <v>411.88</v>
       </c>
       <c r="G247" s="14" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>903.53</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>860.73</v>
+        <v>861.38</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>995.74</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>1132.33</v>
+        <v>1134.62</v>
       </c>
       <c r="G249" s="14" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>1156.56</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>1319.19</v>
+        <v>1319.05</v>
       </c>
       <c r="G250" s="14" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>91.95999999999999</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>111.03</v>
+        <v>111.37</v>
       </c>
       <c r="G251" s="14" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>733.66</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>806.59</v>
+        <v>808.23</v>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>4645.47</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>4851.73</v>
+        <v>4860.38</v>
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>354.41</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>341.65</v>
+        <v>342.66</v>
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>1628.9</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>1576.89</v>
+        <v>1578.95</v>
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>1568.39</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>1488.65</v>
+        <v>1490.45</v>
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>2146.81</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>1951.7</v>
+        <v>1954.96</v>
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>5319.19</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>5520.12</v>
+        <v>5532.24</v>
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>654.9</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>618.41</v>
+        <v>620.42</v>
       </c>
       <c r="G259" s="12" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>398.75</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>414.03</v>
+        <v>414.82</v>
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>126.69</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>131.82</v>
+        <v>132.12</v>
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>3082.57</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>3097.55</v>
+        <v>3101.28</v>
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>555.55</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>523.64</v>
+        <v>525.46</v>
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>283.54</v>
       </c>
       <c r="F265" s="11" t="n">
-        <v>277.13</v>
+        <v>278.09</v>
       </c>
       <c r="G265" s="12" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>1265.06</v>
       </c>
       <c r="F266" s="11" t="n">
-        <v>1195.05</v>
+        <v>1196.23</v>
       </c>
       <c r="G266" s="14" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>18.37</v>
       </c>
       <c r="F268" s="11" t="n">
-        <v>17.44</v>
+        <v>17.51</v>
       </c>
       <c r="G268" s="14" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>143.99</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>121.48</v>
+        <v>121.45</v>
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>235.39</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>210.8</v>
+        <v>211.4</v>
       </c>
       <c r="G270" s="12" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>719.1799999999999</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>737.08</v>
+        <v>737.67</v>
       </c>
       <c r="G271" s="14" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>1172.99</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>1121.51</v>
+        <v>1122.69</v>
       </c>
       <c r="G272" s="14" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>240.4</v>
       </c>
       <c r="F273" s="11" t="n">
-        <v>259.08</v>
+        <v>259.47</v>
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>442.35</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>511.91</v>
+        <v>512.71</v>
       </c>
       <c r="G274" s="14" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>657.14</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>665.83</v>
+        <v>667.02</v>
       </c>
       <c r="G275" s="14" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>963.1900000000001</v>
       </c>
       <c r="F276" s="11" t="n">
-        <v>977.0700000000001</v>
+        <v>979</v>
       </c>
       <c r="G276" s="14" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>278.88</v>
       </c>
       <c r="F277" s="11" t="n">
-        <v>294.81</v>
+        <v>295.88</v>
       </c>
       <c r="G277" s="14" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>706.11</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>820.4</v>
+        <v>822.91</v>
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>1016.33</v>
       </c>
       <c r="F279" s="11" t="n">
-        <v>970.37</v>
+        <v>971.67</v>
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>5168.67</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>4553.78</v>
+        <v>4560.6</v>
       </c>
       <c r="G280" s="14" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>756.33</v>
       </c>
       <c r="F281" s="11" t="n">
-        <v>921.3200000000001</v>
+        <v>921.87</v>
       </c>
       <c r="G281" s="14" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>1104.54</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>1060.84</v>
+        <v>1062.26</v>
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>1288.12</v>
       </c>
       <c r="F283" s="11" t="n">
-        <v>1199.05</v>
+        <v>1201.23</v>
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>376.57</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>423.99</v>
+        <v>425.08</v>
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>290.26</v>
       </c>
       <c r="F285" s="11" t="n">
-        <v>269.46</v>
+        <v>269.59</v>
       </c>
       <c r="G285" s="14" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>3436.24</v>
       </c>
       <c r="F286" s="11" t="n">
-        <v>4224.33</v>
+        <v>4234.71</v>
       </c>
       <c r="G286" s="12" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>530.84</v>
       </c>
       <c r="F287" s="11" t="n">
-        <v>625.99</v>
+        <v>627.99</v>
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>879.61</v>
       </c>
       <c r="F288" s="11" t="n">
-        <v>965.27</v>
+        <v>967.89</v>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>1855.81</v>
       </c>
       <c r="F289" s="11" t="n">
-        <v>1418.61</v>
+        <v>1421.46</v>
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>390.48</v>
       </c>
       <c r="F290" s="11" t="n">
-        <v>399.9</v>
+        <v>400.15</v>
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>750.0700000000001</v>
       </c>
       <c r="F291" s="11" t="n">
-        <v>698.8099999999999</v>
+        <v>698.59</v>
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>279.82</v>
       </c>
       <c r="F292" s="11" t="n">
-        <v>265.02</v>
+        <v>265.27</v>
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>3423.05</v>
       </c>
       <c r="F293" s="11" t="n">
-        <v>3720.44</v>
+        <v>3728.66</v>
       </c>
       <c r="G293" s="14" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>545.4299999999999</v>
       </c>
       <c r="F295" s="11" t="n">
-        <v>542.85</v>
+        <v>544.08</v>
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>393.73</v>
       </c>
       <c r="F296" s="11" t="n">
-        <v>399.29</v>
+        <v>400.57</v>
       </c>
       <c r="G296" s="14" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>4098.15</v>
       </c>
       <c r="F297" s="11" t="n">
-        <v>4686.71</v>
+        <v>4686.94</v>
       </c>
       <c r="G297" s="14" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>4011.92</v>
       </c>
       <c r="F298" s="11" t="n">
-        <v>3862.87</v>
+        <v>3869.01</v>
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>307.72</v>
       </c>
       <c r="F299" s="11" t="n">
-        <v>354.91</v>
+        <v>355.99</v>
       </c>
       <c r="G299" s="14" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>1313.3</v>
       </c>
       <c r="F300" s="11" t="n">
-        <v>1087.33</v>
+        <v>1088.39</v>
       </c>
       <c r="G300" s="12" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>114.12</v>
       </c>
       <c r="F302" s="11" t="n">
-        <v>127.84</v>
+        <v>128.16</v>
       </c>
       <c r="G302" s="12" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>401.98</v>
       </c>
       <c r="F304" s="11" t="n">
-        <v>406.2</v>
+        <v>406.85</v>
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>7120.97</v>
       </c>
       <c r="F305" s="11" t="n">
-        <v>6745.74</v>
+        <v>6757.18</v>
       </c>
       <c r="G305" s="14" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>1690.41</v>
       </c>
       <c r="F306" s="11" t="n">
-        <v>1463.95</v>
+        <v>1469.32</v>
       </c>
       <c r="G306" s="14" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>901.52</v>
       </c>
       <c r="F307" s="11" t="n">
-        <v>994.34</v>
+        <v>999.1900000000001</v>
       </c>
       <c r="G307" s="12" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>2294.62</v>
       </c>
       <c r="F308" s="11" t="n">
-        <v>2194.53</v>
+        <v>2197.47</v>
       </c>
       <c r="G308" s="12" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>67.01000000000001</v>
       </c>
       <c r="F309" s="11" t="n">
-        <v>63.68</v>
+        <v>63.85</v>
       </c>
       <c r="G309" s="14" t="inlineStr">
         <is>
@@ -14323,10 +14323,10 @@
         <v>128022.6</v>
       </c>
       <c r="E310" s="11" t="n">
-        <v>129060.68</v>
+        <v>129060.7</v>
       </c>
       <c r="F310" s="11" t="n">
-        <v>135796.45</v>
+        <v>135991.43</v>
       </c>
       <c r="G310" s="12" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>1118.49</v>
       </c>
       <c r="F311" s="11" t="n">
-        <v>1144.67</v>
+        <v>1145.56</v>
       </c>
       <c r="G311" s="12" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>305.16</v>
       </c>
       <c r="F312" s="11" t="n">
-        <v>314.33</v>
+        <v>314.83</v>
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>3114.28</v>
       </c>
       <c r="F313" s="11" t="n">
-        <v>3246.6</v>
+        <v>3250.17</v>
       </c>
       <c r="G313" s="12" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>306.76</v>
       </c>
       <c r="F314" s="11" t="n">
-        <v>286.86</v>
+        <v>287.05</v>
       </c>
       <c r="G314" s="12" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>160.24</v>
       </c>
       <c r="F315" s="11" t="n">
-        <v>158.39</v>
+        <v>158.32</v>
       </c>
       <c r="G315" s="14" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>2358.84</v>
       </c>
       <c r="F316" s="11" t="n">
-        <v>2288.52</v>
+        <v>2288.12</v>
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>807.38</v>
       </c>
       <c r="F317" s="11" t="n">
-        <v>763.12</v>
+        <v>763.61</v>
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>13372.83</v>
       </c>
       <c r="F318" s="11" t="n">
-        <v>13925.05</v>
+        <v>13927.68</v>
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>1636.94</v>
       </c>
       <c r="F319" s="11" t="n">
-        <v>1608.34</v>
+        <v>1611</v>
       </c>
       <c r="G319" s="14" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>1026.11</v>
       </c>
       <c r="F320" s="11" t="n">
-        <v>1051.12</v>
+        <v>1054.95</v>
       </c>
       <c r="G320" s="12" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>2478.72</v>
       </c>
       <c r="F321" s="11" t="n">
-        <v>2532.78</v>
+        <v>2545.68</v>
       </c>
       <c r="G321" s="14" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>600.25</v>
       </c>
       <c r="F323" s="11" t="n">
-        <v>562.22</v>
+        <v>562.86</v>
       </c>
       <c r="G323" s="12" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>39.04</v>
       </c>
       <c r="F324" s="11" t="n">
-        <v>41</v>
+        <v>41.05</v>
       </c>
       <c r="G324" s="12" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>863.42</v>
       </c>
       <c r="F325" s="11" t="n">
-        <v>823.83</v>
+        <v>825.91</v>
       </c>
       <c r="G325" s="12" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>2283.04</v>
       </c>
       <c r="F326" s="11" t="n">
-        <v>2436.56</v>
+        <v>2440.16</v>
       </c>
       <c r="G326" s="14" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>2889.22</v>
       </c>
       <c r="F327" s="11" t="n">
-        <v>2420.39</v>
+        <v>2422.5</v>
       </c>
       <c r="G327" s="14" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>3251.44</v>
       </c>
       <c r="F328" s="11" t="n">
-        <v>3260.73</v>
+        <v>3266.03</v>
       </c>
       <c r="G328" s="14" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>982.67</v>
       </c>
       <c r="F329" s="11" t="n">
-        <v>950.88</v>
+        <v>951.9400000000001</v>
       </c>
       <c r="G329" s="14" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>100.91</v>
       </c>
       <c r="F330" s="11" t="n">
-        <v>99.84</v>
+        <v>100.07</v>
       </c>
       <c r="G330" s="12" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>153.22</v>
       </c>
       <c r="F331" s="11" t="n">
-        <v>165.28</v>
+        <v>165.81</v>
       </c>
       <c r="G331" s="12" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>77.33</v>
       </c>
       <c r="F332" s="11" t="n">
-        <v>78.38</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="G332" s="12" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>319.66</v>
       </c>
       <c r="F333" s="11" t="n">
-        <v>281.37</v>
+        <v>282.19</v>
       </c>
       <c r="G333" s="14" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>88.12</v>
       </c>
       <c r="F334" s="11" t="n">
-        <v>80.83</v>
+        <v>80.98</v>
       </c>
       <c r="G334" s="14" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45.04</v>
       </c>
       <c r="F335" s="11" t="n">
-        <v>42.03</v>
+        <v>42.14</v>
       </c>
       <c r="G335" s="14" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>100.77</v>
       </c>
       <c r="F336" s="11" t="n">
-        <v>99.23999999999999</v>
+        <v>99.47</v>
       </c>
       <c r="G336" s="14" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>372.86</v>
       </c>
       <c r="F337" s="11" t="n">
-        <v>360.32</v>
+        <v>360.72</v>
       </c>
       <c r="G337" s="14" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>1868.99</v>
       </c>
       <c r="F338" s="11" t="n">
-        <v>1819.66</v>
+        <v>1822.52</v>
       </c>
       <c r="G338" s="12" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>389.37</v>
       </c>
       <c r="F339" s="11" t="n">
-        <v>335.7</v>
+        <v>335.76</v>
       </c>
       <c r="G339" s="14" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>614.2</v>
       </c>
       <c r="F340" s="11" t="n">
-        <v>589.75</v>
+        <v>591.24</v>
       </c>
       <c r="G340" s="14" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>7025.07</v>
       </c>
       <c r="F341" s="11" t="n">
-        <v>6175.3</v>
+        <v>6172.45</v>
       </c>
       <c r="G341" s="12" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>1388.66</v>
       </c>
       <c r="F342" s="11" t="n">
-        <v>1300.64</v>
+        <v>1300.84</v>
       </c>
       <c r="G342" s="12" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>4323.38</v>
       </c>
       <c r="F343" s="11" t="n">
-        <v>3514.29</v>
+        <v>3519.34</v>
       </c>
       <c r="G343" s="12" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>16445.49</v>
       </c>
       <c r="F344" s="11" t="n">
-        <v>14923.17</v>
+        <v>14953.33</v>
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>478.68</v>
       </c>
       <c r="F345" s="11" t="n">
-        <v>631.3200000000001</v>
+        <v>630.53</v>
       </c>
       <c r="G345" s="14" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>1063.67</v>
       </c>
       <c r="F346" s="11" t="n">
-        <v>923.99</v>
+        <v>924.9400000000001</v>
       </c>
       <c r="G346" s="12" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="F347" s="11" t="n">
-        <v>78.73</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="G347" s="12" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>1531.37</v>
       </c>
       <c r="F348" s="11" t="n">
-        <v>1390.7</v>
+        <v>1393.04</v>
       </c>
       <c r="G348" s="12" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>315.7</v>
       </c>
       <c r="F349" s="11" t="n">
-        <v>334.36</v>
+        <v>334.98</v>
       </c>
       <c r="G349" s="14" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>1653.37</v>
       </c>
       <c r="F350" s="11" t="n">
-        <v>1625.62</v>
+        <v>1629.66</v>
       </c>
       <c r="G350" s="12" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>265.71</v>
       </c>
       <c r="F351" s="11" t="n">
-        <v>257.83</v>
+        <v>257.94</v>
       </c>
       <c r="G351" s="14" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>457.67</v>
       </c>
       <c r="F352" s="11" t="n">
-        <v>446.82</v>
+        <v>447.14</v>
       </c>
       <c r="G352" s="14" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>39.51</v>
       </c>
       <c r="F353" s="11" t="n">
-        <v>38.7</v>
+        <v>38.99</v>
       </c>
       <c r="G353" s="14" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>1285.67</v>
       </c>
       <c r="F354" s="11" t="n">
-        <v>1222.02</v>
+        <v>1226.79</v>
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>1103.16</v>
       </c>
       <c r="F355" s="11" t="n">
-        <v>1115.64</v>
+        <v>1118.82</v>
       </c>
       <c r="G355" s="12" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>1673.3</v>
       </c>
       <c r="F356" s="11" t="n">
-        <v>1641.48</v>
+        <v>1647</v>
       </c>
       <c r="G356" s="14" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>9282.02</v>
       </c>
       <c r="F357" s="11" t="n">
-        <v>8242.32</v>
+        <v>8249.99</v>
       </c>
       <c r="G357" s="12" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>1623.06</v>
       </c>
       <c r="F358" s="11" t="n">
-        <v>1640.24</v>
+        <v>1648.94</v>
       </c>
       <c r="G358" s="14" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>293.21</v>
       </c>
       <c r="F359" s="11" t="n">
-        <v>308.87</v>
+        <v>309.54</v>
       </c>
       <c r="G359" s="12" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>514.28</v>
       </c>
       <c r="F360" s="11" t="n">
-        <v>567.92</v>
+        <v>570.4</v>
       </c>
       <c r="G360" s="12" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>2877.31</v>
       </c>
       <c r="F361" s="11" t="n">
-        <v>3150.42</v>
+        <v>3151.77</v>
       </c>
       <c r="G361" s="14" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>997.37</v>
       </c>
       <c r="F362" s="11" t="n">
-        <v>933.4</v>
+        <v>934.8</v>
       </c>
       <c r="G362" s="12" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>17374.13</v>
       </c>
       <c r="F363" s="11" t="n">
-        <v>16713.77</v>
+        <v>16723.46</v>
       </c>
       <c r="G363" s="14" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>982.64</v>
       </c>
       <c r="F364" s="11" t="n">
-        <v>1007.86</v>
+        <v>1011.14</v>
       </c>
       <c r="G364" s="12" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>37834.06</v>
       </c>
       <c r="F365" s="11" t="n">
-        <v>37537.17</v>
+        <v>37575.4</v>
       </c>
       <c r="G365" s="12" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>128.06</v>
       </c>
       <c r="F366" s="11" t="n">
-        <v>136.08</v>
+        <v>136.06</v>
       </c>
       <c r="G366" s="12" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>444.59</v>
       </c>
       <c r="F367" s="11" t="n">
-        <v>501.29</v>
+        <v>501.62</v>
       </c>
       <c r="G367" s="14" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>5017.66</v>
       </c>
       <c r="F368" s="11" t="n">
-        <v>5318.14</v>
+        <v>5322.96</v>
       </c>
       <c r="G368" s="14" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>275.33</v>
       </c>
       <c r="F369" s="11" t="n">
-        <v>275.74</v>
+        <v>276.29</v>
       </c>
       <c r="G369" s="12" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>4624.82</v>
       </c>
       <c r="F370" s="11" t="n">
-        <v>4784.35</v>
+        <v>4783.27</v>
       </c>
       <c r="G370" s="14" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>1781.98</v>
       </c>
       <c r="F371" s="11" t="n">
-        <v>1712.33</v>
+        <v>1712.12</v>
       </c>
       <c r="G371" s="12" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>1485.82</v>
       </c>
       <c r="F373" s="11" t="n">
-        <v>1456.06</v>
+        <v>1455.7</v>
       </c>
       <c r="G373" s="12" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>165.45</v>
       </c>
       <c r="F376" s="11" t="n">
-        <v>171.8</v>
+        <v>172.34</v>
       </c>
       <c r="G376" s="12" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>1497.66</v>
       </c>
       <c r="F377" s="11" t="n">
-        <v>1635.09</v>
+        <v>1636.71</v>
       </c>
       <c r="G377" s="12" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>9116.26</v>
       </c>
       <c r="F378" s="11" t="n">
-        <v>7927.48</v>
+        <v>7945.24</v>
       </c>
       <c r="G378" s="14" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>410.25</v>
       </c>
       <c r="F379" s="11" t="n">
-        <v>423.22</v>
+        <v>424.67</v>
       </c>
       <c r="G379" s="12" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>431.12</v>
       </c>
       <c r="F380" s="11" t="n">
-        <v>408.23</v>
+        <v>408.95</v>
       </c>
       <c r="G380" s="12" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>294.27</v>
       </c>
       <c r="F381" s="11" t="n">
-        <v>287.79</v>
+        <v>288.2</v>
       </c>
       <c r="G381" s="14" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>1017.54</v>
       </c>
       <c r="F382" s="11" t="n">
-        <v>950.04</v>
+        <v>951.87</v>
       </c>
       <c r="G382" s="14" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>1418.45</v>
       </c>
       <c r="F383" s="11" t="n">
-        <v>1444.86</v>
+        <v>1449.19</v>
       </c>
       <c r="G383" s="12" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>106.14</v>
       </c>
       <c r="F384" s="11" t="n">
-        <v>108.4</v>
+        <v>108.54</v>
       </c>
       <c r="G384" s="12" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>1999.04</v>
       </c>
       <c r="F385" s="11" t="n">
-        <v>1591.37</v>
+        <v>1593.84</v>
       </c>
       <c r="G385" s="12" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>346.76</v>
       </c>
       <c r="F386" s="11" t="n">
-        <v>308.47</v>
+        <v>309.02</v>
       </c>
       <c r="G386" s="12" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>349.43</v>
       </c>
       <c r="F387" s="11" t="n">
-        <v>354.04</v>
+        <v>354.71</v>
       </c>
       <c r="G387" s="12" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>387.93</v>
       </c>
       <c r="F388" s="11" t="n">
-        <v>416.35</v>
+        <v>417.6</v>
       </c>
       <c r="G388" s="14" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>209.12</v>
       </c>
       <c r="F389" s="11" t="n">
-        <v>219.41</v>
+        <v>220.42</v>
       </c>
       <c r="G389" s="12" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>3447.08</v>
       </c>
       <c r="F390" s="11" t="n">
-        <v>3091.15</v>
+        <v>3093.65</v>
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>259.57</v>
       </c>
       <c r="F391" s="11" t="n">
-        <v>297.8</v>
+        <v>298.87</v>
       </c>
       <c r="G391" s="14" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>316.42</v>
       </c>
       <c r="F392" s="11" t="n">
-        <v>325.38</v>
+        <v>326.26</v>
       </c>
       <c r="G392" s="14" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>1346.01</v>
       </c>
       <c r="F393" s="11" t="n">
-        <v>1310.51</v>
+        <v>1312.14</v>
       </c>
       <c r="G393" s="12" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>567.65</v>
       </c>
       <c r="F394" s="11" t="n">
-        <v>564.4400000000001</v>
+        <v>566.97</v>
       </c>
       <c r="G394" s="14" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>241.17</v>
       </c>
       <c r="F395" s="11" t="n">
-        <v>246.58</v>
+        <v>246.62</v>
       </c>
       <c r="G395" s="12" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>1335.21</v>
       </c>
       <c r="F396" s="11" t="n">
-        <v>1381.55</v>
+        <v>1381.9</v>
       </c>
       <c r="G396" s="12" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>26.87</v>
       </c>
       <c r="F397" s="11" t="n">
-        <v>31.87</v>
+        <v>32.07</v>
       </c>
       <c r="G397" s="14" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>92.42</v>
       </c>
       <c r="F398" s="11" t="n">
-        <v>96.34</v>
+        <v>96.42</v>
       </c>
       <c r="G398" s="14" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>631.26</v>
       </c>
       <c r="F399" s="11" t="n">
-        <v>734.01</v>
+        <v>734.16</v>
       </c>
       <c r="G399" s="12" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>1823.3</v>
       </c>
       <c r="F400" s="11" t="n">
-        <v>1865.72</v>
+        <v>1867.89</v>
       </c>
       <c r="G400" s="14" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>73.92</v>
       </c>
       <c r="F401" s="11" t="n">
-        <v>77.51000000000001</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="G401" s="14" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>2679.76</v>
       </c>
       <c r="F402" s="11" t="n">
-        <v>2761.83</v>
+        <v>2761.58</v>
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>41.06</v>
       </c>
       <c r="F403" s="11" t="n">
-        <v>43.6</v>
+        <v>43.67</v>
       </c>
       <c r="G403" s="12" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>1133.16</v>
       </c>
       <c r="F404" s="11" t="n">
-        <v>984.88</v>
+        <v>984.97</v>
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>164.35</v>
       </c>
       <c r="F405" s="11" t="n">
-        <v>150.42</v>
+        <v>150.75</v>
       </c>
       <c r="G405" s="14" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>136.65</v>
       </c>
       <c r="F406" s="11" t="n">
-        <v>120.62</v>
+        <v>120.85</v>
       </c>
       <c r="G406" s="12" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>181.38</v>
       </c>
       <c r="F407" s="11" t="n">
-        <v>216.5</v>
+        <v>216.89</v>
       </c>
       <c r="G407" s="14" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>537.36</v>
       </c>
       <c r="F408" s="11" t="n">
-        <v>530.05</v>
+        <v>530.11</v>
       </c>
       <c r="G408" s="14" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>417.61</v>
       </c>
       <c r="F409" s="11" t="n">
-        <v>400.4</v>
+        <v>401.06</v>
       </c>
       <c r="G409" s="12" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>4099.8</v>
       </c>
       <c r="F410" s="11" t="n">
-        <v>3963.84</v>
+        <v>3966.32</v>
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>1203.85</v>
       </c>
       <c r="F411" s="11" t="n">
-        <v>974.4</v>
+        <v>976.16</v>
       </c>
       <c r="G411" s="12" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>300.39</v>
       </c>
       <c r="F412" s="11" t="n">
-        <v>256.31</v>
+        <v>256.8</v>
       </c>
       <c r="G412" s="12" t="inlineStr">
         <is>
@@ -18855,10 +18855,10 @@
         <v>24943.21</v>
       </c>
       <c r="E413" s="11" t="n">
-        <v>24864.27</v>
+        <v>24864.28</v>
       </c>
       <c r="F413" s="11" t="n">
-        <v>26113.7</v>
+        <v>26147.53</v>
       </c>
       <c r="G413" s="12" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>966.59</v>
       </c>
       <c r="F414" s="11" t="n">
-        <v>900.55</v>
+        <v>902.4400000000001</v>
       </c>
       <c r="G414" s="12" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>928.4299999999999</v>
       </c>
       <c r="F415" s="11" t="n">
-        <v>878.38</v>
+        <v>880.1900000000001</v>
       </c>
       <c r="G415" s="14" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>3624.24</v>
       </c>
       <c r="F417" s="11" t="n">
-        <v>3362.01</v>
+        <v>3369.33</v>
       </c>
       <c r="G417" s="14" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>819.34</v>
       </c>
       <c r="F418" s="11" t="n">
-        <v>933</v>
+        <v>934.76</v>
       </c>
       <c r="G418" s="14" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>1380.24</v>
       </c>
       <c r="F419" s="11" t="n">
-        <v>1408.72</v>
+        <v>1409.48</v>
       </c>
       <c r="G419" s="12" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>16971.69</v>
       </c>
       <c r="F420" s="11" t="n">
-        <v>14883.9</v>
+        <v>14893.5</v>
       </c>
       <c r="G420" s="14" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>586.6900000000001</v>
       </c>
       <c r="F421" s="11" t="n">
-        <v>530.67</v>
+        <v>531.6</v>
       </c>
       <c r="G421" s="12" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>273.92</v>
       </c>
       <c r="F422" s="11" t="n">
-        <v>301.06</v>
+        <v>301.42</v>
       </c>
       <c r="G422" s="12" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>525.74</v>
       </c>
       <c r="F423" s="11" t="n">
-        <v>481.63</v>
+        <v>481.56</v>
       </c>
       <c r="G423" s="12" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>1012.75</v>
       </c>
       <c r="F424" s="11" t="n">
-        <v>976.77</v>
+        <v>977.67</v>
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>182.28</v>
       </c>
       <c r="F425" s="11" t="n">
-        <v>159.44</v>
+        <v>159.74</v>
       </c>
       <c r="G425" s="14" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>453.79</v>
       </c>
       <c r="F426" s="11" t="n">
-        <v>459.84</v>
+        <v>460.76</v>
       </c>
       <c r="G426" s="14" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>1808.28</v>
       </c>
       <c r="F427" s="11" t="n">
-        <v>1747.87</v>
+        <v>1749.06</v>
       </c>
       <c r="G427" s="12" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>536.28</v>
       </c>
       <c r="F428" s="11" t="n">
-        <v>560.15</v>
+        <v>561.91</v>
       </c>
       <c r="G428" s="14" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>4509.62</v>
       </c>
       <c r="F429" s="11" t="n">
-        <v>4755.28</v>
+        <v>4754.54</v>
       </c>
       <c r="G429" s="12" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>3558.07</v>
       </c>
       <c r="F430" s="11" t="n">
-        <v>3671.37</v>
+        <v>3674.94</v>
       </c>
       <c r="G430" s="14" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>711.03</v>
       </c>
       <c r="F431" s="11" t="n">
-        <v>694.1799999999999</v>
+        <v>695.12</v>
       </c>
       <c r="G431" s="12" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>54.28</v>
       </c>
       <c r="F432" s="11" t="n">
-        <v>52.63</v>
+        <v>52.77</v>
       </c>
       <c r="G432" s="12" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>327.34</v>
       </c>
       <c r="F433" s="11" t="n">
-        <v>376.74</v>
+        <v>377.94</v>
       </c>
       <c r="G433" s="14" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>262.06</v>
       </c>
       <c r="F434" s="11" t="n">
-        <v>314.23</v>
+        <v>314.48</v>
       </c>
       <c r="G434" s="14" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>447.38</v>
       </c>
       <c r="F435" s="11" t="n">
-        <v>513.52</v>
+        <v>514.84</v>
       </c>
       <c r="G435" s="14" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>1140.3</v>
       </c>
       <c r="F436" s="11" t="n">
-        <v>895.6</v>
+        <v>897.8099999999999</v>
       </c>
       <c r="G436" s="12" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>1299.41</v>
       </c>
       <c r="F437" s="11" t="n">
-        <v>1342.53</v>
+        <v>1344.99</v>
       </c>
       <c r="G437" s="12" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>3464.64</v>
       </c>
       <c r="F438" s="11" t="n">
-        <v>3429.96</v>
+        <v>3432.21</v>
       </c>
       <c r="G438" s="12" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>728.12</v>
       </c>
       <c r="F440" s="11" t="n">
-        <v>753.87</v>
+        <v>755.11</v>
       </c>
       <c r="G440" s="12" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>1814.44</v>
       </c>
       <c r="F441" s="11" t="n">
-        <v>1686.65</v>
+        <v>1689.1</v>
       </c>
       <c r="G441" s="12" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>2281.41</v>
       </c>
       <c r="F442" s="11" t="n">
-        <v>2652.36</v>
+        <v>2652.34</v>
       </c>
       <c r="G442" s="14" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>1135.83</v>
       </c>
       <c r="F443" s="11" t="n">
-        <v>1121.18</v>
+        <v>1121.58</v>
       </c>
       <c r="G443" s="12" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>4186.01</v>
       </c>
       <c r="F444" s="11" t="n">
-        <v>4678.63</v>
+        <v>4686.61</v>
       </c>
       <c r="G444" s="14" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>672.08</v>
       </c>
       <c r="F445" s="11" t="n">
-        <v>677.29</v>
+        <v>677.99</v>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>363.91</v>
       </c>
       <c r="F447" s="11" t="n">
-        <v>412.78</v>
+        <v>413.67</v>
       </c>
       <c r="G447" s="14" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>405.15</v>
       </c>
       <c r="F448" s="11" t="n">
-        <v>393.33</v>
+        <v>394.21</v>
       </c>
       <c r="G448" s="14" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>200.64</v>
       </c>
       <c r="F449" s="11" t="n">
-        <v>187.44</v>
+        <v>187.72</v>
       </c>
       <c r="G449" s="14" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>684.3099999999999</v>
       </c>
       <c r="F450" s="11" t="n">
-        <v>643.73</v>
+        <v>645.51</v>
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>43.24</v>
       </c>
       <c r="F451" s="11" t="n">
-        <v>46.92</v>
+        <v>47</v>
       </c>
       <c r="G451" s="14" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>1452.25</v>
       </c>
       <c r="F452" s="11" t="n">
-        <v>1474.41</v>
+        <v>1472.58</v>
       </c>
       <c r="G452" s="14" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>1117.63</v>
       </c>
       <c r="F453" s="11" t="n">
-        <v>1153.88</v>
+        <v>1158.61</v>
       </c>
       <c r="G453" s="12" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>1725.66</v>
       </c>
       <c r="F454" s="11" t="n">
-        <v>1734.63</v>
+        <v>1737.67</v>
       </c>
       <c r="G454" s="14" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>524.22</v>
       </c>
       <c r="F455" s="11" t="n">
-        <v>499.38</v>
+        <v>501.97</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>163.93</v>
       </c>
       <c r="F457" s="11" t="n">
-        <v>160.8</v>
+        <v>161.25</v>
       </c>
       <c r="G457" s="12" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>913.85</v>
       </c>
       <c r="F458" s="11" t="n">
-        <v>980.5</v>
+        <v>981.5599999999999</v>
       </c>
       <c r="G458" s="12" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>4443.17</v>
       </c>
       <c r="F459" s="11" t="n">
-        <v>3713.89</v>
+        <v>3720.15</v>
       </c>
       <c r="G459" s="12" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>3556.98</v>
       </c>
       <c r="F460" s="11" t="n">
-        <v>3291.18</v>
+        <v>3294.87</v>
       </c>
       <c r="G460" s="12" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>824.86</v>
       </c>
       <c r="F461" s="11" t="n">
-        <v>795.55</v>
+        <v>798.2</v>
       </c>
       <c r="G461" s="12" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>4233.72</v>
       </c>
       <c r="F462" s="11" t="n">
-        <v>4022.84</v>
+        <v>4025.36</v>
       </c>
       <c r="G462" s="12" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>4386.2</v>
       </c>
       <c r="F463" s="11" t="n">
-        <v>4037.97</v>
+        <v>4043.27</v>
       </c>
       <c r="G463" s="12" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>1469.22</v>
       </c>
       <c r="F464" s="11" t="n">
-        <v>1421.2</v>
+        <v>1426.66</v>
       </c>
       <c r="G464" s="14" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>317.3</v>
       </c>
       <c r="F465" s="11" t="n">
-        <v>336.42</v>
+        <v>338.78</v>
       </c>
       <c r="G465" s="12" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>2867.49</v>
       </c>
       <c r="F467" s="11" t="n">
-        <v>3374.85</v>
+        <v>3377.89</v>
       </c>
       <c r="G467" s="12" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>24.91</v>
       </c>
       <c r="F468" s="11" t="n">
-        <v>25.57</v>
+        <v>25.65</v>
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>634.23</v>
       </c>
       <c r="F469" s="11" t="n">
-        <v>561.04</v>
+        <v>563.51</v>
       </c>
       <c r="G469" s="14" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>3030.26</v>
       </c>
       <c r="F470" s="11" t="n">
-        <v>2855.54</v>
+        <v>2856.64</v>
       </c>
       <c r="G470" s="14" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>26.13</v>
       </c>
       <c r="F471" s="11" t="n">
-        <v>27.62</v>
+        <v>27.71</v>
       </c>
       <c r="G471" s="12" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>1104.1</v>
       </c>
       <c r="F472" s="11" t="n">
-        <v>1131.65</v>
+        <v>1134.94</v>
       </c>
       <c r="G472" s="12" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>629.83</v>
       </c>
       <c r="F473" s="11" t="n">
-        <v>665.29</v>
+        <v>666.14</v>
       </c>
       <c r="G473" s="14" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>953.15</v>
       </c>
       <c r="F474" s="11" t="n">
-        <v>1037.66</v>
+        <v>1040.31</v>
       </c>
       <c r="G474" s="14" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>11443.56</v>
       </c>
       <c r="F475" s="11" t="n">
-        <v>11705.45</v>
+        <v>11721.89</v>
       </c>
       <c r="G475" s="12" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>170.84</v>
       </c>
       <c r="F476" s="11" t="n">
-        <v>163.01</v>
+        <v>163.3</v>
       </c>
       <c r="G476" s="12" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>1383.85</v>
       </c>
       <c r="F477" s="11" t="n">
-        <v>1566.55</v>
+        <v>1567.44</v>
       </c>
       <c r="G477" s="14" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>1303.33</v>
       </c>
       <c r="F478" s="11" t="n">
-        <v>1336.36</v>
+        <v>1336.12</v>
       </c>
       <c r="G478" s="12" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>472.85</v>
       </c>
       <c r="F480" s="11" t="n">
-        <v>434.07</v>
+        <v>434.87</v>
       </c>
       <c r="G480" s="14" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>607</v>
       </c>
       <c r="F481" s="11" t="n">
-        <v>524.5</v>
+        <v>525.45</v>
       </c>
       <c r="G481" s="12" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>508.14</v>
       </c>
       <c r="F482" s="11" t="n">
-        <v>482.97</v>
+        <v>484.4</v>
       </c>
       <c r="G482" s="14" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>387.5</v>
       </c>
       <c r="F483" s="11" t="n">
-        <v>496.76</v>
+        <v>497.31</v>
       </c>
       <c r="G483" s="14" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>1233.53</v>
       </c>
       <c r="F484" s="11" t="n">
-        <v>1094.39</v>
+        <v>1096.66</v>
       </c>
       <c r="G484" s="12" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>119.22</v>
       </c>
       <c r="F485" s="11" t="n">
-        <v>123.07</v>
+        <v>122.99</v>
       </c>
       <c r="G485" s="14" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>13.16</v>
       </c>
       <c r="F486" s="11" t="n">
-        <v>10.83</v>
+        <v>10.85</v>
       </c>
       <c r="G486" s="14" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>1321.46</v>
       </c>
       <c r="F487" s="11" t="n">
-        <v>1361.14</v>
+        <v>1362.7</v>
       </c>
       <c r="G487" s="14" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>3082.17</v>
       </c>
       <c r="F488" s="11" t="n">
-        <v>3023.45</v>
+        <v>3029.46</v>
       </c>
       <c r="G488" s="14" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>1289.7</v>
       </c>
       <c r="F489" s="11" t="n">
-        <v>1030.37</v>
+        <v>1030.44</v>
       </c>
       <c r="G489" s="12" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>142.42</v>
       </c>
       <c r="F490" s="11" t="n">
-        <v>132.25</v>
+        <v>132.85</v>
       </c>
       <c r="G490" s="12" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>837.96</v>
       </c>
       <c r="F491" s="11" t="n">
-        <v>946.24</v>
+        <v>947.65</v>
       </c>
       <c r="G491" s="14" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>192.44</v>
       </c>
       <c r="F492" s="11" t="n">
-        <v>215.33</v>
+        <v>215.57</v>
       </c>
       <c r="G492" s="14" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>1757.26</v>
       </c>
       <c r="F493" s="11" t="n">
-        <v>1519.09</v>
+        <v>1524.75</v>
       </c>
       <c r="G493" s="12" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>22.63</v>
       </c>
       <c r="F494" s="11" t="n">
-        <v>21.2</v>
+        <v>21.24</v>
       </c>
       <c r="G494" s="12" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>2475.27</v>
       </c>
       <c r="F495" s="11" t="n">
-        <v>2377.57</v>
+        <v>2377.48</v>
       </c>
       <c r="G495" s="12" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>98.7</v>
       </c>
       <c r="F496" s="11" t="n">
-        <v>95.97</v>
+        <v>96.02</v>
       </c>
       <c r="G496" s="12" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>1700.64</v>
       </c>
       <c r="F497" s="11" t="n">
-        <v>1533.63</v>
+        <v>1534.89</v>
       </c>
       <c r="G497" s="14" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>494.51</v>
       </c>
       <c r="F498" s="11" t="n">
-        <v>601.33</v>
+        <v>602.53</v>
       </c>
       <c r="G498" s="14" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>1031.96</v>
       </c>
       <c r="F499" s="11" t="n">
-        <v>962.92</v>
+        <v>963.65</v>
       </c>
       <c r="G499" s="12" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>497.74</v>
       </c>
       <c r="F500" s="11" t="n">
-        <v>455.07</v>
+        <v>455.43</v>
       </c>
       <c r="G500" s="12" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>1489.17</v>
       </c>
       <c r="F501" s="11" t="n">
-        <v>1716.86</v>
+        <v>1718.41</v>
       </c>
       <c r="G501" s="14" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_500_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_500_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 26-Aug-2026  11:29:17    |    Closing Price Date: 26-Aug-2026</t>
+          <t>Scan Run: 27-Aug-2026  20:57:24    |    Closing Price Date: 26-Aug-2026</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>26-Aug-2026  11:29:17</t>
+          <t>27-Aug-2026  20:57:24</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         <v>1864.2</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1658.65</v>
+        <v>1658.02</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>752.34</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>818.01</v>
+        <v>817.54</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>1128.78</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>1244.44</v>
+        <v>1244.47</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>539.66</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>473.27</v>
+        <v>472.73</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>1397.61</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1359.08</v>
+        <v>1358.64</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>306.54</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>267.57</v>
+        <v>267.67</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>3292.5</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3255.84</v>
+        <v>3253.26</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>1311.81</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1361.23</v>
+        <v>1360.58</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>437.43</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>389.49</v>
+        <v>389.11</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>1376.58</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>1082.96</v>
+        <v>1082.89</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>2783.11</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2954.15</v>
+        <v>2952.82</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>273.65</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>298.42</v>
+        <v>297.92</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>4044.2</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>3667.96</v>
+        <v>3664.96</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>2292.43</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>2507.13</v>
+        <v>2506.34</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>7718.29</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>7205.33</v>
+        <v>7199.66</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>1912.67</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>1894.41</v>
+        <v>1894.03</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>1050.17</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>981.9299999999999</v>
+        <v>981.21</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>181.75</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>200.54</v>
+        <v>200.46</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>298.7</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>277.57</v>
+        <v>277.17</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>1658.16</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>1537.07</v>
+        <v>1536.51</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>419.3</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>419.03</v>
+        <v>419.23</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>2289.99</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>2293.82</v>
+        <v>2291.95</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>620.83</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>802.76</v>
+        <v>801.64</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>1729.2</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1627.49</v>
+        <v>1626.94</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>13677.87</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>13833.45</v>
+        <v>13819.44</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>1265.57</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>1269.2</v>
+        <v>1268.92</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>4004.01</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>3921.15</v>
+        <v>3919.85</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>3603.54</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>4041.51</v>
+        <v>4037.39</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>5351.22</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5154.02</v>
+        <v>5148.35</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>1041.9</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>1003.55</v>
+        <v>1003.17</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>1552.2</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>1486.18</v>
+        <v>1485.33</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>5312.31</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>5304.57</v>
+        <v>5303.66</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>2675.4</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>2572.95</v>
+        <v>2571.52</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>734.86</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>608.48</v>
+        <v>608.01</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>414.87</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>475.79</v>
+        <v>475.24</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>3564.08</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3320.2</v>
+        <v>3319.2</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>13639.37</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>12989.99</v>
+        <v>12989.67</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>1460.93</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>1360.89</v>
+        <v>1359.9</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>1067.58</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>961.77</v>
+        <v>960.99</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>372.96</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>333.64</v>
+        <v>333.5</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>2101.54</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>2206.69</v>
+        <v>2205.04</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>50.21</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>52.14</v>
+        <v>52.09</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>281.18</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>310.11</v>
+        <v>310.09</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>7789.96</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>6898.14</v>
+        <v>6892.93</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>1271.37</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1321.47</v>
+        <v>1321.03</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>1155.25</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1072.25</v>
+        <v>1070.55</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>392.06</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>396.77</v>
+        <v>396.6</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>167.76</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>161.94</v>
+        <v>162.01</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>314.61</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>310.22</v>
+        <v>310.18</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>4393.58</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>3970.6</v>
+        <v>3968.69</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>1907.18</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>1809.74</v>
+        <v>1808.84</v>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>307</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>291.78</v>
+        <v>291.68</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>193.02</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>179.19</v>
+        <v>179.21</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>1671.77</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>1306.06</v>
+        <v>1305.49</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>1013.17</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>947.52</v>
+        <v>947.6900000000001</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>4023.88</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>4095.16</v>
+        <v>4089.64</v>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>206.99</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>145.85</v>
+        <v>145.69</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>2997.53</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>2665.55</v>
+        <v>2663.96</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>4832.26</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>4355.52</v>
+        <v>4353.04</v>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>244.9</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>255.49</v>
+        <v>255.26</v>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>4783.62</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4316.8</v>
+        <v>4315.29</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>1233.86</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>1021.35</v>
+        <v>1022.22</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>18270.35</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>18663.8</v>
+        <v>18659.02</v>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>2902.12</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>2587.57</v>
+        <v>2586.42</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>1408.25</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1227.63</v>
+        <v>1226.8</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>211.61</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>188.04</v>
+        <v>187.99</v>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>33374.7</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>28654.05</v>
+        <v>28649.9</v>
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>883.09</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>809.42</v>
+        <v>809.1900000000001</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>11589.02</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>11567.59</v>
+        <v>11558.38</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>348.46</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>355.24</v>
+        <v>355.14</v>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>1104.38</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>1121.5</v>
+        <v>1120.23</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>11083.54</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>10014.2</v>
+        <v>10002.98</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4018,16 +4018,16 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>364.1</v>
+        <v>360.2</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>382.75</v>
+        <v>378.65</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>399.15</v>
+        <v>394.87</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>403.66</v>
+        <v>398.84</v>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>1496.62</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>1375.12</v>
+        <v>1374.75</v>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>9163.629999999999</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>8421.469999999999</v>
+        <v>8417.879999999999</v>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>343.77</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>308.54</v>
+        <v>308.52</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>458.48</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>472.34</v>
+        <v>471.75</v>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>1298.61</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>956.63</v>
+        <v>956.92</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>4252.38</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>3538.69</v>
+        <v>3537.53</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>407.75</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>401.24</v>
+        <v>400.97</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>102.21</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>99.58</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>3037.9</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>3160.29</v>
+        <v>3158.09</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>13.61</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>11.83</v>
+        <v>11.82</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>143.76</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>141.26</v>
+        <v>141.31</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>5148.31</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>5024.01</v>
+        <v>5018.57</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>318.97</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>280.38</v>
+        <v>280.47</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>1821.19</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>1861.89</v>
+        <v>1861.4</v>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>244.55</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>252.36</v>
+        <v>252.46</v>
       </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>4685.82</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>4479.23</v>
+        <v>4472.6</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>4740.82</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3948.78</v>
+        <v>3946.98</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>2479.5</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>2541.35</v>
+        <v>2538.13</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>2317.88</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>2243.69</v>
+        <v>2241.17</v>
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>189.17</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>187.6</v>
+        <v>187.65</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>708.79</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>596.14</v>
+        <v>596.13</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>291.21</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>416.4</v>
+        <v>416.14</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>2722.42</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>2371.4</v>
+        <v>2372.13</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>11146.69</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>9429.6</v>
+        <v>9422.4</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>42.36</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>43.27</v>
+        <v>43.18</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>7304.11</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>6528.68</v>
+        <v>6524.69</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>2962.23</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>3255.54</v>
+        <v>3251.41</v>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>557.9400000000001</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>626.3</v>
+        <v>626.14</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>417.59</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>447.96</v>
+        <v>447.65</v>
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>2371.36</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2383.06</v>
+        <v>2382.98</v>
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>76</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>66.45</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>372.23</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>380.56</v>
+        <v>380.28</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>405.86</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>344.99</v>
+        <v>345.02</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>8703.08</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8076.88</v>
+        <v>8074.35</v>
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>166.47</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>160.56</v>
+        <v>160.58</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>382.21</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>391.73</v>
+        <v>391.62</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>587.91</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>526.84</v>
+        <v>526.58</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>1543.98</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1422.85</v>
+        <v>1420.88</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>250.79</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>259.45</v>
+        <v>259.32</v>
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>1580.27</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>1315.72</v>
+        <v>1314.94</v>
       </c>
       <c r="G118" s="11" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>279.13</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>285.55</v>
+        <v>285.31</v>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>1033.85</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>990.01</v>
+        <v>989.11</v>
       </c>
       <c r="G120" s="11" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>4445.46</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>3771.51</v>
+        <v>3764.93</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>2885.42</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>2872.69</v>
+        <v>2867.53</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>341.46</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>296.25</v>
+        <v>296.1</v>
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>361.29</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>327.64</v>
+        <v>327.36</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>375.26</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>345.74</v>
+        <v>345.63</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>4345.91</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>4567.95</v>
+        <v>4567.76</v>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>1804.04</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>1686.24</v>
+        <v>1685.22</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>367.88</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>311.66</v>
+        <v>311.29</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>419.48</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>397.75</v>
+        <v>397.38</v>
       </c>
       <c r="G130" s="11" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>313.25</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>317.01</v>
+        <v>316.85</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>1458.7</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>1383.46</v>
+        <v>1383.49</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>157</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>136.48</v>
+        <v>136.4</v>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>1244.51</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1296.8</v>
+        <v>1295.78</v>
       </c>
       <c r="G134" s="11" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>338.14</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>387.78</v>
+        <v>387.35</v>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>269.31</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>275.65</v>
+        <v>275.46</v>
       </c>
       <c r="G136" s="11" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>173.83</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>163.89</v>
+        <v>163.9</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>769.6</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>693.8099999999999</v>
+        <v>693.1799999999999</v>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>15326.55</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>12396.72</v>
+        <v>12381.36</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>127.22</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>128.34</v>
+        <v>128.42</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>2565.24</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>2131.01</v>
+        <v>2131.59</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>372.09</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>449.76</v>
+        <v>449.42</v>
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>1091.17</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1115.59</v>
+        <v>1114.75</v>
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>591.3</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>553.79</v>
+        <v>553.3</v>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>1050.66</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>1063.51</v>
+        <v>1062.56</v>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>1608.28</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>1513.62</v>
+        <v>1512.31</v>
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>5498.68</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>5460.03</v>
+        <v>5457.39</v>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>609.67</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>562.0599999999999</v>
+        <v>561.92</v>
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>128.76</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>129.24</v>
+        <v>129.2</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>845.08</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>795.97</v>
+        <v>795.46</v>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>719.7</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>700.7</v>
+        <v>699.9299999999999</v>
       </c>
       <c r="G152" s="11" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>5354.65</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>4839.89</v>
+        <v>4839.87</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>1586.16</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1520.53</v>
+        <v>1519.71</v>
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>1384.91</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>1239.89</v>
+        <v>1238.67</v>
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>81.91</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>76.5</v>
+        <v>76.44</v>
       </c>
       <c r="G156" s="11" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>18707.56</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>16406.54</v>
+        <v>16397.7</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>182.29</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>178.21</v>
+        <v>177.98</v>
       </c>
       <c r="G158" s="11" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>19.89</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>20.91</v>
+        <v>20.89</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>324.95</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>297.39</v>
+        <v>297.26</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>5400.61</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>4936.74</v>
+        <v>4934.97</v>
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>176.12</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>165.17</v>
+        <v>165.22</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>567.21</v>
       </c>
       <c r="F163" s="10" t="n">
-        <v>553.8200000000001</v>
+        <v>553.3099999999999</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>9834.889999999999</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>8402.98</v>
+        <v>8400.440000000001</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>1213.48</v>
       </c>
       <c r="F165" s="10" t="n">
-        <v>1244.51</v>
+        <v>1244.72</v>
       </c>
       <c r="G165" s="11" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>648.21</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>642.1</v>
+        <v>642.73</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>346.16</v>
       </c>
       <c r="F167" s="10" t="n">
-        <v>348.76</v>
+        <v>348.24</v>
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>574.76</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>522.17</v>
+        <v>521.8099999999999</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>898.75</v>
       </c>
       <c r="F169" s="10" t="n">
-        <v>882.86</v>
+        <v>881.98</v>
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>2081.88</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>2043.41</v>
+        <v>2042.97</v>
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>1144.72</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>1104.3</v>
+        <v>1103.21</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>1937.58</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>1905.58</v>
+        <v>1904.23</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>38202.39</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>38199.23</v>
+        <v>38169.8</v>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>5388.53</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>5483.16</v>
+        <v>5479.54</v>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>79.67</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>100.43</v>
+        <v>100.42</v>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>89.75</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>101.89</v>
+        <v>101.7</v>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>3416.74</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>3043.88</v>
+        <v>3042.7</v>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>154.5</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>133.26</v>
+        <v>133.21</v>
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>641.55</v>
       </c>
       <c r="F179" s="10" t="n">
-        <v>579.97</v>
+        <v>578.59</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>3766.21</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>4359.05</v>
+        <v>4357.09</v>
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>2541.92</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>1958.72</v>
+        <v>1958.57</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>1566.7</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>1601.26</v>
+        <v>1600.71</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>7442.39</v>
       </c>
       <c r="F183" s="10" t="n">
-        <v>7363.37</v>
+        <v>7371.19</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>1054.65</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>976.26</v>
+        <v>976.3</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>2004.84</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>2085.9</v>
+        <v>2082.66</v>
       </c>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>212.58</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>197.68</v>
+        <v>197.78</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>467.15</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>449.65</v>
+        <v>449.58</v>
       </c>
       <c r="G187" s="11" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>547.9</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>569.79</v>
+        <v>571.59</v>
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>22.93</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>22.08</v>
+        <v>22.07</v>
       </c>
       <c r="G189" s="11" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>1217.95</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>1169.92</v>
+        <v>1168.77</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>992.9400000000001</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>916.2</v>
+        <v>916.13</v>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>1428.71</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>1405.57</v>
+        <v>1404.09</v>
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>7815.17</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>6786.59</v>
+        <v>6786.88</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>2150.56</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>2299.39</v>
+        <v>2302.42</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>3245.26</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>2630.1</v>
+        <v>2629.68</v>
       </c>
       <c r="G195" s="11" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>1666.86</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>1654.05</v>
+        <v>1652.2</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>919.85</v>
       </c>
       <c r="F198" s="10" t="n">
-        <v>944.22</v>
+        <v>943.7</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>1274.31</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>1216.79</v>
+        <v>1216.51</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>1572.74</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>1403.46</v>
+        <v>1402.88</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>1797.81</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>1602.74</v>
+        <v>1603.29</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>111.98</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>109.94</v>
+        <v>109.92</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43156.16</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>38558.41</v>
+        <v>38556.59</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>525.1900000000001</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>485.27</v>
+        <v>485.2</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>794.89</v>
       </c>
       <c r="F206" s="10" t="n">
-        <v>901.98</v>
+        <v>902.0599999999999</v>
       </c>
       <c r="G206" s="11" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>426.53</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>465.66</v>
+        <v>465.52</v>
       </c>
       <c r="G207" s="11" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>1995.78</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>1922.51</v>
+        <v>1919.99</v>
       </c>
       <c r="G208" s="11" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>1470.41</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>1544.62</v>
+        <v>1537.95</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>85.45</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>82.47</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>1338.5</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>1347.26</v>
+        <v>1347.17</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>20393.3</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>16905.77</v>
+        <v>16903.05</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>2627.02</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>2604.59</v>
+        <v>2601</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>1292.23</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>1011.25</v>
+        <v>1010.48</v>
       </c>
       <c r="G214" s="11" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>490.23</v>
       </c>
       <c r="F215" s="10" t="n">
-        <v>557.46</v>
+        <v>559.54</v>
       </c>
       <c r="G215" s="11" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>382.44</v>
       </c>
       <c r="F216" s="10" t="n">
-        <v>389.86</v>
+        <v>389.49</v>
       </c>
       <c r="G216" s="11" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>520.9400000000001</v>
       </c>
       <c r="F217" s="10" t="n">
-        <v>596.72</v>
+        <v>604.22</v>
       </c>
       <c r="G217" s="11" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>2272.09</v>
       </c>
       <c r="F218" s="10" t="n">
-        <v>2144.6</v>
+        <v>2144.51</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>301.18</v>
       </c>
       <c r="F219" s="10" t="n">
-        <v>300</v>
+        <v>300.13</v>
       </c>
       <c r="G219" s="11" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>172.69</v>
       </c>
       <c r="F220" s="10" t="n">
-        <v>168.63</v>
+        <v>168.69</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>139.63</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>143.9</v>
+        <v>143.79</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>58.43</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>73.44</v>
+        <v>73.09</v>
       </c>
       <c r="G222" s="11" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>1880.3</v>
       </c>
       <c r="F223" s="10" t="n">
-        <v>1628.28</v>
+        <v>1628.07</v>
       </c>
       <c r="G223" s="11" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>789.83</v>
       </c>
       <c r="F224" s="10" t="n">
-        <v>736.88</v>
+        <v>736.63</v>
       </c>
       <c r="G224" s="11" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>584.58</v>
       </c>
       <c r="F225" s="10" t="n">
-        <v>575.0599999999999</v>
+        <v>576.48</v>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>104.59</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>100.31</v>
+        <v>100.24</v>
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>2654.84</v>
       </c>
       <c r="F227" s="10" t="n">
-        <v>2727.89</v>
+        <v>2726.8</v>
       </c>
       <c r="G227" s="11" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>1098.79</v>
       </c>
       <c r="F228" s="10" t="n">
-        <v>998.14</v>
+        <v>997.6</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>3182.28</v>
       </c>
       <c r="F229" s="10" t="n">
-        <v>2974.41</v>
+        <v>2974.16</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>1487.58</v>
       </c>
       <c r="F230" s="10" t="n">
-        <v>1372.77</v>
+        <v>1372.02</v>
       </c>
       <c r="G230" s="11" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>1931.49</v>
       </c>
       <c r="F232" s="10" t="n">
-        <v>1809.69</v>
+        <v>1808.57</v>
       </c>
       <c r="G232" s="11" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>1958.17</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>1905.79</v>
+        <v>1905.33</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>1112.91</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>1022.76</v>
+        <v>1021.64</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>308.76</v>
       </c>
       <c r="F235" s="10" t="n">
-        <v>283.68</v>
+        <v>283.52</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>1479</v>
       </c>
       <c r="F236" s="10" t="n">
-        <v>1490.61</v>
+        <v>1488.43</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>682.3099999999999</v>
       </c>
       <c r="F238" s="10" t="n">
-        <v>646.29</v>
+        <v>645.29</v>
       </c>
       <c r="G238" s="11" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>39.13</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>39.16</v>
+        <v>39.1</v>
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>515.61</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>529.4299999999999</v>
+        <v>528.91</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>1878.32</v>
       </c>
       <c r="F242" s="10" t="n">
-        <v>1658.31</v>
+        <v>1656.91</v>
       </c>
       <c r="G242" s="11" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>306.49</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>341.87</v>
+        <v>341.78</v>
       </c>
       <c r="G243" s="11" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>919.97</v>
       </c>
       <c r="F244" s="10" t="n">
-        <v>868.63</v>
+        <v>867.8</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>3796.21</v>
       </c>
       <c r="F245" s="10" t="n">
-        <v>3503.92</v>
+        <v>3504.88</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>1291.27</v>
       </c>
       <c r="F246" s="10" t="n">
-        <v>1331.63</v>
+        <v>1330.4</v>
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>2439.04</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>2367.49</v>
+        <v>2366.87</v>
       </c>
       <c r="G247" s="11" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>1196.28</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>1157.71</v>
+        <v>1156.62</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>2594.88</v>
       </c>
       <c r="F249" s="10" t="n">
-        <v>2586.67</v>
+        <v>2585.75</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>142.51</v>
       </c>
       <c r="F250" s="10" t="n">
-        <v>139.81</v>
+        <v>139.75</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>322.92</v>
       </c>
       <c r="F251" s="10" t="n">
-        <v>288.52</v>
+        <v>288.61</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>456.71</v>
       </c>
       <c r="F252" s="10" t="n">
-        <v>449.44</v>
+        <v>449.46</v>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>293.68</v>
       </c>
       <c r="F253" s="10" t="n">
-        <v>285.81</v>
+        <v>285.97</v>
       </c>
       <c r="G253" s="11" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>1106.7</v>
       </c>
       <c r="F255" s="10" t="n">
-        <v>1108.6</v>
+        <v>1107.97</v>
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>1745.04</v>
       </c>
       <c r="F256" s="10" t="n">
-        <v>1704.53</v>
+        <v>1702.11</v>
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>639.64</v>
       </c>
       <c r="F257" s="10" t="n">
-        <v>701.8</v>
+        <v>701.16</v>
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>1681.04</v>
       </c>
       <c r="F258" s="10" t="n">
-        <v>1786.3</v>
+        <v>1785.91</v>
       </c>
       <c r="G258" s="11" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>1363.46</v>
       </c>
       <c r="F259" s="10" t="n">
-        <v>1402.6</v>
+        <v>1401.25</v>
       </c>
       <c r="G259" s="11" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>1318</v>
       </c>
       <c r="F260" s="10" t="n">
-        <v>1375.65</v>
+        <v>1374.59</v>
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>415.38</v>
       </c>
       <c r="F261" s="10" t="n">
-        <v>413.24</v>
+        <v>413.15</v>
       </c>
       <c r="G261" s="11" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>1168.9</v>
       </c>
       <c r="F262" s="10" t="n">
-        <v>1024.41</v>
+        <v>1024.29</v>
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>567.73</v>
       </c>
       <c r="F263" s="10" t="n">
-        <v>542.25</v>
+        <v>541.25</v>
       </c>
       <c r="G263" s="11" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>2086.47</v>
       </c>
       <c r="F264" s="10" t="n">
-        <v>1828.77</v>
+        <v>1827.55</v>
       </c>
       <c r="G264" s="11" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>855.6799999999999</v>
       </c>
       <c r="F265" s="10" t="n">
-        <v>824.6</v>
+        <v>824.5700000000001</v>
       </c>
       <c r="G265" s="12" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>232.22</v>
       </c>
       <c r="F266" s="10" t="n">
-        <v>275.94</v>
+        <v>275.28</v>
       </c>
       <c r="G266" s="11" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>124.9</v>
       </c>
       <c r="F267" s="10" t="n">
-        <v>130.61</v>
+        <v>130.6</v>
       </c>
       <c r="G267" s="11" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>831.02</v>
       </c>
       <c r="F268" s="10" t="n">
-        <v>711.37</v>
+        <v>711.26</v>
       </c>
       <c r="G268" s="11" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>7623.97</v>
       </c>
       <c r="F269" s="10" t="n">
-        <v>7980.45</v>
+        <v>7983.39</v>
       </c>
       <c r="G269" s="11" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>207.77</v>
       </c>
       <c r="F270" s="10" t="n">
-        <v>213.35</v>
+        <v>213.42</v>
       </c>
       <c r="G270" s="12" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>85.68000000000001</v>
       </c>
       <c r="F271" s="10" t="n">
-        <v>91.23999999999999</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="G271" s="11" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>81.05</v>
       </c>
       <c r="F272" s="10" t="n">
-        <v>73.11</v>
+        <v>73.05</v>
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>507.27</v>
       </c>
       <c r="F273" s="10" t="n">
-        <v>548.6900000000001</v>
+        <v>548.27</v>
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>514.89</v>
       </c>
       <c r="F274" s="10" t="n">
-        <v>481.49</v>
+        <v>481.78</v>
       </c>
       <c r="G274" s="11" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>554.48</v>
       </c>
       <c r="F275" s="10" t="n">
-        <v>534.74</v>
+        <v>534.3</v>
       </c>
       <c r="G275" s="11" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>501.43</v>
       </c>
       <c r="F276" s="10" t="n">
-        <v>501.69</v>
+        <v>501.05</v>
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>2119.38</v>
       </c>
       <c r="F277" s="10" t="n">
-        <v>1707.06</v>
+        <v>1706.8</v>
       </c>
       <c r="G277" s="11" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>229.06</v>
       </c>
       <c r="F278" s="10" t="n">
-        <v>203.4</v>
+        <v>203.31</v>
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>111.39</v>
       </c>
       <c r="F279" s="10" t="n">
-        <v>119.63</v>
+        <v>119.46</v>
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>37061.14</v>
       </c>
       <c r="F280" s="10" t="n">
-        <v>35167.17</v>
+        <v>35122.51</v>
       </c>
       <c r="G280" s="11" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>1007.23</v>
       </c>
       <c r="F281" s="10" t="n">
-        <v>1073.86</v>
+        <v>1072.64</v>
       </c>
       <c r="G281" s="11" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>2810.8</v>
       </c>
       <c r="F282" s="10" t="n">
-        <v>2630.54</v>
+        <v>2629.2</v>
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>83.48999999999999</v>
       </c>
       <c r="F283" s="10" t="n">
-        <v>85.98999999999999</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>255.55</v>
       </c>
       <c r="F284" s="10" t="n">
-        <v>266.41</v>
+        <v>266.18</v>
       </c>
       <c r="G284" s="11" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>658.25</v>
       </c>
       <c r="F285" s="10" t="n">
-        <v>592.17</v>
+        <v>592.24</v>
       </c>
       <c r="G285" s="12" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>795.21</v>
       </c>
       <c r="F286" s="10" t="n">
-        <v>720.52</v>
+        <v>720.33</v>
       </c>
       <c r="G286" s="11" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>1788.08</v>
       </c>
       <c r="F287" s="10" t="n">
-        <v>1648.69</v>
+        <v>1649.37</v>
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>1234.6</v>
       </c>
       <c r="F288" s="10" t="n">
-        <v>951.04</v>
+        <v>952.04</v>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>918.5</v>
       </c>
       <c r="F289" s="10" t="n">
-        <v>963.24</v>
+        <v>962.51</v>
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>526.27</v>
       </c>
       <c r="F291" s="10" t="n">
-        <v>513.9299999999999</v>
+        <v>513.2</v>
       </c>
       <c r="G291" s="11" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>1577.99</v>
       </c>
       <c r="F292" s="10" t="n">
-        <v>1653.24</v>
+        <v>1651.92</v>
       </c>
       <c r="G292" s="11" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>4281.99</v>
       </c>
       <c r="F293" s="10" t="n">
-        <v>3945.7</v>
+        <v>3945.25</v>
       </c>
       <c r="G293" s="11" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>281.09</v>
       </c>
       <c r="F294" s="10" t="n">
-        <v>278.66</v>
+        <v>278.51</v>
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>94.63</v>
       </c>
       <c r="F295" s="10" t="n">
-        <v>99.31</v>
+        <v>99.11</v>
       </c>
       <c r="G295" s="11" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>132155.28</v>
       </c>
       <c r="F296" s="10" t="n">
-        <v>135660.1</v>
+        <v>135664</v>
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>523.41</v>
       </c>
       <c r="F297" s="10" t="n">
-        <v>512.62</v>
+        <v>512.47</v>
       </c>
       <c r="G297" s="11" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>1595.59</v>
       </c>
       <c r="F298" s="10" t="n">
-        <v>1582.81</v>
+        <v>1582.67</v>
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>77.69</v>
       </c>
       <c r="F299" s="10" t="n">
-        <v>78.55</v>
+        <v>78.45</v>
       </c>
       <c r="G299" s="11" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>465.27</v>
       </c>
       <c r="F300" s="10" t="n">
-        <v>494.14</v>
+        <v>493.52</v>
       </c>
       <c r="G300" s="12" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>769.98</v>
       </c>
       <c r="F301" s="10" t="n">
-        <v>754.58</v>
+        <v>753.9</v>
       </c>
       <c r="G301" s="11" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>1297.42</v>
       </c>
       <c r="F303" s="10" t="n">
-        <v>1106.95</v>
+        <v>1106.48</v>
       </c>
       <c r="G303" s="11" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>587.3200000000001</v>
       </c>
       <c r="F304" s="10" t="n">
-        <v>578.11</v>
+        <v>578.04</v>
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>989.8200000000001</v>
       </c>
       <c r="F305" s="10" t="n">
-        <v>922.1799999999999</v>
+        <v>922.35</v>
       </c>
       <c r="G305" s="12" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>159.99</v>
       </c>
       <c r="F306" s="10" t="n">
-        <v>155</v>
+        <v>154.83</v>
       </c>
       <c r="G306" s="11" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>655.13</v>
       </c>
       <c r="F307" s="10" t="n">
-        <v>641.25</v>
+        <v>640.95</v>
       </c>
       <c r="G307" s="12" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>93.77</v>
       </c>
       <c r="F308" s="10" t="n">
-        <v>97.25</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="G308" s="11" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>832.55</v>
       </c>
       <c r="F309" s="10" t="n">
-        <v>834.62</v>
+        <v>832.87</v>
       </c>
       <c r="G309" s="12" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>590.22</v>
       </c>
       <c r="F310" s="10" t="n">
-        <v>633.29</v>
+        <v>632.62</v>
       </c>
       <c r="G310" s="12" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>397.25</v>
       </c>
       <c r="F311" s="10" t="n">
-        <v>356.38</v>
+        <v>356.32</v>
       </c>
       <c r="G311" s="12" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>3495.26</v>
       </c>
       <c r="F312" s="10" t="n">
-        <v>3607.97</v>
+        <v>3603.33</v>
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>1351.11</v>
       </c>
       <c r="F313" s="10" t="n">
-        <v>1141.04</v>
+        <v>1140.58</v>
       </c>
       <c r="G313" s="11" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>10977.79</v>
       </c>
       <c r="F314" s="10" t="n">
-        <v>10975.19</v>
+        <v>10933.57</v>
       </c>
       <c r="G314" s="12" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>1365.69</v>
       </c>
       <c r="F315" s="10" t="n">
-        <v>1306.17</v>
+        <v>1304.41</v>
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>880.54</v>
       </c>
       <c r="F316" s="10" t="n">
-        <v>958.5700000000001</v>
+        <v>958.25</v>
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>1108.75</v>
       </c>
       <c r="F317" s="10" t="n">
-        <v>1044.57</v>
+        <v>1043.73</v>
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>1329</v>
       </c>
       <c r="F318" s="10" t="n">
-        <v>1112.66</v>
+        <v>1111.94</v>
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>1751.42</v>
       </c>
       <c r="F319" s="10" t="n">
-        <v>1748.47</v>
+        <v>1750.09</v>
       </c>
       <c r="G319" s="12" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>718.2</v>
       </c>
       <c r="F320" s="10" t="n">
-        <v>787.28</v>
+        <v>787.5700000000001</v>
       </c>
       <c r="G320" s="11" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>3551.44</v>
       </c>
       <c r="F321" s="10" t="n">
-        <v>3544.13</v>
+        <v>3543.24</v>
       </c>
       <c r="G321" s="11" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>1754.84</v>
       </c>
       <c r="F322" s="10" t="n">
-        <v>1290.53</v>
+        <v>1289.99</v>
       </c>
       <c r="G322" s="12" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>466.68</v>
       </c>
       <c r="F323" s="10" t="n">
-        <v>444.71</v>
+        <v>444.58</v>
       </c>
       <c r="G323" s="11" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>1593.35</v>
       </c>
       <c r="F324" s="10" t="n">
-        <v>1688.31</v>
+        <v>1688</v>
       </c>
       <c r="G324" s="11" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>120.79</v>
       </c>
       <c r="F325" s="10" t="n">
-        <v>129.71</v>
+        <v>129.52</v>
       </c>
       <c r="G325" s="12" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>4333.16</v>
       </c>
       <c r="F326" s="10" t="n">
-        <v>3847.91</v>
+        <v>3847.66</v>
       </c>
       <c r="G326" s="12" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>669.87</v>
       </c>
       <c r="F327" s="10" t="n">
-        <v>642.17</v>
+        <v>641.52</v>
       </c>
       <c r="G327" s="11" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>470.1</v>
       </c>
       <c r="F328" s="10" t="n">
-        <v>568.84</v>
+        <v>567.55</v>
       </c>
       <c r="G328" s="11" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>166.92</v>
       </c>
       <c r="F329" s="10" t="n">
-        <v>175.16</v>
+        <v>175.06</v>
       </c>
       <c r="G329" s="12" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>620.64</v>
       </c>
       <c r="F330" s="10" t="n">
-        <v>630.7</v>
+        <v>630.5700000000001</v>
       </c>
       <c r="G330" s="11" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>2653.55</v>
       </c>
       <c r="F331" s="10" t="n">
-        <v>2968.44</v>
+        <v>2967.28</v>
       </c>
       <c r="G331" s="11" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>1833.23</v>
       </c>
       <c r="F332" s="10" t="n">
-        <v>2013.92</v>
+        <v>2013.16</v>
       </c>
       <c r="G332" s="11" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>277</v>
       </c>
       <c r="F333" s="10" t="n">
-        <v>307.42</v>
+        <v>307.44</v>
       </c>
       <c r="G333" s="11" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>1367.22</v>
       </c>
       <c r="F334" s="10" t="n">
-        <v>1257.34</v>
+        <v>1257.71</v>
       </c>
       <c r="G334" s="12" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>1820.69</v>
       </c>
       <c r="F335" s="10" t="n">
-        <v>1901.96</v>
+        <v>1901.69</v>
       </c>
       <c r="G335" s="12" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>6578.74</v>
       </c>
       <c r="F336" s="10" t="n">
-        <v>6492.86</v>
+        <v>6494.97</v>
       </c>
       <c r="G336" s="11" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>111.57</v>
       </c>
       <c r="F337" s="10" t="n">
-        <v>122.57</v>
+        <v>122.43</v>
       </c>
       <c r="G337" s="11" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>1766.26</v>
       </c>
       <c r="F338" s="10" t="n">
-        <v>1726.45</v>
+        <v>1726.09</v>
       </c>
       <c r="G338" s="11" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>1381.16</v>
       </c>
       <c r="F339" s="10" t="n">
-        <v>1424.58</v>
+        <v>1425.68</v>
       </c>
       <c r="G339" s="11" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>936.16</v>
       </c>
       <c r="F340" s="10" t="n">
-        <v>915.95</v>
+        <v>915.6799999999999</v>
       </c>
       <c r="G340" s="11" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>1816.47</v>
       </c>
       <c r="F341" s="10" t="n">
-        <v>1711.92</v>
+        <v>1710.47</v>
       </c>
       <c r="G341" s="12" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>727.52</v>
       </c>
       <c r="F342" s="10" t="n">
-        <v>753.8200000000001</v>
+        <v>753.22</v>
       </c>
       <c r="G342" s="11" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>2516.37</v>
       </c>
       <c r="F343" s="10" t="n">
-        <v>2425.24</v>
+        <v>2422.29</v>
       </c>
       <c r="G343" s="12" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>2057.29</v>
       </c>
       <c r="F344" s="10" t="n">
-        <v>1760.57</v>
+        <v>1760.25</v>
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>454.71</v>
       </c>
       <c r="F345" s="10" t="n">
-        <v>375.87</v>
+        <v>376.05</v>
       </c>
       <c r="G345" s="12" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>535.41</v>
       </c>
       <c r="F346" s="10" t="n">
-        <v>520.34</v>
+        <v>520.22</v>
       </c>
       <c r="G346" s="12" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>3478.97</v>
       </c>
       <c r="F347" s="10" t="n">
-        <v>3626.4</v>
+        <v>3624.23</v>
       </c>
       <c r="G347" s="12" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>1013.85</v>
       </c>
       <c r="F348" s="10" t="n">
-        <v>1166.21</v>
+        <v>1164.68</v>
       </c>
       <c r="G348" s="11" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>24.17</v>
       </c>
       <c r="F349" s="10" t="n">
-        <v>29.45</v>
+        <v>29.41</v>
       </c>
       <c r="G349" s="11" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>1342.39</v>
       </c>
       <c r="F350" s="10" t="n">
-        <v>1283.36</v>
+        <v>1282.42</v>
       </c>
       <c r="G350" s="11" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>1602.76</v>
       </c>
       <c r="F351" s="10" t="n">
-        <v>1633.49</v>
+        <v>1634.49</v>
       </c>
       <c r="G351" s="11" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>25511.5</v>
       </c>
       <c r="F353" s="10" t="n">
-        <v>26118.07</v>
+        <v>26115.04</v>
       </c>
       <c r="G353" s="11" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>1196.93</v>
       </c>
       <c r="F354" s="10" t="n">
-        <v>1120.81</v>
+        <v>1120.23</v>
       </c>
       <c r="G354" s="11" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>195.9</v>
       </c>
       <c r="F355" s="10" t="n">
-        <v>201.4</v>
+        <v>201.06</v>
       </c>
       <c r="G355" s="11" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>39.67</v>
       </c>
       <c r="F356" s="10" t="n">
-        <v>40.45</v>
+        <v>40.42</v>
       </c>
       <c r="G356" s="11" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>258.38</v>
       </c>
       <c r="F358" s="10" t="n">
-        <v>284.59</v>
+        <v>283.82</v>
       </c>
       <c r="G358" s="11" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>443.72</v>
       </c>
       <c r="F359" s="10" t="n">
-        <v>458.54</v>
+        <v>457.82</v>
       </c>
       <c r="G359" s="11" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>504.8</v>
       </c>
       <c r="F361" s="10" t="n">
-        <v>567.35</v>
+        <v>566.59</v>
       </c>
       <c r="G361" s="11" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>292.18</v>
       </c>
       <c r="F362" s="10" t="n">
-        <v>269.67</v>
+        <v>269.39</v>
       </c>
       <c r="G362" s="11" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>690.99</v>
       </c>
       <c r="F363" s="10" t="n">
-        <v>612.6</v>
+        <v>611.95</v>
       </c>
       <c r="G363" s="11" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>1058.94</v>
       </c>
       <c r="F364" s="10" t="n">
-        <v>994.15</v>
+        <v>992.72</v>
       </c>
       <c r="G364" s="12" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>1768.01</v>
       </c>
       <c r="F365" s="10" t="n">
-        <v>1597.68</v>
+        <v>1598.51</v>
       </c>
       <c r="G365" s="12" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>276.62</v>
       </c>
       <c r="F367" s="10" t="n">
-        <v>248.78</v>
+        <v>248.76</v>
       </c>
       <c r="G367" s="12" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>431.86</v>
       </c>
       <c r="F368" s="10" t="n">
-        <v>440.49</v>
+        <v>440.52</v>
       </c>
       <c r="G368" s="12" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>499.88</v>
       </c>
       <c r="F370" s="10" t="n">
-        <v>459.48</v>
+        <v>458.89</v>
       </c>
       <c r="G370" s="12" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>1903.4</v>
       </c>
       <c r="F372" s="10" t="n">
-        <v>1862.95</v>
+        <v>1861.94</v>
       </c>
       <c r="G372" s="12" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>5384.57</v>
       </c>
       <c r="F373" s="10" t="n">
-        <v>5502.15</v>
+        <v>5496.87</v>
       </c>
       <c r="G373" s="11" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>1832.67</v>
       </c>
       <c r="F374" s="10" t="n">
-        <v>1812.82</v>
+        <v>1809.84</v>
       </c>
       <c r="G374" s="12" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>311.83</v>
       </c>
       <c r="F375" s="10" t="n">
-        <v>355.04</v>
+        <v>354.2</v>
       </c>
       <c r="G375" s="11" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>1347.58</v>
       </c>
       <c r="F376" s="10" t="n">
-        <v>1485.72</v>
+        <v>1485.33</v>
       </c>
       <c r="G376" s="12" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>4516.23</v>
       </c>
       <c r="F377" s="10" t="n">
-        <v>4133.12</v>
+        <v>4131.51</v>
       </c>
       <c r="G377" s="11" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>1382.97</v>
       </c>
       <c r="F378" s="10" t="n">
-        <v>1318.92</v>
+        <v>1318.43</v>
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>925.1</v>
       </c>
       <c r="F379" s="10" t="n">
-        <v>941.9400000000001</v>
+        <v>941.36</v>
       </c>
       <c r="G379" s="11" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>159.74</v>
       </c>
       <c r="F380" s="10" t="n">
-        <v>160.69</v>
+        <v>160.74</v>
       </c>
       <c r="G380" s="11" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>833.4400000000001</v>
       </c>
       <c r="F381" s="10" t="n">
-        <v>833.34</v>
+        <v>832.39</v>
       </c>
       <c r="G381" s="12" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>1140.11</v>
       </c>
       <c r="F383" s="10" t="n">
-        <v>1067.18</v>
+        <v>1070.11</v>
       </c>
       <c r="G383" s="11" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>1177.66</v>
       </c>
       <c r="F384" s="10" t="n">
-        <v>1153.05</v>
+        <v>1151.87</v>
       </c>
       <c r="G384" s="11" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>250.74</v>
       </c>
       <c r="F385" s="10" t="n">
-        <v>255.86</v>
+        <v>255.62</v>
       </c>
       <c r="G385" s="12" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>1372.59</v>
       </c>
       <c r="F386" s="10" t="n">
-        <v>1493.63</v>
+        <v>1492.33</v>
       </c>
       <c r="G386" s="11" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>2473.98</v>
       </c>
       <c r="F387" s="10" t="n">
-        <v>2166.43</v>
+        <v>2165.03</v>
       </c>
       <c r="G387" s="11" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>719.63</v>
       </c>
       <c r="F388" s="10" t="n">
-        <v>729.87</v>
+        <v>729.12</v>
       </c>
       <c r="G388" s="11" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>494.98</v>
       </c>
       <c r="F389" s="10" t="n">
-        <v>488.52</v>
+        <v>488.12</v>
       </c>
       <c r="G389" s="11" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>611.7</v>
       </c>
       <c r="F390" s="10" t="n">
-        <v>560.75</v>
+        <v>561.0700000000001</v>
       </c>
       <c r="G390" s="11" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>191.39</v>
       </c>
       <c r="F391" s="10" t="n">
-        <v>205.32</v>
+        <v>205.05</v>
       </c>
       <c r="G391" s="12" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>391.91</v>
       </c>
       <c r="F392" s="10" t="n">
-        <v>407.28</v>
+        <v>407.03</v>
       </c>
       <c r="G392" s="11" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>1457.44</v>
       </c>
       <c r="F393" s="10" t="n">
-        <v>1371</v>
+        <v>1370.55</v>
       </c>
       <c r="G393" s="11" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>1041.08</v>
       </c>
       <c r="F394" s="10" t="n">
-        <v>1095.02</v>
+        <v>1094.32</v>
       </c>
       <c r="G394" s="12" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>346.42</v>
       </c>
       <c r="F395" s="10" t="n">
-        <v>344.02</v>
+        <v>343.68</v>
       </c>
       <c r="G395" s="12" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>4086.15</v>
       </c>
       <c r="F396" s="10" t="n">
-        <v>4040.57</v>
+        <v>4036.25</v>
       </c>
       <c r="G396" s="11" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>26.19</v>
       </c>
       <c r="F397" s="10" t="n">
-        <v>27.09</v>
+        <v>27.06</v>
       </c>
       <c r="G397" s="12" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>1701.69</v>
       </c>
       <c r="F399" s="10" t="n">
-        <v>1684.44</v>
+        <v>1682.78</v>
       </c>
       <c r="G399" s="12" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>307.87</v>
       </c>
       <c r="F400" s="10" t="n">
-        <v>331.7</v>
+        <v>331.03</v>
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>678.8</v>
       </c>
       <c r="F401" s="10" t="n">
-        <v>728.9299999999999</v>
+        <v>728.73</v>
       </c>
       <c r="G401" s="11" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>786.24</v>
       </c>
       <c r="F402" s="10" t="n">
-        <v>749.29</v>
+        <v>749.35</v>
       </c>
       <c r="G402" s="11" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>664.59</v>
       </c>
       <c r="F403" s="10" t="n">
-        <v>673.67</v>
+        <v>673.11</v>
       </c>
       <c r="G403" s="11" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>2019.19</v>
       </c>
       <c r="F404" s="10" t="n">
-        <v>2083.57</v>
+        <v>2079.67</v>
       </c>
       <c r="G404" s="11" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>1247.54</v>
       </c>
       <c r="F405" s="10" t="n">
-        <v>1242.88</v>
+        <v>1243.23</v>
       </c>
       <c r="G405" s="12" t="inlineStr">
         <is>
@@ -18547,7 +18547,7 @@
         <v>610.75</v>
       </c>
       <c r="F406" s="10" t="n">
-        <v>583.37</v>
+        <v>582.75</v>
       </c>
       <c r="G406" s="11" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>803.23</v>
       </c>
       <c r="F407" s="10" t="n">
-        <v>891.6799999999999</v>
+        <v>892.03</v>
       </c>
       <c r="G407" s="11" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>2612.98</v>
       </c>
       <c r="F408" s="10" t="n">
-        <v>2498.38</v>
+        <v>2497.04</v>
       </c>
       <c r="G408" s="12" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>237.81</v>
       </c>
       <c r="F409" s="10" t="n">
-        <v>223.04</v>
+        <v>223.14</v>
       </c>
       <c r="G409" s="12" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>182.59</v>
       </c>
       <c r="F410" s="10" t="n">
-        <v>180.89</v>
+        <v>180.76</v>
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>293.52</v>
       </c>
       <c r="F411" s="10" t="n">
-        <v>317.07</v>
+        <v>316.29</v>
       </c>
       <c r="G411" s="11" t="inlineStr">
         <is>
@@ -18852,10 +18852,10 @@
         <v>1110.77</v>
       </c>
       <c r="E413" s="10" t="n">
-        <v>1090.07</v>
+        <v>1090.08</v>
       </c>
       <c r="F413" s="10" t="n">
-        <v>1029.5</v>
+        <v>1030.17</v>
       </c>
       <c r="G413" s="12" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>1028.45</v>
       </c>
       <c r="F414" s="10" t="n">
-        <v>1118.13</v>
+        <v>1116.35</v>
       </c>
       <c r="G414" s="12" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>516.8</v>
       </c>
       <c r="F415" s="10" t="n">
-        <v>506.17</v>
+        <v>505.92</v>
       </c>
       <c r="G415" s="11" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>407.44</v>
       </c>
       <c r="F416" s="10" t="n">
-        <v>449.37</v>
+        <v>448.08</v>
       </c>
       <c r="G416" s="11" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>574.4</v>
       </c>
       <c r="F418" s="10" t="n">
-        <v>589.3099999999999</v>
+        <v>589.16</v>
       </c>
       <c r="G418" s="12" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>616.03</v>
       </c>
       <c r="F419" s="10" t="n">
-        <v>545.05</v>
+        <v>544.6900000000001</v>
       </c>
       <c r="G419" s="12" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>495.24</v>
       </c>
       <c r="F420" s="10" t="n">
-        <v>439.68</v>
+        <v>439.96</v>
       </c>
       <c r="G420" s="11" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>263.8</v>
       </c>
       <c r="F421" s="10" t="n">
-        <v>229.69</v>
+        <v>229.41</v>
       </c>
       <c r="G421" s="12" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>143.66</v>
       </c>
       <c r="F422" s="10" t="n">
-        <v>157.03</v>
+        <v>156.86</v>
       </c>
       <c r="G422" s="12" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>710.96</v>
       </c>
       <c r="F423" s="10" t="n">
-        <v>700.41</v>
+        <v>700.84</v>
       </c>
       <c r="G423" s="11" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>4531.28</v>
       </c>
       <c r="F424" s="10" t="n">
-        <v>4674.24</v>
+        <v>4674.46</v>
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>6884.08</v>
       </c>
       <c r="F425" s="10" t="n">
-        <v>6837.29</v>
+        <v>6826.3</v>
       </c>
       <c r="G425" s="11" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>458.38</v>
       </c>
       <c r="F426" s="10" t="n">
-        <v>486.58</v>
+        <v>485.84</v>
       </c>
       <c r="G426" s="11" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>839.05</v>
       </c>
       <c r="F427" s="10" t="n">
-        <v>822.13</v>
+        <v>820.16</v>
       </c>
       <c r="G427" s="11" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>126.68</v>
       </c>
       <c r="F428" s="10" t="n">
-        <v>130.93</v>
+        <v>130.89</v>
       </c>
       <c r="G428" s="12" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>176.67</v>
       </c>
       <c r="F429" s="10" t="n">
-        <v>167.68</v>
+        <v>167.41</v>
       </c>
       <c r="G429" s="12" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>1659.52</v>
       </c>
       <c r="F430" s="10" t="n">
-        <v>1705.26</v>
+        <v>1705.72</v>
       </c>
       <c r="G430" s="11" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>4741.01</v>
       </c>
       <c r="F431" s="10" t="n">
-        <v>4727.13</v>
+        <v>4746.1</v>
       </c>
       <c r="G431" s="11" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>390.83</v>
       </c>
       <c r="F433" s="10" t="n">
-        <v>410.69</v>
+        <v>410.37</v>
       </c>
       <c r="G433" s="11" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>1360.12</v>
       </c>
       <c r="F434" s="10" t="n">
-        <v>1399.52</v>
+        <v>1398.73</v>
       </c>
       <c r="G434" s="11" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>492.97</v>
       </c>
       <c r="F435" s="10" t="n">
-        <v>455.76</v>
+        <v>455.73</v>
       </c>
       <c r="G435" s="11" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>154.12</v>
       </c>
       <c r="F436" s="10" t="n">
-        <v>167.54</v>
+        <v>167.3</v>
       </c>
       <c r="G436" s="11" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>1561.68</v>
       </c>
       <c r="F437" s="10" t="n">
-        <v>1584.16</v>
+        <v>1583.4</v>
       </c>
       <c r="G437" s="11" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>3020.69</v>
       </c>
       <c r="F438" s="10" t="n">
-        <v>3152.32</v>
+        <v>3151.4</v>
       </c>
       <c r="G438" s="12" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>779.71</v>
       </c>
       <c r="F439" s="10" t="n">
-        <v>845.8</v>
+        <v>845.73</v>
       </c>
       <c r="G439" s="12" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>683.89</v>
       </c>
       <c r="F440" s="10" t="n">
-        <v>766.88</v>
+        <v>765.76</v>
       </c>
       <c r="G440" s="11" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>788.46</v>
       </c>
       <c r="F441" s="10" t="n">
-        <v>845.1900000000001</v>
+        <v>844.42</v>
       </c>
       <c r="G441" s="12" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>254.62</v>
       </c>
       <c r="F442" s="10" t="n">
-        <v>278.91</v>
+        <v>278.72</v>
       </c>
       <c r="G442" s="11" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>711.3200000000001</v>
       </c>
       <c r="F443" s="10" t="n">
-        <v>684.22</v>
+        <v>683.28</v>
       </c>
       <c r="G443" s="11" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>1126.2</v>
       </c>
       <c r="F444" s="10" t="n">
-        <v>990.36</v>
+        <v>989.37</v>
       </c>
       <c r="G444" s="12" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>18658.3</v>
       </c>
       <c r="F445" s="10" t="n">
-        <v>17407.23</v>
+        <v>17416.62</v>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>1228.97</v>
       </c>
       <c r="F446" s="10" t="n">
-        <v>1125.84</v>
+        <v>1125.86</v>
       </c>
       <c r="G446" s="11" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>294.39</v>
       </c>
       <c r="F447" s="10" t="n">
-        <v>335.34</v>
+        <v>334.97</v>
       </c>
       <c r="G447" s="11" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>440.65</v>
       </c>
       <c r="F448" s="10" t="n">
-        <v>499.74</v>
+        <v>498.78</v>
       </c>
       <c r="G448" s="12" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>1334.59</v>
       </c>
       <c r="F449" s="10" t="n">
-        <v>1251.85</v>
+        <v>1251.69</v>
       </c>
       <c r="G449" s="12" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>511.38</v>
       </c>
       <c r="F450" s="10" t="n">
-        <v>517.78</v>
+        <v>517.63</v>
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>265.89</v>
       </c>
       <c r="F451" s="10" t="n">
-        <v>270.18</v>
+        <v>270.09</v>
       </c>
       <c r="G451" s="11" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>1386.55</v>
       </c>
       <c r="F452" s="10" t="n">
-        <v>1460.71</v>
+        <v>1459.62</v>
       </c>
       <c r="G452" s="11" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>493.02</v>
       </c>
       <c r="F453" s="10" t="n">
-        <v>532.8099999999999</v>
+        <v>532.63</v>
       </c>
       <c r="G453" s="11" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>93.06</v>
       </c>
       <c r="F454" s="10" t="n">
-        <v>95.83</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="G454" s="12" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>165.51</v>
       </c>
       <c r="F455" s="10" t="n">
-        <v>145.95</v>
+        <v>145.79</v>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>26829.9</v>
       </c>
       <c r="F456" s="10" t="n">
-        <v>27040.8</v>
+        <v>27047.08</v>
       </c>
       <c r="G456" s="11" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>39.89</v>
       </c>
       <c r="F457" s="10" t="n">
-        <v>44.41</v>
+        <v>44.33</v>
       </c>
       <c r="G457" s="11" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>577.95</v>
       </c>
       <c r="F458" s="10" t="n">
-        <v>582.37</v>
+        <v>582.02</v>
       </c>
       <c r="G458" s="12" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>1779.49</v>
       </c>
       <c r="F459" s="10" t="n">
-        <v>1668.45</v>
+        <v>1666.36</v>
       </c>
       <c r="G459" s="11" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>836.25</v>
       </c>
       <c r="F460" s="10" t="n">
-        <v>840.91</v>
+        <v>840.89</v>
       </c>
       <c r="G460" s="11" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>1686.54</v>
       </c>
       <c r="F461" s="10" t="n">
-        <v>1669.93</v>
+        <v>1670.26</v>
       </c>
       <c r="G461" s="11" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>3268.28</v>
       </c>
       <c r="F463" s="10" t="n">
-        <v>3284.86</v>
+        <v>3280.47</v>
       </c>
       <c r="G463" s="11" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>129.56</v>
       </c>
       <c r="F465" s="10" t="n">
-        <v>144.18</v>
+        <v>143.81</v>
       </c>
       <c r="G465" s="11" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>31.66</v>
       </c>
       <c r="F466" s="10" t="n">
-        <v>33.77</v>
+        <v>33.71</v>
       </c>
       <c r="G466" s="11" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>361.34</v>
       </c>
       <c r="F467" s="10" t="n">
-        <v>374.07</v>
+        <v>374.02</v>
       </c>
       <c r="G467" s="11" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>4339.12</v>
       </c>
       <c r="F468" s="10" t="n">
-        <v>4362.1</v>
+        <v>4357.12</v>
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>530.5599999999999</v>
       </c>
       <c r="F469" s="10" t="n">
-        <v>488.92</v>
+        <v>489.64</v>
       </c>
       <c r="G469" s="12" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>542.64</v>
       </c>
       <c r="F470" s="10" t="n">
-        <v>523.1799999999999</v>
+        <v>523.59</v>
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>1386.64</v>
       </c>
       <c r="F471" s="10" t="n">
-        <v>1198.01</v>
+        <v>1198.05</v>
       </c>
       <c r="G471" s="12" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>910.54</v>
       </c>
       <c r="F472" s="10" t="n">
-        <v>975.3200000000001</v>
+        <v>975.76</v>
       </c>
       <c r="G472" s="11" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>68.66</v>
       </c>
       <c r="F473" s="10" t="n">
-        <v>74.62</v>
+        <v>74.47</v>
       </c>
       <c r="G473" s="11" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>1034.78</v>
       </c>
       <c r="F474" s="10" t="n">
-        <v>955.38</v>
+        <v>954.47</v>
       </c>
       <c r="G474" s="12" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>591.9299999999999</v>
       </c>
       <c r="F476" s="10" t="n">
-        <v>546.46</v>
+        <v>546.09</v>
       </c>
       <c r="G476" s="12" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>217.95</v>
       </c>
       <c r="F477" s="10" t="n">
-        <v>221.84</v>
+        <v>221.08</v>
       </c>
       <c r="G477" s="11" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>33.84</v>
       </c>
       <c r="F478" s="10" t="n">
-        <v>34.97</v>
+        <v>34.9</v>
       </c>
       <c r="G478" s="11" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>428.1</v>
       </c>
       <c r="F479" s="10" t="n">
-        <v>438.41</v>
+        <v>438.19</v>
       </c>
       <c r="G479" s="11" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>331.43</v>
       </c>
       <c r="F480" s="10" t="n">
-        <v>336.71</v>
+        <v>336.74</v>
       </c>
       <c r="G480" s="11" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>4165.41</v>
       </c>
       <c r="F481" s="10" t="n">
-        <v>4422.5</v>
+        <v>4423.58</v>
       </c>
       <c r="G481" s="11" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>84.44</v>
       </c>
       <c r="F483" s="10" t="n">
-        <v>81.79000000000001</v>
+        <v>81.78</v>
       </c>
       <c r="G483" s="11" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>933.55</v>
       </c>
       <c r="F484" s="10" t="n">
-        <v>964.88</v>
+        <v>966.0700000000001</v>
       </c>
       <c r="G484" s="11" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>1095.87</v>
       </c>
       <c r="F485" s="10" t="n">
-        <v>997.08</v>
+        <v>997.7</v>
       </c>
       <c r="G485" s="11" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>64.48</v>
       </c>
       <c r="F486" s="10" t="n">
-        <v>64.25</v>
+        <v>64.23</v>
       </c>
       <c r="G486" s="11" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>34364.91</v>
       </c>
       <c r="F487" s="10" t="n">
-        <v>33050.27</v>
+        <v>33038.19</v>
       </c>
       <c r="G487" s="11" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>211.23</v>
       </c>
       <c r="F488" s="10" t="n">
-        <v>247.51</v>
+        <v>247.25</v>
       </c>
       <c r="G488" s="11" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>24.91</v>
       </c>
       <c r="F490" s="10" t="n">
-        <v>25.59</v>
+        <v>25.58</v>
       </c>
       <c r="G490" s="11" t="inlineStr">
         <is>
@@ -22278,16 +22278,16 @@
         </is>
       </c>
       <c r="C491" s="10" t="n">
-        <v>2204</v>
+        <v>2200.35</v>
       </c>
       <c r="D491" s="10" t="n">
-        <v>2228.12</v>
+        <v>2224.43</v>
       </c>
       <c r="E491" s="10" t="n">
-        <v>2248.64</v>
+        <v>2244.92</v>
       </c>
       <c r="F491" s="10" t="n">
-        <v>2337.51</v>
+        <v>2323.43</v>
       </c>
       <c r="G491" s="11" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>1396.86</v>
       </c>
       <c r="F492" s="10" t="n">
-        <v>1433.81</v>
+        <v>1434.33</v>
       </c>
       <c r="G492" s="11" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>630.87</v>
       </c>
       <c r="F493" s="10" t="n">
-        <v>661.53</v>
+        <v>661.26</v>
       </c>
       <c r="G493" s="11" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>5040.03</v>
       </c>
       <c r="F494" s="10" t="n">
-        <v>5297.59</v>
+        <v>5298.18</v>
       </c>
       <c r="G494" s="11" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>837.11</v>
       </c>
       <c r="F495" s="10" t="n">
-        <v>857.66</v>
+        <v>858.22</v>
       </c>
       <c r="G495" s="12" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>906.61</v>
       </c>
       <c r="F496" s="10" t="n">
-        <v>887.66</v>
+        <v>887.28</v>
       </c>
       <c r="G496" s="12" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>284.58</v>
       </c>
       <c r="F497" s="10" t="n">
-        <v>290.75</v>
+        <v>290.4</v>
       </c>
       <c r="G497" s="11" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>314.01</v>
       </c>
       <c r="F498" s="10" t="n">
-        <v>328.96</v>
+        <v>329.07</v>
       </c>
       <c r="G498" s="11" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>1489.46</v>
       </c>
       <c r="F499" s="10" t="n">
-        <v>1605.27</v>
+        <v>1605.87</v>
       </c>
       <c r="G499" s="11" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>3059.15</v>
       </c>
       <c r="F500" s="10" t="n">
-        <v>3067.1</v>
+        <v>3066.47</v>
       </c>
       <c r="G500" s="12" t="inlineStr">
         <is>
